--- a/public/pds.xlsx
+++ b/public/pds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cenro\PMS-intern\rsp-hr-tagum-cityhall\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5E11DF-D6A1-4553-96E4-1D160B1A2E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995911BC-F7F2-4A73-8C0B-934CB3125789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1615,7 +1615,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="348">
   <si>
     <t xml:space="preserve">        </t>
   </si>
@@ -2707,9 +2707,6 @@
     <t>Purok</t>
   </si>
   <si>
-    <t>PWD</t>
-  </si>
-  <si>
     <t>ADDITIONAL INFORMATION</t>
   </si>
   <si>
@@ -2732,7 +2729,7 @@
     <numFmt numFmtId="166" formatCode=";;;"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="56">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3098,11 +3095,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
@@ -3781,7 +3773,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="525">
+  <cellXfs count="519">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -4457,122 +4449,300 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="34" fillId="4" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4591,6 +4761,7 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4616,300 +4787,149 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4923,6 +4943,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4937,10 +4969,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4951,59 +4979,6 @@
     <xf numFmtId="49" fontId="51" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -5184,20 +5159,25 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5205,169 +5185,48 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -5416,6 +5275,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5427,14 +5310,19 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5442,53 +5330,135 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5525,31 +5495,31 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$35" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$5" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$E$35" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$5" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$5" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$6" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$5" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$6" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$6" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$18" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$6" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$18" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$21" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5557,43 +5527,43 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$21" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$21" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$30" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$21" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$30" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$30" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$34" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$30" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$34" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$34" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$38" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$34" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$24" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$38" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$24" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$24" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$26" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$24" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$26" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5601,38 +5571,30 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$26" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$9" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$26" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$9" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$9" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$38" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$9" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$36" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$38" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$36" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$36" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$12" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$36" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$12" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$12" noThreeD="1"/>
 </file>
 
@@ -6413,7 +6375,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6500,7 +6462,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6587,7 +6549,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6674,7 +6636,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6761,7 +6723,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6848,7 +6810,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6935,7 +6897,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7022,7 +6984,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7109,7 +7071,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7196,7 +7158,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7283,7 +7245,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7395,170 +7357,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>76200</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>66675</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="590550" cy="180975"/>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="22550" name="Check Box 22" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s22550"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{712397B1-A680-4651-9B03-E1744C123032}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-PH" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma"/>
-                  <a:ea typeface="Tahoma"/>
-                  <a:cs typeface="Tahoma"/>
-                </a:rPr>
-                <a:t> Yes</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="647164" cy="257175"/>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="22551" name="Check Box 23" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s22551"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DCAB5B5-EF8C-4B27-8D8D-CCD80C666A2B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-PH" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma"/>
-                  <a:ea typeface="Tahoma"/>
-                  <a:cs typeface="Tahoma"/>
-                </a:rPr>
-                <a:t> No</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -7921,7 +7719,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8008,7 +7806,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8095,7 +7893,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8182,7 +7980,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8269,7 +8067,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8356,7 +8154,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8443,7 +8241,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8530,7 +8328,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8617,7 +8415,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8704,7 +8502,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8791,7 +8589,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8878,7 +8676,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8965,7 +8763,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9052,7 +8850,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9139,7 +8937,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9226,7 +9024,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9313,7 +9111,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9400,7 +9198,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9487,7 +9285,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9574,7 +9372,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9661,7 +9459,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9748,7 +9546,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10071,7 +9869,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10158,7 +9956,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="45720" rIns="0" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10469,20 +10267,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
-      <c r="A1" s="266"/>
-      <c r="B1" s="267"/>
-      <c r="C1" s="267"/>
-      <c r="D1" s="267"/>
-      <c r="E1" s="267"/>
-      <c r="F1" s="267"/>
-      <c r="G1" s="267"/>
-      <c r="H1" s="267"/>
-      <c r="I1" s="267"/>
-      <c r="J1" s="267"/>
-      <c r="K1" s="267"/>
-      <c r="L1" s="267"/>
-      <c r="M1" s="267"/>
-      <c r="N1" s="268"/>
+      <c r="A1" s="267"/>
+      <c r="B1" s="268"/>
+      <c r="C1" s="268"/>
+      <c r="D1" s="268"/>
+      <c r="E1" s="268"/>
+      <c r="F1" s="268"/>
+      <c r="G1" s="268"/>
+      <c r="H1" s="268"/>
+      <c r="I1" s="268"/>
+      <c r="J1" s="268"/>
+      <c r="K1" s="268"/>
+      <c r="L1" s="268"/>
+      <c r="M1" s="268"/>
+      <c r="N1" s="269"/>
     </row>
     <row r="2" spans="1:22" ht="11.25" customHeight="1">
       <c r="A2" s="40"/>
@@ -10512,73 +10310,73 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="41.25" customHeight="1">
-      <c r="A3" s="269" t="s">
+      <c r="A3" s="270" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="270"/>
-      <c r="C3" s="270"/>
-      <c r="D3" s="270"/>
-      <c r="E3" s="270"/>
-      <c r="F3" s="270"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="270"/>
-      <c r="I3" s="270"/>
-      <c r="J3" s="270"/>
-      <c r="K3" s="270"/>
-      <c r="L3" s="270"/>
-      <c r="M3" s="270"/>
-      <c r="N3" s="271"/>
-      <c r="R3" s="300"/>
-      <c r="S3" s="301"/>
-      <c r="T3" s="301"/>
-      <c r="U3" s="301"/>
-      <c r="V3" s="302"/>
+      <c r="B3" s="271"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="271"/>
+      <c r="E3" s="271"/>
+      <c r="F3" s="271"/>
+      <c r="G3" s="271"/>
+      <c r="H3" s="271"/>
+      <c r="I3" s="271"/>
+      <c r="J3" s="271"/>
+      <c r="K3" s="271"/>
+      <c r="L3" s="271"/>
+      <c r="M3" s="271"/>
+      <c r="N3" s="272"/>
+      <c r="R3" s="225"/>
+      <c r="S3" s="226"/>
+      <c r="T3" s="226"/>
+      <c r="U3" s="226"/>
+      <c r="V3" s="227"/>
     </row>
     <row r="4" spans="1:22" ht="21.75" customHeight="1">
-      <c r="A4" s="272" t="s">
+      <c r="A4" s="273" t="s">
         <v>342</v>
       </c>
-      <c r="B4" s="273"/>
-      <c r="C4" s="273"/>
-      <c r="D4" s="273"/>
-      <c r="E4" s="273"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="273"/>
-      <c r="H4" s="273"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="273"/>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
-      <c r="M4" s="273"/>
-      <c r="N4" s="274"/>
-      <c r="R4" s="303"/>
-      <c r="S4" s="304"/>
-      <c r="T4" s="304"/>
-      <c r="U4" s="304"/>
-      <c r="V4" s="305"/>
+      <c r="B4" s="274"/>
+      <c r="C4" s="274"/>
+      <c r="D4" s="274"/>
+      <c r="E4" s="274"/>
+      <c r="F4" s="274"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="274"/>
+      <c r="I4" s="274"/>
+      <c r="J4" s="274"/>
+      <c r="K4" s="274"/>
+      <c r="L4" s="274"/>
+      <c r="M4" s="274"/>
+      <c r="N4" s="275"/>
+      <c r="R4" s="228"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
     </row>
     <row r="5" spans="1:22" ht="11.25" customHeight="1">
-      <c r="A5" s="275" t="s">
+      <c r="A5" s="276" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="276"/>
-      <c r="C5" s="276"/>
-      <c r="D5" s="276"/>
-      <c r="E5" s="276"/>
-      <c r="F5" s="276"/>
-      <c r="G5" s="276"/>
-      <c r="H5" s="276"/>
-      <c r="I5" s="276"/>
-      <c r="J5" s="276"/>
-      <c r="K5" s="276"/>
-      <c r="L5" s="276"/>
-      <c r="M5" s="276"/>
-      <c r="N5" s="277"/>
-      <c r="R5" s="303"/>
-      <c r="S5" s="304"/>
-      <c r="T5" s="304"/>
-      <c r="U5" s="304"/>
-      <c r="V5" s="305"/>
+      <c r="B5" s="277"/>
+      <c r="C5" s="277"/>
+      <c r="D5" s="277"/>
+      <c r="E5" s="277"/>
+      <c r="F5" s="277"/>
+      <c r="G5" s="277"/>
+      <c r="H5" s="277"/>
+      <c r="I5" s="277"/>
+      <c r="J5" s="277"/>
+      <c r="K5" s="277"/>
+      <c r="L5" s="277"/>
+      <c r="M5" s="277"/>
+      <c r="N5" s="278"/>
+      <c r="R5" s="228"/>
+      <c r="S5" s="229"/>
+      <c r="T5" s="229"/>
+      <c r="U5" s="229"/>
+      <c r="V5" s="230"/>
     </row>
     <row r="6" spans="1:22" ht="36.75" hidden="1" customHeight="1">
       <c r="A6" s="43"/>
@@ -10595,11 +10393,11 @@
       <c r="L6" s="45"/>
       <c r="M6" s="45"/>
       <c r="N6" s="46"/>
-      <c r="R6" s="303"/>
-      <c r="S6" s="304"/>
-      <c r="T6" s="304"/>
-      <c r="U6" s="304"/>
-      <c r="V6" s="305"/>
+      <c r="R6" s="228"/>
+      <c r="S6" s="229"/>
+      <c r="T6" s="229"/>
+      <c r="U6" s="229"/>
+      <c r="V6" s="230"/>
     </row>
     <row r="7" spans="1:22" s="53" customFormat="1" ht="12.75" customHeight="1" thickBot="1">
       <c r="A7" s="47" t="s">
@@ -10617,197 +10415,197 @@
       <c r="K7" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="278" t="s">
+      <c r="L7" s="279" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="279"/>
-      <c r="N7" s="280"/>
-      <c r="R7" s="303"/>
-      <c r="S7" s="304"/>
-      <c r="T7" s="304"/>
-      <c r="U7" s="304"/>
-      <c r="V7" s="305"/>
+      <c r="M7" s="280"/>
+      <c r="N7" s="281"/>
+      <c r="R7" s="228"/>
+      <c r="S7" s="229"/>
+      <c r="T7" s="229"/>
+      <c r="U7" s="229"/>
+      <c r="V7" s="230"/>
     </row>
     <row r="8" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
       <c r="A8" s="54"/>
       <c r="N8" s="55"/>
-      <c r="R8" s="303"/>
-      <c r="S8" s="304"/>
-      <c r="T8" s="304"/>
-      <c r="U8" s="304"/>
-      <c r="V8" s="305"/>
+      <c r="R8" s="228"/>
+      <c r="S8" s="229"/>
+      <c r="T8" s="229"/>
+      <c r="U8" s="229"/>
+      <c r="V8" s="230"/>
     </row>
     <row r="9" spans="1:22" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A9" s="314" t="s">
+      <c r="A9" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="315"/>
-      <c r="C9" s="315"/>
-      <c r="D9" s="315"/>
-      <c r="E9" s="315"/>
-      <c r="F9" s="315"/>
-      <c r="G9" s="315"/>
-      <c r="H9" s="315"/>
-      <c r="I9" s="315"/>
-      <c r="J9" s="315"/>
-      <c r="K9" s="315"/>
-      <c r="L9" s="315"/>
-      <c r="M9" s="315"/>
-      <c r="N9" s="316"/>
-      <c r="R9" s="303"/>
-      <c r="S9" s="304"/>
-      <c r="T9" s="304"/>
-      <c r="U9" s="304"/>
-      <c r="V9" s="305"/>
+      <c r="B9" s="240"/>
+      <c r="C9" s="240"/>
+      <c r="D9" s="240"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="240"/>
+      <c r="G9" s="240"/>
+      <c r="H9" s="240"/>
+      <c r="I9" s="240"/>
+      <c r="J9" s="240"/>
+      <c r="K9" s="240"/>
+      <c r="L9" s="240"/>
+      <c r="M9" s="240"/>
+      <c r="N9" s="241"/>
+      <c r="R9" s="228"/>
+      <c r="S9" s="229"/>
+      <c r="T9" s="229"/>
+      <c r="U9" s="229"/>
+      <c r="V9" s="230"/>
     </row>
     <row r="10" spans="1:22" ht="22.5" customHeight="1">
       <c r="A10" s="56">
         <v>2</v>
       </c>
-      <c r="B10" s="285" t="s">
+      <c r="B10" s="242" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="286"/>
-      <c r="D10" s="317"/>
-      <c r="E10" s="317"/>
-      <c r="F10" s="317"/>
-      <c r="G10" s="317"/>
-      <c r="H10" s="317"/>
-      <c r="I10" s="317"/>
-      <c r="J10" s="317"/>
-      <c r="K10" s="317"/>
-      <c r="L10" s="317"/>
-      <c r="M10" s="317"/>
-      <c r="N10" s="318"/>
+      <c r="C10" s="243"/>
+      <c r="D10" s="244"/>
+      <c r="E10" s="244"/>
+      <c r="F10" s="244"/>
+      <c r="G10" s="244"/>
+      <c r="H10" s="244"/>
+      <c r="I10" s="244"/>
+      <c r="J10" s="244"/>
+      <c r="K10" s="244"/>
+      <c r="L10" s="244"/>
+      <c r="M10" s="244"/>
+      <c r="N10" s="245"/>
       <c r="P10" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="R10" s="303"/>
-      <c r="S10" s="304"/>
-      <c r="T10" s="304"/>
-      <c r="U10" s="304"/>
-      <c r="V10" s="305"/>
+      <c r="R10" s="228"/>
+      <c r="S10" s="229"/>
+      <c r="T10" s="229"/>
+      <c r="U10" s="229"/>
+      <c r="V10" s="230"/>
     </row>
     <row r="11" spans="1:22" ht="22.5" customHeight="1">
       <c r="A11" s="58"/>
-      <c r="B11" s="287" t="s">
+      <c r="B11" s="246" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="288"/>
-      <c r="D11" s="319"/>
-      <c r="E11" s="320"/>
-      <c r="F11" s="320"/>
-      <c r="G11" s="320"/>
-      <c r="H11" s="321"/>
-      <c r="I11" s="322" t="s">
+      <c r="C11" s="247"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="250"/>
+      <c r="I11" s="251" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="323"/>
-      <c r="K11" s="323"/>
-      <c r="L11" s="324"/>
-      <c r="M11" s="325"/>
-      <c r="N11" s="326"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="252"/>
+      <c r="L11" s="253"/>
+      <c r="M11" s="254"/>
+      <c r="N11" s="255"/>
       <c r="P11" s="60" t="s">
         <v>14</v>
       </c>
       <c r="Q11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="R11" s="303"/>
-      <c r="S11" s="304"/>
-      <c r="T11" s="304"/>
-      <c r="U11" s="304"/>
-      <c r="V11" s="305"/>
+      <c r="R11" s="228"/>
+      <c r="S11" s="229"/>
+      <c r="T11" s="229"/>
+      <c r="U11" s="229"/>
+      <c r="V11" s="230"/>
     </row>
     <row r="12" spans="1:22" ht="21.75" customHeight="1" thickBot="1">
       <c r="A12" s="62"/>
-      <c r="B12" s="309" t="s">
+      <c r="B12" s="234" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="310"/>
-      <c r="D12" s="311"/>
-      <c r="E12" s="312"/>
-      <c r="F12" s="312"/>
-      <c r="G12" s="312" t="b">
+      <c r="C12" s="235"/>
+      <c r="D12" s="236"/>
+      <c r="E12" s="237"/>
+      <c r="F12" s="237"/>
+      <c r="G12" s="237" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="312"/>
-      <c r="I12" s="312" t="b">
+      <c r="H12" s="237"/>
+      <c r="I12" s="237" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="312"/>
-      <c r="K12" s="312"/>
-      <c r="L12" s="312"/>
-      <c r="M12" s="312"/>
-      <c r="N12" s="313"/>
+      <c r="J12" s="237"/>
+      <c r="K12" s="237"/>
+      <c r="L12" s="237"/>
+      <c r="M12" s="237"/>
+      <c r="N12" s="238"/>
       <c r="P12" s="60" t="s">
         <v>17</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="R12" s="303"/>
-      <c r="S12" s="304"/>
-      <c r="T12" s="304"/>
-      <c r="U12" s="304"/>
-      <c r="V12" s="305"/>
+      <c r="R12" s="228"/>
+      <c r="S12" s="229"/>
+      <c r="T12" s="229"/>
+      <c r="U12" s="229"/>
+      <c r="V12" s="230"/>
     </row>
     <row r="13" spans="1:22" ht="24" customHeight="1">
       <c r="A13" s="64">
         <v>3</v>
       </c>
-      <c r="B13" s="330" t="s">
+      <c r="B13" s="259" t="s">
         <v>334</v>
       </c>
-      <c r="C13" s="286"/>
-      <c r="D13" s="281"/>
-      <c r="E13" s="282"/>
-      <c r="F13" s="282"/>
-      <c r="G13" s="285" t="s">
+      <c r="C13" s="243"/>
+      <c r="D13" s="282"/>
+      <c r="E13" s="283"/>
+      <c r="F13" s="283"/>
+      <c r="G13" s="242" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="285"/>
-      <c r="I13" s="286"/>
-      <c r="J13" s="289" t="b">
+      <c r="H13" s="242"/>
+      <c r="I13" s="243"/>
+      <c r="J13" s="286" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="290"/>
-      <c r="L13" s="290" t="b">
+      <c r="K13" s="287"/>
+      <c r="L13" s="287" t="b">
         <v>0</v>
       </c>
-      <c r="M13" s="290"/>
-      <c r="N13" s="291"/>
+      <c r="M13" s="287"/>
+      <c r="N13" s="288"/>
       <c r="P13" s="60" t="s">
         <v>20</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="306"/>
-      <c r="S13" s="307"/>
-      <c r="T13" s="307"/>
-      <c r="U13" s="307"/>
-      <c r="V13" s="308"/>
+      <c r="R13" s="231"/>
+      <c r="S13" s="232"/>
+      <c r="T13" s="232"/>
+      <c r="U13" s="232"/>
+      <c r="V13" s="233"/>
     </row>
     <row r="14" spans="1:22" ht="21.6" customHeight="1">
       <c r="A14" s="58"/>
       <c r="B14" s="65"/>
       <c r="C14" s="65"/>
-      <c r="D14" s="283"/>
-      <c r="E14" s="284"/>
-      <c r="F14" s="284"/>
-      <c r="G14" s="287"/>
-      <c r="H14" s="287"/>
-      <c r="I14" s="288"/>
-      <c r="J14" s="292" t="b">
+      <c r="D14" s="284"/>
+      <c r="E14" s="285"/>
+      <c r="F14" s="285"/>
+      <c r="G14" s="246"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="247"/>
+      <c r="J14" s="289" t="b">
         <v>0</v>
       </c>
-      <c r="K14" s="293"/>
-      <c r="L14" s="293" t="b">
+      <c r="K14" s="290"/>
+      <c r="L14" s="290" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="293"/>
-      <c r="N14" s="294"/>
+      <c r="M14" s="290"/>
+      <c r="N14" s="291"/>
       <c r="P14" s="60"/>
       <c r="Q14" s="2"/>
       <c r="S14"/>
@@ -10822,21 +10620,21 @@
         <v>22</v>
       </c>
       <c r="C15" s="67"/>
-      <c r="D15" s="331"/>
-      <c r="E15" s="331"/>
-      <c r="F15" s="332"/>
-      <c r="G15" s="261" t="s">
+      <c r="D15" s="260"/>
+      <c r="E15" s="260"/>
+      <c r="F15" s="261"/>
+      <c r="G15" s="262" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="262"/>
-      <c r="I15" s="262"/>
-      <c r="J15" s="263" t="s">
+      <c r="H15" s="263"/>
+      <c r="I15" s="263"/>
+      <c r="J15" s="264" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="264"/>
-      <c r="L15" s="264"/>
-      <c r="M15" s="264"/>
-      <c r="N15" s="265"/>
+      <c r="K15" s="265"/>
+      <c r="L15" s="265"/>
+      <c r="M15" s="265"/>
+      <c r="N15" s="266"/>
       <c r="P15" s="60" t="s">
         <v>25</v>
       </c>
@@ -10858,22 +10656,22 @@
       <c r="D16" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="247" t="b">
+      <c r="E16" s="296" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="248"/>
-      <c r="G16" s="249" t="s">
+      <c r="F16" s="297"/>
+      <c r="G16" s="298" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="250"/>
-      <c r="I16" s="251"/>
-      <c r="J16" s="327">
+      <c r="H16" s="299"/>
+      <c r="I16" s="300"/>
+      <c r="J16" s="256">
         <v>8</v>
       </c>
-      <c r="K16" s="328"/>
-      <c r="L16" s="328"/>
-      <c r="M16" s="328"/>
-      <c r="N16" s="329"/>
+      <c r="K16" s="257"/>
+      <c r="L16" s="257"/>
+      <c r="M16" s="257"/>
+      <c r="N16" s="258"/>
       <c r="O16" s="70"/>
       <c r="P16" s="60" t="s">
         <v>29</v>
@@ -10883,64 +10681,64 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="27" customHeight="1">
-      <c r="A17" s="214">
+      <c r="A17" s="324">
         <v>6</v>
       </c>
-      <c r="B17" s="226" t="s">
+      <c r="B17" s="334" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="227"/>
+      <c r="C17" s="335"/>
       <c r="D17" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="253" t="b">
+      <c r="E17" s="303" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="254"/>
+      <c r="F17" s="304"/>
       <c r="G17" s="71" t="s">
         <v>32</v>
       </c>
       <c r="H17" s="72"/>
-      <c r="I17" s="213" t="s">
+      <c r="I17" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="J17" s="213"/>
-      <c r="K17" s="213" t="s">
+      <c r="J17" s="292"/>
+      <c r="K17" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="L17" s="213"/>
-      <c r="M17" s="241"/>
-      <c r="N17" s="241"/>
+      <c r="L17" s="292"/>
+      <c r="M17" s="293"/>
+      <c r="N17" s="293"/>
       <c r="Q17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="R17" s="73"/>
     </row>
     <row r="18" spans="1:23" ht="27" customHeight="1">
-      <c r="A18" s="215"/>
-      <c r="B18" s="228"/>
-      <c r="C18" s="229"/>
+      <c r="A18" s="325"/>
+      <c r="B18" s="336"/>
+      <c r="C18" s="337"/>
       <c r="D18" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="259" t="b">
+      <c r="E18" s="223" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="260"/>
+      <c r="F18" s="224"/>
       <c r="G18" s="75"/>
       <c r="H18" s="76"/>
-      <c r="I18" s="242" t="s">
+      <c r="I18" s="212" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242" t="s">
+      <c r="J18" s="212"/>
+      <c r="K18" s="212" t="s">
         <v>343</v>
       </c>
-      <c r="L18" s="242"/>
-      <c r="M18" s="242" t="s">
+      <c r="L18" s="212"/>
+      <c r="M18" s="212" t="s">
         <v>35</v>
       </c>
-      <c r="N18" s="242"/>
+      <c r="N18" s="212"/>
       <c r="Q18" s="2" t="s">
         <v>36</v>
       </c>
@@ -10949,23 +10747,23 @@
       <c r="A19" s="56"/>
       <c r="B19" s="77"/>
       <c r="C19" s="74"/>
-      <c r="D19" s="258" t="b">
+      <c r="D19" s="308" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="259"/>
-      <c r="F19" s="260"/>
+      <c r="E19" s="223"/>
+      <c r="F19" s="224"/>
       <c r="G19" s="75"/>
       <c r="H19" s="76"/>
-      <c r="I19" s="213" t="s">
+      <c r="I19" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="J19" s="225"/>
-      <c r="K19" s="225"/>
-      <c r="L19" s="213" t="s">
+      <c r="J19" s="333"/>
+      <c r="K19" s="333"/>
+      <c r="L19" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="M19" s="241"/>
-      <c r="N19" s="241"/>
+      <c r="M19" s="293"/>
+      <c r="N19" s="293"/>
       <c r="Q19" s="2" t="s">
         <v>37</v>
       </c>
@@ -10974,71 +10772,71 @@
       <c r="A20" s="78"/>
       <c r="B20" s="79"/>
       <c r="C20" s="80"/>
-      <c r="D20" s="255"/>
-      <c r="E20" s="256"/>
-      <c r="F20" s="257"/>
+      <c r="D20" s="305"/>
+      <c r="E20" s="306"/>
+      <c r="F20" s="307"/>
       <c r="G20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="238" t="s">
+      <c r="I20" s="294" t="s">
         <v>38</v>
       </c>
-      <c r="J20" s="243"/>
-      <c r="K20" s="243"/>
-      <c r="L20" s="244" t="s">
+      <c r="J20" s="301"/>
+      <c r="K20" s="301"/>
+      <c r="L20" s="295" t="s">
         <v>39</v>
       </c>
-      <c r="M20" s="252"/>
-      <c r="N20" s="252"/>
+      <c r="M20" s="302"/>
+      <c r="N20" s="302"/>
       <c r="Q20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A21" s="215">
+      <c r="A21" s="325">
         <v>7</v>
       </c>
-      <c r="B21" s="217" t="s">
+      <c r="B21" s="327" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="218"/>
-      <c r="D21" s="224"/>
-      <c r="E21" s="224"/>
-      <c r="F21" s="224"/>
+      <c r="C21" s="328"/>
+      <c r="D21" s="332"/>
+      <c r="E21" s="332"/>
+      <c r="F21" s="332"/>
       <c r="G21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="213" t="s">
+      <c r="I21" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="J21" s="241"/>
-      <c r="K21" s="241"/>
-      <c r="L21" s="213" t="s">
+      <c r="J21" s="293"/>
+      <c r="K21" s="293"/>
+      <c r="L21" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="M21" s="241"/>
-      <c r="N21" s="241"/>
+      <c r="M21" s="293"/>
+      <c r="N21" s="293"/>
       <c r="Q21" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="26.25" customHeight="1">
-      <c r="A22" s="216"/>
-      <c r="B22" s="219"/>
-      <c r="C22" s="220"/>
-      <c r="D22" s="223"/>
-      <c r="E22" s="223"/>
-      <c r="F22" s="223"/>
+      <c r="A22" s="326"/>
+      <c r="B22" s="329"/>
+      <c r="C22" s="330"/>
+      <c r="D22" s="331"/>
+      <c r="E22" s="331"/>
+      <c r="F22" s="331"/>
       <c r="G22" s="58"/>
       <c r="H22" s="59"/>
-      <c r="I22" s="238" t="s">
+      <c r="I22" s="294" t="s">
         <v>43</v>
       </c>
-      <c r="J22" s="238"/>
-      <c r="K22" s="238"/>
-      <c r="L22" s="244" t="s">
+      <c r="J22" s="294"/>
+      <c r="K22" s="294"/>
+      <c r="L22" s="295" t="s">
         <v>44</v>
       </c>
-      <c r="M22" s="244"/>
-      <c r="N22" s="244"/>
+      <c r="M22" s="295"/>
+      <c r="N22" s="295"/>
       <c r="Q22" s="2" t="s">
         <v>45</v>
       </c>
@@ -11047,178 +10845,178 @@
       <c r="A23" s="56">
         <v>8</v>
       </c>
-      <c r="B23" s="245" t="s">
+      <c r="B23" s="309" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="232"/>
-      <c r="D23" s="230"/>
-      <c r="E23" s="230"/>
-      <c r="F23" s="230"/>
-      <c r="G23" s="239" t="s">
+      <c r="C23" s="310"/>
+      <c r="D23" s="311"/>
+      <c r="E23" s="311"/>
+      <c r="F23" s="311"/>
+      <c r="G23" s="312" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="240"/>
-      <c r="I23" s="246"/>
-      <c r="J23" s="246"/>
-      <c r="K23" s="246"/>
-      <c r="L23" s="246"/>
-      <c r="M23" s="246"/>
-      <c r="N23" s="246"/>
+      <c r="H23" s="313"/>
+      <c r="I23" s="314"/>
+      <c r="J23" s="314"/>
+      <c r="K23" s="314"/>
+      <c r="L23" s="314"/>
+      <c r="M23" s="314"/>
+      <c r="N23" s="314"/>
       <c r="Q23" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A24" s="214">
+      <c r="A24" s="324">
         <v>9</v>
       </c>
-      <c r="B24" s="217" t="s">
+      <c r="B24" s="327" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="218"/>
-      <c r="D24" s="222"/>
-      <c r="E24" s="222"/>
-      <c r="F24" s="222"/>
+      <c r="C24" s="328"/>
+      <c r="D24" s="320"/>
+      <c r="E24" s="320"/>
+      <c r="F24" s="320"/>
       <c r="G24" s="84" t="s">
         <v>50</v>
       </c>
       <c r="H24" s="81"/>
-      <c r="I24" s="213" t="s">
+      <c r="I24" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="J24" s="241"/>
-      <c r="K24" s="241"/>
-      <c r="L24" s="213" t="s">
+      <c r="J24" s="293"/>
+      <c r="K24" s="293"/>
+      <c r="L24" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="M24" s="241"/>
-      <c r="N24" s="241"/>
+      <c r="M24" s="293"/>
+      <c r="N24" s="293"/>
       <c r="Q24" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A25" s="216"/>
-      <c r="B25" s="219"/>
-      <c r="C25" s="220"/>
-      <c r="D25" s="223"/>
-      <c r="E25" s="223"/>
-      <c r="F25" s="223"/>
+      <c r="A25" s="326"/>
+      <c r="B25" s="329"/>
+      <c r="C25" s="330"/>
+      <c r="D25" s="331"/>
+      <c r="E25" s="331"/>
+      <c r="F25" s="331"/>
       <c r="G25" s="58"/>
       <c r="H25" s="59"/>
-      <c r="I25" s="242" t="s">
+      <c r="I25" s="212" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="242"/>
-      <c r="K25" s="242"/>
-      <c r="L25" s="242" t="s">
+      <c r="J25" s="212"/>
+      <c r="K25" s="212"/>
+      <c r="L25" s="212" t="s">
         <v>35</v>
       </c>
-      <c r="M25" s="242"/>
-      <c r="N25" s="242"/>
+      <c r="M25" s="212"/>
+      <c r="N25" s="212"/>
       <c r="Q25" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A26" s="214">
+      <c r="A26" s="324">
         <v>10</v>
       </c>
-      <c r="B26" s="217" t="s">
+      <c r="B26" s="327" t="s">
         <v>340</v>
       </c>
-      <c r="C26" s="218"/>
-      <c r="D26" s="222"/>
-      <c r="E26" s="222"/>
-      <c r="F26" s="222"/>
+      <c r="C26" s="328"/>
+      <c r="D26" s="320"/>
+      <c r="E26" s="320"/>
+      <c r="F26" s="320"/>
       <c r="G26" s="75"/>
       <c r="H26" s="76"/>
-      <c r="I26" s="213" t="s">
+      <c r="I26" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="213" t="s">
+      <c r="J26" s="293"/>
+      <c r="K26" s="293"/>
+      <c r="L26" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="M26" s="241"/>
-      <c r="N26" s="241"/>
+      <c r="M26" s="293"/>
+      <c r="N26" s="293"/>
       <c r="Q26" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="35.25" customHeight="1">
-      <c r="A27" s="216"/>
-      <c r="B27" s="219"/>
-      <c r="C27" s="220"/>
-      <c r="D27" s="223"/>
-      <c r="E27" s="223"/>
-      <c r="F27" s="223"/>
+      <c r="A27" s="326"/>
+      <c r="B27" s="329"/>
+      <c r="C27" s="330"/>
+      <c r="D27" s="331"/>
+      <c r="E27" s="331"/>
+      <c r="F27" s="331"/>
       <c r="G27" s="75"/>
       <c r="H27" s="76"/>
-      <c r="I27" s="238" t="s">
+      <c r="I27" s="294" t="s">
         <v>38</v>
       </c>
-      <c r="J27" s="243"/>
-      <c r="K27" s="243"/>
-      <c r="L27" s="244" t="s">
+      <c r="J27" s="301"/>
+      <c r="K27" s="301"/>
+      <c r="L27" s="295" t="s">
         <v>39</v>
       </c>
-      <c r="M27" s="243"/>
-      <c r="N27" s="243"/>
+      <c r="M27" s="301"/>
+      <c r="N27" s="301"/>
       <c r="Q27" s="2" t="s">
         <v>54</v>
       </c>
       <c r="S27" s="85"/>
     </row>
     <row r="28" spans="1:23" ht="33" customHeight="1">
-      <c r="A28" s="214">
+      <c r="A28" s="324">
         <v>11</v>
       </c>
-      <c r="B28" s="217" t="s">
+      <c r="B28" s="327" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="218"/>
-      <c r="D28" s="221" t="s">
+      <c r="C28" s="328"/>
+      <c r="D28" s="319" t="s">
         <v>326</v>
       </c>
-      <c r="E28" s="222"/>
-      <c r="F28" s="222"/>
+      <c r="E28" s="320"/>
+      <c r="F28" s="320"/>
       <c r="G28" s="75"/>
       <c r="H28" s="86"/>
-      <c r="I28" s="234" t="s">
+      <c r="I28" s="315" t="s">
         <v>326</v>
       </c>
-      <c r="J28" s="235"/>
-      <c r="K28" s="235"/>
-      <c r="L28" s="236" t="s">
+      <c r="J28" s="316"/>
+      <c r="K28" s="316"/>
+      <c r="L28" s="317" t="s">
         <v>326</v>
       </c>
-      <c r="M28" s="237"/>
-      <c r="N28" s="237"/>
+      <c r="M28" s="318"/>
+      <c r="N28" s="318"/>
       <c r="Q28" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="32.25" customHeight="1">
-      <c r="A29" s="216"/>
-      <c r="B29" s="219"/>
-      <c r="C29" s="220"/>
-      <c r="D29" s="223"/>
-      <c r="E29" s="223"/>
-      <c r="F29" s="223"/>
+      <c r="A29" s="326"/>
+      <c r="B29" s="329"/>
+      <c r="C29" s="330"/>
+      <c r="D29" s="331"/>
+      <c r="E29" s="331"/>
+      <c r="F29" s="331"/>
       <c r="G29" s="75"/>
       <c r="H29" s="86"/>
-      <c r="I29" s="238" t="s">
+      <c r="I29" s="294" t="s">
         <v>43</v>
       </c>
-      <c r="J29" s="238"/>
-      <c r="K29" s="238"/>
-      <c r="L29" s="238" t="s">
+      <c r="J29" s="294"/>
+      <c r="K29" s="294"/>
+      <c r="L29" s="294" t="s">
         <v>44</v>
       </c>
-      <c r="M29" s="238"/>
-      <c r="N29" s="238"/>
+      <c r="M29" s="294"/>
+      <c r="N29" s="294"/>
       <c r="Q29" s="2" t="s">
         <v>57</v>
       </c>
@@ -11232,21 +11030,21 @@
         <v>58</v>
       </c>
       <c r="C30" s="69"/>
-      <c r="D30" s="221" t="s">
+      <c r="D30" s="319" t="s">
         <v>326</v>
       </c>
-      <c r="E30" s="222"/>
-      <c r="F30" s="222"/>
-      <c r="G30" s="239" t="s">
+      <c r="E30" s="320"/>
+      <c r="F30" s="320"/>
+      <c r="G30" s="312" t="s">
         <v>47</v>
       </c>
-      <c r="H30" s="240"/>
-      <c r="I30" s="241"/>
-      <c r="J30" s="241"/>
-      <c r="K30" s="241"/>
-      <c r="L30" s="241"/>
-      <c r="M30" s="241"/>
-      <c r="N30" s="241"/>
+      <c r="H30" s="313"/>
+      <c r="I30" s="293"/>
+      <c r="J30" s="293"/>
+      <c r="K30" s="293"/>
+      <c r="L30" s="293"/>
+      <c r="M30" s="293"/>
+      <c r="N30" s="293"/>
       <c r="Q30" s="2" t="s">
         <v>59</v>
       </c>
@@ -11263,44 +11061,44 @@
         <v>339</v>
       </c>
       <c r="C31" s="69"/>
-      <c r="D31" s="230"/>
-      <c r="E31" s="230"/>
-      <c r="F31" s="230"/>
+      <c r="D31" s="311"/>
+      <c r="E31" s="311"/>
+      <c r="F31" s="311"/>
       <c r="G31" s="87" t="s">
         <v>60</v>
       </c>
       <c r="H31" s="83"/>
-      <c r="I31" s="213" t="s">
+      <c r="I31" s="292" t="s">
         <v>326</v>
       </c>
-      <c r="J31" s="213"/>
-      <c r="K31" s="213"/>
-      <c r="L31" s="213"/>
-      <c r="M31" s="213"/>
-      <c r="N31" s="213"/>
+      <c r="J31" s="292"/>
+      <c r="K31" s="292"/>
+      <c r="L31" s="292"/>
+      <c r="M31" s="292"/>
+      <c r="N31" s="292"/>
       <c r="Q31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="39.75" customHeight="1">
-      <c r="A32" s="231" t="s">
+      <c r="A32" s="321" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="232"/>
-      <c r="C32" s="233"/>
-      <c r="D32" s="230"/>
-      <c r="E32" s="230"/>
-      <c r="F32" s="230"/>
+      <c r="B32" s="310"/>
+      <c r="C32" s="322"/>
+      <c r="D32" s="311"/>
+      <c r="E32" s="311"/>
+      <c r="F32" s="311"/>
       <c r="G32" s="88" t="s">
         <v>63</v>
       </c>
       <c r="H32" s="89"/>
-      <c r="I32" s="213"/>
-      <c r="J32" s="213"/>
-      <c r="K32" s="213"/>
-      <c r="L32" s="213"/>
-      <c r="M32" s="213"/>
-      <c r="N32" s="213"/>
+      <c r="I32" s="292"/>
+      <c r="J32" s="292"/>
+      <c r="K32" s="292"/>
+      <c r="L32" s="292"/>
+      <c r="M32" s="292"/>
+      <c r="N32" s="292"/>
       <c r="Q32" s="2" t="s">
         <v>64</v>
       </c>
@@ -11309,75 +11107,69 @@
       <c r="A33" s="66">
         <v>15</v>
       </c>
-      <c r="B33" s="298" t="s">
+      <c r="B33" s="221" t="s">
         <v>338</v>
       </c>
-      <c r="C33" s="299"/>
-      <c r="D33" s="295"/>
-      <c r="E33" s="296"/>
-      <c r="F33" s="297"/>
+      <c r="C33" s="222"/>
+      <c r="D33" s="218"/>
+      <c r="E33" s="219"/>
+      <c r="F33" s="220"/>
       <c r="G33" s="90" t="s">
         <v>65</v>
       </c>
       <c r="H33" s="83"/>
-      <c r="I33" s="212"/>
-      <c r="J33" s="213"/>
-      <c r="K33" s="213"/>
-      <c r="L33" s="213"/>
-      <c r="M33" s="213"/>
-      <c r="N33" s="213"/>
+      <c r="I33" s="323"/>
+      <c r="J33" s="292"/>
+      <c r="K33" s="292"/>
+      <c r="L33" s="292"/>
+      <c r="M33" s="292"/>
+      <c r="N33" s="292"/>
       <c r="Q33" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A34" s="338" t="s">
-        <v>345</v>
-      </c>
-      <c r="B34" s="339"/>
-      <c r="C34" s="339"/>
-      <c r="D34" s="339"/>
-      <c r="E34" s="339"/>
-      <c r="F34" s="339"/>
-      <c r="G34" s="339"/>
-      <c r="H34" s="339"/>
-      <c r="I34" s="339"/>
-      <c r="J34" s="339"/>
-      <c r="K34" s="339"/>
-      <c r="L34" s="339"/>
-      <c r="M34" s="339"/>
-      <c r="N34" s="340"/>
+      <c r="A34" s="214" t="s">
+        <v>344</v>
+      </c>
+      <c r="B34" s="215"/>
+      <c r="C34" s="215"/>
+      <c r="D34" s="215"/>
+      <c r="E34" s="215"/>
+      <c r="F34" s="215"/>
+      <c r="G34" s="215"/>
+      <c r="H34" s="215"/>
+      <c r="I34" s="215"/>
+      <c r="J34" s="215"/>
+      <c r="K34" s="215"/>
+      <c r="L34" s="215"/>
+      <c r="M34" s="215"/>
+      <c r="N34" s="216"/>
       <c r="Q34" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="21" customHeight="1">
-      <c r="A35" s="341" t="s">
-        <v>344</v>
-      </c>
-      <c r="B35" s="341"/>
-      <c r="C35" s="341"/>
-      <c r="D35" s="523" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" s="524" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" s="524"/>
-      <c r="G35" s="522" t="s">
+      <c r="A35" s="217" t="s">
+        <v>345</v>
+      </c>
+      <c r="B35" s="217"/>
+      <c r="C35" s="217"/>
+      <c r="D35" s="213" t="s">
+        <v>347</v>
+      </c>
+      <c r="E35" s="213"/>
+      <c r="F35" s="213"/>
+      <c r="G35" s="517" t="s">
         <v>346</v>
       </c>
-      <c r="H35" s="342"/>
-      <c r="I35" s="333" t="s">
-        <v>348</v>
-      </c>
-      <c r="J35" s="334"/>
-      <c r="K35" s="335" t="s">
-        <v>347</v>
-      </c>
-      <c r="L35" s="336"/>
-      <c r="M35" s="337"/>
-      <c r="N35" s="337"/>
+      <c r="H35" s="518"/>
+      <c r="I35" s="213"/>
+      <c r="J35" s="213"/>
+      <c r="K35" s="213"/>
+      <c r="L35" s="213"/>
+      <c r="M35" s="213"/>
+      <c r="N35" s="213"/>
       <c r="Q35" s="2" t="s">
         <v>68</v>
       </c>
@@ -15221,86 +15013,11 @@
       <c r="N263" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="arAUbBnIVD8wqcWtD4/iXK1zi5k9qiJuth6tDtWHogGoZMJRjIpWyE9XDTvJEcYlzU26yWIAvGCJ1IT+47d4Ug==" saltValue="7kDanjRvYXtB1WKT5RwJEw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="94">
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="A34:N34"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vcZpRSeL7MD/5liJ7jQWiHSvb8cKjUkNOVcwICP1wgx7dy3imgNB0NJ/LQ0ARj8+D7aOpeJJ2530d3Jn5aC8cw==" saltValue="Jyye/obUWyzWvVaD//eRmg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="92">
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="R3:V13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:N15"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:I14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:N23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="I31:N31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="I35:N35"/>
     <mergeCell ref="I33:N33"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A21:A22"/>
@@ -15317,9 +15034,82 @@
     <mergeCell ref="D26:F27"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="I31:N31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:N23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:N15"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:I14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="R3:V13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I35:J35" xr:uid="{5EC3205D-4079-402B-BBE7-9B917DF21EB0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35" xr:uid="{5EC3205D-4079-402B-BBE7-9B917DF21EB0}">
       <formula1>"Straight, Gay, Lesbian, Bisexual, Pansexual, Asexual, Queer, Prefer not to say, Other(please specify)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15798,50 +15588,6 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="22550" r:id="rId218" name="Check Box 22">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>76200</xdr:colOff>
-                    <xdr:row>34</xdr:row>
-                    <xdr:rowOff>66675</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>666750</xdr:colOff>
-                    <xdr:row>34</xdr:row>
-                    <xdr:rowOff>247650</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="22551" r:id="rId219" name="Check Box 23">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>34</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>247650</xdr:colOff>
-                    <xdr:row>35</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>
@@ -15866,177 +15612,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1">
-      <c r="A1" s="485"/>
-      <c r="B1" s="486"/>
-      <c r="C1" s="486"/>
-      <c r="D1" s="486"/>
-      <c r="E1" s="486"/>
-      <c r="F1" s="486"/>
-      <c r="G1" s="486"/>
-      <c r="H1" s="486"/>
-      <c r="I1" s="486"/>
-      <c r="J1" s="486"/>
+      <c r="A1" s="443"/>
+      <c r="B1" s="444"/>
+      <c r="C1" s="444"/>
+      <c r="D1" s="444"/>
+      <c r="E1" s="444"/>
+      <c r="F1" s="444"/>
+      <c r="G1" s="444"/>
+      <c r="H1" s="444"/>
+      <c r="I1" s="444"/>
+      <c r="J1" s="444"/>
     </row>
     <row r="2" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A2" s="487">
+      <c r="A2" s="445">
         <v>34</v>
       </c>
-      <c r="B2" s="488"/>
-      <c r="C2" s="489" t="s">
+      <c r="B2" s="446"/>
+      <c r="C2" s="447" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="489"/>
-      <c r="E2" s="489"/>
-      <c r="F2" s="490"/>
-      <c r="G2" s="493"/>
-      <c r="H2" s="494"/>
-      <c r="I2" s="494"/>
-      <c r="J2" s="494"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="448"/>
+      <c r="G2" s="451"/>
+      <c r="H2" s="452"/>
+      <c r="I2" s="452"/>
+      <c r="J2" s="452"/>
       <c r="K2" s="181"/>
     </row>
     <row r="3" spans="1:11" ht="12.75" customHeight="1">
       <c r="A3" s="182"/>
       <c r="B3" s="183"/>
-      <c r="C3" s="491" t="s">
+      <c r="C3" s="449" t="s">
         <v>295</v>
       </c>
-      <c r="D3" s="491"/>
-      <c r="E3" s="491"/>
-      <c r="F3" s="492"/>
-      <c r="G3" s="495"/>
-      <c r="H3" s="496"/>
-      <c r="I3" s="496"/>
-      <c r="J3" s="496"/>
+      <c r="D3" s="449"/>
+      <c r="E3" s="449"/>
+      <c r="F3" s="450"/>
+      <c r="G3" s="453"/>
+      <c r="H3" s="454"/>
+      <c r="I3" s="454"/>
+      <c r="J3" s="454"/>
       <c r="K3" s="181"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="182"/>
       <c r="B4" s="183"/>
-      <c r="C4" s="491" t="s">
+      <c r="C4" s="449" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="491"/>
-      <c r="E4" s="491"/>
-      <c r="F4" s="492"/>
-      <c r="G4" s="495"/>
-      <c r="H4" s="496"/>
-      <c r="I4" s="496"/>
-      <c r="J4" s="496"/>
+      <c r="D4" s="449"/>
+      <c r="E4" s="449"/>
+      <c r="F4" s="450"/>
+      <c r="G4" s="453"/>
+      <c r="H4" s="454"/>
+      <c r="I4" s="454"/>
+      <c r="J4" s="454"/>
       <c r="K4" s="181"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="182"/>
       <c r="B5" s="183"/>
-      <c r="C5" s="491" t="s">
+      <c r="C5" s="449" t="s">
         <v>297</v>
       </c>
-      <c r="D5" s="491"/>
-      <c r="E5" s="491"/>
-      <c r="F5" s="492"/>
-      <c r="G5" s="456" t="b">
+      <c r="D5" s="449"/>
+      <c r="E5" s="449"/>
+      <c r="F5" s="450"/>
+      <c r="G5" s="435" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="441"/>
-      <c r="I5" s="441" t="b">
+      <c r="H5" s="434"/>
+      <c r="I5" s="434" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="441"/>
+      <c r="J5" s="434"/>
       <c r="K5" s="181"/>
     </row>
     <row r="6" spans="1:11" ht="24" customHeight="1">
       <c r="A6" s="182"/>
       <c r="B6" s="183"/>
-      <c r="C6" s="491" t="s">
+      <c r="C6" s="449" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="491"/>
-      <c r="E6" s="491"/>
-      <c r="F6" s="492"/>
-      <c r="G6" s="456" t="b">
+      <c r="D6" s="449"/>
+      <c r="E6" s="449"/>
+      <c r="F6" s="450"/>
+      <c r="G6" s="435" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="441"/>
-      <c r="I6" s="441" t="b">
+      <c r="H6" s="434"/>
+      <c r="I6" s="434" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="441"/>
+      <c r="J6" s="434"/>
       <c r="K6" s="181"/>
     </row>
     <row r="7" spans="1:11" ht="27" customHeight="1">
       <c r="A7" s="182"/>
       <c r="B7" s="183"/>
-      <c r="C7" s="491"/>
-      <c r="D7" s="491"/>
-      <c r="E7" s="491"/>
-      <c r="F7" s="491"/>
+      <c r="C7" s="449"/>
+      <c r="D7" s="449"/>
+      <c r="E7" s="449"/>
+      <c r="F7" s="449"/>
       <c r="G7" s="184" t="s">
         <v>322</v>
       </c>
       <c r="H7" s="185"/>
-      <c r="I7" s="511"/>
-      <c r="J7" s="511"/>
+      <c r="I7" s="436"/>
+      <c r="J7" s="436"/>
       <c r="K7" s="181"/>
     </row>
     <row r="8" spans="1:11" ht="31.5" customHeight="1">
       <c r="A8" s="186"/>
       <c r="B8" s="187"/>
-      <c r="C8" s="502"/>
-      <c r="D8" s="502"/>
-      <c r="E8" s="502"/>
-      <c r="F8" s="503"/>
-      <c r="G8" s="509"/>
-      <c r="H8" s="510"/>
-      <c r="I8" s="510"/>
-      <c r="J8" s="510"/>
+      <c r="C8" s="468"/>
+      <c r="D8" s="468"/>
+      <c r="E8" s="468"/>
+      <c r="F8" s="469"/>
+      <c r="G8" s="477"/>
+      <c r="H8" s="478"/>
+      <c r="I8" s="478"/>
+      <c r="J8" s="478"/>
       <c r="K8" s="181"/>
     </row>
     <row r="9" spans="1:11" ht="20.45" customHeight="1">
-      <c r="A9" s="504">
+      <c r="A9" s="470">
         <v>35</v>
       </c>
-      <c r="B9" s="505"/>
-      <c r="C9" s="470" t="s">
+      <c r="B9" s="471"/>
+      <c r="C9" s="472" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="470"/>
-      <c r="E9" s="381"/>
-      <c r="F9" s="506"/>
-      <c r="G9" s="462" t="b">
+      <c r="D9" s="472"/>
+      <c r="E9" s="376"/>
+      <c r="F9" s="473"/>
+      <c r="G9" s="438" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="463"/>
-      <c r="I9" s="463" t="b">
+      <c r="H9" s="437"/>
+      <c r="I9" s="437" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="463"/>
+      <c r="J9" s="437"/>
       <c r="K9" s="181"/>
     </row>
     <row r="10" spans="1:11" ht="26.25" customHeight="1">
       <c r="A10" s="188"/>
       <c r="B10" s="189"/>
-      <c r="C10" s="470"/>
-      <c r="D10" s="470"/>
-      <c r="E10" s="381"/>
-      <c r="F10" s="506"/>
-      <c r="G10" s="512" t="s">
+      <c r="C10" s="472"/>
+      <c r="D10" s="472"/>
+      <c r="E10" s="376"/>
+      <c r="F10" s="473"/>
+      <c r="G10" s="439" t="s">
         <v>322</v>
       </c>
-      <c r="H10" s="513"/>
-      <c r="I10" s="508"/>
-      <c r="J10" s="508"/>
+      <c r="H10" s="440"/>
+      <c r="I10" s="427"/>
+      <c r="J10" s="427"/>
       <c r="K10" s="181"/>
     </row>
     <row r="11" spans="1:11" ht="21.75" customHeight="1">
       <c r="A11" s="188"/>
       <c r="B11" s="189"/>
-      <c r="C11" s="381"/>
-      <c r="D11" s="381"/>
-      <c r="E11" s="381"/>
-      <c r="F11" s="381"/>
-      <c r="G11" s="483"/>
-      <c r="H11" s="484"/>
-      <c r="I11" s="484"/>
-      <c r="J11" s="484"/>
+      <c r="C11" s="376"/>
+      <c r="D11" s="376"/>
+      <c r="E11" s="376"/>
+      <c r="F11" s="376"/>
+      <c r="G11" s="425"/>
+      <c r="H11" s="426"/>
+      <c r="I11" s="426"/>
+      <c r="J11" s="426"/>
       <c r="K11" s="181"/>
     </row>
     <row r="12" spans="1:11" ht="18.75" customHeight="1">
@@ -16046,172 +15792,172 @@
       <c r="D12" s="192"/>
       <c r="E12" s="193"/>
       <c r="F12" s="194"/>
-      <c r="G12" s="514" t="b">
+      <c r="G12" s="441" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="515"/>
-      <c r="I12" s="515" t="b">
+      <c r="H12" s="442"/>
+      <c r="I12" s="442" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="515"/>
+      <c r="J12" s="442"/>
       <c r="K12" s="181"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1">
       <c r="A13" s="190"/>
       <c r="B13" s="191"/>
-      <c r="C13" s="497" t="s">
+      <c r="C13" s="455" t="s">
         <v>300</v>
       </c>
-      <c r="D13" s="497"/>
-      <c r="E13" s="498"/>
-      <c r="F13" s="499"/>
-      <c r="G13" s="514"/>
-      <c r="H13" s="515"/>
-      <c r="I13" s="515"/>
-      <c r="J13" s="515"/>
+      <c r="D13" s="455"/>
+      <c r="E13" s="456"/>
+      <c r="F13" s="457"/>
+      <c r="G13" s="441"/>
+      <c r="H13" s="442"/>
+      <c r="I13" s="442"/>
+      <c r="J13" s="442"/>
       <c r="K13" s="181"/>
     </row>
     <row r="14" spans="1:11" ht="23.25" customHeight="1">
       <c r="A14" s="190"/>
       <c r="B14" s="191"/>
-      <c r="C14" s="497"/>
-      <c r="D14" s="497"/>
-      <c r="E14" s="498"/>
-      <c r="F14" s="499"/>
-      <c r="G14" s="433" t="s">
+      <c r="C14" s="455"/>
+      <c r="D14" s="455"/>
+      <c r="E14" s="456"/>
+      <c r="F14" s="457"/>
+      <c r="G14" s="429" t="s">
         <v>325</v>
       </c>
-      <c r="H14" s="434"/>
-      <c r="I14" s="519"/>
-      <c r="J14" s="519"/>
+      <c r="H14" s="430"/>
+      <c r="I14" s="431"/>
+      <c r="J14" s="431"/>
       <c r="K14" s="181"/>
     </row>
     <row r="15" spans="1:11" ht="21" customHeight="1">
       <c r="A15" s="190"/>
       <c r="B15" s="191"/>
-      <c r="C15" s="497"/>
-      <c r="D15" s="497"/>
-      <c r="E15" s="498"/>
-      <c r="F15" s="499"/>
-      <c r="G15" s="516" t="s">
+      <c r="C15" s="455"/>
+      <c r="D15" s="455"/>
+      <c r="E15" s="456"/>
+      <c r="F15" s="457"/>
+      <c r="G15" s="423" t="s">
         <v>301</v>
       </c>
-      <c r="H15" s="517"/>
-      <c r="I15" s="508"/>
-      <c r="J15" s="508"/>
+      <c r="H15" s="424"/>
+      <c r="I15" s="427"/>
+      <c r="J15" s="427"/>
       <c r="K15" s="181"/>
     </row>
     <row r="16" spans="1:11" ht="27.75" customHeight="1">
       <c r="A16" s="190"/>
       <c r="B16" s="191"/>
-      <c r="C16" s="497"/>
-      <c r="D16" s="497"/>
-      <c r="E16" s="498"/>
-      <c r="F16" s="499"/>
-      <c r="G16" s="520" t="s">
+      <c r="C16" s="455"/>
+      <c r="D16" s="455"/>
+      <c r="E16" s="456"/>
+      <c r="F16" s="457"/>
+      <c r="G16" s="432" t="s">
         <v>302</v>
       </c>
-      <c r="H16" s="521"/>
-      <c r="I16" s="518"/>
-      <c r="J16" s="518"/>
+      <c r="H16" s="433"/>
+      <c r="I16" s="428"/>
+      <c r="J16" s="428"/>
       <c r="K16" s="181"/>
     </row>
     <row r="17" spans="1:12" ht="21" customHeight="1">
       <c r="A17" s="195"/>
       <c r="B17" s="196"/>
-      <c r="C17" s="500"/>
-      <c r="D17" s="500"/>
-      <c r="E17" s="500"/>
-      <c r="F17" s="501"/>
-      <c r="G17" s="483" t="s">
+      <c r="C17" s="458"/>
+      <c r="D17" s="458"/>
+      <c r="E17" s="458"/>
+      <c r="F17" s="459"/>
+      <c r="G17" s="425" t="s">
         <v>303</v>
       </c>
-      <c r="H17" s="484"/>
-      <c r="I17" s="484"/>
-      <c r="J17" s="484"/>
+      <c r="H17" s="426"/>
+      <c r="I17" s="426"/>
+      <c r="J17" s="426"/>
       <c r="K17" s="181"/>
     </row>
     <row r="18" spans="1:12" ht="33" customHeight="1">
-      <c r="A18" s="458">
+      <c r="A18" s="466">
         <v>36</v>
       </c>
-      <c r="B18" s="459"/>
-      <c r="C18" s="481" t="s">
+      <c r="B18" s="467"/>
+      <c r="C18" s="460" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="481"/>
-      <c r="E18" s="481"/>
-      <c r="F18" s="482"/>
-      <c r="G18" s="462" t="b">
+      <c r="D18" s="460"/>
+      <c r="E18" s="460"/>
+      <c r="F18" s="461"/>
+      <c r="G18" s="438" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="463"/>
-      <c r="I18" s="463" t="b">
+      <c r="H18" s="437"/>
+      <c r="I18" s="437" t="b">
         <v>0</v>
       </c>
-      <c r="J18" s="463"/>
+      <c r="J18" s="437"/>
       <c r="K18" s="181"/>
     </row>
     <row r="19" spans="1:12" ht="26.25" customHeight="1">
       <c r="A19" s="188"/>
       <c r="B19" s="189"/>
-      <c r="C19" s="437"/>
-      <c r="D19" s="437"/>
-      <c r="E19" s="437"/>
-      <c r="F19" s="438"/>
-      <c r="G19" s="464" t="s">
+      <c r="C19" s="462"/>
+      <c r="D19" s="462"/>
+      <c r="E19" s="462"/>
+      <c r="F19" s="463"/>
+      <c r="G19" s="475" t="s">
         <v>324</v>
       </c>
-      <c r="H19" s="465"/>
-      <c r="I19" s="508"/>
-      <c r="J19" s="508"/>
+      <c r="H19" s="476"/>
+      <c r="I19" s="427"/>
+      <c r="J19" s="427"/>
       <c r="K19" s="199"/>
     </row>
     <row r="20" spans="1:12" ht="25.5" customHeight="1">
       <c r="A20" s="200"/>
       <c r="B20" s="201"/>
-      <c r="C20" s="466"/>
-      <c r="D20" s="466"/>
-      <c r="E20" s="466"/>
-      <c r="F20" s="467"/>
-      <c r="G20" s="483"/>
-      <c r="H20" s="484"/>
-      <c r="I20" s="507"/>
-      <c r="J20" s="507"/>
+      <c r="C20" s="464"/>
+      <c r="D20" s="464"/>
+      <c r="E20" s="464"/>
+      <c r="F20" s="465"/>
+      <c r="G20" s="425"/>
+      <c r="H20" s="426"/>
+      <c r="I20" s="474"/>
+      <c r="J20" s="474"/>
       <c r="K20" s="181"/>
     </row>
     <row r="21" spans="1:12" ht="26.25" customHeight="1">
-      <c r="A21" s="458">
+      <c r="A21" s="466">
         <v>37</v>
       </c>
-      <c r="B21" s="459"/>
-      <c r="C21" s="481" t="s">
+      <c r="B21" s="467"/>
+      <c r="C21" s="460" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="481"/>
-      <c r="E21" s="481"/>
-      <c r="F21" s="482"/>
-      <c r="G21" s="462" t="b">
+      <c r="D21" s="460"/>
+      <c r="E21" s="460"/>
+      <c r="F21" s="461"/>
+      <c r="G21" s="438" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="463"/>
-      <c r="I21" s="463" t="b">
+      <c r="H21" s="437"/>
+      <c r="I21" s="437" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="463"/>
+      <c r="J21" s="437"/>
       <c r="K21" s="181"/>
     </row>
     <row r="22" spans="1:12" ht="27.75" customHeight="1">
       <c r="A22" s="188"/>
       <c r="B22" s="189"/>
-      <c r="C22" s="437"/>
-      <c r="D22" s="437"/>
-      <c r="E22" s="437"/>
-      <c r="F22" s="438"/>
-      <c r="G22" s="464" t="s">
+      <c r="C22" s="462"/>
+      <c r="D22" s="462"/>
+      <c r="E22" s="462"/>
+      <c r="F22" s="463"/>
+      <c r="G22" s="475" t="s">
         <v>323</v>
       </c>
-      <c r="H22" s="465"/>
+      <c r="H22" s="476"/>
       <c r="I22" s="480"/>
       <c r="J22" s="480"/>
       <c r="K22" s="181"/>
@@ -16219,51 +15965,51 @@
     <row r="23" spans="1:12" ht="39.75" customHeight="1">
       <c r="A23" s="200"/>
       <c r="B23" s="201"/>
-      <c r="C23" s="466"/>
-      <c r="D23" s="466"/>
-      <c r="E23" s="466"/>
-      <c r="F23" s="467"/>
-      <c r="G23" s="483"/>
-      <c r="H23" s="484"/>
-      <c r="I23" s="484"/>
-      <c r="J23" s="484"/>
+      <c r="C23" s="464"/>
+      <c r="D23" s="464"/>
+      <c r="E23" s="464"/>
+      <c r="F23" s="465"/>
+      <c r="G23" s="425"/>
+      <c r="H23" s="426"/>
+      <c r="I23" s="426"/>
+      <c r="J23" s="426"/>
       <c r="K23" s="202"/>
     </row>
     <row r="24" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A24" s="458">
+      <c r="A24" s="466">
         <v>38</v>
       </c>
-      <c r="B24" s="459"/>
-      <c r="C24" s="481" t="s">
+      <c r="B24" s="467"/>
+      <c r="C24" s="460" t="s">
         <v>306</v>
       </c>
-      <c r="D24" s="481"/>
-      <c r="E24" s="481"/>
-      <c r="F24" s="482"/>
-      <c r="G24" s="462" t="b">
+      <c r="D24" s="460"/>
+      <c r="E24" s="460"/>
+      <c r="F24" s="461"/>
+      <c r="G24" s="438" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="463"/>
-      <c r="I24" s="463" t="b">
+      <c r="H24" s="437"/>
+      <c r="I24" s="437" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="463"/>
+      <c r="J24" s="437"/>
       <c r="K24" s="181"/>
       <c r="L24" s="203"/>
     </row>
     <row r="25" spans="1:12" ht="28.5" customHeight="1">
       <c r="A25" s="188"/>
       <c r="B25" s="189"/>
-      <c r="C25" s="437"/>
-      <c r="D25" s="437"/>
-      <c r="E25" s="437"/>
-      <c r="F25" s="438"/>
-      <c r="G25" s="433" t="s">
+      <c r="C25" s="462"/>
+      <c r="D25" s="462"/>
+      <c r="E25" s="462"/>
+      <c r="F25" s="463"/>
+      <c r="G25" s="429" t="s">
         <v>307</v>
       </c>
-      <c r="H25" s="434"/>
-      <c r="I25" s="436"/>
-      <c r="J25" s="436"/>
+      <c r="H25" s="430"/>
+      <c r="I25" s="479"/>
+      <c r="J25" s="479"/>
       <c r="K25" s="181"/>
     </row>
     <row r="26" spans="1:12" ht="23.25" customHeight="1">
@@ -16273,123 +16019,123 @@
       <c r="D26" s="197"/>
       <c r="E26" s="197"/>
       <c r="F26" s="198"/>
-      <c r="G26" s="474" t="b">
+      <c r="G26" s="489" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="475"/>
-      <c r="I26" s="476" t="b">
+      <c r="H26" s="490"/>
+      <c r="I26" s="491" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="476"/>
+      <c r="J26" s="491"/>
       <c r="K26" s="181"/>
     </row>
     <row r="27" spans="1:12" ht="24.75" customHeight="1">
       <c r="A27" s="188"/>
       <c r="B27" s="189"/>
-      <c r="C27" s="437" t="s">
+      <c r="C27" s="462" t="s">
         <v>308</v>
       </c>
-      <c r="D27" s="437"/>
-      <c r="E27" s="437"/>
-      <c r="F27" s="438"/>
-      <c r="G27" s="474"/>
-      <c r="H27" s="475"/>
-      <c r="I27" s="477"/>
-      <c r="J27" s="477"/>
+      <c r="D27" s="462"/>
+      <c r="E27" s="462"/>
+      <c r="F27" s="463"/>
+      <c r="G27" s="489"/>
+      <c r="H27" s="490"/>
+      <c r="I27" s="492"/>
+      <c r="J27" s="492"/>
       <c r="K27" s="181"/>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="188"/>
       <c r="B28" s="189"/>
-      <c r="C28" s="437"/>
-      <c r="D28" s="437"/>
-      <c r="E28" s="437"/>
-      <c r="F28" s="438"/>
-      <c r="G28" s="433" t="s">
+      <c r="C28" s="462"/>
+      <c r="D28" s="462"/>
+      <c r="E28" s="462"/>
+      <c r="F28" s="463"/>
+      <c r="G28" s="429" t="s">
         <v>307</v>
       </c>
-      <c r="H28" s="434"/>
-      <c r="I28" s="436"/>
-      <c r="J28" s="436"/>
+      <c r="H28" s="430"/>
+      <c r="I28" s="479"/>
+      <c r="J28" s="479"/>
       <c r="K28" s="181"/>
     </row>
     <row r="29" spans="1:12" ht="30.75" customHeight="1">
       <c r="A29" s="200"/>
       <c r="B29" s="201"/>
-      <c r="C29" s="466"/>
-      <c r="D29" s="466"/>
-      <c r="E29" s="466"/>
-      <c r="F29" s="467"/>
-      <c r="G29" s="460"/>
-      <c r="H29" s="461"/>
-      <c r="I29" s="461"/>
-      <c r="J29" s="461"/>
+      <c r="C29" s="464"/>
+      <c r="D29" s="464"/>
+      <c r="E29" s="464"/>
+      <c r="F29" s="465"/>
+      <c r="G29" s="481"/>
+      <c r="H29" s="482"/>
+      <c r="I29" s="482"/>
+      <c r="J29" s="482"/>
       <c r="K29" s="181"/>
     </row>
     <row r="30" spans="1:12" ht="23.45" customHeight="1">
-      <c r="A30" s="458">
+      <c r="A30" s="466">
         <v>39</v>
       </c>
-      <c r="B30" s="459"/>
-      <c r="C30" s="468" t="s">
+      <c r="B30" s="467"/>
+      <c r="C30" s="484" t="s">
         <v>309</v>
       </c>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="469"/>
-      <c r="G30" s="462" t="b">
+      <c r="D30" s="484"/>
+      <c r="E30" s="484"/>
+      <c r="F30" s="485"/>
+      <c r="G30" s="438" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="463"/>
-      <c r="I30" s="463" t="b">
+      <c r="H30" s="437"/>
+      <c r="I30" s="437" t="b">
         <v>0</v>
       </c>
-      <c r="J30" s="463"/>
+      <c r="J30" s="437"/>
       <c r="K30" s="181"/>
     </row>
     <row r="31" spans="1:12" ht="27" customHeight="1">
       <c r="A31" s="188"/>
       <c r="B31" s="189"/>
-      <c r="C31" s="470"/>
-      <c r="D31" s="470"/>
-      <c r="E31" s="470"/>
-      <c r="F31" s="471"/>
-      <c r="G31" s="464" t="s">
+      <c r="C31" s="472"/>
+      <c r="D31" s="472"/>
+      <c r="E31" s="472"/>
+      <c r="F31" s="486"/>
+      <c r="G31" s="475" t="s">
         <v>310</v>
       </c>
-      <c r="H31" s="465"/>
-      <c r="I31" s="435"/>
-      <c r="J31" s="436"/>
+      <c r="H31" s="476"/>
+      <c r="I31" s="483"/>
+      <c r="J31" s="479"/>
       <c r="K31" s="181"/>
     </row>
     <row r="32" spans="1:12" ht="33.75" customHeight="1">
       <c r="A32" s="200"/>
       <c r="B32" s="201"/>
-      <c r="C32" s="472"/>
-      <c r="D32" s="472"/>
-      <c r="E32" s="472"/>
-      <c r="F32" s="473"/>
-      <c r="G32" s="478"/>
-      <c r="H32" s="479"/>
-      <c r="I32" s="479"/>
-      <c r="J32" s="479"/>
+      <c r="C32" s="487"/>
+      <c r="D32" s="487"/>
+      <c r="E32" s="487"/>
+      <c r="F32" s="488"/>
+      <c r="G32" s="493"/>
+      <c r="H32" s="494"/>
+      <c r="I32" s="494"/>
+      <c r="J32" s="494"/>
       <c r="K32" s="181"/>
     </row>
     <row r="33" spans="1:11" ht="46.5" customHeight="1">
-      <c r="A33" s="452">
+      <c r="A33" s="495">
         <v>40</v>
       </c>
-      <c r="B33" s="453"/>
-      <c r="C33" s="437" t="s">
+      <c r="B33" s="496"/>
+      <c r="C33" s="462" t="s">
         <v>311</v>
       </c>
-      <c r="D33" s="437"/>
-      <c r="E33" s="437"/>
-      <c r="F33" s="438"/>
-      <c r="G33" s="454"/>
-      <c r="H33" s="455"/>
-      <c r="I33" s="455"/>
-      <c r="J33" s="455"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="463"/>
+      <c r="G33" s="497"/>
+      <c r="H33" s="498"/>
+      <c r="I33" s="498"/>
+      <c r="J33" s="498"/>
       <c r="K33" s="181"/>
     </row>
     <row r="34" spans="1:11" ht="39.75" customHeight="1">
@@ -16397,35 +16143,35 @@
         <v>312</v>
       </c>
       <c r="B34" s="205"/>
-      <c r="C34" s="437" t="s">
+      <c r="C34" s="462" t="s">
         <v>313</v>
       </c>
-      <c r="D34" s="437"/>
-      <c r="E34" s="437"/>
-      <c r="F34" s="438"/>
-      <c r="G34" s="456" t="b">
+      <c r="D34" s="462"/>
+      <c r="E34" s="462"/>
+      <c r="F34" s="463"/>
+      <c r="G34" s="435" t="b">
         <v>0</v>
       </c>
-      <c r="H34" s="441"/>
-      <c r="I34" s="441" t="b">
+      <c r="H34" s="434"/>
+      <c r="I34" s="434" t="b">
         <v>0</v>
       </c>
-      <c r="J34" s="441"/>
+      <c r="J34" s="434"/>
       <c r="K34" s="181"/>
     </row>
     <row r="35" spans="1:11" ht="36.75" customHeight="1">
       <c r="A35" s="206"/>
       <c r="B35" s="205"/>
-      <c r="C35" s="437"/>
-      <c r="D35" s="437"/>
-      <c r="E35" s="437"/>
-      <c r="F35" s="438"/>
-      <c r="G35" s="433" t="s">
+      <c r="C35" s="462"/>
+      <c r="D35" s="462"/>
+      <c r="E35" s="462"/>
+      <c r="F35" s="463"/>
+      <c r="G35" s="429" t="s">
         <v>307</v>
       </c>
-      <c r="H35" s="434"/>
-      <c r="I35" s="435"/>
-      <c r="J35" s="436"/>
+      <c r="H35" s="430"/>
+      <c r="I35" s="483"/>
+      <c r="J35" s="479"/>
       <c r="K35" s="207"/>
     </row>
     <row r="36" spans="1:11" ht="33" customHeight="1">
@@ -16433,35 +16179,35 @@
         <v>314</v>
       </c>
       <c r="B36" s="205"/>
-      <c r="C36" s="438" t="s">
+      <c r="C36" s="463" t="s">
         <v>315</v>
       </c>
-      <c r="D36" s="438"/>
-      <c r="E36" s="438"/>
-      <c r="F36" s="438"/>
-      <c r="G36" s="456" t="b">
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
+      <c r="G36" s="435" t="b">
         <v>0</v>
       </c>
-      <c r="H36" s="441"/>
-      <c r="I36" s="457" t="b">
+      <c r="H36" s="434"/>
+      <c r="I36" s="499" t="b">
         <v>0</v>
       </c>
-      <c r="J36" s="457"/>
+      <c r="J36" s="499"/>
       <c r="K36" s="181"/>
     </row>
     <row r="37" spans="1:11" ht="34.5" customHeight="1">
       <c r="A37" s="206"/>
       <c r="B37" s="205"/>
-      <c r="C37" s="438"/>
-      <c r="D37" s="438"/>
-      <c r="E37" s="438"/>
-      <c r="F37" s="438"/>
-      <c r="G37" s="433" t="s">
+      <c r="C37" s="463"/>
+      <c r="D37" s="463"/>
+      <c r="E37" s="463"/>
+      <c r="F37" s="463"/>
+      <c r="G37" s="429" t="s">
         <v>307</v>
       </c>
-      <c r="H37" s="434"/>
-      <c r="I37" s="435"/>
-      <c r="J37" s="436"/>
+      <c r="H37" s="430"/>
+      <c r="I37" s="483"/>
+      <c r="J37" s="479"/>
       <c r="K37" s="207"/>
     </row>
     <row r="38" spans="1:11" ht="30.75" customHeight="1">
@@ -16469,55 +16215,55 @@
         <v>316</v>
       </c>
       <c r="B38" s="205"/>
-      <c r="C38" s="437" t="s">
+      <c r="C38" s="462" t="s">
         <v>317</v>
       </c>
-      <c r="D38" s="437"/>
+      <c r="D38" s="462"/>
       <c r="E38" s="208"/>
       <c r="F38" s="209"/>
-      <c r="G38" s="439" t="b">
+      <c r="G38" s="500" t="b">
         <v>0</v>
       </c>
-      <c r="H38" s="440"/>
-      <c r="I38" s="441" t="b">
+      <c r="H38" s="501"/>
+      <c r="I38" s="434" t="b">
         <v>0</v>
       </c>
-      <c r="J38" s="441"/>
+      <c r="J38" s="434"/>
       <c r="K38" s="181"/>
     </row>
     <row r="39" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A39" s="444"/>
-      <c r="B39" s="445"/>
-      <c r="C39" s="445"/>
-      <c r="D39" s="445"/>
-      <c r="E39" s="445"/>
-      <c r="F39" s="446"/>
-      <c r="G39" s="433" t="s">
+      <c r="A39" s="504"/>
+      <c r="B39" s="505"/>
+      <c r="C39" s="505"/>
+      <c r="D39" s="505"/>
+      <c r="E39" s="505"/>
+      <c r="F39" s="506"/>
+      <c r="G39" s="429" t="s">
         <v>307</v>
       </c>
-      <c r="H39" s="434"/>
-      <c r="I39" s="435"/>
-      <c r="J39" s="436"/>
+      <c r="H39" s="430"/>
+      <c r="I39" s="483"/>
+      <c r="J39" s="479"/>
       <c r="K39" s="207"/>
     </row>
     <row r="40" spans="1:11" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A40" s="447"/>
-      <c r="B40" s="448"/>
-      <c r="C40" s="448"/>
-      <c r="D40" s="448"/>
-      <c r="E40" s="448"/>
-      <c r="F40" s="449"/>
-      <c r="G40" s="450"/>
-      <c r="H40" s="451"/>
-      <c r="I40" s="451"/>
-      <c r="J40" s="451"/>
+      <c r="A40" s="507"/>
+      <c r="B40" s="508"/>
+      <c r="C40" s="508"/>
+      <c r="D40" s="508"/>
+      <c r="E40" s="508"/>
+      <c r="F40" s="509"/>
+      <c r="G40" s="510"/>
+      <c r="H40" s="511"/>
+      <c r="I40" s="511"/>
+      <c r="J40" s="511"/>
       <c r="K40" s="207"/>
     </row>
     <row r="41" spans="1:11" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A41" s="442">
+      <c r="A41" s="502">
         <v>41</v>
       </c>
-      <c r="B41" s="443"/>
+      <c r="B41" s="503"/>
       <c r="C41" s="210" t="s">
         <v>318</v>
       </c>
@@ -16531,146 +16277,146 @@
       <c r="K41" s="181"/>
     </row>
     <row r="42" spans="1:11" ht="18" customHeight="1">
-      <c r="A42" s="428" t="s">
+      <c r="A42" s="512" t="s">
         <v>319</v>
       </c>
-      <c r="B42" s="429"/>
-      <c r="C42" s="429"/>
-      <c r="D42" s="429"/>
-      <c r="E42" s="430"/>
-      <c r="F42" s="428" t="s">
+      <c r="B42" s="513"/>
+      <c r="C42" s="513"/>
+      <c r="D42" s="513"/>
+      <c r="E42" s="514"/>
+      <c r="F42" s="512" t="s">
         <v>320</v>
       </c>
-      <c r="G42" s="429"/>
-      <c r="H42" s="429"/>
-      <c r="I42" s="431" t="s">
+      <c r="G42" s="513"/>
+      <c r="H42" s="513"/>
+      <c r="I42" s="515" t="s">
         <v>321</v>
       </c>
-      <c r="J42" s="432"/>
+      <c r="J42" s="516"/>
       <c r="K42" s="181"/>
     </row>
     <row r="43" spans="1:11" ht="24" customHeight="1">
-      <c r="A43" s="426"/>
-      <c r="B43" s="426"/>
-      <c r="C43" s="426"/>
-      <c r="D43" s="426"/>
-      <c r="E43" s="426"/>
-      <c r="F43" s="426"/>
-      <c r="G43" s="426"/>
-      <c r="H43" s="426"/>
-      <c r="I43" s="427"/>
-      <c r="J43" s="427"/>
+      <c r="A43" s="421"/>
+      <c r="B43" s="421"/>
+      <c r="C43" s="421"/>
+      <c r="D43" s="421"/>
+      <c r="E43" s="421"/>
+      <c r="F43" s="421"/>
+      <c r="G43" s="421"/>
+      <c r="H43" s="421"/>
+      <c r="I43" s="422"/>
+      <c r="J43" s="422"/>
       <c r="K43" s="181"/>
     </row>
     <row r="44" spans="1:11" ht="24" customHeight="1">
-      <c r="A44" s="426"/>
-      <c r="B44" s="426"/>
-      <c r="C44" s="426"/>
-      <c r="D44" s="426"/>
-      <c r="E44" s="426"/>
-      <c r="F44" s="426"/>
-      <c r="G44" s="426"/>
-      <c r="H44" s="426"/>
-      <c r="I44" s="427"/>
-      <c r="J44" s="427"/>
+      <c r="A44" s="421"/>
+      <c r="B44" s="421"/>
+      <c r="C44" s="421"/>
+      <c r="D44" s="421"/>
+      <c r="E44" s="421"/>
+      <c r="F44" s="421"/>
+      <c r="G44" s="421"/>
+      <c r="H44" s="421"/>
+      <c r="I44" s="422"/>
+      <c r="J44" s="422"/>
       <c r="K44" s="181"/>
     </row>
     <row r="45" spans="1:11" ht="24" customHeight="1">
-      <c r="A45" s="426"/>
-      <c r="B45" s="426"/>
-      <c r="C45" s="426"/>
-      <c r="D45" s="426"/>
-      <c r="E45" s="426"/>
-      <c r="F45" s="426"/>
-      <c r="G45" s="426"/>
-      <c r="H45" s="426"/>
-      <c r="I45" s="427"/>
-      <c r="J45" s="427"/>
+      <c r="A45" s="421"/>
+      <c r="B45" s="421"/>
+      <c r="C45" s="421"/>
+      <c r="D45" s="421"/>
+      <c r="E45" s="421"/>
+      <c r="F45" s="421"/>
+      <c r="G45" s="421"/>
+      <c r="H45" s="421"/>
+      <c r="I45" s="422"/>
+      <c r="J45" s="422"/>
       <c r="K45" s="181"/>
     </row>
     <row r="46" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A46" s="426"/>
-      <c r="B46" s="426"/>
-      <c r="C46" s="426"/>
-      <c r="D46" s="426"/>
-      <c r="E46" s="426"/>
-      <c r="F46" s="426"/>
-      <c r="G46" s="426"/>
-      <c r="H46" s="426"/>
-      <c r="I46" s="427"/>
-      <c r="J46" s="427"/>
+      <c r="A46" s="421"/>
+      <c r="B46" s="421"/>
+      <c r="C46" s="421"/>
+      <c r="D46" s="421"/>
+      <c r="E46" s="421"/>
+      <c r="F46" s="421"/>
+      <c r="G46" s="421"/>
+      <c r="H46" s="421"/>
+      <c r="I46" s="422"/>
+      <c r="J46" s="422"/>
     </row>
     <row r="47" spans="1:11" ht="24.75" customHeight="1">
-      <c r="A47" s="426"/>
-      <c r="B47" s="426"/>
-      <c r="C47" s="426"/>
-      <c r="D47" s="426"/>
-      <c r="E47" s="426"/>
-      <c r="F47" s="426"/>
-      <c r="G47" s="426"/>
-      <c r="H47" s="426"/>
-      <c r="I47" s="427"/>
-      <c r="J47" s="427"/>
+      <c r="A47" s="421"/>
+      <c r="B47" s="421"/>
+      <c r="C47" s="421"/>
+      <c r="D47" s="421"/>
+      <c r="E47" s="421"/>
+      <c r="F47" s="421"/>
+      <c r="G47" s="421"/>
+      <c r="H47" s="421"/>
+      <c r="I47" s="422"/>
+      <c r="J47" s="422"/>
     </row>
     <row r="48" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A48" s="426"/>
-      <c r="B48" s="426"/>
-      <c r="C48" s="426"/>
-      <c r="D48" s="426"/>
-      <c r="E48" s="426"/>
-      <c r="F48" s="426"/>
-      <c r="G48" s="426"/>
-      <c r="H48" s="426"/>
-      <c r="I48" s="427"/>
-      <c r="J48" s="427"/>
+      <c r="A48" s="421"/>
+      <c r="B48" s="421"/>
+      <c r="C48" s="421"/>
+      <c r="D48" s="421"/>
+      <c r="E48" s="421"/>
+      <c r="F48" s="421"/>
+      <c r="G48" s="421"/>
+      <c r="H48" s="421"/>
+      <c r="I48" s="422"/>
+      <c r="J48" s="422"/>
     </row>
     <row r="49" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A49" s="426"/>
-      <c r="B49" s="426"/>
-      <c r="C49" s="426"/>
-      <c r="D49" s="426"/>
-      <c r="E49" s="426"/>
-      <c r="F49" s="426"/>
-      <c r="G49" s="426"/>
-      <c r="H49" s="426"/>
-      <c r="I49" s="427"/>
-      <c r="J49" s="427"/>
+      <c r="A49" s="421"/>
+      <c r="B49" s="421"/>
+      <c r="C49" s="421"/>
+      <c r="D49" s="421"/>
+      <c r="E49" s="421"/>
+      <c r="F49" s="421"/>
+      <c r="G49" s="421"/>
+      <c r="H49" s="421"/>
+      <c r="I49" s="422"/>
+      <c r="J49" s="422"/>
     </row>
     <row r="50" spans="1:10" ht="21" customHeight="1">
-      <c r="A50" s="426"/>
-      <c r="B50" s="426"/>
-      <c r="C50" s="426"/>
-      <c r="D50" s="426"/>
-      <c r="E50" s="426"/>
-      <c r="F50" s="426"/>
-      <c r="G50" s="426"/>
-      <c r="H50" s="426"/>
-      <c r="I50" s="427"/>
-      <c r="J50" s="427"/>
+      <c r="A50" s="421"/>
+      <c r="B50" s="421"/>
+      <c r="C50" s="421"/>
+      <c r="D50" s="421"/>
+      <c r="E50" s="421"/>
+      <c r="F50" s="421"/>
+      <c r="G50" s="421"/>
+      <c r="H50" s="421"/>
+      <c r="I50" s="422"/>
+      <c r="J50" s="422"/>
     </row>
     <row r="51" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A51" s="426"/>
-      <c r="B51" s="426"/>
-      <c r="C51" s="426"/>
-      <c r="D51" s="426"/>
-      <c r="E51" s="426"/>
-      <c r="F51" s="426"/>
-      <c r="G51" s="426"/>
-      <c r="H51" s="426"/>
-      <c r="I51" s="427"/>
-      <c r="J51" s="427"/>
+      <c r="A51" s="421"/>
+      <c r="B51" s="421"/>
+      <c r="C51" s="421"/>
+      <c r="D51" s="421"/>
+      <c r="E51" s="421"/>
+      <c r="F51" s="421"/>
+      <c r="G51" s="421"/>
+      <c r="H51" s="421"/>
+      <c r="I51" s="422"/>
+      <c r="J51" s="422"/>
     </row>
     <row r="52" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A52" s="426"/>
-      <c r="B52" s="426"/>
-      <c r="C52" s="426"/>
-      <c r="D52" s="426"/>
-      <c r="E52" s="426"/>
-      <c r="F52" s="426"/>
-      <c r="G52" s="426"/>
-      <c r="H52" s="426"/>
-      <c r="I52" s="427"/>
-      <c r="J52" s="427"/>
+      <c r="A52" s="421"/>
+      <c r="B52" s="421"/>
+      <c r="C52" s="421"/>
+      <c r="D52" s="421"/>
+      <c r="E52" s="421"/>
+      <c r="F52" s="421"/>
+      <c r="G52" s="421"/>
+      <c r="H52" s="421"/>
+      <c r="I52" s="422"/>
+      <c r="J52" s="422"/>
     </row>
     <row r="53" spans="1:10" ht="9" customHeight="1"/>
     <row r="54" spans="1:10" ht="12" customHeight="1"/>
@@ -16685,43 +16431,51 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="pO7kRHJ2iPqPcZnI3aAaPN8FWn7ShmqQspkUSBiEWlhMz2IYlb2TtMzEa6lNKkrpoouNdSgx63KCE43+up6wVQ==" saltValue="5fqhLEo0sF6DU83eWXcREA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="120">
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C36:F37"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A39:F40"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="C27:F29"/>
+    <mergeCell ref="C30:F32"/>
+    <mergeCell ref="G26:H27"/>
+    <mergeCell ref="I26:J27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="G32:J32"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:F2"/>
@@ -16746,6 +16500,25 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="I48:J48"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="I25:J25"/>
@@ -16760,51 +16533,24 @@
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="C27:F29"/>
-    <mergeCell ref="C30:F32"/>
-    <mergeCell ref="G26:H27"/>
-    <mergeCell ref="I26:J27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C36:F37"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A39:F40"/>
-    <mergeCell ref="G40:J40"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="I51:J51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -17363,17 +17109,17 @@
       <c r="A1" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="360" t="s">
+      <c r="B1" s="338" t="s">
         <v>250</v>
       </c>
-      <c r="C1" s="360"/>
-      <c r="D1" s="360"/>
-      <c r="E1" s="360"/>
-      <c r="F1" s="360"/>
-      <c r="G1" s="360"/>
-      <c r="H1" s="360"/>
-      <c r="I1" s="360"/>
-      <c r="J1" s="360"/>
+      <c r="C1" s="338"/>
+      <c r="D1" s="338"/>
+      <c r="E1" s="338"/>
+      <c r="F1" s="338"/>
+      <c r="G1" s="338"/>
+      <c r="H1" s="338"/>
+      <c r="I1" s="338"/>
+      <c r="J1" s="338"/>
     </row>
     <row r="2" spans="1:10" ht="21" customHeight="1">
       <c r="A2" s="95">
@@ -17383,13 +17129,13 @@
         <v>251</v>
       </c>
       <c r="C2" s="97"/>
-      <c r="D2" s="361"/>
-      <c r="E2" s="362"/>
-      <c r="F2" s="362"/>
-      <c r="G2" s="362"/>
-      <c r="H2" s="362"/>
-      <c r="I2" s="362"/>
-      <c r="J2" s="363"/>
+      <c r="D2" s="339"/>
+      <c r="E2" s="340"/>
+      <c r="F2" s="340"/>
+      <c r="G2" s="340"/>
+      <c r="H2" s="340"/>
+      <c r="I2" s="340"/>
+      <c r="J2" s="341"/>
     </row>
     <row r="3" spans="1:10" ht="21" customHeight="1">
       <c r="A3" s="98"/>
@@ -17397,15 +17143,15 @@
         <v>12</v>
       </c>
       <c r="C3" s="86"/>
-      <c r="D3" s="354"/>
-      <c r="E3" s="355"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="365" t="s">
+      <c r="D3" s="342"/>
+      <c r="E3" s="343"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="345" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="366"/>
-      <c r="I3" s="367"/>
-      <c r="J3" s="350"/>
+      <c r="H3" s="346"/>
+      <c r="I3" s="347"/>
+      <c r="J3" s="348"/>
     </row>
     <row r="4" spans="1:10" ht="21" customHeight="1">
       <c r="A4" s="98"/>
@@ -17413,13 +17159,13 @@
         <v>16</v>
       </c>
       <c r="C4" s="101"/>
-      <c r="D4" s="354"/>
-      <c r="E4" s="355"/>
-      <c r="F4" s="355"/>
-      <c r="G4" s="355"/>
-      <c r="H4" s="355"/>
-      <c r="I4" s="355"/>
-      <c r="J4" s="356"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="343"/>
+      <c r="F4" s="343"/>
+      <c r="G4" s="343"/>
+      <c r="H4" s="343"/>
+      <c r="I4" s="343"/>
+      <c r="J4" s="349"/>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1">
       <c r="A5" s="102"/>
@@ -17427,13 +17173,13 @@
         <v>252</v>
       </c>
       <c r="C5" s="69"/>
-      <c r="D5" s="343"/>
-      <c r="E5" s="344"/>
-      <c r="F5" s="344"/>
-      <c r="G5" s="344"/>
-      <c r="H5" s="344"/>
-      <c r="I5" s="344"/>
-      <c r="J5" s="345"/>
+      <c r="D5" s="350"/>
+      <c r="E5" s="351"/>
+      <c r="F5" s="351"/>
+      <c r="G5" s="351"/>
+      <c r="H5" s="351"/>
+      <c r="I5" s="351"/>
+      <c r="J5" s="352"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="102"/>
@@ -17441,13 +17187,13 @@
         <v>253</v>
       </c>
       <c r="C6" s="69"/>
-      <c r="D6" s="343"/>
-      <c r="E6" s="344"/>
-      <c r="F6" s="344"/>
-      <c r="G6" s="344"/>
-      <c r="H6" s="344"/>
-      <c r="I6" s="344"/>
-      <c r="J6" s="345"/>
+      <c r="D6" s="350"/>
+      <c r="E6" s="351"/>
+      <c r="F6" s="351"/>
+      <c r="G6" s="351"/>
+      <c r="H6" s="351"/>
+      <c r="I6" s="351"/>
+      <c r="J6" s="352"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="102"/>
@@ -17455,13 +17201,13 @@
         <v>254</v>
       </c>
       <c r="C7" s="69"/>
-      <c r="D7" s="357"/>
-      <c r="E7" s="358"/>
-      <c r="F7" s="358"/>
-      <c r="G7" s="358"/>
-      <c r="H7" s="358"/>
-      <c r="I7" s="358"/>
-      <c r="J7" s="359"/>
+      <c r="D7" s="353"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
+      <c r="G7" s="354"/>
+      <c r="H7" s="354"/>
+      <c r="I7" s="354"/>
+      <c r="J7" s="355"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="102"/>
@@ -17469,13 +17215,13 @@
         <v>255</v>
       </c>
       <c r="C8" s="105"/>
-      <c r="D8" s="357"/>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="G8" s="358"/>
-      <c r="H8" s="358"/>
-      <c r="I8" s="358"/>
-      <c r="J8" s="359"/>
+      <c r="D8" s="353"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
+      <c r="G8" s="354"/>
+      <c r="H8" s="354"/>
+      <c r="I8" s="354"/>
+      <c r="J8" s="355"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="106">
@@ -17485,13 +17231,13 @@
         <v>256</v>
       </c>
       <c r="C9" s="107"/>
-      <c r="D9" s="343"/>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
-      <c r="G9" s="344"/>
-      <c r="H9" s="344"/>
-      <c r="I9" s="344"/>
-      <c r="J9" s="345"/>
+      <c r="D9" s="350"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
+      <c r="G9" s="351"/>
+      <c r="H9" s="351"/>
+      <c r="I9" s="351"/>
+      <c r="J9" s="352"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="98"/>
@@ -17499,15 +17245,15 @@
         <v>12</v>
       </c>
       <c r="C10" s="59"/>
-      <c r="D10" s="343"/>
-      <c r="E10" s="344"/>
-      <c r="F10" s="346"/>
-      <c r="G10" s="347" t="s">
+      <c r="D10" s="350"/>
+      <c r="E10" s="351"/>
+      <c r="F10" s="356"/>
+      <c r="G10" s="357" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="348"/>
-      <c r="I10" s="349"/>
-      <c r="J10" s="350"/>
+      <c r="H10" s="358"/>
+      <c r="I10" s="359"/>
+      <c r="J10" s="348"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="98"/>
@@ -17515,29 +17261,29 @@
         <v>16</v>
       </c>
       <c r="C11" s="82"/>
-      <c r="D11" s="351"/>
-      <c r="E11" s="344"/>
-      <c r="F11" s="344"/>
-      <c r="G11" s="344"/>
-      <c r="H11" s="344"/>
-      <c r="I11" s="344"/>
-      <c r="J11" s="345"/>
+      <c r="D11" s="360"/>
+      <c r="E11" s="351"/>
+      <c r="F11" s="351"/>
+      <c r="G11" s="351"/>
+      <c r="H11" s="351"/>
+      <c r="I11" s="351"/>
+      <c r="J11" s="352"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="110">
         <v>25</v>
       </c>
-      <c r="B12" s="352" t="s">
+      <c r="B12" s="361" t="s">
         <v>257</v>
       </c>
-      <c r="C12" s="352"/>
-      <c r="D12" s="352"/>
-      <c r="E12" s="352"/>
-      <c r="F12" s="352"/>
-      <c r="G12" s="352"/>
-      <c r="H12" s="352"/>
-      <c r="I12" s="352"/>
-      <c r="J12" s="353"/>
+      <c r="C12" s="361"/>
+      <c r="D12" s="361"/>
+      <c r="E12" s="361"/>
+      <c r="F12" s="361"/>
+      <c r="G12" s="361"/>
+      <c r="H12" s="361"/>
+      <c r="I12" s="361"/>
+      <c r="J12" s="362"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="98"/>
@@ -17545,13 +17291,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="59"/>
-      <c r="D13" s="343"/>
-      <c r="E13" s="344"/>
-      <c r="F13" s="344"/>
-      <c r="G13" s="344"/>
-      <c r="H13" s="344"/>
-      <c r="I13" s="344"/>
-      <c r="J13" s="345"/>
+      <c r="D13" s="350"/>
+      <c r="E13" s="351"/>
+      <c r="F13" s="351"/>
+      <c r="G13" s="351"/>
+      <c r="H13" s="351"/>
+      <c r="I13" s="351"/>
+      <c r="J13" s="352"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="98"/>
@@ -17559,13 +17305,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="59"/>
-      <c r="D14" s="343"/>
-      <c r="E14" s="344"/>
-      <c r="F14" s="344"/>
-      <c r="G14" s="344"/>
-      <c r="H14" s="344"/>
-      <c r="I14" s="344"/>
-      <c r="J14" s="345"/>
+      <c r="D14" s="350"/>
+      <c r="E14" s="351"/>
+      <c r="F14" s="351"/>
+      <c r="G14" s="351"/>
+      <c r="H14" s="351"/>
+      <c r="I14" s="351"/>
+      <c r="J14" s="352"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1" thickBot="1">
       <c r="A15" s="111"/>
@@ -17573,27 +17319,17 @@
         <v>16</v>
       </c>
       <c r="C15" s="63"/>
-      <c r="D15" s="343"/>
-      <c r="E15" s="344"/>
-      <c r="F15" s="344"/>
-      <c r="G15" s="344"/>
-      <c r="H15" s="344"/>
-      <c r="I15" s="344"/>
-      <c r="J15" s="345"/>
+      <c r="D15" s="350"/>
+      <c r="E15" s="351"/>
+      <c r="F15" s="351"/>
+      <c r="G15" s="351"/>
+      <c r="H15" s="351"/>
+      <c r="I15" s="351"/>
+      <c r="J15" s="352"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="AlSiBTM1dRhXo9ORvo/dRyVY3Jlgq0tY8I1Lt7Z1RfI7T5btNF7ArQMjcgXOFy3gstkxkeBRdVuavcsER8i7fQ==" saltValue="im7eNRRObcswndBJ71jiCQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D14:J14"/>
     <mergeCell ref="D15:J15"/>
@@ -17603,6 +17339,16 @@
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="D11:J11"/>
     <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17753,14 +17499,14 @@
       <c r="F1" s="135"/>
       <c r="G1" s="136"/>
       <c r="H1" s="134"/>
-      <c r="I1" s="368" t="s">
+      <c r="I1" s="363" t="s">
         <v>261</v>
       </c>
-      <c r="J1" s="368"/>
-      <c r="K1" s="368"/>
-      <c r="L1" s="368"/>
-      <c r="M1" s="368"/>
-      <c r="N1" s="368"/>
+      <c r="J1" s="363"/>
+      <c r="K1" s="363"/>
+      <c r="L1" s="363"/>
+      <c r="M1" s="363"/>
+      <c r="N1" s="363"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1">
       <c r="A2" s="122" t="s">
@@ -17768,17 +17514,17 @@
       </c>
       <c r="B2" s="123"/>
       <c r="C2" s="123"/>
-      <c r="D2" s="375" t="s">
+      <c r="D2" s="370" t="s">
         <v>262</v>
       </c>
-      <c r="E2" s="376"/>
-      <c r="F2" s="369" t="s">
+      <c r="E2" s="371"/>
+      <c r="F2" s="364" t="s">
         <v>263</v>
       </c>
-      <c r="G2" s="369" t="s">
+      <c r="G2" s="364" t="s">
         <v>328</v>
       </c>
-      <c r="H2" s="372" t="s">
+      <c r="H2" s="367" t="s">
         <v>264</v>
       </c>
     </row>
@@ -17792,11 +17538,11 @@
       <c r="C3" s="125" t="s">
         <v>266</v>
       </c>
-      <c r="D3" s="377"/>
-      <c r="E3" s="378"/>
-      <c r="F3" s="370"/>
-      <c r="G3" s="370"/>
-      <c r="H3" s="373"/>
+      <c r="D3" s="372"/>
+      <c r="E3" s="373"/>
+      <c r="F3" s="365"/>
+      <c r="G3" s="365"/>
+      <c r="H3" s="368"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1">
       <c r="A4" s="126"/>
@@ -17808,9 +17554,9 @@
       <c r="E4" s="130" t="s">
         <v>268</v>
       </c>
-      <c r="F4" s="371"/>
-      <c r="G4" s="371"/>
-      <c r="H4" s="374"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="369"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="137"/>
@@ -17987,13 +17733,13 @@
       <c r="D1" s="148"/>
       <c r="E1" s="148"/>
       <c r="F1" s="148"/>
-      <c r="G1" s="381"/>
-      <c r="H1" s="381"/>
-      <c r="I1" s="381"/>
-      <c r="J1" s="381"/>
-      <c r="K1" s="381"/>
-      <c r="L1" s="381"/>
-      <c r="M1" s="381"/>
+      <c r="G1" s="376"/>
+      <c r="H1" s="376"/>
+      <c r="I1" s="376"/>
+      <c r="J1" s="376"/>
+      <c r="K1" s="376"/>
+      <c r="L1" s="376"/>
+      <c r="M1" s="376"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1">
       <c r="A2" s="149"/>
@@ -18017,10 +17763,10 @@
       <c r="D3" s="156" t="s">
         <v>271</v>
       </c>
-      <c r="E3" s="379" t="s">
+      <c r="E3" s="374" t="s">
         <v>272</v>
       </c>
-      <c r="F3" s="380"/>
+      <c r="F3" s="375"/>
       <c r="N3" s="118"/>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1">
@@ -19012,63 +18758,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A1" s="382" t="s">
+      <c r="A1" s="377" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="383"/>
-      <c r="C1" s="383"/>
-      <c r="D1" s="383"/>
-      <c r="E1" s="383"/>
-      <c r="F1" s="383"/>
-      <c r="G1" s="383"/>
-      <c r="H1" s="384"/>
+      <c r="B1" s="378"/>
+      <c r="C1" s="378"/>
+      <c r="D1" s="378"/>
+      <c r="E1" s="378"/>
+      <c r="F1" s="378"/>
+      <c r="G1" s="378"/>
+      <c r="H1" s="379"/>
     </row>
     <row r="2" spans="1:14" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A2" s="385" t="s">
+      <c r="A2" s="380" t="s">
         <v>275</v>
       </c>
-      <c r="B2" s="386"/>
-      <c r="C2" s="386"/>
-      <c r="D2" s="386"/>
-      <c r="E2" s="386"/>
-      <c r="F2" s="386"/>
-      <c r="G2" s="386"/>
-      <c r="H2" s="387"/>
+      <c r="B2" s="381"/>
+      <c r="C2" s="381"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
+      <c r="G2" s="381"/>
+      <c r="H2" s="382"/>
     </row>
     <row r="3" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A3" s="397" t="s">
+      <c r="A3" s="392" t="s">
         <v>331</v>
       </c>
-      <c r="B3" s="398"/>
-      <c r="C3" s="388" t="s">
+      <c r="B3" s="393"/>
+      <c r="C3" s="383" t="s">
         <v>276</v>
       </c>
-      <c r="D3" s="391" t="s">
+      <c r="D3" s="386" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="391" t="s">
+      <c r="E3" s="386" t="s">
         <v>278</v>
       </c>
-      <c r="F3" s="391" t="s">
+      <c r="F3" s="386" t="s">
         <v>279</v>
       </c>
-      <c r="G3" s="369" t="s">
+      <c r="G3" s="364" t="s">
         <v>280</v>
       </c>
-      <c r="H3" s="394" t="s">
+      <c r="H3" s="389" t="s">
         <v>327</v>
       </c>
       <c r="N3" s="167"/>
     </row>
     <row r="4" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A4" s="399"/>
-      <c r="B4" s="400"/>
-      <c r="C4" s="389"/>
-      <c r="D4" s="392"/>
-      <c r="E4" s="392"/>
-      <c r="F4" s="392"/>
-      <c r="G4" s="370"/>
-      <c r="H4" s="395"/>
+      <c r="A4" s="394"/>
+      <c r="B4" s="395"/>
+      <c r="C4" s="384"/>
+      <c r="D4" s="387"/>
+      <c r="E4" s="387"/>
+      <c r="F4" s="387"/>
+      <c r="G4" s="365"/>
+      <c r="H4" s="390"/>
       <c r="N4" s="167"/>
     </row>
     <row r="5" spans="1:14" ht="30.75" customHeight="1">
@@ -19078,12 +18824,12 @@
       <c r="B5" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="C5" s="390"/>
-      <c r="D5" s="393"/>
-      <c r="E5" s="393"/>
-      <c r="F5" s="393"/>
-      <c r="G5" s="371"/>
-      <c r="H5" s="396"/>
+      <c r="C5" s="385"/>
+      <c r="D5" s="388"/>
+      <c r="E5" s="388"/>
+      <c r="F5" s="388"/>
+      <c r="G5" s="366"/>
+      <c r="H5" s="391"/>
       <c r="N5" s="167"/>
     </row>
     <row r="6" spans="1:14">
@@ -19395,17 +19141,17 @@
       <c r="Q1" s="157"/>
     </row>
     <row r="2" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A2" s="401" t="s">
+      <c r="A2" s="396" t="s">
         <v>282</v>
       </c>
-      <c r="B2" s="388" t="s">
+      <c r="B2" s="383" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="407"/>
-      <c r="D2" s="391" t="s">
+      <c r="C2" s="402"/>
+      <c r="D2" s="386" t="s">
         <v>283</v>
       </c>
-      <c r="E2" s="404" t="s">
+      <c r="E2" s="399" t="s">
         <v>284</v>
       </c>
       <c r="F2" s="173"/>
@@ -19422,11 +19168,11 @@
       <c r="Q2" s="157"/>
     </row>
     <row r="3" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A3" s="402"/>
-      <c r="B3" s="389"/>
-      <c r="C3" s="408"/>
-      <c r="D3" s="392"/>
-      <c r="E3" s="405"/>
+      <c r="A3" s="397"/>
+      <c r="B3" s="384"/>
+      <c r="C3" s="403"/>
+      <c r="D3" s="387"/>
+      <c r="E3" s="400"/>
       <c r="F3" s="173"/>
       <c r="G3" s="157"/>
       <c r="H3" s="157"/>
@@ -19441,15 +19187,15 @@
       <c r="Q3" s="157"/>
     </row>
     <row r="4" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A4" s="403"/>
+      <c r="A4" s="398"/>
       <c r="B4" s="161" t="s">
         <v>267</v>
       </c>
       <c r="C4" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="393"/>
-      <c r="E4" s="406"/>
+      <c r="D4" s="388"/>
+      <c r="E4" s="401"/>
       <c r="F4" s="173"/>
       <c r="G4" s="157"/>
       <c r="H4" s="157"/>
@@ -19938,62 +19684,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A1" s="409" t="s">
+      <c r="A1" s="404" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="410"/>
-      <c r="C1" s="410"/>
-      <c r="D1" s="410"/>
-      <c r="E1" s="410"/>
-      <c r="F1" s="411"/>
+      <c r="B1" s="405"/>
+      <c r="C1" s="405"/>
+      <c r="D1" s="405"/>
+      <c r="E1" s="405"/>
+      <c r="F1" s="406"/>
     </row>
     <row r="2" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A2" s="412" t="s">
+      <c r="A2" s="407" t="s">
         <v>286</v>
       </c>
-      <c r="B2" s="413"/>
-      <c r="C2" s="413"/>
-      <c r="D2" s="413"/>
-      <c r="E2" s="413"/>
-      <c r="F2" s="414"/>
+      <c r="B2" s="408"/>
+      <c r="C2" s="408"/>
+      <c r="D2" s="408"/>
+      <c r="E2" s="408"/>
+      <c r="F2" s="409"/>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A3" s="415" t="s">
+      <c r="A3" s="410" t="s">
         <v>287</v>
       </c>
-      <c r="B3" s="420" t="s">
+      <c r="B3" s="415" t="s">
         <v>333</v>
       </c>
-      <c r="C3" s="421"/>
-      <c r="D3" s="417" t="s">
+      <c r="C3" s="416"/>
+      <c r="D3" s="412" t="s">
         <v>283</v>
       </c>
-      <c r="E3" s="392" t="s">
+      <c r="E3" s="387" t="s">
         <v>288</v>
       </c>
-      <c r="F3" s="419" t="s">
+      <c r="F3" s="414" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A4" s="416"/>
-      <c r="B4" s="389"/>
-      <c r="C4" s="422"/>
-      <c r="D4" s="417"/>
-      <c r="E4" s="392"/>
-      <c r="F4" s="405"/>
+      <c r="A4" s="411"/>
+      <c r="B4" s="384"/>
+      <c r="C4" s="417"/>
+      <c r="D4" s="412"/>
+      <c r="E4" s="387"/>
+      <c r="F4" s="400"/>
     </row>
     <row r="5" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A5" s="399"/>
+      <c r="A5" s="394"/>
       <c r="B5" s="161" t="s">
         <v>267</v>
       </c>
       <c r="C5" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="418"/>
-      <c r="E5" s="393"/>
-      <c r="F5" s="406"/>
+      <c r="D5" s="413"/>
+      <c r="E5" s="388"/>
+      <c r="F5" s="401"/>
     </row>
     <row r="6" spans="1:8" ht="18.75" customHeight="1">
       <c r="A6" s="176"/>
@@ -20195,11 +19941,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A1" s="423" t="s">
+      <c r="A1" s="418" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="424"/>
-      <c r="C1" s="425"/>
+      <c r="B1" s="419"/>
+      <c r="C1" s="420"/>
     </row>
     <row r="2" spans="1:13" ht="38.25" customHeight="1">
       <c r="A2" s="178" t="s">

--- a/public/pds.xlsx
+++ b/public/pds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cenro\PMS-intern\rsp-hr-tagum-cityhall\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995911BC-F7F2-4A73-8C0B-934CB3125789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748BEF02-84E2-43CB-B29F-FAED4735F307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1615,7 +1615,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="347">
   <si>
     <t xml:space="preserve">        </t>
   </si>
@@ -2650,10 +2650,6 @@
     <t xml:space="preserve">     If YES, give details</t>
   </si>
   <si>
-    <t xml:space="preserve">
-</t>
-  </si>
-  <si>
     <t>GOV'T SERVICE                                                                                                                                       (Yes/ No)</t>
   </si>
   <si>
@@ -2729,7 +2725,7 @@
     <numFmt numFmtId="166" formatCode=";;;"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="55">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2987,12 +2983,6 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -3773,7 +3763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="519">
+  <cellXfs count="513">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -3844,63 +3834,405 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3908,363 +4240,21 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="52" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4310,7 +4300,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -4327,10 +4317,10 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4346,7 +4336,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -4449,39 +4439,117 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="34" fillId="4" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4491,6 +4559,161 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4554,25 +4777,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -4593,298 +4804,126 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="28" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4901,14 +4940,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -4923,62 +4954,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -4991,25 +4966,25 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5019,22 +4994,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5100,22 +5075,22 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5142,13 +5117,13 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5159,25 +5134,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5185,48 +5155,147 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -5281,18 +5350,6 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5311,18 +5368,19 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5330,135 +5388,46 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5479,7 +5448,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="50" dropStyle="combo" dx="22" fmlaLink="$J$16" fmlaRange="Q11:Q215" sel="8" val="7"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="50" dropStyle="combo" dx="22" fmlaLink="$J$16" fmlaRange="Q11:Q215" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7296,8 +7265,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9286876" y="535781"/>
-          <a:ext cx="2046386" cy="1808262"/>
+          <a:off x="9534847" y="540475"/>
+          <a:ext cx="2042608" cy="1830243"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10267,20 +10236,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
-      <c r="A1" s="267"/>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="268"/>
-      <c r="E1" s="268"/>
-      <c r="F1" s="268"/>
-      <c r="G1" s="268"/>
-      <c r="H1" s="268"/>
-      <c r="I1" s="268"/>
-      <c r="J1" s="268"/>
-      <c r="K1" s="268"/>
-      <c r="L1" s="268"/>
-      <c r="M1" s="268"/>
-      <c r="N1" s="269"/>
+      <c r="A1" s="247"/>
+      <c r="B1" s="248"/>
+      <c r="C1" s="248"/>
+      <c r="D1" s="248"/>
+      <c r="E1" s="248"/>
+      <c r="F1" s="248"/>
+      <c r="G1" s="248"/>
+      <c r="H1" s="248"/>
+      <c r="I1" s="248"/>
+      <c r="J1" s="248"/>
+      <c r="K1" s="248"/>
+      <c r="L1" s="248"/>
+      <c r="M1" s="248"/>
+      <c r="N1" s="249"/>
     </row>
     <row r="2" spans="1:22" ht="11.25" customHeight="1">
       <c r="A2" s="40"/>
@@ -10310,73 +10279,73 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="41.25" customHeight="1">
-      <c r="A3" s="270" t="s">
+      <c r="A3" s="250" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="271"/>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
-      <c r="F3" s="271"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="271"/>
-      <c r="I3" s="271"/>
-      <c r="J3" s="271"/>
-      <c r="K3" s="271"/>
-      <c r="L3" s="271"/>
-      <c r="M3" s="271"/>
-      <c r="N3" s="272"/>
-      <c r="R3" s="225"/>
-      <c r="S3" s="226"/>
-      <c r="T3" s="226"/>
-      <c r="U3" s="226"/>
-      <c r="V3" s="227"/>
+      <c r="B3" s="251"/>
+      <c r="C3" s="251"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="251"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
+      <c r="M3" s="251"/>
+      <c r="N3" s="252"/>
+      <c r="R3" s="292"/>
+      <c r="S3" s="293"/>
+      <c r="T3" s="293"/>
+      <c r="U3" s="293"/>
+      <c r="V3" s="294"/>
     </row>
     <row r="4" spans="1:22" ht="21.75" customHeight="1">
-      <c r="A4" s="273" t="s">
-        <v>342</v>
-      </c>
-      <c r="B4" s="274"/>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="274"/>
-      <c r="I4" s="274"/>
-      <c r="J4" s="274"/>
-      <c r="K4" s="274"/>
-      <c r="L4" s="274"/>
-      <c r="M4" s="274"/>
-      <c r="N4" s="275"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
+      <c r="A4" s="253" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="254"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="254"/>
+      <c r="E4" s="254"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="254"/>
+      <c r="J4" s="254"/>
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="M4" s="254"/>
+      <c r="N4" s="255"/>
+      <c r="R4" s="295"/>
+      <c r="S4" s="296"/>
+      <c r="T4" s="296"/>
+      <c r="U4" s="296"/>
+      <c r="V4" s="297"/>
     </row>
     <row r="5" spans="1:22" ht="11.25" customHeight="1">
-      <c r="A5" s="276" t="s">
+      <c r="A5" s="256" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="277"/>
-      <c r="C5" s="277"/>
-      <c r="D5" s="277"/>
-      <c r="E5" s="277"/>
-      <c r="F5" s="277"/>
-      <c r="G5" s="277"/>
-      <c r="H5" s="277"/>
-      <c r="I5" s="277"/>
-      <c r="J5" s="277"/>
-      <c r="K5" s="277"/>
-      <c r="L5" s="277"/>
-      <c r="M5" s="277"/>
-      <c r="N5" s="278"/>
-      <c r="R5" s="228"/>
-      <c r="S5" s="229"/>
-      <c r="T5" s="229"/>
-      <c r="U5" s="229"/>
-      <c r="V5" s="230"/>
+      <c r="B5" s="257"/>
+      <c r="C5" s="257"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="257"/>
+      <c r="H5" s="257"/>
+      <c r="I5" s="257"/>
+      <c r="J5" s="257"/>
+      <c r="K5" s="257"/>
+      <c r="L5" s="257"/>
+      <c r="M5" s="257"/>
+      <c r="N5" s="258"/>
+      <c r="R5" s="295"/>
+      <c r="S5" s="296"/>
+      <c r="T5" s="296"/>
+      <c r="U5" s="296"/>
+      <c r="V5" s="297"/>
     </row>
     <row r="6" spans="1:22" ht="36.75" hidden="1" customHeight="1">
       <c r="A6" s="43"/>
@@ -10393,11 +10362,11 @@
       <c r="L6" s="45"/>
       <c r="M6" s="45"/>
       <c r="N6" s="46"/>
-      <c r="R6" s="228"/>
-      <c r="S6" s="229"/>
-      <c r="T6" s="229"/>
-      <c r="U6" s="229"/>
-      <c r="V6" s="230"/>
+      <c r="R6" s="295"/>
+      <c r="S6" s="296"/>
+      <c r="T6" s="296"/>
+      <c r="U6" s="296"/>
+      <c r="V6" s="297"/>
     </row>
     <row r="7" spans="1:22" s="53" customFormat="1" ht="12.75" customHeight="1" thickBot="1">
       <c r="A7" s="47" t="s">
@@ -10415,197 +10384,197 @@
       <c r="K7" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="279" t="s">
+      <c r="L7" s="259" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="280"/>
-      <c r="N7" s="281"/>
-      <c r="R7" s="228"/>
-      <c r="S7" s="229"/>
-      <c r="T7" s="229"/>
-      <c r="U7" s="229"/>
-      <c r="V7" s="230"/>
+      <c r="M7" s="260"/>
+      <c r="N7" s="261"/>
+      <c r="R7" s="295"/>
+      <c r="S7" s="296"/>
+      <c r="T7" s="296"/>
+      <c r="U7" s="296"/>
+      <c r="V7" s="297"/>
     </row>
     <row r="8" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
       <c r="A8" s="54"/>
       <c r="N8" s="55"/>
-      <c r="R8" s="228"/>
-      <c r="S8" s="229"/>
-      <c r="T8" s="229"/>
-      <c r="U8" s="229"/>
-      <c r="V8" s="230"/>
+      <c r="R8" s="295"/>
+      <c r="S8" s="296"/>
+      <c r="T8" s="296"/>
+      <c r="U8" s="296"/>
+      <c r="V8" s="297"/>
     </row>
     <row r="9" spans="1:22" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A9" s="239" t="s">
+      <c r="A9" s="306" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="240"/>
-      <c r="C9" s="240"/>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
-      <c r="M9" s="240"/>
-      <c r="N9" s="241"/>
-      <c r="R9" s="228"/>
-      <c r="S9" s="229"/>
-      <c r="T9" s="229"/>
-      <c r="U9" s="229"/>
-      <c r="V9" s="230"/>
+      <c r="B9" s="307"/>
+      <c r="C9" s="307"/>
+      <c r="D9" s="307"/>
+      <c r="E9" s="307"/>
+      <c r="F9" s="307"/>
+      <c r="G9" s="307"/>
+      <c r="H9" s="307"/>
+      <c r="I9" s="307"/>
+      <c r="J9" s="307"/>
+      <c r="K9" s="307"/>
+      <c r="L9" s="307"/>
+      <c r="M9" s="307"/>
+      <c r="N9" s="308"/>
+      <c r="R9" s="295"/>
+      <c r="S9" s="296"/>
+      <c r="T9" s="296"/>
+      <c r="U9" s="296"/>
+      <c r="V9" s="297"/>
     </row>
     <row r="10" spans="1:22" ht="22.5" customHeight="1">
       <c r="A10" s="56">
         <v>2</v>
       </c>
-      <c r="B10" s="242" t="s">
+      <c r="B10" s="278" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="243"/>
-      <c r="D10" s="244"/>
-      <c r="E10" s="244"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="244"/>
-      <c r="H10" s="244"/>
-      <c r="I10" s="244"/>
-      <c r="J10" s="244"/>
-      <c r="K10" s="244"/>
-      <c r="L10" s="244"/>
-      <c r="M10" s="244"/>
-      <c r="N10" s="245"/>
+      <c r="C10" s="266"/>
+      <c r="D10" s="309"/>
+      <c r="E10" s="309"/>
+      <c r="F10" s="309"/>
+      <c r="G10" s="309"/>
+      <c r="H10" s="309"/>
+      <c r="I10" s="309"/>
+      <c r="J10" s="309"/>
+      <c r="K10" s="309"/>
+      <c r="L10" s="309"/>
+      <c r="M10" s="309"/>
+      <c r="N10" s="310"/>
       <c r="P10" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="R10" s="228"/>
-      <c r="S10" s="229"/>
-      <c r="T10" s="229"/>
-      <c r="U10" s="229"/>
-      <c r="V10" s="230"/>
+      <c r="R10" s="295"/>
+      <c r="S10" s="296"/>
+      <c r="T10" s="296"/>
+      <c r="U10" s="296"/>
+      <c r="V10" s="297"/>
     </row>
     <row r="11" spans="1:22" ht="22.5" customHeight="1">
       <c r="A11" s="58"/>
-      <c r="B11" s="246" t="s">
+      <c r="B11" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="247"/>
-      <c r="D11" s="248"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="250"/>
-      <c r="I11" s="251" t="s">
+      <c r="C11" s="280"/>
+      <c r="D11" s="311"/>
+      <c r="E11" s="312"/>
+      <c r="F11" s="312"/>
+      <c r="G11" s="312"/>
+      <c r="H11" s="313"/>
+      <c r="I11" s="314" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="252"/>
-      <c r="K11" s="252"/>
-      <c r="L11" s="253"/>
-      <c r="M11" s="254"/>
-      <c r="N11" s="255"/>
+      <c r="J11" s="315"/>
+      <c r="K11" s="315"/>
+      <c r="L11" s="316"/>
+      <c r="M11" s="317"/>
+      <c r="N11" s="318"/>
       <c r="P11" s="60" t="s">
         <v>14</v>
       </c>
       <c r="Q11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="R11" s="228"/>
-      <c r="S11" s="229"/>
-      <c r="T11" s="229"/>
-      <c r="U11" s="229"/>
-      <c r="V11" s="230"/>
+      <c r="R11" s="295"/>
+      <c r="S11" s="296"/>
+      <c r="T11" s="296"/>
+      <c r="U11" s="296"/>
+      <c r="V11" s="297"/>
     </row>
     <row r="12" spans="1:22" ht="21.75" customHeight="1" thickBot="1">
       <c r="A12" s="62"/>
-      <c r="B12" s="234" t="s">
+      <c r="B12" s="301" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="235"/>
-      <c r="D12" s="236"/>
-      <c r="E12" s="237"/>
-      <c r="F12" s="237"/>
-      <c r="G12" s="237" t="b">
+      <c r="C12" s="302"/>
+      <c r="D12" s="303"/>
+      <c r="E12" s="304"/>
+      <c r="F12" s="304"/>
+      <c r="G12" s="304" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="237"/>
-      <c r="I12" s="237" t="b">
+      <c r="H12" s="304"/>
+      <c r="I12" s="304" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="237"/>
-      <c r="K12" s="237"/>
-      <c r="L12" s="237"/>
-      <c r="M12" s="237"/>
-      <c r="N12" s="238"/>
+      <c r="J12" s="304"/>
+      <c r="K12" s="304"/>
+      <c r="L12" s="304"/>
+      <c r="M12" s="304"/>
+      <c r="N12" s="305"/>
       <c r="P12" s="60" t="s">
         <v>17</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="R12" s="228"/>
-      <c r="S12" s="229"/>
-      <c r="T12" s="229"/>
-      <c r="U12" s="229"/>
-      <c r="V12" s="230"/>
+      <c r="R12" s="295"/>
+      <c r="S12" s="296"/>
+      <c r="T12" s="296"/>
+      <c r="U12" s="296"/>
+      <c r="V12" s="297"/>
     </row>
     <row r="13" spans="1:22" ht="24" customHeight="1">
       <c r="A13" s="64">
         <v>3</v>
       </c>
-      <c r="B13" s="259" t="s">
-        <v>334</v>
-      </c>
-      <c r="C13" s="243"/>
-      <c r="D13" s="282"/>
-      <c r="E13" s="283"/>
-      <c r="F13" s="283"/>
-      <c r="G13" s="242" t="s">
+      <c r="B13" s="265" t="s">
+        <v>333</v>
+      </c>
+      <c r="C13" s="266"/>
+      <c r="D13" s="274"/>
+      <c r="E13" s="275"/>
+      <c r="F13" s="275"/>
+      <c r="G13" s="278" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="242"/>
-      <c r="I13" s="243"/>
-      <c r="J13" s="286" t="b">
+      <c r="H13" s="278"/>
+      <c r="I13" s="266"/>
+      <c r="J13" s="281" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="287"/>
-      <c r="L13" s="287" t="b">
+      <c r="K13" s="282"/>
+      <c r="L13" s="282" t="b">
         <v>0</v>
       </c>
-      <c r="M13" s="287"/>
-      <c r="N13" s="288"/>
+      <c r="M13" s="282"/>
+      <c r="N13" s="283"/>
       <c r="P13" s="60" t="s">
         <v>20</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="231"/>
-      <c r="S13" s="232"/>
-      <c r="T13" s="232"/>
-      <c r="U13" s="232"/>
-      <c r="V13" s="233"/>
+      <c r="R13" s="298"/>
+      <c r="S13" s="299"/>
+      <c r="T13" s="299"/>
+      <c r="U13" s="299"/>
+      <c r="V13" s="300"/>
     </row>
     <row r="14" spans="1:22" ht="21.6" customHeight="1">
       <c r="A14" s="58"/>
       <c r="B14" s="65"/>
       <c r="C14" s="65"/>
-      <c r="D14" s="284"/>
-      <c r="E14" s="285"/>
-      <c r="F14" s="285"/>
-      <c r="G14" s="246"/>
-      <c r="H14" s="246"/>
-      <c r="I14" s="247"/>
-      <c r="J14" s="289" t="b">
+      <c r="D14" s="276"/>
+      <c r="E14" s="277"/>
+      <c r="F14" s="277"/>
+      <c r="G14" s="279"/>
+      <c r="H14" s="279"/>
+      <c r="I14" s="280"/>
+      <c r="J14" s="284" t="b">
         <v>0</v>
       </c>
-      <c r="K14" s="290"/>
-      <c r="L14" s="290" t="b">
+      <c r="K14" s="285"/>
+      <c r="L14" s="285" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="290"/>
-      <c r="N14" s="291"/>
+      <c r="M14" s="285"/>
+      <c r="N14" s="286"/>
       <c r="P14" s="60"/>
       <c r="Q14" s="2"/>
       <c r="S14"/>
@@ -10620,21 +10589,21 @@
         <v>22</v>
       </c>
       <c r="C15" s="67"/>
-      <c r="D15" s="260"/>
-      <c r="E15" s="260"/>
-      <c r="F15" s="261"/>
-      <c r="G15" s="262" t="s">
+      <c r="D15" s="267"/>
+      <c r="E15" s="267"/>
+      <c r="F15" s="268"/>
+      <c r="G15" s="269" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="263"/>
-      <c r="I15" s="263"/>
-      <c r="J15" s="264" t="s">
+      <c r="H15" s="270"/>
+      <c r="I15" s="270"/>
+      <c r="J15" s="271" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="265"/>
-      <c r="L15" s="265"/>
-      <c r="M15" s="265"/>
-      <c r="N15" s="266"/>
+      <c r="K15" s="272"/>
+      <c r="L15" s="272"/>
+      <c r="M15" s="272"/>
+      <c r="N15" s="273"/>
       <c r="P15" s="60" t="s">
         <v>25</v>
       </c>
@@ -10656,22 +10625,22 @@
       <c r="D16" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="296" t="b">
+      <c r="E16" s="287" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="297"/>
-      <c r="G16" s="298" t="s">
+      <c r="F16" s="288"/>
+      <c r="G16" s="289" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="299"/>
-      <c r="I16" s="300"/>
-      <c r="J16" s="256">
-        <v>8</v>
-      </c>
-      <c r="K16" s="257"/>
-      <c r="L16" s="257"/>
-      <c r="M16" s="257"/>
-      <c r="N16" s="258"/>
+      <c r="H16" s="290"/>
+      <c r="I16" s="291"/>
+      <c r="J16" s="262">
+        <v>1</v>
+      </c>
+      <c r="K16" s="263"/>
+      <c r="L16" s="263"/>
+      <c r="M16" s="263"/>
+      <c r="N16" s="264"/>
       <c r="O16" s="70"/>
       <c r="P16" s="60" t="s">
         <v>29</v>
@@ -10681,64 +10650,60 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="27" customHeight="1">
-      <c r="A17" s="324">
+      <c r="A17" s="216">
         <v>6</v>
       </c>
-      <c r="B17" s="334" t="s">
+      <c r="B17" s="330" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="335"/>
+      <c r="C17" s="331"/>
       <c r="D17" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="303" t="b">
+      <c r="E17" s="239" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="304"/>
+      <c r="F17" s="240"/>
       <c r="G17" s="71" t="s">
         <v>32</v>
       </c>
       <c r="H17" s="72"/>
-      <c r="I17" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="J17" s="292"/>
-      <c r="K17" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="L17" s="292"/>
-      <c r="M17" s="293"/>
-      <c r="N17" s="293"/>
+      <c r="I17" s="215"/>
+      <c r="J17" s="215"/>
+      <c r="K17" s="215"/>
+      <c r="L17" s="215"/>
+      <c r="M17" s="232"/>
+      <c r="N17" s="232"/>
       <c r="Q17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="R17" s="73"/>
     </row>
     <row r="18" spans="1:23" ht="27" customHeight="1">
-      <c r="A18" s="325"/>
-      <c r="B18" s="336"/>
-      <c r="C18" s="337"/>
+      <c r="A18" s="217"/>
+      <c r="B18" s="332"/>
+      <c r="C18" s="333"/>
       <c r="D18" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="223" t="b">
+      <c r="E18" s="245" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="224"/>
+      <c r="F18" s="246"/>
       <c r="G18" s="75"/>
       <c r="H18" s="76"/>
-      <c r="I18" s="212" t="s">
+      <c r="I18" s="233" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="212"/>
-      <c r="K18" s="212" t="s">
-        <v>343</v>
-      </c>
-      <c r="L18" s="212"/>
-      <c r="M18" s="212" t="s">
+      <c r="J18" s="233"/>
+      <c r="K18" s="233" t="s">
+        <v>342</v>
+      </c>
+      <c r="L18" s="233"/>
+      <c r="M18" s="233" t="s">
         <v>35</v>
       </c>
-      <c r="N18" s="212"/>
+      <c r="N18" s="233"/>
       <c r="Q18" s="2" t="s">
         <v>36</v>
       </c>
@@ -10747,23 +10712,19 @@
       <c r="A19" s="56"/>
       <c r="B19" s="77"/>
       <c r="C19" s="74"/>
-      <c r="D19" s="308" t="b">
+      <c r="D19" s="244" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="223"/>
-      <c r="F19" s="224"/>
+      <c r="E19" s="245"/>
+      <c r="F19" s="246"/>
       <c r="G19" s="75"/>
       <c r="H19" s="76"/>
-      <c r="I19" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="J19" s="333"/>
-      <c r="K19" s="333"/>
-      <c r="L19" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="M19" s="293"/>
-      <c r="N19" s="293"/>
+      <c r="I19" s="215"/>
+      <c r="J19" s="232"/>
+      <c r="K19" s="232"/>
+      <c r="L19" s="215"/>
+      <c r="M19" s="232"/>
+      <c r="N19" s="232"/>
       <c r="Q19" s="2" t="s">
         <v>37</v>
       </c>
@@ -10772,71 +10733,67 @@
       <c r="A20" s="78"/>
       <c r="B20" s="79"/>
       <c r="C20" s="80"/>
-      <c r="D20" s="305"/>
-      <c r="E20" s="306"/>
-      <c r="F20" s="307"/>
+      <c r="D20" s="241"/>
+      <c r="E20" s="242"/>
+      <c r="F20" s="243"/>
       <c r="G20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="294" t="s">
+      <c r="I20" s="234" t="s">
         <v>38</v>
       </c>
-      <c r="J20" s="301"/>
-      <c r="K20" s="301"/>
-      <c r="L20" s="295" t="s">
+      <c r="J20" s="235"/>
+      <c r="K20" s="235"/>
+      <c r="L20" s="236" t="s">
         <v>39</v>
       </c>
-      <c r="M20" s="302"/>
-      <c r="N20" s="302"/>
+      <c r="M20" s="329"/>
+      <c r="N20" s="329"/>
       <c r="Q20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A21" s="325">
+      <c r="A21" s="217">
         <v>7</v>
       </c>
-      <c r="B21" s="327" t="s">
+      <c r="B21" s="219" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="328"/>
-      <c r="D21" s="332"/>
-      <c r="E21" s="332"/>
-      <c r="F21" s="332"/>
+      <c r="C21" s="220"/>
+      <c r="D21" s="226"/>
+      <c r="E21" s="226"/>
+      <c r="F21" s="226"/>
       <c r="G21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="J21" s="293"/>
-      <c r="K21" s="293"/>
-      <c r="L21" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="M21" s="293"/>
-      <c r="N21" s="293"/>
+      <c r="I21" s="215"/>
+      <c r="J21" s="232"/>
+      <c r="K21" s="232"/>
+      <c r="L21" s="215"/>
+      <c r="M21" s="232"/>
+      <c r="N21" s="232"/>
       <c r="Q21" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="26.25" customHeight="1">
-      <c r="A22" s="326"/>
-      <c r="B22" s="329"/>
-      <c r="C22" s="330"/>
-      <c r="D22" s="331"/>
-      <c r="E22" s="331"/>
-      <c r="F22" s="331"/>
+      <c r="A22" s="218"/>
+      <c r="B22" s="221"/>
+      <c r="C22" s="222"/>
+      <c r="D22" s="225"/>
+      <c r="E22" s="225"/>
+      <c r="F22" s="225"/>
       <c r="G22" s="58"/>
       <c r="H22" s="59"/>
-      <c r="I22" s="294" t="s">
+      <c r="I22" s="234" t="s">
         <v>43</v>
       </c>
-      <c r="J22" s="294"/>
-      <c r="K22" s="294"/>
-      <c r="L22" s="295" t="s">
+      <c r="J22" s="234"/>
+      <c r="K22" s="234"/>
+      <c r="L22" s="236" t="s">
         <v>44</v>
       </c>
-      <c r="M22" s="295"/>
-      <c r="N22" s="295"/>
+      <c r="M22" s="236"/>
+      <c r="N22" s="236"/>
       <c r="Q22" s="2" t="s">
         <v>45</v>
       </c>
@@ -10845,178 +10802,164 @@
       <c r="A23" s="56">
         <v>8</v>
       </c>
-      <c r="B23" s="309" t="s">
+      <c r="B23" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="310"/>
-      <c r="D23" s="311"/>
-      <c r="E23" s="311"/>
-      <c r="F23" s="311"/>
-      <c r="G23" s="312" t="s">
+      <c r="C23" s="228"/>
+      <c r="D23" s="229"/>
+      <c r="E23" s="229"/>
+      <c r="F23" s="229"/>
+      <c r="G23" s="230" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="313"/>
-      <c r="I23" s="314"/>
-      <c r="J23" s="314"/>
-      <c r="K23" s="314"/>
-      <c r="L23" s="314"/>
-      <c r="M23" s="314"/>
-      <c r="N23" s="314"/>
+      <c r="H23" s="231"/>
+      <c r="I23" s="232"/>
+      <c r="J23" s="232"/>
+      <c r="K23" s="232"/>
+      <c r="L23" s="232"/>
+      <c r="M23" s="232"/>
+      <c r="N23" s="232"/>
       <c r="Q23" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A24" s="324">
+      <c r="A24" s="216">
         <v>9</v>
       </c>
-      <c r="B24" s="327" t="s">
+      <c r="B24" s="219" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="328"/>
-      <c r="D24" s="320"/>
-      <c r="E24" s="320"/>
-      <c r="F24" s="320"/>
+      <c r="C24" s="220"/>
+      <c r="D24" s="224"/>
+      <c r="E24" s="224"/>
+      <c r="F24" s="224"/>
       <c r="G24" s="84" t="s">
         <v>50</v>
       </c>
       <c r="H24" s="81"/>
-      <c r="I24" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="J24" s="293"/>
-      <c r="K24" s="293"/>
-      <c r="L24" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="M24" s="293"/>
-      <c r="N24" s="293"/>
+      <c r="I24" s="215"/>
+      <c r="J24" s="232"/>
+      <c r="K24" s="232"/>
+      <c r="L24" s="215"/>
+      <c r="M24" s="232"/>
+      <c r="N24" s="232"/>
       <c r="Q24" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A25" s="326"/>
-      <c r="B25" s="329"/>
-      <c r="C25" s="330"/>
-      <c r="D25" s="331"/>
-      <c r="E25" s="331"/>
-      <c r="F25" s="331"/>
+      <c r="A25" s="218"/>
+      <c r="B25" s="221"/>
+      <c r="C25" s="222"/>
+      <c r="D25" s="225"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="225"/>
       <c r="G25" s="58"/>
       <c r="H25" s="59"/>
-      <c r="I25" s="212" t="s">
+      <c r="I25" s="233" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="212"/>
-      <c r="K25" s="212"/>
-      <c r="L25" s="212" t="s">
+      <c r="J25" s="233"/>
+      <c r="K25" s="233"/>
+      <c r="L25" s="233" t="s">
         <v>35</v>
       </c>
-      <c r="M25" s="212"/>
-      <c r="N25" s="212"/>
+      <c r="M25" s="233"/>
+      <c r="N25" s="233"/>
       <c r="Q25" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A26" s="324">
+      <c r="A26" s="216">
         <v>10</v>
       </c>
-      <c r="B26" s="327" t="s">
-        <v>340</v>
-      </c>
-      <c r="C26" s="328"/>
-      <c r="D26" s="320"/>
-      <c r="E26" s="320"/>
-      <c r="F26" s="320"/>
+      <c r="B26" s="219" t="s">
+        <v>339</v>
+      </c>
+      <c r="C26" s="220"/>
+      <c r="D26" s="224"/>
+      <c r="E26" s="224"/>
+      <c r="F26" s="224"/>
       <c r="G26" s="75"/>
       <c r="H26" s="76"/>
-      <c r="I26" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="J26" s="293"/>
-      <c r="K26" s="293"/>
-      <c r="L26" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="M26" s="293"/>
-      <c r="N26" s="293"/>
+      <c r="I26" s="215"/>
+      <c r="J26" s="232"/>
+      <c r="K26" s="232"/>
+      <c r="L26" s="215"/>
+      <c r="M26" s="232"/>
+      <c r="N26" s="232"/>
       <c r="Q26" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="35.25" customHeight="1">
-      <c r="A27" s="326"/>
-      <c r="B27" s="329"/>
-      <c r="C27" s="330"/>
-      <c r="D27" s="331"/>
-      <c r="E27" s="331"/>
-      <c r="F27" s="331"/>
+      <c r="A27" s="218"/>
+      <c r="B27" s="221"/>
+      <c r="C27" s="222"/>
+      <c r="D27" s="225"/>
+      <c r="E27" s="225"/>
+      <c r="F27" s="225"/>
       <c r="G27" s="75"/>
       <c r="H27" s="76"/>
-      <c r="I27" s="294" t="s">
+      <c r="I27" s="234" t="s">
         <v>38</v>
       </c>
-      <c r="J27" s="301"/>
-      <c r="K27" s="301"/>
-      <c r="L27" s="295" t="s">
+      <c r="J27" s="235"/>
+      <c r="K27" s="235"/>
+      <c r="L27" s="236" t="s">
         <v>39</v>
       </c>
-      <c r="M27" s="301"/>
-      <c r="N27" s="301"/>
+      <c r="M27" s="235"/>
+      <c r="N27" s="235"/>
       <c r="Q27" s="2" t="s">
         <v>54</v>
       </c>
       <c r="S27" s="85"/>
     </row>
     <row r="28" spans="1:23" ht="33" customHeight="1">
-      <c r="A28" s="324">
+      <c r="A28" s="216">
         <v>11</v>
       </c>
-      <c r="B28" s="327" t="s">
+      <c r="B28" s="219" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="328"/>
-      <c r="D28" s="319" t="s">
-        <v>326</v>
-      </c>
-      <c r="E28" s="320"/>
-      <c r="F28" s="320"/>
+      <c r="C28" s="220"/>
+      <c r="D28" s="223"/>
+      <c r="E28" s="224"/>
+      <c r="F28" s="224"/>
       <c r="G28" s="75"/>
       <c r="H28" s="86"/>
-      <c r="I28" s="315" t="s">
-        <v>326</v>
-      </c>
-      <c r="J28" s="316"/>
-      <c r="K28" s="316"/>
-      <c r="L28" s="317" t="s">
-        <v>326</v>
-      </c>
-      <c r="M28" s="318"/>
-      <c r="N28" s="318"/>
+      <c r="I28" s="215"/>
+      <c r="J28" s="232"/>
+      <c r="K28" s="232"/>
+      <c r="L28" s="215"/>
+      <c r="M28" s="232"/>
+      <c r="N28" s="232"/>
       <c r="Q28" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="32.25" customHeight="1">
-      <c r="A29" s="326"/>
-      <c r="B29" s="329"/>
-      <c r="C29" s="330"/>
-      <c r="D29" s="331"/>
-      <c r="E29" s="331"/>
-      <c r="F29" s="331"/>
+      <c r="A29" s="218"/>
+      <c r="B29" s="221"/>
+      <c r="C29" s="222"/>
+      <c r="D29" s="225"/>
+      <c r="E29" s="225"/>
+      <c r="F29" s="225"/>
       <c r="G29" s="75"/>
       <c r="H29" s="86"/>
-      <c r="I29" s="294" t="s">
+      <c r="I29" s="234" t="s">
         <v>43</v>
       </c>
-      <c r="J29" s="294"/>
-      <c r="K29" s="294"/>
-      <c r="L29" s="294" t="s">
+      <c r="J29" s="234"/>
+      <c r="K29" s="234"/>
+      <c r="L29" s="234" t="s">
         <v>44</v>
       </c>
-      <c r="M29" s="294"/>
-      <c r="N29" s="294"/>
+      <c r="M29" s="234"/>
+      <c r="N29" s="234"/>
       <c r="Q29" s="2" t="s">
         <v>57</v>
       </c>
@@ -11030,21 +10973,19 @@
         <v>58</v>
       </c>
       <c r="C30" s="69"/>
-      <c r="D30" s="319" t="s">
-        <v>326</v>
-      </c>
-      <c r="E30" s="320"/>
-      <c r="F30" s="320"/>
-      <c r="G30" s="312" t="s">
+      <c r="D30" s="223"/>
+      <c r="E30" s="224"/>
+      <c r="F30" s="224"/>
+      <c r="G30" s="230" t="s">
         <v>47</v>
       </c>
-      <c r="H30" s="313"/>
-      <c r="I30" s="293"/>
-      <c r="J30" s="293"/>
-      <c r="K30" s="293"/>
-      <c r="L30" s="293"/>
-      <c r="M30" s="293"/>
-      <c r="N30" s="293"/>
+      <c r="H30" s="231"/>
+      <c r="I30" s="232"/>
+      <c r="J30" s="232"/>
+      <c r="K30" s="232"/>
+      <c r="L30" s="232"/>
+      <c r="M30" s="232"/>
+      <c r="N30" s="232"/>
       <c r="Q30" s="2" t="s">
         <v>59</v>
       </c>
@@ -11058,47 +10999,45 @@
         <v>13</v>
       </c>
       <c r="B31" s="67" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C31" s="69"/>
-      <c r="D31" s="311"/>
-      <c r="E31" s="311"/>
-      <c r="F31" s="311"/>
+      <c r="D31" s="229"/>
+      <c r="E31" s="229"/>
+      <c r="F31" s="229"/>
       <c r="G31" s="87" t="s">
         <v>60</v>
       </c>
       <c r="H31" s="83"/>
-      <c r="I31" s="292" t="s">
-        <v>326</v>
-      </c>
-      <c r="J31" s="292"/>
-      <c r="K31" s="292"/>
-      <c r="L31" s="292"/>
-      <c r="M31" s="292"/>
-      <c r="N31" s="292"/>
+      <c r="I31" s="215"/>
+      <c r="J31" s="215"/>
+      <c r="K31" s="215"/>
+      <c r="L31" s="215"/>
+      <c r="M31" s="215"/>
+      <c r="N31" s="215"/>
       <c r="Q31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="39.75" customHeight="1">
-      <c r="A32" s="321" t="s">
+      <c r="A32" s="237" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="310"/>
-      <c r="C32" s="322"/>
-      <c r="D32" s="311"/>
-      <c r="E32" s="311"/>
-      <c r="F32" s="311"/>
+      <c r="B32" s="228"/>
+      <c r="C32" s="238"/>
+      <c r="D32" s="229"/>
+      <c r="E32" s="229"/>
+      <c r="F32" s="229"/>
       <c r="G32" s="88" t="s">
         <v>63</v>
       </c>
       <c r="H32" s="89"/>
-      <c r="I32" s="292"/>
-      <c r="J32" s="292"/>
-      <c r="K32" s="292"/>
-      <c r="L32" s="292"/>
-      <c r="M32" s="292"/>
-      <c r="N32" s="292"/>
+      <c r="I32" s="215"/>
+      <c r="J32" s="215"/>
+      <c r="K32" s="215"/>
+      <c r="L32" s="215"/>
+      <c r="M32" s="215"/>
+      <c r="N32" s="215"/>
       <c r="Q32" s="2" t="s">
         <v>64</v>
       </c>
@@ -11107,63 +11046,63 @@
       <c r="A33" s="66">
         <v>15</v>
       </c>
-      <c r="B33" s="221" t="s">
-        <v>338</v>
-      </c>
-      <c r="C33" s="222"/>
-      <c r="D33" s="218"/>
-      <c r="E33" s="219"/>
-      <c r="F33" s="220"/>
+      <c r="B33" s="327" t="s">
+        <v>337</v>
+      </c>
+      <c r="C33" s="328"/>
+      <c r="D33" s="324"/>
+      <c r="E33" s="325"/>
+      <c r="F33" s="326"/>
       <c r="G33" s="90" t="s">
         <v>65</v>
       </c>
       <c r="H33" s="83"/>
-      <c r="I33" s="323"/>
-      <c r="J33" s="292"/>
-      <c r="K33" s="292"/>
-      <c r="L33" s="292"/>
-      <c r="M33" s="292"/>
-      <c r="N33" s="292"/>
+      <c r="I33" s="214"/>
+      <c r="J33" s="215"/>
+      <c r="K33" s="215"/>
+      <c r="L33" s="215"/>
+      <c r="M33" s="215"/>
+      <c r="N33" s="215"/>
       <c r="Q33" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A34" s="214" t="s">
-        <v>344</v>
-      </c>
-      <c r="B34" s="215"/>
-      <c r="C34" s="215"/>
-      <c r="D34" s="215"/>
-      <c r="E34" s="215"/>
-      <c r="F34" s="215"/>
-      <c r="G34" s="215"/>
-      <c r="H34" s="215"/>
-      <c r="I34" s="215"/>
-      <c r="J34" s="215"/>
-      <c r="K34" s="215"/>
-      <c r="L34" s="215"/>
-      <c r="M34" s="215"/>
-      <c r="N34" s="216"/>
+      <c r="A34" s="321" t="s">
+        <v>343</v>
+      </c>
+      <c r="B34" s="322"/>
+      <c r="C34" s="322"/>
+      <c r="D34" s="322"/>
+      <c r="E34" s="322"/>
+      <c r="F34" s="322"/>
+      <c r="G34" s="322"/>
+      <c r="H34" s="322"/>
+      <c r="I34" s="322"/>
+      <c r="J34" s="322"/>
+      <c r="K34" s="322"/>
+      <c r="L34" s="322"/>
+      <c r="M34" s="322"/>
+      <c r="N34" s="323"/>
       <c r="Q34" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="21" customHeight="1">
-      <c r="A35" s="217" t="s">
-        <v>345</v>
-      </c>
-      <c r="B35" s="217"/>
-      <c r="C35" s="217"/>
+      <c r="A35" s="212" t="s">
+        <v>344</v>
+      </c>
+      <c r="B35" s="212"/>
+      <c r="C35" s="212"/>
       <c r="D35" s="213" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E35" s="213"/>
       <c r="F35" s="213"/>
-      <c r="G35" s="517" t="s">
-        <v>346</v>
-      </c>
-      <c r="H35" s="518"/>
+      <c r="G35" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="H35" s="320"/>
       <c r="I35" s="213"/>
       <c r="J35" s="213"/>
       <c r="K35" s="213"/>
@@ -15013,8 +14952,84 @@
       <c r="N263" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vcZpRSeL7MD/5liJ7jQWiHSvb8cKjUkNOVcwICP1wgx7dy3imgNB0NJ/LQ0ARj8+D7aOpeJJ2530d3Jn5aC8cw==" saltValue="Jyye/obUWyzWvVaD//eRmg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="a8qq29ZlI3R54ZoD8FVfNYmfvN4etlIbTOVSEgEF8lpGPbTgEWSgo1lzSaUPdRrL9ue2Qo2JOsbZMdcUQky+ng==" saltValue="AuXW3/CaPjwkTWWL+jhPjw==" spinCount="100000" sheet="1" scenarios="1"/>
   <mergeCells count="92">
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="I31:N31"/>
+    <mergeCell ref="R3:V13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:N15"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:I14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="D26:F27"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:N23"/>
+    <mergeCell ref="I24:K24"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="I35:N35"/>
@@ -15031,82 +15046,6 @@
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="D24:F25"/>
     <mergeCell ref="B26:C27"/>
-    <mergeCell ref="D26:F27"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="I31:N31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:N23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:N15"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:I14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="R3:V13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35" xr:uid="{5EC3205D-4079-402B-BBE7-9B917DF21EB0}">
@@ -15612,177 +15551,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1">
-      <c r="A1" s="443"/>
-      <c r="B1" s="444"/>
-      <c r="C1" s="444"/>
-      <c r="D1" s="444"/>
-      <c r="E1" s="444"/>
-      <c r="F1" s="444"/>
-      <c r="G1" s="444"/>
-      <c r="H1" s="444"/>
-      <c r="I1" s="444"/>
-      <c r="J1" s="444"/>
+      <c r="A1" s="469"/>
+      <c r="B1" s="470"/>
+      <c r="C1" s="470"/>
+      <c r="D1" s="470"/>
+      <c r="E1" s="470"/>
+      <c r="F1" s="470"/>
+      <c r="G1" s="470"/>
+      <c r="H1" s="470"/>
+      <c r="I1" s="470"/>
+      <c r="J1" s="470"/>
     </row>
     <row r="2" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A2" s="445">
+      <c r="A2" s="471">
         <v>34</v>
       </c>
-      <c r="B2" s="446"/>
-      <c r="C2" s="447" t="s">
+      <c r="B2" s="472"/>
+      <c r="C2" s="473" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="447"/>
-      <c r="E2" s="447"/>
-      <c r="F2" s="448"/>
-      <c r="G2" s="451"/>
-      <c r="H2" s="452"/>
-      <c r="I2" s="452"/>
-      <c r="J2" s="452"/>
+      <c r="D2" s="473"/>
+      <c r="E2" s="473"/>
+      <c r="F2" s="474"/>
+      <c r="G2" s="477"/>
+      <c r="H2" s="478"/>
+      <c r="I2" s="478"/>
+      <c r="J2" s="478"/>
       <c r="K2" s="181"/>
     </row>
     <row r="3" spans="1:11" ht="12.75" customHeight="1">
       <c r="A3" s="182"/>
       <c r="B3" s="183"/>
-      <c r="C3" s="449" t="s">
+      <c r="C3" s="475" t="s">
         <v>295</v>
       </c>
-      <c r="D3" s="449"/>
-      <c r="E3" s="449"/>
-      <c r="F3" s="450"/>
-      <c r="G3" s="453"/>
-      <c r="H3" s="454"/>
-      <c r="I3" s="454"/>
-      <c r="J3" s="454"/>
+      <c r="D3" s="475"/>
+      <c r="E3" s="475"/>
+      <c r="F3" s="476"/>
+      <c r="G3" s="479"/>
+      <c r="H3" s="480"/>
+      <c r="I3" s="480"/>
+      <c r="J3" s="480"/>
       <c r="K3" s="181"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="182"/>
       <c r="B4" s="183"/>
-      <c r="C4" s="449" t="s">
+      <c r="C4" s="475" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="449"/>
-      <c r="E4" s="449"/>
-      <c r="F4" s="450"/>
-      <c r="G4" s="453"/>
-      <c r="H4" s="454"/>
-      <c r="I4" s="454"/>
-      <c r="J4" s="454"/>
+      <c r="D4" s="475"/>
+      <c r="E4" s="475"/>
+      <c r="F4" s="476"/>
+      <c r="G4" s="479"/>
+      <c r="H4" s="480"/>
+      <c r="I4" s="480"/>
+      <c r="J4" s="480"/>
       <c r="K4" s="181"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="182"/>
       <c r="B5" s="183"/>
-      <c r="C5" s="449" t="s">
+      <c r="C5" s="475" t="s">
         <v>297</v>
       </c>
-      <c r="D5" s="449"/>
-      <c r="E5" s="449"/>
-      <c r="F5" s="450"/>
-      <c r="G5" s="435" t="b">
+      <c r="D5" s="475"/>
+      <c r="E5" s="475"/>
+      <c r="F5" s="476"/>
+      <c r="G5" s="447" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="434"/>
-      <c r="I5" s="434" t="b">
+      <c r="H5" s="432"/>
+      <c r="I5" s="432" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="434"/>
+      <c r="J5" s="432"/>
       <c r="K5" s="181"/>
     </row>
     <row r="6" spans="1:11" ht="24" customHeight="1">
       <c r="A6" s="182"/>
       <c r="B6" s="183"/>
-      <c r="C6" s="449" t="s">
+      <c r="C6" s="475" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="449"/>
-      <c r="E6" s="449"/>
-      <c r="F6" s="450"/>
-      <c r="G6" s="435" t="b">
+      <c r="D6" s="475"/>
+      <c r="E6" s="475"/>
+      <c r="F6" s="476"/>
+      <c r="G6" s="447" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="434"/>
-      <c r="I6" s="434" t="b">
+      <c r="H6" s="432"/>
+      <c r="I6" s="432" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="434"/>
+      <c r="J6" s="432"/>
       <c r="K6" s="181"/>
     </row>
     <row r="7" spans="1:11" ht="27" customHeight="1">
       <c r="A7" s="182"/>
       <c r="B7" s="183"/>
-      <c r="C7" s="449"/>
-      <c r="D7" s="449"/>
-      <c r="E7" s="449"/>
-      <c r="F7" s="449"/>
+      <c r="C7" s="475"/>
+      <c r="D7" s="475"/>
+      <c r="E7" s="475"/>
+      <c r="F7" s="475"/>
       <c r="G7" s="184" t="s">
         <v>322</v>
       </c>
       <c r="H7" s="185"/>
-      <c r="I7" s="436"/>
-      <c r="J7" s="436"/>
+      <c r="I7" s="501"/>
+      <c r="J7" s="501"/>
       <c r="K7" s="181"/>
     </row>
     <row r="8" spans="1:11" ht="31.5" customHeight="1">
       <c r="A8" s="186"/>
       <c r="B8" s="187"/>
-      <c r="C8" s="468"/>
-      <c r="D8" s="468"/>
-      <c r="E8" s="468"/>
-      <c r="F8" s="469"/>
-      <c r="G8" s="477"/>
-      <c r="H8" s="478"/>
-      <c r="I8" s="478"/>
-      <c r="J8" s="478"/>
+      <c r="C8" s="490"/>
+      <c r="D8" s="490"/>
+      <c r="E8" s="490"/>
+      <c r="F8" s="491"/>
+      <c r="G8" s="499"/>
+      <c r="H8" s="500"/>
+      <c r="I8" s="500"/>
+      <c r="J8" s="500"/>
       <c r="K8" s="181"/>
     </row>
     <row r="9" spans="1:11" ht="20.45" customHeight="1">
-      <c r="A9" s="470">
+      <c r="A9" s="492">
         <v>35</v>
       </c>
-      <c r="B9" s="471"/>
-      <c r="C9" s="472" t="s">
+      <c r="B9" s="493"/>
+      <c r="C9" s="459" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="472"/>
-      <c r="E9" s="376"/>
-      <c r="F9" s="473"/>
-      <c r="G9" s="438" t="b">
+      <c r="D9" s="459"/>
+      <c r="E9" s="372"/>
+      <c r="F9" s="494"/>
+      <c r="G9" s="451" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="437"/>
-      <c r="I9" s="437" t="b">
+      <c r="H9" s="452"/>
+      <c r="I9" s="452" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="437"/>
+      <c r="J9" s="452"/>
       <c r="K9" s="181"/>
     </row>
     <row r="10" spans="1:11" ht="26.25" customHeight="1">
       <c r="A10" s="188"/>
       <c r="B10" s="189"/>
-      <c r="C10" s="472"/>
-      <c r="D10" s="472"/>
-      <c r="E10" s="376"/>
-      <c r="F10" s="473"/>
-      <c r="G10" s="439" t="s">
+      <c r="C10" s="459"/>
+      <c r="D10" s="459"/>
+      <c r="E10" s="372"/>
+      <c r="F10" s="494"/>
+      <c r="G10" s="502" t="s">
         <v>322</v>
       </c>
-      <c r="H10" s="440"/>
-      <c r="I10" s="427"/>
-      <c r="J10" s="427"/>
+      <c r="H10" s="503"/>
+      <c r="I10" s="498"/>
+      <c r="J10" s="498"/>
       <c r="K10" s="181"/>
     </row>
     <row r="11" spans="1:11" ht="21.75" customHeight="1">
       <c r="A11" s="188"/>
       <c r="B11" s="189"/>
-      <c r="C11" s="376"/>
-      <c r="D11" s="376"/>
-      <c r="E11" s="376"/>
-      <c r="F11" s="376"/>
-      <c r="G11" s="425"/>
-      <c r="H11" s="426"/>
-      <c r="I11" s="426"/>
-      <c r="J11" s="426"/>
+      <c r="C11" s="372"/>
+      <c r="D11" s="372"/>
+      <c r="E11" s="372"/>
+      <c r="F11" s="372"/>
+      <c r="G11" s="495"/>
+      <c r="H11" s="496"/>
+      <c r="I11" s="496"/>
+      <c r="J11" s="496"/>
       <c r="K11" s="181"/>
     </row>
     <row r="12" spans="1:11" ht="18.75" customHeight="1">
@@ -15792,224 +15731,224 @@
       <c r="D12" s="192"/>
       <c r="E12" s="193"/>
       <c r="F12" s="194"/>
-      <c r="G12" s="441" t="b">
+      <c r="G12" s="504" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="442"/>
-      <c r="I12" s="442" t="b">
+      <c r="H12" s="505"/>
+      <c r="I12" s="505" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="442"/>
+      <c r="J12" s="505"/>
       <c r="K12" s="181"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1">
       <c r="A13" s="190"/>
       <c r="B13" s="191"/>
-      <c r="C13" s="455" t="s">
+      <c r="C13" s="481" t="s">
         <v>300</v>
       </c>
-      <c r="D13" s="455"/>
-      <c r="E13" s="456"/>
-      <c r="F13" s="457"/>
-      <c r="G13" s="441"/>
-      <c r="H13" s="442"/>
-      <c r="I13" s="442"/>
-      <c r="J13" s="442"/>
+      <c r="D13" s="481"/>
+      <c r="E13" s="482"/>
+      <c r="F13" s="483"/>
+      <c r="G13" s="504"/>
+      <c r="H13" s="505"/>
+      <c r="I13" s="505"/>
+      <c r="J13" s="505"/>
       <c r="K13" s="181"/>
     </row>
     <row r="14" spans="1:11" ht="23.25" customHeight="1">
       <c r="A14" s="190"/>
       <c r="B14" s="191"/>
-      <c r="C14" s="455"/>
-      <c r="D14" s="455"/>
-      <c r="E14" s="456"/>
-      <c r="F14" s="457"/>
-      <c r="G14" s="429" t="s">
+      <c r="C14" s="481"/>
+      <c r="D14" s="481"/>
+      <c r="E14" s="482"/>
+      <c r="F14" s="483"/>
+      <c r="G14" s="424" t="s">
         <v>325</v>
       </c>
-      <c r="H14" s="430"/>
-      <c r="I14" s="431"/>
-      <c r="J14" s="431"/>
+      <c r="H14" s="425"/>
+      <c r="I14" s="509"/>
+      <c r="J14" s="509"/>
       <c r="K14" s="181"/>
     </row>
     <row r="15" spans="1:11" ht="21" customHeight="1">
       <c r="A15" s="190"/>
       <c r="B15" s="191"/>
-      <c r="C15" s="455"/>
-      <c r="D15" s="455"/>
-      <c r="E15" s="456"/>
-      <c r="F15" s="457"/>
-      <c r="G15" s="423" t="s">
+      <c r="C15" s="481"/>
+      <c r="D15" s="481"/>
+      <c r="E15" s="482"/>
+      <c r="F15" s="483"/>
+      <c r="G15" s="506" t="s">
         <v>301</v>
       </c>
-      <c r="H15" s="424"/>
-      <c r="I15" s="427"/>
-      <c r="J15" s="427"/>
+      <c r="H15" s="507"/>
+      <c r="I15" s="498"/>
+      <c r="J15" s="498"/>
       <c r="K15" s="181"/>
     </row>
     <row r="16" spans="1:11" ht="27.75" customHeight="1">
       <c r="A16" s="190"/>
       <c r="B16" s="191"/>
-      <c r="C16" s="455"/>
-      <c r="D16" s="455"/>
-      <c r="E16" s="456"/>
-      <c r="F16" s="457"/>
-      <c r="G16" s="432" t="s">
+      <c r="C16" s="481"/>
+      <c r="D16" s="481"/>
+      <c r="E16" s="482"/>
+      <c r="F16" s="483"/>
+      <c r="G16" s="510" t="s">
         <v>302</v>
       </c>
-      <c r="H16" s="433"/>
-      <c r="I16" s="428"/>
-      <c r="J16" s="428"/>
+      <c r="H16" s="511"/>
+      <c r="I16" s="508"/>
+      <c r="J16" s="508"/>
       <c r="K16" s="181"/>
     </row>
     <row r="17" spans="1:12" ht="21" customHeight="1">
       <c r="A17" s="195"/>
       <c r="B17" s="196"/>
-      <c r="C17" s="458"/>
-      <c r="D17" s="458"/>
-      <c r="E17" s="458"/>
-      <c r="F17" s="459"/>
-      <c r="G17" s="425" t="s">
+      <c r="C17" s="484"/>
+      <c r="D17" s="484"/>
+      <c r="E17" s="484"/>
+      <c r="F17" s="485"/>
+      <c r="G17" s="495" t="s">
         <v>303</v>
       </c>
-      <c r="H17" s="426"/>
-      <c r="I17" s="426"/>
-      <c r="J17" s="426"/>
+      <c r="H17" s="496"/>
+      <c r="I17" s="496"/>
+      <c r="J17" s="496"/>
       <c r="K17" s="181"/>
     </row>
     <row r="18" spans="1:12" ht="33" customHeight="1">
-      <c r="A18" s="466">
+      <c r="A18" s="488">
         <v>36</v>
       </c>
-      <c r="B18" s="467"/>
-      <c r="C18" s="460" t="s">
+      <c r="B18" s="489"/>
+      <c r="C18" s="486" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="460"/>
-      <c r="E18" s="460"/>
-      <c r="F18" s="461"/>
-      <c r="G18" s="438" t="b">
+      <c r="D18" s="486"/>
+      <c r="E18" s="486"/>
+      <c r="F18" s="487"/>
+      <c r="G18" s="451" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="437"/>
-      <c r="I18" s="437" t="b">
+      <c r="H18" s="452"/>
+      <c r="I18" s="452" t="b">
         <v>0</v>
       </c>
-      <c r="J18" s="437"/>
+      <c r="J18" s="452"/>
       <c r="K18" s="181"/>
     </row>
     <row r="19" spans="1:12" ht="26.25" customHeight="1">
       <c r="A19" s="188"/>
       <c r="B19" s="189"/>
-      <c r="C19" s="462"/>
-      <c r="D19" s="462"/>
-      <c r="E19" s="462"/>
-      <c r="F19" s="463"/>
-      <c r="G19" s="475" t="s">
+      <c r="C19" s="428"/>
+      <c r="D19" s="428"/>
+      <c r="E19" s="428"/>
+      <c r="F19" s="429"/>
+      <c r="G19" s="453" t="s">
         <v>324</v>
       </c>
-      <c r="H19" s="476"/>
-      <c r="I19" s="427"/>
-      <c r="J19" s="427"/>
+      <c r="H19" s="454"/>
+      <c r="I19" s="498"/>
+      <c r="J19" s="498"/>
       <c r="K19" s="199"/>
     </row>
     <row r="20" spans="1:12" ht="25.5" customHeight="1">
       <c r="A20" s="200"/>
       <c r="B20" s="201"/>
-      <c r="C20" s="464"/>
-      <c r="D20" s="464"/>
-      <c r="E20" s="464"/>
-      <c r="F20" s="465"/>
-      <c r="G20" s="425"/>
-      <c r="H20" s="426"/>
-      <c r="I20" s="474"/>
-      <c r="J20" s="474"/>
+      <c r="C20" s="455"/>
+      <c r="D20" s="455"/>
+      <c r="E20" s="455"/>
+      <c r="F20" s="456"/>
+      <c r="G20" s="495"/>
+      <c r="H20" s="496"/>
+      <c r="I20" s="497"/>
+      <c r="J20" s="497"/>
       <c r="K20" s="181"/>
     </row>
     <row r="21" spans="1:12" ht="26.25" customHeight="1">
-      <c r="A21" s="466">
+      <c r="A21" s="488">
         <v>37</v>
       </c>
-      <c r="B21" s="467"/>
-      <c r="C21" s="460" t="s">
+      <c r="B21" s="489"/>
+      <c r="C21" s="486" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="460"/>
-      <c r="E21" s="460"/>
-      <c r="F21" s="461"/>
-      <c r="G21" s="438" t="b">
+      <c r="D21" s="486"/>
+      <c r="E21" s="486"/>
+      <c r="F21" s="487"/>
+      <c r="G21" s="451" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="437"/>
-      <c r="I21" s="437" t="b">
+      <c r="H21" s="452"/>
+      <c r="I21" s="452" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="437"/>
+      <c r="J21" s="452"/>
       <c r="K21" s="181"/>
     </row>
     <row r="22" spans="1:12" ht="27.75" customHeight="1">
       <c r="A22" s="188"/>
       <c r="B22" s="189"/>
-      <c r="C22" s="462"/>
-      <c r="D22" s="462"/>
-      <c r="E22" s="462"/>
-      <c r="F22" s="463"/>
-      <c r="G22" s="475" t="s">
+      <c r="C22" s="428"/>
+      <c r="D22" s="428"/>
+      <c r="E22" s="428"/>
+      <c r="F22" s="429"/>
+      <c r="G22" s="453" t="s">
         <v>323</v>
       </c>
-      <c r="H22" s="476"/>
-      <c r="I22" s="480"/>
-      <c r="J22" s="480"/>
+      <c r="H22" s="454"/>
+      <c r="I22" s="512"/>
+      <c r="J22" s="512"/>
       <c r="K22" s="181"/>
     </row>
     <row r="23" spans="1:12" ht="39.75" customHeight="1">
       <c r="A23" s="200"/>
       <c r="B23" s="201"/>
-      <c r="C23" s="464"/>
-      <c r="D23" s="464"/>
-      <c r="E23" s="464"/>
-      <c r="F23" s="465"/>
-      <c r="G23" s="425"/>
-      <c r="H23" s="426"/>
-      <c r="I23" s="426"/>
-      <c r="J23" s="426"/>
+      <c r="C23" s="455"/>
+      <c r="D23" s="455"/>
+      <c r="E23" s="455"/>
+      <c r="F23" s="456"/>
+      <c r="G23" s="495"/>
+      <c r="H23" s="496"/>
+      <c r="I23" s="496"/>
+      <c r="J23" s="496"/>
       <c r="K23" s="202"/>
     </row>
     <row r="24" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A24" s="466">
+      <c r="A24" s="488">
         <v>38</v>
       </c>
-      <c r="B24" s="467"/>
-      <c r="C24" s="460" t="s">
+      <c r="B24" s="489"/>
+      <c r="C24" s="486" t="s">
         <v>306</v>
       </c>
-      <c r="D24" s="460"/>
-      <c r="E24" s="460"/>
-      <c r="F24" s="461"/>
-      <c r="G24" s="438" t="b">
+      <c r="D24" s="486"/>
+      <c r="E24" s="486"/>
+      <c r="F24" s="487"/>
+      <c r="G24" s="451" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="437"/>
-      <c r="I24" s="437" t="b">
+      <c r="H24" s="452"/>
+      <c r="I24" s="452" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="437"/>
+      <c r="J24" s="452"/>
       <c r="K24" s="181"/>
       <c r="L24" s="203"/>
     </row>
     <row r="25" spans="1:12" ht="28.5" customHeight="1">
       <c r="A25" s="188"/>
       <c r="B25" s="189"/>
-      <c r="C25" s="462"/>
-      <c r="D25" s="462"/>
-      <c r="E25" s="462"/>
-      <c r="F25" s="463"/>
-      <c r="G25" s="429" t="s">
+      <c r="C25" s="428"/>
+      <c r="D25" s="428"/>
+      <c r="E25" s="428"/>
+      <c r="F25" s="429"/>
+      <c r="G25" s="424" t="s">
         <v>307</v>
       </c>
-      <c r="H25" s="430"/>
-      <c r="I25" s="479"/>
-      <c r="J25" s="479"/>
+      <c r="H25" s="425"/>
+      <c r="I25" s="427"/>
+      <c r="J25" s="427"/>
       <c r="K25" s="181"/>
     </row>
     <row r="26" spans="1:12" ht="23.25" customHeight="1">
@@ -16019,123 +15958,123 @@
       <c r="D26" s="197"/>
       <c r="E26" s="197"/>
       <c r="F26" s="198"/>
-      <c r="G26" s="489" t="b">
+      <c r="G26" s="463" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="490"/>
-      <c r="I26" s="491" t="b">
+      <c r="H26" s="464"/>
+      <c r="I26" s="465" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="491"/>
+      <c r="J26" s="465"/>
       <c r="K26" s="181"/>
     </row>
     <row r="27" spans="1:12" ht="24.75" customHeight="1">
       <c r="A27" s="188"/>
       <c r="B27" s="189"/>
-      <c r="C27" s="462" t="s">
+      <c r="C27" s="428" t="s">
         <v>308</v>
       </c>
-      <c r="D27" s="462"/>
-      <c r="E27" s="462"/>
-      <c r="F27" s="463"/>
-      <c r="G27" s="489"/>
-      <c r="H27" s="490"/>
-      <c r="I27" s="492"/>
-      <c r="J27" s="492"/>
+      <c r="D27" s="428"/>
+      <c r="E27" s="428"/>
+      <c r="F27" s="429"/>
+      <c r="G27" s="463"/>
+      <c r="H27" s="464"/>
+      <c r="I27" s="466"/>
+      <c r="J27" s="466"/>
       <c r="K27" s="181"/>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="188"/>
       <c r="B28" s="189"/>
-      <c r="C28" s="462"/>
-      <c r="D28" s="462"/>
-      <c r="E28" s="462"/>
-      <c r="F28" s="463"/>
-      <c r="G28" s="429" t="s">
+      <c r="C28" s="428"/>
+      <c r="D28" s="428"/>
+      <c r="E28" s="428"/>
+      <c r="F28" s="429"/>
+      <c r="G28" s="424" t="s">
         <v>307</v>
       </c>
-      <c r="H28" s="430"/>
-      <c r="I28" s="479"/>
-      <c r="J28" s="479"/>
+      <c r="H28" s="425"/>
+      <c r="I28" s="427"/>
+      <c r="J28" s="427"/>
       <c r="K28" s="181"/>
     </row>
     <row r="29" spans="1:12" ht="30.75" customHeight="1">
       <c r="A29" s="200"/>
       <c r="B29" s="201"/>
-      <c r="C29" s="464"/>
-      <c r="D29" s="464"/>
-      <c r="E29" s="464"/>
-      <c r="F29" s="465"/>
-      <c r="G29" s="481"/>
-      <c r="H29" s="482"/>
-      <c r="I29" s="482"/>
-      <c r="J29" s="482"/>
+      <c r="C29" s="455"/>
+      <c r="D29" s="455"/>
+      <c r="E29" s="455"/>
+      <c r="F29" s="456"/>
+      <c r="G29" s="449"/>
+      <c r="H29" s="450"/>
+      <c r="I29" s="450"/>
+      <c r="J29" s="450"/>
       <c r="K29" s="181"/>
     </row>
     <row r="30" spans="1:12" ht="23.45" customHeight="1">
-      <c r="A30" s="466">
+      <c r="A30" s="488">
         <v>39</v>
       </c>
-      <c r="B30" s="467"/>
-      <c r="C30" s="484" t="s">
+      <c r="B30" s="489"/>
+      <c r="C30" s="457" t="s">
         <v>309</v>
       </c>
-      <c r="D30" s="484"/>
-      <c r="E30" s="484"/>
-      <c r="F30" s="485"/>
-      <c r="G30" s="438" t="b">
+      <c r="D30" s="457"/>
+      <c r="E30" s="457"/>
+      <c r="F30" s="458"/>
+      <c r="G30" s="451" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="437"/>
-      <c r="I30" s="437" t="b">
+      <c r="H30" s="452"/>
+      <c r="I30" s="452" t="b">
         <v>0</v>
       </c>
-      <c r="J30" s="437"/>
+      <c r="J30" s="452"/>
       <c r="K30" s="181"/>
     </row>
     <row r="31" spans="1:12" ht="27" customHeight="1">
       <c r="A31" s="188"/>
       <c r="B31" s="189"/>
-      <c r="C31" s="472"/>
-      <c r="D31" s="472"/>
-      <c r="E31" s="472"/>
-      <c r="F31" s="486"/>
-      <c r="G31" s="475" t="s">
+      <c r="C31" s="459"/>
+      <c r="D31" s="459"/>
+      <c r="E31" s="459"/>
+      <c r="F31" s="460"/>
+      <c r="G31" s="453" t="s">
         <v>310</v>
       </c>
-      <c r="H31" s="476"/>
-      <c r="I31" s="483"/>
-      <c r="J31" s="479"/>
+      <c r="H31" s="454"/>
+      <c r="I31" s="426"/>
+      <c r="J31" s="427"/>
       <c r="K31" s="181"/>
     </row>
     <row r="32" spans="1:12" ht="33.75" customHeight="1">
       <c r="A32" s="200"/>
       <c r="B32" s="201"/>
-      <c r="C32" s="487"/>
-      <c r="D32" s="487"/>
-      <c r="E32" s="487"/>
-      <c r="F32" s="488"/>
-      <c r="G32" s="493"/>
-      <c r="H32" s="494"/>
-      <c r="I32" s="494"/>
-      <c r="J32" s="494"/>
+      <c r="C32" s="461"/>
+      <c r="D32" s="461"/>
+      <c r="E32" s="461"/>
+      <c r="F32" s="462"/>
+      <c r="G32" s="467"/>
+      <c r="H32" s="468"/>
+      <c r="I32" s="468"/>
+      <c r="J32" s="468"/>
       <c r="K32" s="181"/>
     </row>
     <row r="33" spans="1:11" ht="46.5" customHeight="1">
-      <c r="A33" s="495">
+      <c r="A33" s="443">
         <v>40</v>
       </c>
-      <c r="B33" s="496"/>
-      <c r="C33" s="462" t="s">
+      <c r="B33" s="444"/>
+      <c r="C33" s="428" t="s">
         <v>311</v>
       </c>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="463"/>
-      <c r="G33" s="497"/>
-      <c r="H33" s="498"/>
-      <c r="I33" s="498"/>
-      <c r="J33" s="498"/>
+      <c r="D33" s="428"/>
+      <c r="E33" s="428"/>
+      <c r="F33" s="429"/>
+      <c r="G33" s="445"/>
+      <c r="H33" s="446"/>
+      <c r="I33" s="446"/>
+      <c r="J33" s="446"/>
       <c r="K33" s="181"/>
     </row>
     <row r="34" spans="1:11" ht="39.75" customHeight="1">
@@ -16143,35 +16082,35 @@
         <v>312</v>
       </c>
       <c r="B34" s="205"/>
-      <c r="C34" s="462" t="s">
+      <c r="C34" s="428" t="s">
         <v>313</v>
       </c>
-      <c r="D34" s="462"/>
-      <c r="E34" s="462"/>
-      <c r="F34" s="463"/>
-      <c r="G34" s="435" t="b">
+      <c r="D34" s="428"/>
+      <c r="E34" s="428"/>
+      <c r="F34" s="429"/>
+      <c r="G34" s="447" t="b">
         <v>0</v>
       </c>
-      <c r="H34" s="434"/>
-      <c r="I34" s="434" t="b">
+      <c r="H34" s="432"/>
+      <c r="I34" s="432" t="b">
         <v>0</v>
       </c>
-      <c r="J34" s="434"/>
+      <c r="J34" s="432"/>
       <c r="K34" s="181"/>
     </row>
     <row r="35" spans="1:11" ht="36.75" customHeight="1">
       <c r="A35" s="206"/>
       <c r="B35" s="205"/>
-      <c r="C35" s="462"/>
-      <c r="D35" s="462"/>
-      <c r="E35" s="462"/>
-      <c r="F35" s="463"/>
-      <c r="G35" s="429" t="s">
+      <c r="C35" s="428"/>
+      <c r="D35" s="428"/>
+      <c r="E35" s="428"/>
+      <c r="F35" s="429"/>
+      <c r="G35" s="424" t="s">
         <v>307</v>
       </c>
-      <c r="H35" s="430"/>
-      <c r="I35" s="483"/>
-      <c r="J35" s="479"/>
+      <c r="H35" s="425"/>
+      <c r="I35" s="426"/>
+      <c r="J35" s="427"/>
       <c r="K35" s="207"/>
     </row>
     <row r="36" spans="1:11" ht="33" customHeight="1">
@@ -16179,35 +16118,35 @@
         <v>314</v>
       </c>
       <c r="B36" s="205"/>
-      <c r="C36" s="463" t="s">
+      <c r="C36" s="429" t="s">
         <v>315</v>
       </c>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
-      <c r="G36" s="435" t="b">
+      <c r="D36" s="429"/>
+      <c r="E36" s="429"/>
+      <c r="F36" s="429"/>
+      <c r="G36" s="447" t="b">
         <v>0</v>
       </c>
-      <c r="H36" s="434"/>
-      <c r="I36" s="499" t="b">
+      <c r="H36" s="432"/>
+      <c r="I36" s="448" t="b">
         <v>0</v>
       </c>
-      <c r="J36" s="499"/>
+      <c r="J36" s="448"/>
       <c r="K36" s="181"/>
     </row>
     <row r="37" spans="1:11" ht="34.5" customHeight="1">
       <c r="A37" s="206"/>
       <c r="B37" s="205"/>
-      <c r="C37" s="463"/>
-      <c r="D37" s="463"/>
-      <c r="E37" s="463"/>
-      <c r="F37" s="463"/>
-      <c r="G37" s="429" t="s">
+      <c r="C37" s="429"/>
+      <c r="D37" s="429"/>
+      <c r="E37" s="429"/>
+      <c r="F37" s="429"/>
+      <c r="G37" s="424" t="s">
         <v>307</v>
       </c>
-      <c r="H37" s="430"/>
-      <c r="I37" s="483"/>
-      <c r="J37" s="479"/>
+      <c r="H37" s="425"/>
+      <c r="I37" s="426"/>
+      <c r="J37" s="427"/>
       <c r="K37" s="207"/>
     </row>
     <row r="38" spans="1:11" ht="30.75" customHeight="1">
@@ -16215,55 +16154,55 @@
         <v>316</v>
       </c>
       <c r="B38" s="205"/>
-      <c r="C38" s="462" t="s">
+      <c r="C38" s="428" t="s">
         <v>317</v>
       </c>
-      <c r="D38" s="462"/>
+      <c r="D38" s="428"/>
       <c r="E38" s="208"/>
       <c r="F38" s="209"/>
-      <c r="G38" s="500" t="b">
+      <c r="G38" s="430" t="b">
         <v>0</v>
       </c>
-      <c r="H38" s="501"/>
-      <c r="I38" s="434" t="b">
+      <c r="H38" s="431"/>
+      <c r="I38" s="432" t="b">
         <v>0</v>
       </c>
-      <c r="J38" s="434"/>
+      <c r="J38" s="432"/>
       <c r="K38" s="181"/>
     </row>
     <row r="39" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A39" s="504"/>
-      <c r="B39" s="505"/>
-      <c r="C39" s="505"/>
-      <c r="D39" s="505"/>
-      <c r="E39" s="505"/>
-      <c r="F39" s="506"/>
-      <c r="G39" s="429" t="s">
+      <c r="A39" s="435"/>
+      <c r="B39" s="436"/>
+      <c r="C39" s="436"/>
+      <c r="D39" s="436"/>
+      <c r="E39" s="436"/>
+      <c r="F39" s="437"/>
+      <c r="G39" s="424" t="s">
         <v>307</v>
       </c>
-      <c r="H39" s="430"/>
-      <c r="I39" s="483"/>
-      <c r="J39" s="479"/>
+      <c r="H39" s="425"/>
+      <c r="I39" s="426"/>
+      <c r="J39" s="427"/>
       <c r="K39" s="207"/>
     </row>
     <row r="40" spans="1:11" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A40" s="507"/>
-      <c r="B40" s="508"/>
-      <c r="C40" s="508"/>
-      <c r="D40" s="508"/>
-      <c r="E40" s="508"/>
-      <c r="F40" s="509"/>
-      <c r="G40" s="510"/>
-      <c r="H40" s="511"/>
-      <c r="I40" s="511"/>
-      <c r="J40" s="511"/>
+      <c r="A40" s="438"/>
+      <c r="B40" s="439"/>
+      <c r="C40" s="439"/>
+      <c r="D40" s="439"/>
+      <c r="E40" s="439"/>
+      <c r="F40" s="440"/>
+      <c r="G40" s="441"/>
+      <c r="H40" s="442"/>
+      <c r="I40" s="442"/>
+      <c r="J40" s="442"/>
       <c r="K40" s="207"/>
     </row>
     <row r="41" spans="1:11" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A41" s="502">
+      <c r="A41" s="433">
         <v>41</v>
       </c>
-      <c r="B41" s="503"/>
+      <c r="B41" s="434"/>
       <c r="C41" s="210" t="s">
         <v>318</v>
       </c>
@@ -16277,146 +16216,146 @@
       <c r="K41" s="181"/>
     </row>
     <row r="42" spans="1:11" ht="18" customHeight="1">
-      <c r="A42" s="512" t="s">
+      <c r="A42" s="419" t="s">
         <v>319</v>
       </c>
-      <c r="B42" s="513"/>
-      <c r="C42" s="513"/>
-      <c r="D42" s="513"/>
-      <c r="E42" s="514"/>
-      <c r="F42" s="512" t="s">
+      <c r="B42" s="420"/>
+      <c r="C42" s="420"/>
+      <c r="D42" s="420"/>
+      <c r="E42" s="421"/>
+      <c r="F42" s="419" t="s">
         <v>320</v>
       </c>
-      <c r="G42" s="513"/>
-      <c r="H42" s="513"/>
-      <c r="I42" s="515" t="s">
+      <c r="G42" s="420"/>
+      <c r="H42" s="420"/>
+      <c r="I42" s="422" t="s">
         <v>321</v>
       </c>
-      <c r="J42" s="516"/>
+      <c r="J42" s="423"/>
       <c r="K42" s="181"/>
     </row>
     <row r="43" spans="1:11" ht="24" customHeight="1">
-      <c r="A43" s="421"/>
-      <c r="B43" s="421"/>
-      <c r="C43" s="421"/>
-      <c r="D43" s="421"/>
-      <c r="E43" s="421"/>
-      <c r="F43" s="421"/>
-      <c r="G43" s="421"/>
-      <c r="H43" s="421"/>
-      <c r="I43" s="422"/>
-      <c r="J43" s="422"/>
+      <c r="A43" s="417"/>
+      <c r="B43" s="417"/>
+      <c r="C43" s="417"/>
+      <c r="D43" s="417"/>
+      <c r="E43" s="417"/>
+      <c r="F43" s="417"/>
+      <c r="G43" s="417"/>
+      <c r="H43" s="417"/>
+      <c r="I43" s="418"/>
+      <c r="J43" s="418"/>
       <c r="K43" s="181"/>
     </row>
     <row r="44" spans="1:11" ht="24" customHeight="1">
-      <c r="A44" s="421"/>
-      <c r="B44" s="421"/>
-      <c r="C44" s="421"/>
-      <c r="D44" s="421"/>
-      <c r="E44" s="421"/>
-      <c r="F44" s="421"/>
-      <c r="G44" s="421"/>
-      <c r="H44" s="421"/>
-      <c r="I44" s="422"/>
-      <c r="J44" s="422"/>
+      <c r="A44" s="417"/>
+      <c r="B44" s="417"/>
+      <c r="C44" s="417"/>
+      <c r="D44" s="417"/>
+      <c r="E44" s="417"/>
+      <c r="F44" s="417"/>
+      <c r="G44" s="417"/>
+      <c r="H44" s="417"/>
+      <c r="I44" s="418"/>
+      <c r="J44" s="418"/>
       <c r="K44" s="181"/>
     </row>
     <row r="45" spans="1:11" ht="24" customHeight="1">
-      <c r="A45" s="421"/>
-      <c r="B45" s="421"/>
-      <c r="C45" s="421"/>
-      <c r="D45" s="421"/>
-      <c r="E45" s="421"/>
-      <c r="F45" s="421"/>
-      <c r="G45" s="421"/>
-      <c r="H45" s="421"/>
-      <c r="I45" s="422"/>
-      <c r="J45" s="422"/>
+      <c r="A45" s="417"/>
+      <c r="B45" s="417"/>
+      <c r="C45" s="417"/>
+      <c r="D45" s="417"/>
+      <c r="E45" s="417"/>
+      <c r="F45" s="417"/>
+      <c r="G45" s="417"/>
+      <c r="H45" s="417"/>
+      <c r="I45" s="418"/>
+      <c r="J45" s="418"/>
       <c r="K45" s="181"/>
     </row>
     <row r="46" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A46" s="421"/>
-      <c r="B46" s="421"/>
-      <c r="C46" s="421"/>
-      <c r="D46" s="421"/>
-      <c r="E46" s="421"/>
-      <c r="F46" s="421"/>
-      <c r="G46" s="421"/>
-      <c r="H46" s="421"/>
-      <c r="I46" s="422"/>
-      <c r="J46" s="422"/>
+      <c r="A46" s="417"/>
+      <c r="B46" s="417"/>
+      <c r="C46" s="417"/>
+      <c r="D46" s="417"/>
+      <c r="E46" s="417"/>
+      <c r="F46" s="417"/>
+      <c r="G46" s="417"/>
+      <c r="H46" s="417"/>
+      <c r="I46" s="418"/>
+      <c r="J46" s="418"/>
     </row>
     <row r="47" spans="1:11" ht="24.75" customHeight="1">
-      <c r="A47" s="421"/>
-      <c r="B47" s="421"/>
-      <c r="C47" s="421"/>
-      <c r="D47" s="421"/>
-      <c r="E47" s="421"/>
-      <c r="F47" s="421"/>
-      <c r="G47" s="421"/>
-      <c r="H47" s="421"/>
-      <c r="I47" s="422"/>
-      <c r="J47" s="422"/>
+      <c r="A47" s="417"/>
+      <c r="B47" s="417"/>
+      <c r="C47" s="417"/>
+      <c r="D47" s="417"/>
+      <c r="E47" s="417"/>
+      <c r="F47" s="417"/>
+      <c r="G47" s="417"/>
+      <c r="H47" s="417"/>
+      <c r="I47" s="418"/>
+      <c r="J47" s="418"/>
     </row>
     <row r="48" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A48" s="421"/>
-      <c r="B48" s="421"/>
-      <c r="C48" s="421"/>
-      <c r="D48" s="421"/>
-      <c r="E48" s="421"/>
-      <c r="F48" s="421"/>
-      <c r="G48" s="421"/>
-      <c r="H48" s="421"/>
-      <c r="I48" s="422"/>
-      <c r="J48" s="422"/>
+      <c r="A48" s="417"/>
+      <c r="B48" s="417"/>
+      <c r="C48" s="417"/>
+      <c r="D48" s="417"/>
+      <c r="E48" s="417"/>
+      <c r="F48" s="417"/>
+      <c r="G48" s="417"/>
+      <c r="H48" s="417"/>
+      <c r="I48" s="418"/>
+      <c r="J48" s="418"/>
     </row>
     <row r="49" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A49" s="421"/>
-      <c r="B49" s="421"/>
-      <c r="C49" s="421"/>
-      <c r="D49" s="421"/>
-      <c r="E49" s="421"/>
-      <c r="F49" s="421"/>
-      <c r="G49" s="421"/>
-      <c r="H49" s="421"/>
-      <c r="I49" s="422"/>
-      <c r="J49" s="422"/>
+      <c r="A49" s="417"/>
+      <c r="B49" s="417"/>
+      <c r="C49" s="417"/>
+      <c r="D49" s="417"/>
+      <c r="E49" s="417"/>
+      <c r="F49" s="417"/>
+      <c r="G49" s="417"/>
+      <c r="H49" s="417"/>
+      <c r="I49" s="418"/>
+      <c r="J49" s="418"/>
     </row>
     <row r="50" spans="1:10" ht="21" customHeight="1">
-      <c r="A50" s="421"/>
-      <c r="B50" s="421"/>
-      <c r="C50" s="421"/>
-      <c r="D50" s="421"/>
-      <c r="E50" s="421"/>
-      <c r="F50" s="421"/>
-      <c r="G50" s="421"/>
-      <c r="H50" s="421"/>
-      <c r="I50" s="422"/>
-      <c r="J50" s="422"/>
+      <c r="A50" s="417"/>
+      <c r="B50" s="417"/>
+      <c r="C50" s="417"/>
+      <c r="D50" s="417"/>
+      <c r="E50" s="417"/>
+      <c r="F50" s="417"/>
+      <c r="G50" s="417"/>
+      <c r="H50" s="417"/>
+      <c r="I50" s="418"/>
+      <c r="J50" s="418"/>
     </row>
     <row r="51" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A51" s="421"/>
-      <c r="B51" s="421"/>
-      <c r="C51" s="421"/>
-      <c r="D51" s="421"/>
-      <c r="E51" s="421"/>
-      <c r="F51" s="421"/>
-      <c r="G51" s="421"/>
-      <c r="H51" s="421"/>
-      <c r="I51" s="422"/>
-      <c r="J51" s="422"/>
+      <c r="A51" s="417"/>
+      <c r="B51" s="417"/>
+      <c r="C51" s="417"/>
+      <c r="D51" s="417"/>
+      <c r="E51" s="417"/>
+      <c r="F51" s="417"/>
+      <c r="G51" s="417"/>
+      <c r="H51" s="417"/>
+      <c r="I51" s="418"/>
+      <c r="J51" s="418"/>
     </row>
     <row r="52" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A52" s="421"/>
-      <c r="B52" s="421"/>
-      <c r="C52" s="421"/>
-      <c r="D52" s="421"/>
-      <c r="E52" s="421"/>
-      <c r="F52" s="421"/>
-      <c r="G52" s="421"/>
-      <c r="H52" s="421"/>
-      <c r="I52" s="422"/>
-      <c r="J52" s="422"/>
+      <c r="A52" s="417"/>
+      <c r="B52" s="417"/>
+      <c r="C52" s="417"/>
+      <c r="D52" s="417"/>
+      <c r="E52" s="417"/>
+      <c r="F52" s="417"/>
+      <c r="G52" s="417"/>
+      <c r="H52" s="417"/>
+      <c r="I52" s="418"/>
+      <c r="J52" s="418"/>
     </row>
     <row r="53" spans="1:10" ht="9" customHeight="1"/>
     <row r="54" spans="1:10" ht="12" customHeight="1"/>
@@ -16431,51 +16370,57 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="pO7kRHJ2iPqPcZnI3aAaPN8FWn7ShmqQspkUSBiEWlhMz2IYlb2TtMzEa6lNKkrpoouNdSgx63KCE43+up6wVQ==" saltValue="5fqhLEo0sF6DU83eWXcREA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="120">
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C36:F37"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A39:F40"/>
-    <mergeCell ref="G40:J40"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="C27:F29"/>
-    <mergeCell ref="C30:F32"/>
-    <mergeCell ref="G26:H27"/>
-    <mergeCell ref="I26:J27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="C24:F25"/>
+    <mergeCell ref="C21:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="G11:J11"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:F2"/>
@@ -16500,57 +16445,51 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="C24:F25"/>
-    <mergeCell ref="C21:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="C27:F29"/>
+    <mergeCell ref="C30:F32"/>
+    <mergeCell ref="G26:H27"/>
+    <mergeCell ref="I26:J27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C36:F37"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A39:F40"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="I44:J44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -17109,17 +17048,17 @@
       <c r="A1" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="338" t="s">
+      <c r="B1" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
-      <c r="H1" s="338"/>
-      <c r="I1" s="338"/>
-      <c r="J1" s="338"/>
+      <c r="C1" s="351"/>
+      <c r="D1" s="351"/>
+      <c r="E1" s="351"/>
+      <c r="F1" s="351"/>
+      <c r="G1" s="351"/>
+      <c r="H1" s="351"/>
+      <c r="I1" s="351"/>
+      <c r="J1" s="351"/>
     </row>
     <row r="2" spans="1:10" ht="21" customHeight="1">
       <c r="A2" s="95">
@@ -17129,13 +17068,13 @@
         <v>251</v>
       </c>
       <c r="C2" s="97"/>
-      <c r="D2" s="339"/>
-      <c r="E2" s="340"/>
-      <c r="F2" s="340"/>
-      <c r="G2" s="340"/>
-      <c r="H2" s="340"/>
-      <c r="I2" s="340"/>
-      <c r="J2" s="341"/>
+      <c r="D2" s="352"/>
+      <c r="E2" s="353"/>
+      <c r="F2" s="353"/>
+      <c r="G2" s="353"/>
+      <c r="H2" s="353"/>
+      <c r="I2" s="353"/>
+      <c r="J2" s="354"/>
     </row>
     <row r="3" spans="1:10" ht="21" customHeight="1">
       <c r="A3" s="98"/>
@@ -17143,15 +17082,15 @@
         <v>12</v>
       </c>
       <c r="C3" s="86"/>
-      <c r="D3" s="342"/>
-      <c r="E3" s="343"/>
-      <c r="F3" s="344"/>
-      <c r="G3" s="345" t="s">
+      <c r="D3" s="345"/>
+      <c r="E3" s="346"/>
+      <c r="F3" s="355"/>
+      <c r="G3" s="356" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="346"/>
-      <c r="I3" s="347"/>
-      <c r="J3" s="348"/>
+      <c r="H3" s="357"/>
+      <c r="I3" s="358"/>
+      <c r="J3" s="341"/>
     </row>
     <row r="4" spans="1:10" ht="21" customHeight="1">
       <c r="A4" s="98"/>
@@ -17159,13 +17098,13 @@
         <v>16</v>
       </c>
       <c r="C4" s="101"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="343"/>
-      <c r="F4" s="343"/>
-      <c r="G4" s="343"/>
-      <c r="H4" s="343"/>
-      <c r="I4" s="343"/>
-      <c r="J4" s="349"/>
+      <c r="D4" s="345"/>
+      <c r="E4" s="346"/>
+      <c r="F4" s="346"/>
+      <c r="G4" s="346"/>
+      <c r="H4" s="346"/>
+      <c r="I4" s="346"/>
+      <c r="J4" s="347"/>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1">
       <c r="A5" s="102"/>
@@ -17173,13 +17112,13 @@
         <v>252</v>
       </c>
       <c r="C5" s="69"/>
-      <c r="D5" s="350"/>
-      <c r="E5" s="351"/>
-      <c r="F5" s="351"/>
-      <c r="G5" s="351"/>
-      <c r="H5" s="351"/>
-      <c r="I5" s="351"/>
-      <c r="J5" s="352"/>
+      <c r="D5" s="334"/>
+      <c r="E5" s="335"/>
+      <c r="F5" s="335"/>
+      <c r="G5" s="335"/>
+      <c r="H5" s="335"/>
+      <c r="I5" s="335"/>
+      <c r="J5" s="336"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="102"/>
@@ -17187,13 +17126,13 @@
         <v>253</v>
       </c>
       <c r="C6" s="69"/>
-      <c r="D6" s="350"/>
-      <c r="E6" s="351"/>
-      <c r="F6" s="351"/>
-      <c r="G6" s="351"/>
-      <c r="H6" s="351"/>
-      <c r="I6" s="351"/>
-      <c r="J6" s="352"/>
+      <c r="D6" s="334"/>
+      <c r="E6" s="335"/>
+      <c r="F6" s="335"/>
+      <c r="G6" s="335"/>
+      <c r="H6" s="335"/>
+      <c r="I6" s="335"/>
+      <c r="J6" s="336"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="102"/>
@@ -17201,13 +17140,13 @@
         <v>254</v>
       </c>
       <c r="C7" s="69"/>
-      <c r="D7" s="353"/>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
-      <c r="G7" s="354"/>
-      <c r="H7" s="354"/>
-      <c r="I7" s="354"/>
-      <c r="J7" s="355"/>
+      <c r="D7" s="348"/>
+      <c r="E7" s="349"/>
+      <c r="F7" s="349"/>
+      <c r="G7" s="349"/>
+      <c r="H7" s="349"/>
+      <c r="I7" s="349"/>
+      <c r="J7" s="350"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="102"/>
@@ -17215,13 +17154,13 @@
         <v>255</v>
       </c>
       <c r="C8" s="105"/>
-      <c r="D8" s="353"/>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
-      <c r="G8" s="354"/>
-      <c r="H8" s="354"/>
-      <c r="I8" s="354"/>
-      <c r="J8" s="355"/>
+      <c r="D8" s="348"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
+      <c r="G8" s="349"/>
+      <c r="H8" s="349"/>
+      <c r="I8" s="349"/>
+      <c r="J8" s="350"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="106">
@@ -17231,13 +17170,13 @@
         <v>256</v>
       </c>
       <c r="C9" s="107"/>
-      <c r="D9" s="350"/>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
-      <c r="G9" s="351"/>
-      <c r="H9" s="351"/>
-      <c r="I9" s="351"/>
-      <c r="J9" s="352"/>
+      <c r="D9" s="334"/>
+      <c r="E9" s="335"/>
+      <c r="F9" s="335"/>
+      <c r="G9" s="335"/>
+      <c r="H9" s="335"/>
+      <c r="I9" s="335"/>
+      <c r="J9" s="336"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="98"/>
@@ -17245,15 +17184,15 @@
         <v>12</v>
       </c>
       <c r="C10" s="59"/>
-      <c r="D10" s="350"/>
-      <c r="E10" s="351"/>
-      <c r="F10" s="356"/>
-      <c r="G10" s="357" t="s">
+      <c r="D10" s="334"/>
+      <c r="E10" s="335"/>
+      <c r="F10" s="337"/>
+      <c r="G10" s="338" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="358"/>
-      <c r="I10" s="359"/>
-      <c r="J10" s="348"/>
+      <c r="H10" s="339"/>
+      <c r="I10" s="340"/>
+      <c r="J10" s="341"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="98"/>
@@ -17261,29 +17200,29 @@
         <v>16</v>
       </c>
       <c r="C11" s="82"/>
-      <c r="D11" s="360"/>
-      <c r="E11" s="351"/>
-      <c r="F11" s="351"/>
-      <c r="G11" s="351"/>
-      <c r="H11" s="351"/>
-      <c r="I11" s="351"/>
-      <c r="J11" s="352"/>
+      <c r="D11" s="342"/>
+      <c r="E11" s="335"/>
+      <c r="F11" s="335"/>
+      <c r="G11" s="335"/>
+      <c r="H11" s="335"/>
+      <c r="I11" s="335"/>
+      <c r="J11" s="336"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="110">
         <v>25</v>
       </c>
-      <c r="B12" s="361" t="s">
+      <c r="B12" s="343" t="s">
         <v>257</v>
       </c>
-      <c r="C12" s="361"/>
-      <c r="D12" s="361"/>
-      <c r="E12" s="361"/>
-      <c r="F12" s="361"/>
-      <c r="G12" s="361"/>
-      <c r="H12" s="361"/>
-      <c r="I12" s="361"/>
-      <c r="J12" s="362"/>
+      <c r="C12" s="343"/>
+      <c r="D12" s="343"/>
+      <c r="E12" s="343"/>
+      <c r="F12" s="343"/>
+      <c r="G12" s="343"/>
+      <c r="H12" s="343"/>
+      <c r="I12" s="343"/>
+      <c r="J12" s="344"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="98"/>
@@ -17291,13 +17230,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="59"/>
-      <c r="D13" s="350"/>
-      <c r="E13" s="351"/>
-      <c r="F13" s="351"/>
-      <c r="G13" s="351"/>
-      <c r="H13" s="351"/>
-      <c r="I13" s="351"/>
-      <c r="J13" s="352"/>
+      <c r="D13" s="334"/>
+      <c r="E13" s="335"/>
+      <c r="F13" s="335"/>
+      <c r="G13" s="335"/>
+      <c r="H13" s="335"/>
+      <c r="I13" s="335"/>
+      <c r="J13" s="336"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="98"/>
@@ -17305,13 +17244,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="59"/>
-      <c r="D14" s="350"/>
-      <c r="E14" s="351"/>
-      <c r="F14" s="351"/>
-      <c r="G14" s="351"/>
-      <c r="H14" s="351"/>
-      <c r="I14" s="351"/>
-      <c r="J14" s="352"/>
+      <c r="D14" s="334"/>
+      <c r="E14" s="335"/>
+      <c r="F14" s="335"/>
+      <c r="G14" s="335"/>
+      <c r="H14" s="335"/>
+      <c r="I14" s="335"/>
+      <c r="J14" s="336"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1" thickBot="1">
       <c r="A15" s="111"/>
@@ -17319,17 +17258,27 @@
         <v>16</v>
       </c>
       <c r="C15" s="63"/>
-      <c r="D15" s="350"/>
-      <c r="E15" s="351"/>
-      <c r="F15" s="351"/>
-      <c r="G15" s="351"/>
-      <c r="H15" s="351"/>
-      <c r="I15" s="351"/>
-      <c r="J15" s="352"/>
+      <c r="D15" s="334"/>
+      <c r="E15" s="335"/>
+      <c r="F15" s="335"/>
+      <c r="G15" s="335"/>
+      <c r="H15" s="335"/>
+      <c r="I15" s="335"/>
+      <c r="J15" s="336"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="AlSiBTM1dRhXo9ORvo/dRyVY3Jlgq0tY8I1Lt7Z1RfI7T5btNF7ArQMjcgXOFy3gstkxkeBRdVuavcsER8i7fQ==" saltValue="im7eNRRObcswndBJ71jiCQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D14:J14"/>
     <mergeCell ref="D15:J15"/>
@@ -17339,16 +17288,6 @@
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="D11:J11"/>
     <mergeCell ref="B12:J12"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17375,7 +17314,7 @@
         <v>259</v>
       </c>
       <c r="B2" s="117" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -17499,38 +17438,38 @@
       <c r="F1" s="135"/>
       <c r="G1" s="136"/>
       <c r="H1" s="134"/>
-      <c r="I1" s="363" t="s">
+      <c r="I1" s="359" t="s">
         <v>261</v>
       </c>
-      <c r="J1" s="363"/>
-      <c r="K1" s="363"/>
-      <c r="L1" s="363"/>
-      <c r="M1" s="363"/>
-      <c r="N1" s="363"/>
+      <c r="J1" s="359"/>
+      <c r="K1" s="359"/>
+      <c r="L1" s="359"/>
+      <c r="M1" s="359"/>
+      <c r="N1" s="359"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1">
       <c r="A2" s="122" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B2" s="123"/>
       <c r="C2" s="123"/>
-      <c r="D2" s="370" t="s">
+      <c r="D2" s="366" t="s">
         <v>262</v>
       </c>
-      <c r="E2" s="371"/>
-      <c r="F2" s="364" t="s">
+      <c r="E2" s="367"/>
+      <c r="F2" s="360" t="s">
         <v>263</v>
       </c>
-      <c r="G2" s="364" t="s">
-        <v>328</v>
-      </c>
-      <c r="H2" s="367" t="s">
+      <c r="G2" s="360" t="s">
+        <v>327</v>
+      </c>
+      <c r="H2" s="363" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1">
       <c r="A3" s="124" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B3" s="125" t="s">
         <v>265</v>
@@ -17538,11 +17477,11 @@
       <c r="C3" s="125" t="s">
         <v>266</v>
       </c>
-      <c r="D3" s="372"/>
-      <c r="E3" s="373"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="368"/>
+      <c r="D3" s="368"/>
+      <c r="E3" s="369"/>
+      <c r="F3" s="361"/>
+      <c r="G3" s="361"/>
+      <c r="H3" s="364"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1">
       <c r="A4" s="126"/>
@@ -17554,9 +17493,9 @@
       <c r="E4" s="130" t="s">
         <v>268</v>
       </c>
-      <c r="F4" s="366"/>
-      <c r="G4" s="366"/>
-      <c r="H4" s="369"/>
+      <c r="F4" s="362"/>
+      <c r="G4" s="362"/>
+      <c r="H4" s="365"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="137"/>
@@ -17733,13 +17672,13 @@
       <c r="D1" s="148"/>
       <c r="E1" s="148"/>
       <c r="F1" s="148"/>
-      <c r="G1" s="376"/>
-      <c r="H1" s="376"/>
-      <c r="I1" s="376"/>
-      <c r="J1" s="376"/>
-      <c r="K1" s="376"/>
-      <c r="L1" s="376"/>
-      <c r="M1" s="376"/>
+      <c r="G1" s="372"/>
+      <c r="H1" s="372"/>
+      <c r="I1" s="372"/>
+      <c r="J1" s="372"/>
+      <c r="K1" s="372"/>
+      <c r="L1" s="372"/>
+      <c r="M1" s="372"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1">
       <c r="A2" s="149"/>
@@ -17752,21 +17691,21 @@
     </row>
     <row r="3" spans="1:14" s="157" customFormat="1" ht="39.75" customHeight="1">
       <c r="A3" s="154" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B3" s="155" t="s">
         <v>270</v>
       </c>
       <c r="C3" s="154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D3" s="156" t="s">
         <v>271</v>
       </c>
-      <c r="E3" s="374" t="s">
+      <c r="E3" s="370" t="s">
         <v>272</v>
       </c>
-      <c r="F3" s="375"/>
+      <c r="F3" s="371"/>
       <c r="N3" s="118"/>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1">
@@ -17778,7 +17717,7 @@
         <v>273</v>
       </c>
       <c r="F4" s="162" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -18758,63 +18697,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A1" s="377" t="s">
+      <c r="A1" s="373" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="378"/>
-      <c r="C1" s="378"/>
-      <c r="D1" s="378"/>
-      <c r="E1" s="378"/>
-      <c r="F1" s="378"/>
-      <c r="G1" s="378"/>
-      <c r="H1" s="379"/>
+      <c r="B1" s="374"/>
+      <c r="C1" s="374"/>
+      <c r="D1" s="374"/>
+      <c r="E1" s="374"/>
+      <c r="F1" s="374"/>
+      <c r="G1" s="374"/>
+      <c r="H1" s="375"/>
     </row>
     <row r="2" spans="1:14" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A2" s="380" t="s">
+      <c r="A2" s="376" t="s">
         <v>275</v>
       </c>
-      <c r="B2" s="381"/>
-      <c r="C2" s="381"/>
-      <c r="D2" s="381"/>
-      <c r="E2" s="381"/>
-      <c r="F2" s="381"/>
-      <c r="G2" s="381"/>
-      <c r="H2" s="382"/>
+      <c r="B2" s="377"/>
+      <c r="C2" s="377"/>
+      <c r="D2" s="377"/>
+      <c r="E2" s="377"/>
+      <c r="F2" s="377"/>
+      <c r="G2" s="377"/>
+      <c r="H2" s="378"/>
     </row>
     <row r="3" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A3" s="392" t="s">
-        <v>331</v>
-      </c>
-      <c r="B3" s="393"/>
-      <c r="C3" s="383" t="s">
+      <c r="A3" s="388" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="389"/>
+      <c r="C3" s="379" t="s">
         <v>276</v>
       </c>
-      <c r="D3" s="386" t="s">
+      <c r="D3" s="382" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="386" t="s">
+      <c r="E3" s="382" t="s">
         <v>278</v>
       </c>
-      <c r="F3" s="386" t="s">
+      <c r="F3" s="382" t="s">
         <v>279</v>
       </c>
-      <c r="G3" s="364" t="s">
+      <c r="G3" s="360" t="s">
         <v>280</v>
       </c>
-      <c r="H3" s="389" t="s">
-        <v>327</v>
+      <c r="H3" s="385" t="s">
+        <v>326</v>
       </c>
       <c r="N3" s="167"/>
     </row>
     <row r="4" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A4" s="394"/>
-      <c r="B4" s="395"/>
-      <c r="C4" s="384"/>
-      <c r="D4" s="387"/>
-      <c r="E4" s="387"/>
-      <c r="F4" s="387"/>
-      <c r="G4" s="365"/>
-      <c r="H4" s="390"/>
+      <c r="A4" s="390"/>
+      <c r="B4" s="391"/>
+      <c r="C4" s="380"/>
+      <c r="D4" s="383"/>
+      <c r="E4" s="383"/>
+      <c r="F4" s="383"/>
+      <c r="G4" s="361"/>
+      <c r="H4" s="386"/>
       <c r="N4" s="167"/>
     </row>
     <row r="5" spans="1:14" ht="30.75" customHeight="1">
@@ -18824,12 +18763,12 @@
       <c r="B5" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="C5" s="385"/>
-      <c r="D5" s="388"/>
-      <c r="E5" s="388"/>
-      <c r="F5" s="388"/>
-      <c r="G5" s="366"/>
-      <c r="H5" s="391"/>
+      <c r="C5" s="381"/>
+      <c r="D5" s="384"/>
+      <c r="E5" s="384"/>
+      <c r="F5" s="384"/>
+      <c r="G5" s="362"/>
+      <c r="H5" s="387"/>
       <c r="N5" s="167"/>
     </row>
     <row r="6" spans="1:14">
@@ -19141,17 +19080,17 @@
       <c r="Q1" s="157"/>
     </row>
     <row r="2" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A2" s="396" t="s">
+      <c r="A2" s="392" t="s">
         <v>282</v>
       </c>
-      <c r="B2" s="383" t="s">
-        <v>332</v>
-      </c>
-      <c r="C2" s="402"/>
-      <c r="D2" s="386" t="s">
+      <c r="B2" s="379" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2" s="398"/>
+      <c r="D2" s="382" t="s">
         <v>283</v>
       </c>
-      <c r="E2" s="399" t="s">
+      <c r="E2" s="395" t="s">
         <v>284</v>
       </c>
       <c r="F2" s="173"/>
@@ -19168,11 +19107,11 @@
       <c r="Q2" s="157"/>
     </row>
     <row r="3" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A3" s="397"/>
-      <c r="B3" s="384"/>
-      <c r="C3" s="403"/>
-      <c r="D3" s="387"/>
-      <c r="E3" s="400"/>
+      <c r="A3" s="393"/>
+      <c r="B3" s="380"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="383"/>
+      <c r="E3" s="396"/>
       <c r="F3" s="173"/>
       <c r="G3" s="157"/>
       <c r="H3" s="157"/>
@@ -19187,15 +19126,15 @@
       <c r="Q3" s="157"/>
     </row>
     <row r="4" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A4" s="398"/>
+      <c r="A4" s="394"/>
       <c r="B4" s="161" t="s">
         <v>267</v>
       </c>
       <c r="C4" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="388"/>
-      <c r="E4" s="401"/>
+      <c r="D4" s="384"/>
+      <c r="E4" s="397"/>
       <c r="F4" s="173"/>
       <c r="G4" s="157"/>
       <c r="H4" s="157"/>
@@ -19684,62 +19623,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A1" s="404" t="s">
+      <c r="A1" s="400" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="405"/>
-      <c r="C1" s="405"/>
-      <c r="D1" s="405"/>
-      <c r="E1" s="405"/>
-      <c r="F1" s="406"/>
+      <c r="B1" s="401"/>
+      <c r="C1" s="401"/>
+      <c r="D1" s="401"/>
+      <c r="E1" s="401"/>
+      <c r="F1" s="402"/>
     </row>
     <row r="2" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A2" s="407" t="s">
+      <c r="A2" s="403" t="s">
         <v>286</v>
       </c>
-      <c r="B2" s="408"/>
-      <c r="C2" s="408"/>
-      <c r="D2" s="408"/>
-      <c r="E2" s="408"/>
-      <c r="F2" s="409"/>
+      <c r="B2" s="404"/>
+      <c r="C2" s="404"/>
+      <c r="D2" s="404"/>
+      <c r="E2" s="404"/>
+      <c r="F2" s="405"/>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A3" s="410" t="s">
+      <c r="A3" s="406" t="s">
         <v>287</v>
       </c>
-      <c r="B3" s="415" t="s">
-        <v>333</v>
-      </c>
-      <c r="C3" s="416"/>
-      <c r="D3" s="412" t="s">
+      <c r="B3" s="411" t="s">
+        <v>332</v>
+      </c>
+      <c r="C3" s="412"/>
+      <c r="D3" s="408" t="s">
         <v>283</v>
       </c>
-      <c r="E3" s="387" t="s">
+      <c r="E3" s="383" t="s">
         <v>288</v>
       </c>
-      <c r="F3" s="414" t="s">
+      <c r="F3" s="410" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A4" s="411"/>
-      <c r="B4" s="384"/>
-      <c r="C4" s="417"/>
-      <c r="D4" s="412"/>
-      <c r="E4" s="387"/>
-      <c r="F4" s="400"/>
+      <c r="A4" s="407"/>
+      <c r="B4" s="380"/>
+      <c r="C4" s="413"/>
+      <c r="D4" s="408"/>
+      <c r="E4" s="383"/>
+      <c r="F4" s="396"/>
     </row>
     <row r="5" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A5" s="394"/>
+      <c r="A5" s="390"/>
       <c r="B5" s="161" t="s">
         <v>267</v>
       </c>
       <c r="C5" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="413"/>
-      <c r="E5" s="388"/>
-      <c r="F5" s="401"/>
+      <c r="D5" s="409"/>
+      <c r="E5" s="384"/>
+      <c r="F5" s="397"/>
     </row>
     <row r="6" spans="1:8" ht="18.75" customHeight="1">
       <c r="A6" s="176"/>
@@ -19941,11 +19880,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A1" s="418" t="s">
+      <c r="A1" s="414" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="419"/>
-      <c r="C1" s="420"/>
+      <c r="B1" s="415"/>
+      <c r="C1" s="416"/>
     </row>
     <row r="2" spans="1:13" ht="38.25" customHeight="1">
       <c r="A2" s="178" t="s">

--- a/public/pds.xlsx
+++ b/public/pds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cenro\PMS-intern\rsp-hr-tagum-cityhall\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDF96B4-E011-4EA7-9329-A31EC9CEACE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D5EEFF-FECB-4AA3-B426-EC2F25DEE780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3745,7 +3745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="513">
+  <cellXfs count="508">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -4289,6 +4289,453 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="34" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="28" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4322,29 +4769,6 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4358,10 +4782,6 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4370,341 +4790,78 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="50" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4721,14 +4878,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -4743,68 +4892,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -4977,117 +5064,361 @@
     <xf numFmtId="49" fontId="52" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -5095,94 +5426,6 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -5191,271 +5434,17 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5596,15 +5585,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$J$37" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$K$37" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$L$37" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5612,19 +5601,19 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$M$37" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$N$37" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$O$37" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$37" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10011,15 +10000,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>46892</xdr:colOff>
+          <xdr:colOff>47626</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>125291</xdr:rowOff>
+          <xdr:rowOff>101844</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>1304191</xdr:colOff>
+          <xdr:colOff>1304926</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>306266</xdr:rowOff>
+          <xdr:rowOff>282819</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10029,7 +10018,7 @@
                   <a14:compatExt spid="_x0000_s8229"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{877A183D-C7E5-4755-B9F5-98AC516E9CDB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000025200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10098,15 +10087,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>35903</xdr:colOff>
+          <xdr:colOff>60080</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>134082</xdr:rowOff>
+          <xdr:rowOff>96716</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>1926981</xdr:colOff>
+          <xdr:colOff>1946030</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>315057</xdr:rowOff>
+          <xdr:rowOff>277691</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10116,7 +10105,7 @@
                   <a14:compatExt spid="_x0000_s8230"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1C06AC6-81B5-2886-D48E-091F1536A5A6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000026200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10184,16 +10173,16 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>1962883</xdr:colOff>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>20514</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>120895</xdr:rowOff>
+          <xdr:rowOff>101844</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>1047749</xdr:colOff>
+          <xdr:colOff>1084384</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>299672</xdr:rowOff>
+          <xdr:rowOff>273294</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10203,7 +10192,7 @@
                   <a14:compatExt spid="_x0000_s8231"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{179F85BE-4337-4794-09E0-D8C630AA8EB4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000027200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10271,16 +10260,16 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>1096841</xdr:colOff>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>32972</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>112101</xdr:rowOff>
+          <xdr:rowOff>99646</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>1003789</xdr:colOff>
+          <xdr:colOff>1044087</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>293076</xdr:rowOff>
+          <xdr:rowOff>280621</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10290,7 +10279,7 @@
                   <a14:compatExt spid="_x0000_s8232"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2ED2173-5E50-E791-98A2-CBE4BD8778A2}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000028200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10359,15 +10348,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>8793</xdr:colOff>
+          <xdr:colOff>16851</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>118695</xdr:rowOff>
+          <xdr:rowOff>106973</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>1003789</xdr:colOff>
+          <xdr:colOff>1007451</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>303334</xdr:rowOff>
+          <xdr:rowOff>297473</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10377,7 +10366,7 @@
                   <a14:compatExt spid="_x0000_s8233"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF906BA-A8B6-B0EB-CD48-5D49E2B03DE0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000029200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10446,15 +10435,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>13</xdr:col>
-          <xdr:colOff>1466</xdr:colOff>
+          <xdr:colOff>29308</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>113567</xdr:rowOff>
+          <xdr:rowOff>106973</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>13</xdr:col>
-          <xdr:colOff>1160585</xdr:colOff>
+          <xdr:colOff>1191358</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>304067</xdr:rowOff>
+          <xdr:rowOff>297473</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10464,7 +10453,7 @@
                   <a14:compatExt spid="_x0000_s8234"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F9906E9-C46F-55F3-9A77-B3DB84DF4000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-00002A200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10533,15 +10522,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>16853</xdr:colOff>
+          <xdr:colOff>19050</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>126023</xdr:rowOff>
+          <xdr:rowOff>94517</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>1355481</xdr:colOff>
+          <xdr:colOff>1352550</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>306998</xdr:rowOff>
+          <xdr:rowOff>275492</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10551,7 +10540,7 @@
                   <a14:compatExt spid="_x0000_s8235"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F30C2D7-4E9B-A78E-9153-8F82BD8CAC72}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-00002B200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10901,20 +10890,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
-      <c r="A1" s="246"/>
-      <c r="B1" s="247"/>
-      <c r="C1" s="247"/>
-      <c r="D1" s="247"/>
-      <c r="E1" s="247"/>
-      <c r="F1" s="247"/>
-      <c r="G1" s="247"/>
-      <c r="H1" s="247"/>
-      <c r="I1" s="247"/>
-      <c r="J1" s="247"/>
-      <c r="K1" s="247"/>
-      <c r="L1" s="247"/>
-      <c r="M1" s="247"/>
-      <c r="N1" s="248"/>
+      <c r="A1" s="226"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="228"/>
     </row>
     <row r="2" spans="1:22" ht="11.25" customHeight="1">
       <c r="A2" s="40"/>
@@ -10944,73 +10933,73 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="41.25" customHeight="1">
-      <c r="A3" s="249" t="s">
+      <c r="A3" s="229" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="250"/>
-      <c r="C3" s="250"/>
-      <c r="D3" s="250"/>
-      <c r="E3" s="250"/>
-      <c r="F3" s="250"/>
-      <c r="G3" s="250"/>
-      <c r="H3" s="250"/>
-      <c r="I3" s="250"/>
-      <c r="J3" s="250"/>
-      <c r="K3" s="250"/>
-      <c r="L3" s="250"/>
-      <c r="M3" s="250"/>
-      <c r="N3" s="251"/>
-      <c r="R3" s="191"/>
-      <c r="S3" s="192"/>
-      <c r="T3" s="192"/>
-      <c r="U3" s="192"/>
-      <c r="V3" s="193"/>
+      <c r="B3" s="230"/>
+      <c r="C3" s="230"/>
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="230"/>
+      <c r="H3" s="230"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="M3" s="230"/>
+      <c r="N3" s="231"/>
+      <c r="R3" s="271"/>
+      <c r="S3" s="272"/>
+      <c r="T3" s="272"/>
+      <c r="U3" s="272"/>
+      <c r="V3" s="273"/>
     </row>
     <row r="4" spans="1:22" ht="21.75" customHeight="1">
-      <c r="A4" s="252" t="s">
+      <c r="A4" s="232" t="s">
         <v>340</v>
       </c>
-      <c r="B4" s="253"/>
-      <c r="C4" s="253"/>
-      <c r="D4" s="253"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="253"/>
-      <c r="G4" s="253"/>
-      <c r="H4" s="253"/>
-      <c r="I4" s="253"/>
-      <c r="J4" s="253"/>
-      <c r="K4" s="253"/>
-      <c r="L4" s="253"/>
-      <c r="M4" s="253"/>
-      <c r="N4" s="254"/>
-      <c r="R4" s="194"/>
-      <c r="S4" s="195"/>
-      <c r="T4" s="195"/>
-      <c r="U4" s="195"/>
-      <c r="V4" s="196"/>
+      <c r="B4" s="233"/>
+      <c r="C4" s="233"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
+      <c r="M4" s="233"/>
+      <c r="N4" s="234"/>
+      <c r="R4" s="274"/>
+      <c r="S4" s="275"/>
+      <c r="T4" s="275"/>
+      <c r="U4" s="275"/>
+      <c r="V4" s="276"/>
     </row>
     <row r="5" spans="1:22" ht="11.25" customHeight="1">
-      <c r="A5" s="255" t="s">
+      <c r="A5" s="235" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="256"/>
-      <c r="C5" s="256"/>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
-      <c r="F5" s="256"/>
-      <c r="G5" s="256"/>
-      <c r="H5" s="256"/>
-      <c r="I5" s="256"/>
-      <c r="J5" s="256"/>
-      <c r="K5" s="256"/>
-      <c r="L5" s="256"/>
-      <c r="M5" s="256"/>
-      <c r="N5" s="257"/>
-      <c r="R5" s="194"/>
-      <c r="S5" s="195"/>
-      <c r="T5" s="195"/>
-      <c r="U5" s="195"/>
-      <c r="V5" s="196"/>
+      <c r="B5" s="236"/>
+      <c r="C5" s="236"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="236"/>
+      <c r="M5" s="236"/>
+      <c r="N5" s="237"/>
+      <c r="R5" s="274"/>
+      <c r="S5" s="275"/>
+      <c r="T5" s="275"/>
+      <c r="U5" s="275"/>
+      <c r="V5" s="276"/>
     </row>
     <row r="6" spans="1:22" ht="36.75" hidden="1" customHeight="1">
       <c r="A6" s="43"/>
@@ -11027,11 +11016,11 @@
       <c r="L6" s="45"/>
       <c r="M6" s="45"/>
       <c r="N6" s="46"/>
-      <c r="R6" s="194"/>
-      <c r="S6" s="195"/>
-      <c r="T6" s="195"/>
-      <c r="U6" s="195"/>
-      <c r="V6" s="196"/>
+      <c r="R6" s="274"/>
+      <c r="S6" s="275"/>
+      <c r="T6" s="275"/>
+      <c r="U6" s="275"/>
+      <c r="V6" s="276"/>
     </row>
     <row r="7" spans="1:22" s="53" customFormat="1" ht="12.75" customHeight="1" thickBot="1">
       <c r="A7" s="47" t="s">
@@ -11049,197 +11038,197 @@
       <c r="K7" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="258" t="s">
+      <c r="L7" s="238" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="259"/>
-      <c r="N7" s="260"/>
-      <c r="R7" s="194"/>
-      <c r="S7" s="195"/>
-      <c r="T7" s="195"/>
-      <c r="U7" s="195"/>
-      <c r="V7" s="196"/>
+      <c r="M7" s="239"/>
+      <c r="N7" s="240"/>
+      <c r="R7" s="274"/>
+      <c r="S7" s="275"/>
+      <c r="T7" s="275"/>
+      <c r="U7" s="275"/>
+      <c r="V7" s="276"/>
     </row>
     <row r="8" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
       <c r="A8" s="54"/>
       <c r="N8" s="55"/>
-      <c r="R8" s="194"/>
-      <c r="S8" s="195"/>
-      <c r="T8" s="195"/>
-      <c r="U8" s="195"/>
-      <c r="V8" s="196"/>
+      <c r="R8" s="274"/>
+      <c r="S8" s="275"/>
+      <c r="T8" s="275"/>
+      <c r="U8" s="275"/>
+      <c r="V8" s="276"/>
     </row>
     <row r="9" spans="1:22" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="285" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="206"/>
-      <c r="C9" s="206"/>
-      <c r="D9" s="206"/>
-      <c r="E9" s="206"/>
-      <c r="F9" s="206"/>
-      <c r="G9" s="206"/>
-      <c r="H9" s="206"/>
-      <c r="I9" s="206"/>
-      <c r="J9" s="206"/>
-      <c r="K9" s="206"/>
-      <c r="L9" s="206"/>
-      <c r="M9" s="206"/>
-      <c r="N9" s="207"/>
-      <c r="R9" s="194"/>
-      <c r="S9" s="195"/>
-      <c r="T9" s="195"/>
-      <c r="U9" s="195"/>
-      <c r="V9" s="196"/>
+      <c r="B9" s="286"/>
+      <c r="C9" s="286"/>
+      <c r="D9" s="286"/>
+      <c r="E9" s="286"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="286"/>
+      <c r="H9" s="286"/>
+      <c r="I9" s="286"/>
+      <c r="J9" s="286"/>
+      <c r="K9" s="286"/>
+      <c r="L9" s="286"/>
+      <c r="M9" s="286"/>
+      <c r="N9" s="287"/>
+      <c r="R9" s="274"/>
+      <c r="S9" s="275"/>
+      <c r="T9" s="275"/>
+      <c r="U9" s="275"/>
+      <c r="V9" s="276"/>
     </row>
     <row r="10" spans="1:22" ht="22.5" customHeight="1">
       <c r="A10" s="56">
         <v>2</v>
       </c>
-      <c r="B10" s="208" t="s">
+      <c r="B10" s="257" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="209"/>
-      <c r="D10" s="511"/>
-      <c r="E10" s="511"/>
-      <c r="F10" s="511"/>
-      <c r="G10" s="511"/>
-      <c r="H10" s="511"/>
-      <c r="I10" s="511"/>
-      <c r="J10" s="511"/>
-      <c r="K10" s="511"/>
-      <c r="L10" s="511"/>
-      <c r="M10" s="511"/>
-      <c r="N10" s="512"/>
+      <c r="C10" s="245"/>
+      <c r="D10" s="288"/>
+      <c r="E10" s="288"/>
+      <c r="F10" s="288"/>
+      <c r="G10" s="288"/>
+      <c r="H10" s="288"/>
+      <c r="I10" s="288"/>
+      <c r="J10" s="288"/>
+      <c r="K10" s="288"/>
+      <c r="L10" s="288"/>
+      <c r="M10" s="288"/>
+      <c r="N10" s="289"/>
       <c r="P10" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="R10" s="194"/>
-      <c r="S10" s="195"/>
-      <c r="T10" s="195"/>
-      <c r="U10" s="195"/>
-      <c r="V10" s="196"/>
+      <c r="R10" s="274"/>
+      <c r="S10" s="275"/>
+      <c r="T10" s="275"/>
+      <c r="U10" s="275"/>
+      <c r="V10" s="276"/>
     </row>
     <row r="11" spans="1:22" ht="22.5" customHeight="1">
       <c r="A11" s="58"/>
-      <c r="B11" s="210" t="s">
+      <c r="B11" s="258" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="211"/>
-      <c r="D11" s="212"/>
-      <c r="E11" s="213"/>
-      <c r="F11" s="213"/>
-      <c r="G11" s="213"/>
-      <c r="H11" s="214"/>
-      <c r="I11" s="215" t="s">
+      <c r="C11" s="259"/>
+      <c r="D11" s="290"/>
+      <c r="E11" s="291"/>
+      <c r="F11" s="291"/>
+      <c r="G11" s="291"/>
+      <c r="H11" s="292"/>
+      <c r="I11" s="293" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="216"/>
-      <c r="K11" s="216"/>
-      <c r="L11" s="217"/>
-      <c r="M11" s="218"/>
-      <c r="N11" s="219"/>
+      <c r="J11" s="294"/>
+      <c r="K11" s="294"/>
+      <c r="L11" s="295"/>
+      <c r="M11" s="296"/>
+      <c r="N11" s="297"/>
       <c r="P11" s="60" t="s">
         <v>14</v>
       </c>
       <c r="Q11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="R11" s="194"/>
-      <c r="S11" s="195"/>
-      <c r="T11" s="195"/>
-      <c r="U11" s="195"/>
-      <c r="V11" s="196"/>
+      <c r="R11" s="274"/>
+      <c r="S11" s="275"/>
+      <c r="T11" s="275"/>
+      <c r="U11" s="275"/>
+      <c r="V11" s="276"/>
     </row>
     <row r="12" spans="1:22" ht="21.75" customHeight="1" thickBot="1">
       <c r="A12" s="62"/>
-      <c r="B12" s="200" t="s">
+      <c r="B12" s="280" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="201"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="203" t="b">
+      <c r="C12" s="281"/>
+      <c r="D12" s="282"/>
+      <c r="E12" s="283"/>
+      <c r="F12" s="283"/>
+      <c r="G12" s="283" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="203"/>
-      <c r="I12" s="203" t="b">
+      <c r="H12" s="283"/>
+      <c r="I12" s="283" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="203"/>
-      <c r="K12" s="203"/>
-      <c r="L12" s="203"/>
-      <c r="M12" s="203"/>
-      <c r="N12" s="204"/>
+      <c r="J12" s="283"/>
+      <c r="K12" s="283"/>
+      <c r="L12" s="283"/>
+      <c r="M12" s="283"/>
+      <c r="N12" s="284"/>
       <c r="P12" s="60" t="s">
         <v>17</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="R12" s="194"/>
-      <c r="S12" s="195"/>
-      <c r="T12" s="195"/>
-      <c r="U12" s="195"/>
-      <c r="V12" s="196"/>
+      <c r="R12" s="274"/>
+      <c r="S12" s="275"/>
+      <c r="T12" s="275"/>
+      <c r="U12" s="275"/>
+      <c r="V12" s="276"/>
     </row>
     <row r="13" spans="1:22" ht="24" customHeight="1">
       <c r="A13" s="63">
         <v>3</v>
       </c>
-      <c r="B13" s="223" t="s">
+      <c r="B13" s="244" t="s">
         <v>332</v>
       </c>
-      <c r="C13" s="209"/>
-      <c r="D13" s="231"/>
-      <c r="E13" s="232"/>
-      <c r="F13" s="232"/>
-      <c r="G13" s="208" t="s">
+      <c r="C13" s="245"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="254"/>
+      <c r="F13" s="254"/>
+      <c r="G13" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="208"/>
-      <c r="I13" s="209"/>
-      <c r="J13" s="235" t="b">
+      <c r="H13" s="257"/>
+      <c r="I13" s="245"/>
+      <c r="J13" s="260" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="236"/>
-      <c r="L13" s="236" t="b">
+      <c r="K13" s="261"/>
+      <c r="L13" s="261" t="b">
         <v>0</v>
       </c>
-      <c r="M13" s="236"/>
-      <c r="N13" s="237"/>
+      <c r="M13" s="261"/>
+      <c r="N13" s="262"/>
       <c r="P13" s="60" t="s">
         <v>20</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="197"/>
-      <c r="S13" s="198"/>
-      <c r="T13" s="198"/>
-      <c r="U13" s="198"/>
-      <c r="V13" s="199"/>
+      <c r="R13" s="277"/>
+      <c r="S13" s="278"/>
+      <c r="T13" s="278"/>
+      <c r="U13" s="278"/>
+      <c r="V13" s="279"/>
     </row>
     <row r="14" spans="1:22" ht="21.6" customHeight="1">
       <c r="A14" s="58"/>
       <c r="B14" s="64"/>
       <c r="C14" s="64"/>
-      <c r="D14" s="233"/>
-      <c r="E14" s="234"/>
-      <c r="F14" s="234"/>
-      <c r="G14" s="210"/>
-      <c r="H14" s="210"/>
-      <c r="I14" s="211"/>
-      <c r="J14" s="238" t="b">
+      <c r="D14" s="255"/>
+      <c r="E14" s="256"/>
+      <c r="F14" s="256"/>
+      <c r="G14" s="258"/>
+      <c r="H14" s="258"/>
+      <c r="I14" s="259"/>
+      <c r="J14" s="263" t="b">
         <v>0</v>
       </c>
-      <c r="K14" s="239"/>
-      <c r="L14" s="239" t="b">
+      <c r="K14" s="264"/>
+      <c r="L14" s="264" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="239"/>
-      <c r="N14" s="240"/>
+      <c r="M14" s="264"/>
+      <c r="N14" s="265"/>
       <c r="P14" s="60"/>
       <c r="Q14" s="2"/>
       <c r="S14"/>
@@ -11254,21 +11243,21 @@
         <v>22</v>
       </c>
       <c r="C15" s="66"/>
-      <c r="D15" s="224"/>
-      <c r="E15" s="224"/>
-      <c r="F15" s="225"/>
-      <c r="G15" s="226" t="s">
+      <c r="D15" s="246"/>
+      <c r="E15" s="246"/>
+      <c r="F15" s="247"/>
+      <c r="G15" s="248" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="227"/>
-      <c r="I15" s="227"/>
-      <c r="J15" s="228" t="s">
+      <c r="H15" s="249"/>
+      <c r="I15" s="249"/>
+      <c r="J15" s="250" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="229"/>
-      <c r="L15" s="229"/>
-      <c r="M15" s="229"/>
-      <c r="N15" s="230"/>
+      <c r="K15" s="251"/>
+      <c r="L15" s="251"/>
+      <c r="M15" s="251"/>
+      <c r="N15" s="252"/>
       <c r="P15" s="60" t="s">
         <v>25</v>
       </c>
@@ -11290,22 +11279,22 @@
       <c r="D16" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="241" t="b">
+      <c r="E16" s="266" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="242"/>
-      <c r="G16" s="243" t="s">
+      <c r="F16" s="267"/>
+      <c r="G16" s="268" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="244"/>
-      <c r="I16" s="245"/>
-      <c r="J16" s="220">
+      <c r="H16" s="269"/>
+      <c r="I16" s="270"/>
+      <c r="J16" s="241">
         <v>1</v>
       </c>
-      <c r="K16" s="221"/>
-      <c r="L16" s="221"/>
-      <c r="M16" s="221"/>
-      <c r="N16" s="222"/>
+      <c r="K16" s="242"/>
+      <c r="L16" s="242"/>
+      <c r="M16" s="242"/>
+      <c r="N16" s="243"/>
       <c r="O16" s="69"/>
       <c r="P16" s="60" t="s">
         <v>29</v>
@@ -11315,60 +11304,60 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="27" customHeight="1">
-      <c r="A17" s="278">
+      <c r="A17" s="197">
         <v>6</v>
       </c>
-      <c r="B17" s="184" t="s">
+      <c r="B17" s="309" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="185"/>
+      <c r="C17" s="310"/>
       <c r="D17" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="189" t="b">
+      <c r="E17" s="313" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="190"/>
+      <c r="F17" s="314"/>
       <c r="G17" s="70" t="s">
         <v>32</v>
       </c>
       <c r="H17" s="71"/>
-      <c r="I17" s="178"/>
-      <c r="J17" s="178"/>
-      <c r="K17" s="178"/>
-      <c r="L17" s="178"/>
-      <c r="M17" s="179"/>
-      <c r="N17" s="179"/>
+      <c r="I17" s="196"/>
+      <c r="J17" s="196"/>
+      <c r="K17" s="196"/>
+      <c r="L17" s="196"/>
+      <c r="M17" s="213"/>
+      <c r="N17" s="213"/>
       <c r="Q17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="R17" s="72"/>
     </row>
     <row r="18" spans="1:23" ht="27" customHeight="1">
-      <c r="A18" s="279"/>
-      <c r="B18" s="186"/>
-      <c r="C18" s="187"/>
+      <c r="A18" s="198"/>
+      <c r="B18" s="311"/>
+      <c r="C18" s="312"/>
       <c r="D18" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="176" t="b">
+      <c r="E18" s="222" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="177"/>
+      <c r="F18" s="223"/>
       <c r="G18" s="74"/>
       <c r="H18" s="75"/>
-      <c r="I18" s="261" t="s">
+      <c r="I18" s="217" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="261"/>
-      <c r="K18" s="261" t="s">
+      <c r="J18" s="217"/>
+      <c r="K18" s="217" t="s">
         <v>341</v>
       </c>
-      <c r="L18" s="261"/>
-      <c r="M18" s="261" t="s">
+      <c r="L18" s="217"/>
+      <c r="M18" s="217" t="s">
         <v>35</v>
       </c>
-      <c r="N18" s="261"/>
+      <c r="N18" s="217"/>
       <c r="Q18" s="2" t="s">
         <v>36</v>
       </c>
@@ -11377,19 +11366,19 @@
       <c r="A19" s="56"/>
       <c r="B19" s="76"/>
       <c r="C19" s="73"/>
-      <c r="D19" s="273" t="b">
+      <c r="D19" s="221" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="176"/>
-      <c r="F19" s="177"/>
+      <c r="E19" s="222"/>
+      <c r="F19" s="223"/>
       <c r="G19" s="74"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="178"/>
-      <c r="J19" s="179"/>
-      <c r="K19" s="179"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="179"/>
-      <c r="N19" s="179"/>
+      <c r="I19" s="196"/>
+      <c r="J19" s="213"/>
+      <c r="K19" s="213"/>
+      <c r="L19" s="196"/>
+      <c r="M19" s="213"/>
+      <c r="N19" s="213"/>
       <c r="Q19" s="2" t="s">
         <v>37</v>
       </c>
@@ -11398,67 +11387,67 @@
       <c r="A20" s="77"/>
       <c r="B20" s="78"/>
       <c r="C20" s="79"/>
-      <c r="D20" s="270"/>
-      <c r="E20" s="271"/>
-      <c r="F20" s="272"/>
+      <c r="D20" s="218"/>
+      <c r="E20" s="219"/>
+      <c r="F20" s="220"/>
       <c r="G20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="180" t="s">
+      <c r="I20" s="214" t="s">
         <v>38</v>
       </c>
-      <c r="J20" s="182"/>
-      <c r="K20" s="182"/>
-      <c r="L20" s="181" t="s">
+      <c r="J20" s="215"/>
+      <c r="K20" s="215"/>
+      <c r="L20" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="M20" s="183"/>
-      <c r="N20" s="183"/>
+      <c r="M20" s="308"/>
+      <c r="N20" s="308"/>
       <c r="Q20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A21" s="279">
+      <c r="A21" s="198">
         <v>7</v>
       </c>
-      <c r="B21" s="281" t="s">
+      <c r="B21" s="200" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="282"/>
-      <c r="D21" s="285"/>
-      <c r="E21" s="285"/>
-      <c r="F21" s="285"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="207"/>
+      <c r="E21" s="207"/>
+      <c r="F21" s="207"/>
       <c r="G21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="178"/>
-      <c r="J21" s="179"/>
-      <c r="K21" s="179"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="179"/>
-      <c r="N21" s="179"/>
+      <c r="I21" s="196"/>
+      <c r="J21" s="213"/>
+      <c r="K21" s="213"/>
+      <c r="L21" s="196"/>
+      <c r="M21" s="213"/>
+      <c r="N21" s="213"/>
       <c r="Q21" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="26.25" customHeight="1">
-      <c r="A22" s="280"/>
-      <c r="B22" s="283"/>
-      <c r="C22" s="284"/>
-      <c r="D22" s="269"/>
-      <c r="E22" s="269"/>
-      <c r="F22" s="269"/>
+      <c r="A22" s="199"/>
+      <c r="B22" s="202"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="206"/>
+      <c r="E22" s="206"/>
+      <c r="F22" s="206"/>
       <c r="G22" s="58"/>
       <c r="H22" s="59"/>
-      <c r="I22" s="180" t="s">
+      <c r="I22" s="214" t="s">
         <v>43</v>
       </c>
-      <c r="J22" s="180"/>
-      <c r="K22" s="180"/>
-      <c r="L22" s="181" t="s">
+      <c r="J22" s="214"/>
+      <c r="K22" s="214"/>
+      <c r="L22" s="216" t="s">
         <v>44</v>
       </c>
-      <c r="M22" s="181"/>
-      <c r="N22" s="181"/>
+      <c r="M22" s="216"/>
+      <c r="N22" s="216"/>
       <c r="Q22" s="2" t="s">
         <v>45</v>
       </c>
@@ -11467,166 +11456,166 @@
       <c r="A23" s="56">
         <v>8</v>
       </c>
-      <c r="B23" s="274" t="s">
+      <c r="B23" s="208" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="263"/>
-      <c r="D23" s="188"/>
-      <c r="E23" s="188"/>
-      <c r="F23" s="188"/>
-      <c r="G23" s="267" t="s">
+      <c r="C23" s="209"/>
+      <c r="D23" s="210"/>
+      <c r="E23" s="210"/>
+      <c r="F23" s="210"/>
+      <c r="G23" s="211" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="268"/>
-      <c r="I23" s="179"/>
-      <c r="J23" s="179"/>
-      <c r="K23" s="179"/>
-      <c r="L23" s="179"/>
-      <c r="M23" s="179"/>
-      <c r="N23" s="179"/>
+      <c r="H23" s="212"/>
+      <c r="I23" s="213"/>
+      <c r="J23" s="213"/>
+      <c r="K23" s="213"/>
+      <c r="L23" s="213"/>
+      <c r="M23" s="213"/>
+      <c r="N23" s="213"/>
       <c r="Q23" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A24" s="278">
+      <c r="A24" s="197">
         <v>9</v>
       </c>
-      <c r="B24" s="281" t="s">
+      <c r="B24" s="200" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="282"/>
-      <c r="D24" s="266"/>
-      <c r="E24" s="266"/>
-      <c r="F24" s="266"/>
+      <c r="C24" s="201"/>
+      <c r="D24" s="205"/>
+      <c r="E24" s="205"/>
+      <c r="F24" s="205"/>
       <c r="G24" s="82" t="s">
         <v>50</v>
       </c>
       <c r="H24" s="80"/>
-      <c r="I24" s="178"/>
-      <c r="J24" s="178"/>
-      <c r="K24" s="178"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="179"/>
-      <c r="N24" s="179"/>
+      <c r="I24" s="196"/>
+      <c r="J24" s="196"/>
+      <c r="K24" s="196"/>
+      <c r="L24" s="196"/>
+      <c r="M24" s="213"/>
+      <c r="N24" s="213"/>
       <c r="Q24" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A25" s="280"/>
-      <c r="B25" s="283"/>
-      <c r="C25" s="284"/>
-      <c r="D25" s="269"/>
-      <c r="E25" s="269"/>
-      <c r="F25" s="269"/>
+      <c r="A25" s="199"/>
+      <c r="B25" s="202"/>
+      <c r="C25" s="203"/>
+      <c r="D25" s="206"/>
+      <c r="E25" s="206"/>
+      <c r="F25" s="206"/>
       <c r="G25" s="58"/>
       <c r="H25" s="59"/>
-      <c r="I25" s="261" t="s">
+      <c r="I25" s="217" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="261"/>
-      <c r="K25" s="261" t="s">
+      <c r="J25" s="217"/>
+      <c r="K25" s="217" t="s">
         <v>341</v>
       </c>
-      <c r="L25" s="261"/>
-      <c r="M25" s="261" t="s">
+      <c r="L25" s="217"/>
+      <c r="M25" s="217" t="s">
         <v>35</v>
       </c>
-      <c r="N25" s="261"/>
+      <c r="N25" s="217"/>
       <c r="Q25" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A26" s="278">
+      <c r="A26" s="197">
         <v>10</v>
       </c>
-      <c r="B26" s="281" t="s">
+      <c r="B26" s="200" t="s">
         <v>338</v>
       </c>
-      <c r="C26" s="282"/>
-      <c r="D26" s="266"/>
-      <c r="E26" s="266"/>
-      <c r="F26" s="266"/>
+      <c r="C26" s="201"/>
+      <c r="D26" s="205"/>
+      <c r="E26" s="205"/>
+      <c r="F26" s="205"/>
       <c r="G26" s="74"/>
       <c r="H26" s="75"/>
-      <c r="I26" s="178"/>
-      <c r="J26" s="179"/>
-      <c r="K26" s="179"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="179"/>
-      <c r="N26" s="179"/>
+      <c r="I26" s="196"/>
+      <c r="J26" s="213"/>
+      <c r="K26" s="213"/>
+      <c r="L26" s="196"/>
+      <c r="M26" s="213"/>
+      <c r="N26" s="213"/>
       <c r="Q26" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="35.25" customHeight="1">
-      <c r="A27" s="280"/>
-      <c r="B27" s="283"/>
-      <c r="C27" s="284"/>
-      <c r="D27" s="269"/>
-      <c r="E27" s="269"/>
-      <c r="F27" s="269"/>
+      <c r="A27" s="199"/>
+      <c r="B27" s="202"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="206"/>
+      <c r="E27" s="206"/>
+      <c r="F27" s="206"/>
       <c r="G27" s="74"/>
       <c r="H27" s="75"/>
-      <c r="I27" s="180" t="s">
+      <c r="I27" s="214" t="s">
         <v>38</v>
       </c>
-      <c r="J27" s="182"/>
-      <c r="K27" s="182"/>
-      <c r="L27" s="181" t="s">
+      <c r="J27" s="215"/>
+      <c r="K27" s="215"/>
+      <c r="L27" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="M27" s="182"/>
-      <c r="N27" s="182"/>
+      <c r="M27" s="215"/>
+      <c r="N27" s="215"/>
       <c r="Q27" s="2" t="s">
         <v>54</v>
       </c>
       <c r="S27" s="83"/>
     </row>
     <row r="28" spans="1:23" ht="33" customHeight="1">
-      <c r="A28" s="278">
+      <c r="A28" s="197">
         <v>11</v>
       </c>
-      <c r="B28" s="281" t="s">
+      <c r="B28" s="200" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="282"/>
-      <c r="D28" s="265"/>
-      <c r="E28" s="266"/>
-      <c r="F28" s="266"/>
+      <c r="C28" s="201"/>
+      <c r="D28" s="204"/>
+      <c r="E28" s="205"/>
+      <c r="F28" s="205"/>
       <c r="G28" s="74"/>
       <c r="H28" s="84"/>
-      <c r="I28" s="178"/>
-      <c r="J28" s="179"/>
-      <c r="K28" s="179"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="179"/>
-      <c r="N28" s="179"/>
+      <c r="I28" s="196"/>
+      <c r="J28" s="213"/>
+      <c r="K28" s="213"/>
+      <c r="L28" s="196"/>
+      <c r="M28" s="213"/>
+      <c r="N28" s="213"/>
       <c r="Q28" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="32.25" customHeight="1">
-      <c r="A29" s="280"/>
-      <c r="B29" s="283"/>
-      <c r="C29" s="284"/>
-      <c r="D29" s="269"/>
-      <c r="E29" s="269"/>
-      <c r="F29" s="269"/>
+      <c r="A29" s="199"/>
+      <c r="B29" s="202"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="206"/>
+      <c r="E29" s="206"/>
+      <c r="F29" s="206"/>
       <c r="G29" s="74"/>
       <c r="H29" s="84"/>
-      <c r="I29" s="180" t="s">
+      <c r="I29" s="214" t="s">
         <v>43</v>
       </c>
-      <c r="J29" s="180"/>
-      <c r="K29" s="180"/>
-      <c r="L29" s="180" t="s">
+      <c r="J29" s="214"/>
+      <c r="K29" s="214"/>
+      <c r="L29" s="214" t="s">
         <v>44</v>
       </c>
-      <c r="M29" s="180"/>
-      <c r="N29" s="180"/>
+      <c r="M29" s="214"/>
+      <c r="N29" s="214"/>
       <c r="Q29" s="2" t="s">
         <v>57</v>
       </c>
@@ -11640,19 +11629,19 @@
         <v>58</v>
       </c>
       <c r="C30" s="68"/>
-      <c r="D30" s="265"/>
-      <c r="E30" s="266"/>
-      <c r="F30" s="266"/>
-      <c r="G30" s="267" t="s">
+      <c r="D30" s="204"/>
+      <c r="E30" s="205"/>
+      <c r="F30" s="205"/>
+      <c r="G30" s="211" t="s">
         <v>47</v>
       </c>
-      <c r="H30" s="268"/>
-      <c r="I30" s="179"/>
-      <c r="J30" s="179"/>
-      <c r="K30" s="179"/>
-      <c r="L30" s="179"/>
-      <c r="M30" s="179"/>
-      <c r="N30" s="179"/>
+      <c r="H30" s="212"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="213"/>
+      <c r="M30" s="213"/>
+      <c r="N30" s="213"/>
       <c r="Q30" s="2" t="s">
         <v>59</v>
       </c>
@@ -11669,42 +11658,42 @@
         <v>337</v>
       </c>
       <c r="C31" s="68"/>
-      <c r="D31" s="188"/>
-      <c r="E31" s="188"/>
-      <c r="F31" s="188"/>
+      <c r="D31" s="210"/>
+      <c r="E31" s="210"/>
+      <c r="F31" s="210"/>
       <c r="G31" s="85" t="s">
         <v>60</v>
       </c>
       <c r="H31" s="81"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="178"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="178"/>
-      <c r="N31" s="178"/>
+      <c r="I31" s="196"/>
+      <c r="J31" s="196"/>
+      <c r="K31" s="196"/>
+      <c r="L31" s="196"/>
+      <c r="M31" s="196"/>
+      <c r="N31" s="196"/>
       <c r="Q31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="39.75" customHeight="1">
-      <c r="A32" s="262" t="s">
+      <c r="A32" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="263"/>
-      <c r="C32" s="264"/>
-      <c r="D32" s="188"/>
-      <c r="E32" s="188"/>
-      <c r="F32" s="188"/>
+      <c r="B32" s="209"/>
+      <c r="C32" s="225"/>
+      <c r="D32" s="210"/>
+      <c r="E32" s="210"/>
+      <c r="F32" s="210"/>
       <c r="G32" s="86" t="s">
         <v>63</v>
       </c>
       <c r="H32" s="87"/>
-      <c r="I32" s="178"/>
-      <c r="J32" s="178"/>
-      <c r="K32" s="178"/>
-      <c r="L32" s="178"/>
-      <c r="M32" s="178"/>
-      <c r="N32" s="178"/>
+      <c r="I32" s="196"/>
+      <c r="J32" s="196"/>
+      <c r="K32" s="196"/>
+      <c r="L32" s="196"/>
+      <c r="M32" s="196"/>
+      <c r="N32" s="196"/>
       <c r="Q32" s="2" t="s">
         <v>64</v>
       </c>
@@ -11713,69 +11702,69 @@
       <c r="A33" s="65">
         <v>15</v>
       </c>
-      <c r="B33" s="174" t="s">
+      <c r="B33" s="306" t="s">
         <v>336</v>
       </c>
-      <c r="C33" s="175"/>
-      <c r="D33" s="171"/>
-      <c r="E33" s="172"/>
-      <c r="F33" s="173"/>
+      <c r="C33" s="307"/>
+      <c r="D33" s="303"/>
+      <c r="E33" s="304"/>
+      <c r="F33" s="305"/>
       <c r="G33" s="88" t="s">
         <v>65</v>
       </c>
       <c r="H33" s="81"/>
-      <c r="I33" s="277"/>
-      <c r="J33" s="178"/>
-      <c r="K33" s="178"/>
-      <c r="L33" s="178"/>
-      <c r="M33" s="178"/>
-      <c r="N33" s="178"/>
+      <c r="I33" s="195"/>
+      <c r="J33" s="196"/>
+      <c r="K33" s="196"/>
+      <c r="L33" s="196"/>
+      <c r="M33" s="196"/>
+      <c r="N33" s="196"/>
       <c r="Q33" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A34" s="168" t="s">
+      <c r="A34" s="300" t="s">
         <v>342</v>
       </c>
-      <c r="B34" s="169"/>
-      <c r="C34" s="169"/>
-      <c r="D34" s="169"/>
-      <c r="E34" s="169"/>
-      <c r="F34" s="169"/>
-      <c r="G34" s="169"/>
-      <c r="H34" s="169"/>
-      <c r="I34" s="169"/>
-      <c r="J34" s="169"/>
-      <c r="K34" s="169"/>
-      <c r="L34" s="169"/>
-      <c r="M34" s="169"/>
-      <c r="N34" s="170"/>
+      <c r="B34" s="301"/>
+      <c r="C34" s="301"/>
+      <c r="D34" s="301"/>
+      <c r="E34" s="301"/>
+      <c r="F34" s="301"/>
+      <c r="G34" s="301"/>
+      <c r="H34" s="301"/>
+      <c r="I34" s="301"/>
+      <c r="J34" s="301"/>
+      <c r="K34" s="301"/>
+      <c r="L34" s="301"/>
+      <c r="M34" s="301"/>
+      <c r="N34" s="302"/>
       <c r="Q34" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="21" customHeight="1">
-      <c r="A35" s="275" t="s">
+      <c r="A35" s="193" t="s">
         <v>343</v>
       </c>
-      <c r="B35" s="275"/>
-      <c r="C35" s="275"/>
-      <c r="D35" s="276" t="s">
+      <c r="B35" s="193"/>
+      <c r="C35" s="193"/>
+      <c r="D35" s="194" t="s">
         <v>345</v>
       </c>
-      <c r="E35" s="276"/>
-      <c r="F35" s="276"/>
-      <c r="G35" s="166" t="s">
+      <c r="E35" s="194"/>
+      <c r="F35" s="194"/>
+      <c r="G35" s="298" t="s">
         <v>344</v>
       </c>
-      <c r="H35" s="167"/>
-      <c r="I35" s="276"/>
-      <c r="J35" s="276"/>
-      <c r="K35" s="276"/>
-      <c r="L35" s="276"/>
-      <c r="M35" s="276"/>
-      <c r="N35" s="276"/>
+      <c r="H35" s="299"/>
+      <c r="I35" s="194"/>
+      <c r="J35" s="194"/>
+      <c r="K35" s="194"/>
+      <c r="L35" s="194"/>
+      <c r="M35" s="194"/>
+      <c r="N35" s="194"/>
       <c r="Q35" s="2" t="s">
         <v>68</v>
       </c>
@@ -15619,7 +15608,86 @@
       <c r="N263" s="90"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="/BaTTcDf+hqrv5TIoBNyRq0Sgn7nIwb4e4ttNsiQ6OfLPr1xfXEFwk9PJciGh81xM7VBkq1YdaQd4Z9lMQvbfg==" saltValue="KdyJu3hMujoMijewA5fQqg==" spinCount="100000" sheet="1" scenarios="1"/>
   <mergeCells count="94">
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="I31:N31"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="R3:V13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:N15"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:I14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="D26:F27"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:N23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="I35:N35"/>
@@ -15636,84 +15704,6 @@
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="D24:F25"/>
     <mergeCell ref="B26:C27"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:N23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="D26:F27"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:N15"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:I14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="R3:V13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="I31:N31"/>
-    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35" xr:uid="{5EC3205D-4079-402B-BBE7-9B917DF21EB0}">
@@ -16207,944 +16197,1039 @@
   <dimension ref="A1:O62"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="447" customWidth="1"/>
-    <col min="2" max="2" width="1.7109375" style="447" customWidth="1"/>
-    <col min="3" max="3" width="13" style="447" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="447" customWidth="1"/>
-    <col min="5" max="5" width="3" style="447" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" style="447" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="447" customWidth="1"/>
-    <col min="8" max="8" width="10" style="447" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" style="447" customWidth="1"/>
-    <col min="10" max="10" width="29.7109375" style="447" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" style="447" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" style="447" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="447" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" style="447" customWidth="1"/>
-    <col min="15" max="15" width="21.42578125" style="447" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="447"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="2" max="2" width="1.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="29.7109375" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" customWidth="1"/>
+    <col min="15" max="15" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="3" customHeight="1" thickBot="1">
-      <c r="A1" s="445"/>
-      <c r="B1" s="446"/>
-      <c r="C1" s="446"/>
-      <c r="D1" s="446"/>
-      <c r="E1" s="446"/>
-      <c r="F1" s="446"/>
-      <c r="G1" s="446"/>
-      <c r="H1" s="446"/>
-      <c r="I1" s="446"/>
-      <c r="J1" s="446"/>
+      <c r="A1" s="476"/>
+      <c r="B1" s="477"/>
+      <c r="C1" s="477"/>
+      <c r="D1" s="477"/>
+      <c r="E1" s="477"/>
+      <c r="F1" s="477"/>
+      <c r="G1" s="477"/>
+      <c r="H1" s="477"/>
+      <c r="I1" s="477"/>
+      <c r="J1" s="477"/>
     </row>
     <row r="2" spans="1:15" ht="13.5" customHeight="1">
-      <c r="A2" s="448">
+      <c r="A2" s="478">
         <v>34</v>
       </c>
-      <c r="B2" s="449"/>
-      <c r="C2" s="450" t="s">
+      <c r="B2" s="479"/>
+      <c r="C2" s="480" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="450"/>
-      <c r="E2" s="450"/>
-      <c r="F2" s="451"/>
-      <c r="G2" s="409"/>
-      <c r="H2" s="410"/>
-      <c r="I2" s="410"/>
-      <c r="J2" s="410"/>
-      <c r="K2" s="410"/>
-      <c r="L2" s="410"/>
-      <c r="M2" s="410"/>
-      <c r="N2" s="410"/>
-      <c r="O2" s="411"/>
+      <c r="D2" s="480"/>
+      <c r="E2" s="480"/>
+      <c r="F2" s="481"/>
+      <c r="G2" s="431"/>
+      <c r="H2" s="432"/>
+      <c r="I2" s="432"/>
+      <c r="J2" s="432"/>
+      <c r="K2" s="432"/>
+      <c r="L2" s="432"/>
+      <c r="M2" s="432"/>
+      <c r="N2" s="432"/>
+      <c r="O2" s="433"/>
     </row>
     <row r="3" spans="1:15" ht="12.75" customHeight="1">
-      <c r="A3" s="452"/>
-      <c r="B3" s="453"/>
-      <c r="C3" s="454" t="s">
+      <c r="A3" s="170"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="482" t="s">
         <v>295</v>
       </c>
-      <c r="D3" s="454"/>
-      <c r="E3" s="454"/>
-      <c r="F3" s="455"/>
-      <c r="G3" s="409"/>
-      <c r="H3" s="410"/>
-      <c r="I3" s="410"/>
-      <c r="J3" s="410"/>
-      <c r="K3" s="410"/>
-      <c r="L3" s="410"/>
-      <c r="M3" s="410"/>
-      <c r="N3" s="410"/>
-      <c r="O3" s="411"/>
+      <c r="D3" s="482"/>
+      <c r="E3" s="482"/>
+      <c r="F3" s="483"/>
+      <c r="G3" s="431"/>
+      <c r="H3" s="432"/>
+      <c r="I3" s="432"/>
+      <c r="J3" s="432"/>
+      <c r="K3" s="432"/>
+      <c r="L3" s="432"/>
+      <c r="M3" s="432"/>
+      <c r="N3" s="432"/>
+      <c r="O3" s="433"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="452"/>
-      <c r="B4" s="453"/>
-      <c r="C4" s="454" t="s">
+      <c r="A4" s="170"/>
+      <c r="B4" s="171"/>
+      <c r="C4" s="482" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="454"/>
-      <c r="E4" s="454"/>
-      <c r="F4" s="455"/>
-      <c r="G4" s="409"/>
-      <c r="H4" s="410"/>
-      <c r="I4" s="410"/>
-      <c r="J4" s="410"/>
-      <c r="K4" s="410"/>
-      <c r="L4" s="410"/>
-      <c r="M4" s="410"/>
-      <c r="N4" s="410"/>
-      <c r="O4" s="411"/>
+      <c r="D4" s="482"/>
+      <c r="E4" s="482"/>
+      <c r="F4" s="483"/>
+      <c r="G4" s="431"/>
+      <c r="H4" s="432"/>
+      <c r="I4" s="432"/>
+      <c r="J4" s="432"/>
+      <c r="K4" s="432"/>
+      <c r="L4" s="432"/>
+      <c r="M4" s="432"/>
+      <c r="N4" s="432"/>
+      <c r="O4" s="433"/>
     </row>
     <row r="5" spans="1:15" ht="24.75" customHeight="1">
-      <c r="A5" s="452"/>
-      <c r="B5" s="453"/>
-      <c r="C5" s="454" t="s">
+      <c r="A5" s="170"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="482" t="s">
         <v>297</v>
       </c>
-      <c r="D5" s="454"/>
-      <c r="E5" s="454"/>
-      <c r="F5" s="455"/>
-      <c r="G5" s="377" t="b">
+      <c r="D5" s="482"/>
+      <c r="E5" s="482"/>
+      <c r="F5" s="483"/>
+      <c r="G5" s="458" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="388"/>
-      <c r="I5" s="388" t="b">
+      <c r="H5" s="434"/>
+      <c r="I5" s="434" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="388"/>
-      <c r="K5" s="388"/>
-      <c r="L5" s="388"/>
-      <c r="M5" s="388"/>
-      <c r="N5" s="388"/>
-      <c r="O5" s="389"/>
+      <c r="J5" s="434"/>
+      <c r="K5" s="434"/>
+      <c r="L5" s="434"/>
+      <c r="M5" s="434"/>
+      <c r="N5" s="434"/>
+      <c r="O5" s="435"/>
     </row>
     <row r="6" spans="1:15" ht="24" customHeight="1">
-      <c r="A6" s="452"/>
-      <c r="B6" s="453"/>
-      <c r="C6" s="454" t="s">
+      <c r="A6" s="170"/>
+      <c r="B6" s="171"/>
+      <c r="C6" s="482" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="454"/>
-      <c r="E6" s="454"/>
-      <c r="F6" s="455"/>
-      <c r="G6" s="377" t="b">
+      <c r="D6" s="482"/>
+      <c r="E6" s="482"/>
+      <c r="F6" s="483"/>
+      <c r="G6" s="458" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="388"/>
-      <c r="I6" s="388" t="b">
+      <c r="H6" s="434"/>
+      <c r="I6" s="434" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="388"/>
-      <c r="K6" s="388"/>
-      <c r="L6" s="388"/>
-      <c r="M6" s="388"/>
-      <c r="N6" s="388"/>
-      <c r="O6" s="389"/>
+      <c r="J6" s="434"/>
+      <c r="K6" s="434"/>
+      <c r="L6" s="434"/>
+      <c r="M6" s="434"/>
+      <c r="N6" s="434"/>
+      <c r="O6" s="435"/>
     </row>
     <row r="7" spans="1:15" ht="27" customHeight="1">
-      <c r="A7" s="452"/>
-      <c r="B7" s="453"/>
-      <c r="C7" s="454"/>
-      <c r="D7" s="454"/>
-      <c r="E7" s="454"/>
-      <c r="F7" s="454"/>
-      <c r="G7" s="412" t="s">
+      <c r="A7" s="170"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="482"/>
+      <c r="D7" s="482"/>
+      <c r="E7" s="482"/>
+      <c r="F7" s="482"/>
+      <c r="G7" s="167" t="s">
         <v>321</v>
       </c>
-      <c r="H7" s="413"/>
-      <c r="I7" s="384"/>
-      <c r="J7" s="384"/>
-      <c r="K7" s="384"/>
-      <c r="L7" s="384"/>
-      <c r="M7" s="384"/>
-      <c r="N7" s="384"/>
-      <c r="O7" s="387"/>
+      <c r="H7" s="168"/>
+      <c r="I7" s="436"/>
+      <c r="J7" s="436"/>
+      <c r="K7" s="436"/>
+      <c r="L7" s="436"/>
+      <c r="M7" s="436"/>
+      <c r="N7" s="436"/>
+      <c r="O7" s="437"/>
     </row>
     <row r="8" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A8" s="456"/>
-      <c r="B8" s="457"/>
-      <c r="C8" s="458"/>
-      <c r="D8" s="458"/>
-      <c r="E8" s="458"/>
-      <c r="F8" s="459"/>
-      <c r="G8" s="414"/>
-      <c r="H8" s="415"/>
-      <c r="I8" s="415"/>
-      <c r="J8" s="415"/>
-      <c r="K8" s="415"/>
-      <c r="L8" s="415"/>
-      <c r="M8" s="415"/>
-      <c r="N8" s="415"/>
-      <c r="O8" s="416"/>
+      <c r="A8" s="172"/>
+      <c r="B8" s="173"/>
+      <c r="C8" s="493"/>
+      <c r="D8" s="493"/>
+      <c r="E8" s="493"/>
+      <c r="F8" s="494"/>
+      <c r="G8" s="438"/>
+      <c r="H8" s="439"/>
+      <c r="I8" s="439"/>
+      <c r="J8" s="439"/>
+      <c r="K8" s="439"/>
+      <c r="L8" s="439"/>
+      <c r="M8" s="439"/>
+      <c r="N8" s="439"/>
+      <c r="O8" s="440"/>
     </row>
     <row r="9" spans="1:15" ht="20.45" customHeight="1">
-      <c r="A9" s="460">
+      <c r="A9" s="495">
         <v>35</v>
       </c>
-      <c r="B9" s="461"/>
-      <c r="C9" s="462" t="s">
+      <c r="B9" s="496"/>
+      <c r="C9" s="470" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="462"/>
-      <c r="E9" s="463"/>
-      <c r="F9" s="464"/>
-      <c r="G9" s="385" t="b">
+      <c r="D9" s="470"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="497"/>
+      <c r="G9" s="462" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="386"/>
-      <c r="I9" s="376" t="b">
+      <c r="H9" s="463"/>
+      <c r="I9" s="409" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="376"/>
-      <c r="K9" s="376"/>
-      <c r="L9" s="376"/>
-      <c r="M9" s="376"/>
-      <c r="N9" s="376"/>
-      <c r="O9" s="399"/>
+      <c r="J9" s="409"/>
+      <c r="K9" s="409"/>
+      <c r="L9" s="409"/>
+      <c r="M9" s="409"/>
+      <c r="N9" s="409"/>
+      <c r="O9" s="410"/>
     </row>
     <row r="10" spans="1:15" ht="26.25" customHeight="1">
-      <c r="A10" s="465"/>
-      <c r="B10" s="466"/>
-      <c r="C10" s="462"/>
-      <c r="D10" s="462"/>
-      <c r="E10" s="463"/>
-      <c r="F10" s="464"/>
-      <c r="G10" s="417" t="s">
+      <c r="A10" s="174"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="470"/>
+      <c r="D10" s="470"/>
+      <c r="E10" s="356"/>
+      <c r="F10" s="497"/>
+      <c r="G10" s="498" t="s">
         <v>321</v>
       </c>
-      <c r="H10" s="418"/>
-      <c r="I10" s="373"/>
-      <c r="J10" s="373"/>
-      <c r="K10" s="373"/>
-      <c r="L10" s="373"/>
-      <c r="M10" s="373"/>
-      <c r="N10" s="373"/>
-      <c r="O10" s="400"/>
+      <c r="H10" s="499"/>
+      <c r="I10" s="427"/>
+      <c r="J10" s="427"/>
+      <c r="K10" s="427"/>
+      <c r="L10" s="427"/>
+      <c r="M10" s="427"/>
+      <c r="N10" s="427"/>
+      <c r="O10" s="428"/>
     </row>
     <row r="11" spans="1:15" ht="21.75" customHeight="1">
-      <c r="A11" s="465"/>
-      <c r="B11" s="466"/>
-      <c r="C11" s="463"/>
-      <c r="D11" s="463"/>
-      <c r="E11" s="463"/>
-      <c r="F11" s="463"/>
-      <c r="G11" s="419"/>
-      <c r="H11" s="420"/>
-      <c r="I11" s="420"/>
-      <c r="J11" s="420"/>
-      <c r="K11" s="420"/>
-      <c r="L11" s="420"/>
-      <c r="M11" s="420"/>
-      <c r="N11" s="420"/>
-      <c r="O11" s="421"/>
+      <c r="A11" s="174"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="356"/>
+      <c r="D11" s="356"/>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="G11" s="441"/>
+      <c r="H11" s="442"/>
+      <c r="I11" s="442"/>
+      <c r="J11" s="442"/>
+      <c r="K11" s="442"/>
+      <c r="L11" s="442"/>
+      <c r="M11" s="442"/>
+      <c r="N11" s="442"/>
+      <c r="O11" s="443"/>
     </row>
     <row r="12" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A12" s="467"/>
-      <c r="B12" s="468"/>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="471"/>
-      <c r="G12" s="378" t="b">
+      <c r="A12" s="176"/>
+      <c r="B12" s="177"/>
+      <c r="C12" s="178"/>
+      <c r="D12" s="178"/>
+      <c r="E12" s="179"/>
+      <c r="F12" s="180"/>
+      <c r="G12" s="500" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="392"/>
-      <c r="I12" s="392" t="b">
+      <c r="H12" s="501"/>
+      <c r="I12" s="501" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="392"/>
-      <c r="K12" s="392"/>
-      <c r="L12" s="392"/>
-      <c r="M12" s="392"/>
-      <c r="N12" s="392"/>
-      <c r="O12" s="401"/>
+      <c r="J12" s="501"/>
+      <c r="K12" s="501"/>
+      <c r="L12" s="501"/>
+      <c r="M12" s="501"/>
+      <c r="N12" s="501"/>
+      <c r="O12" s="502"/>
     </row>
     <row r="13" spans="1:15" ht="21.75" customHeight="1">
-      <c r="A13" s="467"/>
-      <c r="B13" s="468"/>
-      <c r="C13" s="472" t="s">
+      <c r="A13" s="176"/>
+      <c r="B13" s="177"/>
+      <c r="C13" s="484" t="s">
         <v>300</v>
       </c>
-      <c r="D13" s="472"/>
-      <c r="E13" s="473"/>
-      <c r="F13" s="474"/>
-      <c r="G13" s="378"/>
-      <c r="H13" s="392"/>
-      <c r="I13" s="392"/>
-      <c r="J13" s="392"/>
-      <c r="K13" s="392"/>
-      <c r="L13" s="392"/>
-      <c r="M13" s="392"/>
-      <c r="N13" s="392"/>
-      <c r="O13" s="401"/>
+      <c r="D13" s="484"/>
+      <c r="E13" s="485"/>
+      <c r="F13" s="486"/>
+      <c r="G13" s="500"/>
+      <c r="H13" s="501"/>
+      <c r="I13" s="501"/>
+      <c r="J13" s="501"/>
+      <c r="K13" s="501"/>
+      <c r="L13" s="501"/>
+      <c r="M13" s="501"/>
+      <c r="N13" s="501"/>
+      <c r="O13" s="502"/>
     </row>
     <row r="14" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A14" s="467"/>
-      <c r="B14" s="468"/>
-      <c r="C14" s="472"/>
-      <c r="D14" s="472"/>
-      <c r="E14" s="473"/>
-      <c r="F14" s="474"/>
-      <c r="G14" s="422" t="s">
+      <c r="A14" s="176"/>
+      <c r="B14" s="177"/>
+      <c r="C14" s="484"/>
+      <c r="D14" s="484"/>
+      <c r="E14" s="485"/>
+      <c r="F14" s="486"/>
+      <c r="G14" s="444" t="s">
         <v>324</v>
       </c>
-      <c r="H14" s="423"/>
-      <c r="I14" s="390"/>
-      <c r="J14" s="390"/>
-      <c r="K14" s="390"/>
-      <c r="L14" s="390"/>
-      <c r="M14" s="390"/>
-      <c r="N14" s="390"/>
-      <c r="O14" s="402"/>
+      <c r="H14" s="445"/>
+      <c r="I14" s="425"/>
+      <c r="J14" s="425"/>
+      <c r="K14" s="425"/>
+      <c r="L14" s="425"/>
+      <c r="M14" s="425"/>
+      <c r="N14" s="425"/>
+      <c r="O14" s="426"/>
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1">
-      <c r="A15" s="467"/>
-      <c r="B15" s="468"/>
-      <c r="C15" s="472"/>
-      <c r="D15" s="472"/>
-      <c r="E15" s="473"/>
-      <c r="F15" s="474"/>
-      <c r="G15" s="424" t="s">
+      <c r="A15" s="176"/>
+      <c r="B15" s="177"/>
+      <c r="C15" s="484"/>
+      <c r="D15" s="484"/>
+      <c r="E15" s="485"/>
+      <c r="F15" s="486"/>
+      <c r="G15" s="503" t="s">
         <v>301</v>
       </c>
-      <c r="H15" s="390"/>
-      <c r="I15" s="373"/>
-      <c r="J15" s="373"/>
-      <c r="K15" s="373"/>
-      <c r="L15" s="373"/>
-      <c r="M15" s="373"/>
-      <c r="N15" s="373"/>
-      <c r="O15" s="400"/>
+      <c r="H15" s="425"/>
+      <c r="I15" s="427"/>
+      <c r="J15" s="427"/>
+      <c r="K15" s="427"/>
+      <c r="L15" s="427"/>
+      <c r="M15" s="427"/>
+      <c r="N15" s="427"/>
+      <c r="O15" s="428"/>
     </row>
     <row r="16" spans="1:15" ht="27.75" customHeight="1">
-      <c r="A16" s="467"/>
-      <c r="B16" s="468"/>
-      <c r="C16" s="472"/>
-      <c r="D16" s="472"/>
-      <c r="E16" s="473"/>
-      <c r="F16" s="474"/>
-      <c r="G16" s="425" t="s">
+      <c r="A16" s="176"/>
+      <c r="B16" s="177"/>
+      <c r="C16" s="484"/>
+      <c r="D16" s="484"/>
+      <c r="E16" s="485"/>
+      <c r="F16" s="486"/>
+      <c r="G16" s="504" t="s">
         <v>302</v>
       </c>
-      <c r="H16" s="426"/>
-      <c r="I16" s="374"/>
-      <c r="J16" s="374"/>
-      <c r="K16" s="374"/>
-      <c r="L16" s="374"/>
-      <c r="M16" s="374"/>
-      <c r="N16" s="374"/>
-      <c r="O16" s="403"/>
+      <c r="H16" s="505"/>
+      <c r="I16" s="429"/>
+      <c r="J16" s="429"/>
+      <c r="K16" s="429"/>
+      <c r="L16" s="429"/>
+      <c r="M16" s="429"/>
+      <c r="N16" s="429"/>
+      <c r="O16" s="430"/>
     </row>
     <row r="17" spans="1:15" ht="21" customHeight="1">
-      <c r="A17" s="475"/>
-      <c r="B17" s="476"/>
-      <c r="C17" s="477"/>
-      <c r="D17" s="477"/>
-      <c r="E17" s="477"/>
-      <c r="F17" s="478"/>
-      <c r="G17" s="427" t="s">
+      <c r="A17" s="181"/>
+      <c r="B17" s="182"/>
+      <c r="C17" s="487"/>
+      <c r="D17" s="487"/>
+      <c r="E17" s="487"/>
+      <c r="F17" s="488"/>
+      <c r="G17" s="406" t="s">
         <v>303</v>
       </c>
-      <c r="H17" s="428"/>
-      <c r="I17" s="428"/>
-      <c r="J17" s="428"/>
-      <c r="K17" s="428"/>
-      <c r="L17" s="428"/>
-      <c r="M17" s="428"/>
-      <c r="N17" s="428"/>
-      <c r="O17" s="429"/>
+      <c r="H17" s="407"/>
+      <c r="I17" s="407"/>
+      <c r="J17" s="407"/>
+      <c r="K17" s="407"/>
+      <c r="L17" s="407"/>
+      <c r="M17" s="407"/>
+      <c r="N17" s="407"/>
+      <c r="O17" s="408"/>
     </row>
     <row r="18" spans="1:15" ht="33" customHeight="1">
-      <c r="A18" s="479">
+      <c r="A18" s="491">
         <v>36</v>
       </c>
-      <c r="B18" s="480"/>
-      <c r="C18" s="481" t="s">
+      <c r="B18" s="492"/>
+      <c r="C18" s="489" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="481" t="b">
+      <c r="D18" s="489" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="481"/>
-      <c r="F18" s="482"/>
-      <c r="G18" s="385" t="b">
+      <c r="E18" s="489"/>
+      <c r="F18" s="490"/>
+      <c r="G18" s="462" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="386"/>
-      <c r="I18" s="376" t="b">
+      <c r="H18" s="463"/>
+      <c r="I18" s="409" t="b">
         <v>0</v>
       </c>
-      <c r="J18" s="376"/>
-      <c r="K18" s="376"/>
-      <c r="L18" s="376"/>
-      <c r="M18" s="376"/>
-      <c r="N18" s="376"/>
-      <c r="O18" s="399"/>
+      <c r="J18" s="409"/>
+      <c r="K18" s="409"/>
+      <c r="L18" s="409"/>
+      <c r="M18" s="409"/>
+      <c r="N18" s="409"/>
+      <c r="O18" s="410"/>
     </row>
     <row r="19" spans="1:15" ht="26.25" customHeight="1">
-      <c r="A19" s="465"/>
-      <c r="B19" s="466"/>
-      <c r="C19" s="483"/>
-      <c r="D19" s="483"/>
-      <c r="E19" s="483"/>
-      <c r="F19" s="484"/>
-      <c r="G19" s="430" t="s">
+      <c r="A19" s="174"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="446"/>
+      <c r="D19" s="446"/>
+      <c r="E19" s="446"/>
+      <c r="F19" s="447"/>
+      <c r="G19" s="464" t="s">
         <v>323</v>
       </c>
-      <c r="H19" s="431"/>
-      <c r="I19" s="373"/>
-      <c r="J19" s="373"/>
-      <c r="K19" s="373"/>
-      <c r="L19" s="373"/>
-      <c r="M19" s="373"/>
-      <c r="N19" s="373"/>
-      <c r="O19" s="400"/>
+      <c r="H19" s="465"/>
+      <c r="I19" s="427"/>
+      <c r="J19" s="427"/>
+      <c r="K19" s="427"/>
+      <c r="L19" s="427"/>
+      <c r="M19" s="427"/>
+      <c r="N19" s="427"/>
+      <c r="O19" s="428"/>
     </row>
     <row r="20" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A20" s="485"/>
-      <c r="B20" s="486"/>
-      <c r="C20" s="487"/>
-      <c r="D20" s="487"/>
-      <c r="E20" s="487"/>
-      <c r="F20" s="488"/>
-      <c r="G20" s="427"/>
-      <c r="H20" s="428"/>
-      <c r="I20" s="428"/>
-      <c r="J20" s="428"/>
-      <c r="K20" s="428"/>
-      <c r="L20" s="428"/>
-      <c r="M20" s="428"/>
-      <c r="N20" s="428"/>
-      <c r="O20" s="429"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="186"/>
+      <c r="C20" s="466"/>
+      <c r="D20" s="466"/>
+      <c r="E20" s="466"/>
+      <c r="F20" s="467"/>
+      <c r="G20" s="406"/>
+      <c r="H20" s="407"/>
+      <c r="I20" s="407"/>
+      <c r="J20" s="407"/>
+      <c r="K20" s="407"/>
+      <c r="L20" s="407"/>
+      <c r="M20" s="407"/>
+      <c r="N20" s="407"/>
+      <c r="O20" s="408"/>
     </row>
     <row r="21" spans="1:15" ht="26.25" customHeight="1">
-      <c r="A21" s="479">
+      <c r="A21" s="491">
         <v>37</v>
       </c>
-      <c r="B21" s="480"/>
-      <c r="C21" s="481" t="s">
+      <c r="B21" s="492"/>
+      <c r="C21" s="489" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="481"/>
-      <c r="E21" s="481"/>
-      <c r="F21" s="482"/>
-      <c r="G21" s="385" t="b">
+      <c r="D21" s="489"/>
+      <c r="E21" s="489"/>
+      <c r="F21" s="490"/>
+      <c r="G21" s="462" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="386"/>
-      <c r="I21" s="376" t="b">
+      <c r="H21" s="463"/>
+      <c r="I21" s="409" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="376"/>
-      <c r="K21" s="376"/>
-      <c r="L21" s="376"/>
-      <c r="M21" s="376"/>
-      <c r="N21" s="376"/>
-      <c r="O21" s="399"/>
+      <c r="J21" s="409"/>
+      <c r="K21" s="409"/>
+      <c r="L21" s="409"/>
+      <c r="M21" s="409"/>
+      <c r="N21" s="409"/>
+      <c r="O21" s="410"/>
     </row>
     <row r="22" spans="1:15" ht="27.75" customHeight="1">
-      <c r="A22" s="465"/>
-      <c r="B22" s="466"/>
-      <c r="C22" s="483"/>
-      <c r="D22" s="483"/>
-      <c r="E22" s="483"/>
-      <c r="F22" s="484"/>
-      <c r="G22" s="430" t="s">
+      <c r="A22" s="174"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="446"/>
+      <c r="D22" s="446"/>
+      <c r="E22" s="446"/>
+      <c r="F22" s="447"/>
+      <c r="G22" s="464" t="s">
         <v>322</v>
       </c>
-      <c r="H22" s="431"/>
-      <c r="I22" s="373"/>
-      <c r="J22" s="373"/>
-      <c r="K22" s="373"/>
-      <c r="L22" s="373"/>
-      <c r="M22" s="373"/>
-      <c r="N22" s="373"/>
-      <c r="O22" s="400"/>
+      <c r="H22" s="465"/>
+      <c r="I22" s="427"/>
+      <c r="J22" s="427"/>
+      <c r="K22" s="427"/>
+      <c r="L22" s="427"/>
+      <c r="M22" s="427"/>
+      <c r="N22" s="427"/>
+      <c r="O22" s="428"/>
     </row>
     <row r="23" spans="1:15" ht="39.75" customHeight="1">
-      <c r="A23" s="485"/>
-      <c r="B23" s="486"/>
-      <c r="C23" s="487"/>
-      <c r="D23" s="487"/>
-      <c r="E23" s="487"/>
-      <c r="F23" s="488"/>
-      <c r="G23" s="427"/>
-      <c r="H23" s="428"/>
-      <c r="I23" s="428"/>
-      <c r="J23" s="428"/>
-      <c r="K23" s="428"/>
-      <c r="L23" s="428"/>
-      <c r="M23" s="428"/>
-      <c r="N23" s="428"/>
-      <c r="O23" s="429"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="186"/>
+      <c r="C23" s="466"/>
+      <c r="D23" s="466"/>
+      <c r="E23" s="466"/>
+      <c r="F23" s="467"/>
+      <c r="G23" s="406"/>
+      <c r="H23" s="407"/>
+      <c r="I23" s="407"/>
+      <c r="J23" s="407"/>
+      <c r="K23" s="407"/>
+      <c r="L23" s="407"/>
+      <c r="M23" s="407"/>
+      <c r="N23" s="407"/>
+      <c r="O23" s="408"/>
     </row>
     <row r="24" spans="1:15" ht="38.25" customHeight="1">
-      <c r="A24" s="479">
+      <c r="A24" s="491">
         <v>38</v>
       </c>
-      <c r="B24" s="480"/>
-      <c r="C24" s="481" t="s">
+      <c r="B24" s="492"/>
+      <c r="C24" s="489" t="s">
         <v>306</v>
       </c>
-      <c r="D24" s="481"/>
-      <c r="E24" s="481"/>
-      <c r="F24" s="482"/>
-      <c r="G24" s="385" t="b">
+      <c r="D24" s="489"/>
+      <c r="E24" s="489"/>
+      <c r="F24" s="490"/>
+      <c r="G24" s="462" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="386"/>
-      <c r="I24" s="376" t="b">
+      <c r="H24" s="463"/>
+      <c r="I24" s="409" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="376"/>
-      <c r="K24" s="376"/>
-      <c r="L24" s="376"/>
-      <c r="M24" s="376"/>
-      <c r="N24" s="376"/>
-      <c r="O24" s="399"/>
+      <c r="J24" s="409"/>
+      <c r="K24" s="409"/>
+      <c r="L24" s="409"/>
+      <c r="M24" s="409"/>
+      <c r="N24" s="409"/>
+      <c r="O24" s="410"/>
     </row>
     <row r="25" spans="1:15" ht="28.5" customHeight="1">
-      <c r="A25" s="465"/>
-      <c r="B25" s="466"/>
-      <c r="C25" s="483"/>
-      <c r="D25" s="483"/>
-      <c r="E25" s="483"/>
-      <c r="F25" s="484"/>
-      <c r="G25" s="422" t="s">
+      <c r="A25" s="174"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="446"/>
+      <c r="D25" s="446"/>
+      <c r="E25" s="446"/>
+      <c r="F25" s="447"/>
+      <c r="G25" s="444" t="s">
         <v>307</v>
       </c>
-      <c r="H25" s="423"/>
-      <c r="I25" s="375"/>
-      <c r="J25" s="375"/>
-      <c r="K25" s="375"/>
-      <c r="L25" s="375"/>
-      <c r="M25" s="375"/>
-      <c r="N25" s="375"/>
-      <c r="O25" s="404"/>
+      <c r="H25" s="445"/>
+      <c r="I25" s="411"/>
+      <c r="J25" s="411"/>
+      <c r="K25" s="411"/>
+      <c r="L25" s="411"/>
+      <c r="M25" s="411"/>
+      <c r="N25" s="411"/>
+      <c r="O25" s="412"/>
     </row>
     <row r="26" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A26" s="465"/>
-      <c r="B26" s="466"/>
-      <c r="C26" s="489"/>
-      <c r="D26" s="489"/>
-      <c r="E26" s="489"/>
-      <c r="F26" s="490"/>
-      <c r="G26" s="380" t="b">
+      <c r="A26" s="174"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="183"/>
+      <c r="D26" s="183"/>
+      <c r="E26" s="183"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="474" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="393"/>
-      <c r="I26" s="381" t="b">
+      <c r="H26" s="475"/>
+      <c r="I26" s="413" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="381"/>
-      <c r="K26" s="381"/>
-      <c r="L26" s="381"/>
-      <c r="M26" s="381"/>
-      <c r="N26" s="381"/>
-      <c r="O26" s="405"/>
+      <c r="J26" s="413"/>
+      <c r="K26" s="413"/>
+      <c r="L26" s="413"/>
+      <c r="M26" s="413"/>
+      <c r="N26" s="413"/>
+      <c r="O26" s="414"/>
     </row>
     <row r="27" spans="1:15" ht="24.75" customHeight="1">
-      <c r="A27" s="465"/>
-      <c r="B27" s="466"/>
-      <c r="C27" s="483" t="s">
+      <c r="A27" s="174"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="446" t="s">
         <v>308</v>
       </c>
-      <c r="D27" s="483"/>
-      <c r="E27" s="483"/>
-      <c r="F27" s="484"/>
-      <c r="G27" s="380"/>
-      <c r="H27" s="393"/>
-      <c r="I27" s="391"/>
-      <c r="J27" s="391"/>
-      <c r="K27" s="391"/>
-      <c r="L27" s="391"/>
-      <c r="M27" s="391"/>
-      <c r="N27" s="391"/>
-      <c r="O27" s="406"/>
+      <c r="D27" s="446"/>
+      <c r="E27" s="446"/>
+      <c r="F27" s="447"/>
+      <c r="G27" s="474"/>
+      <c r="H27" s="475"/>
+      <c r="I27" s="415"/>
+      <c r="J27" s="415"/>
+      <c r="K27" s="415"/>
+      <c r="L27" s="415"/>
+      <c r="M27" s="415"/>
+      <c r="N27" s="415"/>
+      <c r="O27" s="416"/>
     </row>
     <row r="28" spans="1:15" ht="36" customHeight="1">
-      <c r="A28" s="465"/>
-      <c r="B28" s="466"/>
-      <c r="C28" s="483"/>
-      <c r="D28" s="483"/>
-      <c r="E28" s="483"/>
-      <c r="F28" s="484"/>
-      <c r="G28" s="422" t="s">
+      <c r="A28" s="174"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="446"/>
+      <c r="D28" s="446"/>
+      <c r="E28" s="446"/>
+      <c r="F28" s="447"/>
+      <c r="G28" s="444" t="s">
         <v>307</v>
       </c>
-      <c r="H28" s="423"/>
-      <c r="I28" s="375"/>
-      <c r="J28" s="375"/>
-      <c r="K28" s="375"/>
-      <c r="L28" s="375"/>
-      <c r="M28" s="375"/>
-      <c r="N28" s="375"/>
-      <c r="O28" s="404"/>
+      <c r="H28" s="445"/>
+      <c r="I28" s="411"/>
+      <c r="J28" s="411"/>
+      <c r="K28" s="411"/>
+      <c r="L28" s="411"/>
+      <c r="M28" s="411"/>
+      <c r="N28" s="411"/>
+      <c r="O28" s="412"/>
     </row>
     <row r="29" spans="1:15" ht="30.75" customHeight="1">
-      <c r="A29" s="485"/>
-      <c r="B29" s="486"/>
-      <c r="C29" s="487"/>
-      <c r="D29" s="487"/>
-      <c r="E29" s="487"/>
-      <c r="F29" s="488"/>
-      <c r="G29" s="432"/>
-      <c r="H29" s="433"/>
-      <c r="I29" s="433"/>
-      <c r="J29" s="433"/>
-      <c r="K29" s="433"/>
-      <c r="L29" s="433"/>
-      <c r="M29" s="433"/>
-      <c r="N29" s="433"/>
-      <c r="O29" s="434"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="186"/>
+      <c r="C29" s="466"/>
+      <c r="D29" s="466"/>
+      <c r="E29" s="466"/>
+      <c r="F29" s="467"/>
+      <c r="G29" s="417"/>
+      <c r="H29" s="418"/>
+      <c r="I29" s="418"/>
+      <c r="J29" s="418"/>
+      <c r="K29" s="418"/>
+      <c r="L29" s="418"/>
+      <c r="M29" s="418"/>
+      <c r="N29" s="418"/>
+      <c r="O29" s="419"/>
     </row>
     <row r="30" spans="1:15" ht="23.45" customHeight="1">
-      <c r="A30" s="479">
+      <c r="A30" s="491">
         <v>39</v>
       </c>
-      <c r="B30" s="480"/>
-      <c r="C30" s="491" t="s">
+      <c r="B30" s="492"/>
+      <c r="C30" s="468" t="s">
         <v>309</v>
       </c>
-      <c r="D30" s="491"/>
-      <c r="E30" s="491"/>
-      <c r="F30" s="492"/>
-      <c r="G30" s="385" t="b">
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="469"/>
+      <c r="G30" s="462" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="386"/>
-      <c r="I30" s="376" t="b">
+      <c r="H30" s="463"/>
+      <c r="I30" s="409" t="b">
         <v>0</v>
       </c>
-      <c r="J30" s="376"/>
-      <c r="K30" s="376"/>
-      <c r="L30" s="376"/>
-      <c r="M30" s="376"/>
-      <c r="N30" s="376"/>
-      <c r="O30" s="399"/>
+      <c r="J30" s="409"/>
+      <c r="K30" s="409"/>
+      <c r="L30" s="409"/>
+      <c r="M30" s="409"/>
+      <c r="N30" s="409"/>
+      <c r="O30" s="410"/>
     </row>
     <row r="31" spans="1:15" ht="27" customHeight="1">
-      <c r="A31" s="465"/>
-      <c r="B31" s="466"/>
-      <c r="C31" s="462"/>
-      <c r="D31" s="462"/>
-      <c r="E31" s="462"/>
-      <c r="F31" s="493"/>
-      <c r="G31" s="430" t="s">
+      <c r="A31" s="174"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="470"/>
+      <c r="D31" s="470"/>
+      <c r="E31" s="470"/>
+      <c r="F31" s="471"/>
+      <c r="G31" s="464" t="s">
         <v>310</v>
       </c>
-      <c r="H31" s="431"/>
-      <c r="I31" s="379"/>
-      <c r="J31" s="379"/>
-      <c r="K31" s="379"/>
-      <c r="L31" s="379"/>
-      <c r="M31" s="379"/>
-      <c r="N31" s="379"/>
-      <c r="O31" s="407"/>
+      <c r="H31" s="465"/>
+      <c r="I31" s="420"/>
+      <c r="J31" s="420"/>
+      <c r="K31" s="420"/>
+      <c r="L31" s="420"/>
+      <c r="M31" s="420"/>
+      <c r="N31" s="420"/>
+      <c r="O31" s="421"/>
     </row>
     <row r="32" spans="1:15" ht="33.75" customHeight="1">
-      <c r="A32" s="485"/>
-      <c r="B32" s="486"/>
-      <c r="C32" s="494"/>
-      <c r="D32" s="494"/>
-      <c r="E32" s="494"/>
-      <c r="F32" s="495"/>
-      <c r="G32" s="435"/>
-      <c r="H32" s="436"/>
-      <c r="I32" s="436"/>
-      <c r="J32" s="436"/>
-      <c r="K32" s="436"/>
-      <c r="L32" s="436"/>
-      <c r="M32" s="436"/>
-      <c r="N32" s="436"/>
-      <c r="O32" s="437"/>
+      <c r="A32" s="185"/>
+      <c r="B32" s="186"/>
+      <c r="C32" s="472"/>
+      <c r="D32" s="472"/>
+      <c r="E32" s="472"/>
+      <c r="F32" s="473"/>
+      <c r="G32" s="422"/>
+      <c r="H32" s="423"/>
+      <c r="I32" s="423"/>
+      <c r="J32" s="423"/>
+      <c r="K32" s="423"/>
+      <c r="L32" s="423"/>
+      <c r="M32" s="423"/>
+      <c r="N32" s="423"/>
+      <c r="O32" s="424"/>
     </row>
     <row r="33" spans="1:15" ht="46.5" customHeight="1">
-      <c r="A33" s="496">
+      <c r="A33" s="456">
         <v>40</v>
       </c>
-      <c r="B33" s="497"/>
-      <c r="C33" s="483" t="s">
+      <c r="B33" s="457"/>
+      <c r="C33" s="446" t="s">
         <v>311</v>
       </c>
-      <c r="D33" s="483"/>
-      <c r="E33" s="483"/>
-      <c r="F33" s="484"/>
-      <c r="G33" s="438"/>
-      <c r="H33" s="439"/>
-      <c r="I33" s="439"/>
-      <c r="J33" s="439"/>
-      <c r="K33" s="439"/>
-      <c r="L33" s="439"/>
-      <c r="M33" s="439"/>
-      <c r="N33" s="439"/>
-      <c r="O33" s="440"/>
+      <c r="D33" s="446"/>
+      <c r="E33" s="446"/>
+      <c r="F33" s="447"/>
+      <c r="G33" s="459"/>
+      <c r="H33" s="460"/>
+      <c r="I33" s="460"/>
+      <c r="J33" s="460"/>
+      <c r="K33" s="460"/>
+      <c r="L33" s="460"/>
+      <c r="M33" s="460"/>
+      <c r="N33" s="460"/>
+      <c r="O33" s="461"/>
     </row>
     <row r="34" spans="1:15" ht="39.75" customHeight="1">
-      <c r="A34" s="498" t="s">
+      <c r="A34" s="187" t="s">
         <v>312</v>
       </c>
-      <c r="B34" s="499"/>
-      <c r="C34" s="483" t="s">
+      <c r="B34" s="188"/>
+      <c r="C34" s="446" t="s">
         <v>313</v>
       </c>
-      <c r="D34" s="483"/>
-      <c r="E34" s="483"/>
-      <c r="F34" s="484"/>
-      <c r="G34" s="377" t="b">
+      <c r="D34" s="446"/>
+      <c r="E34" s="446"/>
+      <c r="F34" s="447"/>
+      <c r="G34" s="458" t="b">
         <v>0</v>
       </c>
-      <c r="H34" s="388"/>
-      <c r="I34" s="388" t="b">
+      <c r="H34" s="434"/>
+      <c r="I34" s="434" t="b">
         <v>0</v>
       </c>
-      <c r="J34" s="388"/>
-      <c r="K34" s="388"/>
-      <c r="L34" s="388"/>
-      <c r="M34" s="388"/>
-      <c r="N34" s="388"/>
-      <c r="O34" s="389"/>
+      <c r="J34" s="434"/>
+      <c r="K34" s="434"/>
+      <c r="L34" s="434"/>
+      <c r="M34" s="434"/>
+      <c r="N34" s="434"/>
+      <c r="O34" s="435"/>
     </row>
     <row r="35" spans="1:15" ht="36.75" customHeight="1">
-      <c r="A35" s="500"/>
-      <c r="B35" s="499"/>
-      <c r="C35" s="483"/>
-      <c r="D35" s="483"/>
-      <c r="E35" s="483"/>
-      <c r="F35" s="484"/>
-      <c r="G35" s="422" t="s">
+      <c r="A35" s="189"/>
+      <c r="B35" s="188"/>
+      <c r="C35" s="446"/>
+      <c r="D35" s="446"/>
+      <c r="E35" s="446"/>
+      <c r="F35" s="447"/>
+      <c r="G35" s="444" t="s">
         <v>307</v>
       </c>
-      <c r="H35" s="423"/>
-      <c r="I35" s="379"/>
-      <c r="J35" s="379"/>
-      <c r="K35" s="379"/>
-      <c r="L35" s="379"/>
-      <c r="M35" s="379"/>
-      <c r="N35" s="379"/>
-      <c r="O35" s="407"/>
+      <c r="H35" s="445"/>
+      <c r="I35" s="420"/>
+      <c r="J35" s="420"/>
+      <c r="K35" s="420"/>
+      <c r="L35" s="420"/>
+      <c r="M35" s="420"/>
+      <c r="N35" s="420"/>
+      <c r="O35" s="421"/>
     </row>
     <row r="36" spans="1:15" ht="33" customHeight="1">
-      <c r="A36" s="498" t="s">
+      <c r="A36" s="187" t="s">
         <v>314</v>
       </c>
-      <c r="B36" s="499"/>
-      <c r="C36" s="484" t="s">
+      <c r="B36" s="188"/>
+      <c r="C36" s="447" t="s">
         <v>315</v>
       </c>
-      <c r="D36" s="484"/>
-      <c r="E36" s="484"/>
-      <c r="F36" s="484"/>
-      <c r="G36" s="377" t="b">
+      <c r="D36" s="447"/>
+      <c r="E36" s="447"/>
+      <c r="F36" s="447"/>
+      <c r="G36" s="458" t="b">
         <v>0</v>
       </c>
-      <c r="H36" s="388"/>
-      <c r="I36" s="382" t="b">
+      <c r="H36" s="434"/>
+      <c r="I36" s="453" t="b">
         <v>0</v>
       </c>
-      <c r="J36" s="382"/>
-      <c r="K36" s="382"/>
-      <c r="L36" s="382"/>
-      <c r="M36" s="382"/>
-      <c r="N36" s="382"/>
-      <c r="O36" s="408"/>
-    </row>
-    <row r="37" spans="1:15" ht="34.5" customHeight="1">
-      <c r="A37" s="500"/>
-      <c r="B37" s="499"/>
-      <c r="C37" s="484"/>
-      <c r="D37" s="484"/>
-      <c r="E37" s="484"/>
-      <c r="F37" s="484"/>
-      <c r="G37" s="422" t="s">
+      <c r="J36" s="453"/>
+      <c r="K36" s="453"/>
+      <c r="L36" s="453"/>
+      <c r="M36" s="453"/>
+      <c r="N36" s="453"/>
+      <c r="O36" s="454"/>
+    </row>
+    <row r="37" spans="1:15" ht="27.75" customHeight="1">
+      <c r="A37" s="189"/>
+      <c r="B37" s="188"/>
+      <c r="C37" s="447"/>
+      <c r="D37" s="447"/>
+      <c r="E37" s="447"/>
+      <c r="F37" s="447"/>
+      <c r="G37" s="444" t="s">
         <v>307</v>
       </c>
-      <c r="H37" s="423"/>
-      <c r="I37" s="394" t="b">
+      <c r="H37" s="445"/>
+      <c r="I37" s="506" t="b">
         <v>0</v>
       </c>
-      <c r="J37" s="398"/>
-      <c r="K37" s="441"/>
-      <c r="L37" s="442"/>
-      <c r="M37" s="442"/>
-      <c r="N37" s="442"/>
-      <c r="O37" s="443"/>
+      <c r="J37" s="506" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" s="506" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" s="506" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" s="506" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" s="506" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" s="507" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:15" ht="30.75" customHeight="1">
-      <c r="A38" s="498" t="s">
+      <c r="A38" s="187" t="s">
         <v>316</v>
       </c>
-      <c r="B38" s="499"/>
-      <c r="C38" s="483" t="s">
+      <c r="B38" s="188"/>
+      <c r="C38" s="446" t="s">
         <v>317</v>
       </c>
-      <c r="D38" s="483"/>
-      <c r="E38" s="501"/>
-      <c r="F38" s="502"/>
-      <c r="G38" s="383" t="b">
+      <c r="D38" s="446"/>
+      <c r="E38" s="190"/>
+      <c r="F38" s="191"/>
+      <c r="G38" s="448" t="b">
         <v>0</v>
       </c>
-      <c r="H38" s="395"/>
-      <c r="I38" s="396" t="b">
+      <c r="H38" s="449"/>
+      <c r="I38" s="166" t="b">
         <v>0</v>
       </c>
-      <c r="J38" s="396"/>
-      <c r="K38" s="442"/>
-      <c r="L38" s="442"/>
-      <c r="M38" s="442"/>
-      <c r="N38" s="442"/>
-      <c r="O38" s="443"/>
+      <c r="J38" s="166"/>
+      <c r="K38" s="106"/>
+      <c r="L38" s="106"/>
+      <c r="M38" s="106"/>
+      <c r="N38" s="106"/>
+      <c r="O38" s="169"/>
     </row>
     <row r="39" spans="1:15" ht="28.5" customHeight="1">
-      <c r="A39" s="503"/>
-      <c r="B39" s="504"/>
-      <c r="C39" s="504"/>
-      <c r="D39" s="504"/>
-      <c r="E39" s="504"/>
-      <c r="F39" s="505"/>
-      <c r="G39" s="422" t="s">
+      <c r="A39" s="450"/>
+      <c r="B39" s="451"/>
+      <c r="C39" s="451"/>
+      <c r="D39" s="451"/>
+      <c r="E39" s="451"/>
+      <c r="F39" s="452"/>
+      <c r="G39" s="444" t="s">
         <v>307</v>
       </c>
-      <c r="H39" s="423"/>
-      <c r="I39" s="379"/>
-      <c r="J39" s="379"/>
-      <c r="K39" s="379"/>
-      <c r="L39" s="379"/>
-      <c r="M39" s="379"/>
-      <c r="N39" s="379"/>
-      <c r="O39" s="407"/>
+      <c r="H39" s="445"/>
+      <c r="I39" s="420"/>
+      <c r="J39" s="420"/>
+      <c r="K39" s="420"/>
+      <c r="L39" s="420"/>
+      <c r="M39" s="420"/>
+      <c r="N39" s="420"/>
+      <c r="O39" s="421"/>
     </row>
     <row r="40" spans="1:15" ht="37.5" customHeight="1">
-      <c r="A40" s="503"/>
-      <c r="B40" s="506"/>
-      <c r="C40" s="506"/>
-      <c r="D40" s="506"/>
-      <c r="E40" s="506"/>
-      <c r="F40" s="505"/>
-      <c r="G40" s="422"/>
-      <c r="H40" s="423"/>
-      <c r="I40" s="423"/>
-      <c r="J40" s="423"/>
-      <c r="K40" s="423"/>
-      <c r="L40" s="423"/>
-      <c r="M40" s="423"/>
-      <c r="N40" s="423"/>
-      <c r="O40" s="444"/>
+      <c r="A40" s="450"/>
+      <c r="B40" s="451"/>
+      <c r="C40" s="451"/>
+      <c r="D40" s="451"/>
+      <c r="E40" s="451"/>
+      <c r="F40" s="452"/>
+      <c r="G40" s="444"/>
+      <c r="H40" s="445"/>
+      <c r="I40" s="445"/>
+      <c r="J40" s="445"/>
+      <c r="K40" s="445"/>
+      <c r="L40" s="445"/>
+      <c r="M40" s="445"/>
+      <c r="N40" s="445"/>
+      <c r="O40" s="455"/>
     </row>
     <row r="41" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A41" s="507" t="s">
+      <c r="A41" s="403" t="s">
         <v>346</v>
       </c>
-      <c r="B41" s="507"/>
-      <c r="C41" s="507"/>
-      <c r="D41" s="507"/>
-      <c r="E41" s="507"/>
-      <c r="F41" s="507"/>
-      <c r="G41" s="507"/>
-      <c r="H41" s="507"/>
-      <c r="I41" s="507"/>
-      <c r="J41" s="507"/>
-      <c r="K41" s="507"/>
-      <c r="L41" s="507"/>
-      <c r="M41" s="507"/>
-      <c r="N41" s="507"/>
-      <c r="O41" s="507"/>
+      <c r="B41" s="403"/>
+      <c r="C41" s="403"/>
+      <c r="D41" s="403"/>
+      <c r="E41" s="403"/>
+      <c r="F41" s="403"/>
+      <c r="G41" s="403"/>
+      <c r="H41" s="403"/>
+      <c r="I41" s="403"/>
+      <c r="J41" s="403"/>
+      <c r="K41" s="403"/>
+      <c r="L41" s="403"/>
+      <c r="M41" s="403"/>
+      <c r="N41" s="403"/>
+      <c r="O41" s="403"/>
     </row>
     <row r="42" spans="1:15" ht="18" customHeight="1">
-      <c r="A42" s="508" t="s">
+      <c r="A42" s="404" t="s">
         <v>318</v>
       </c>
-      <c r="B42" s="508"/>
-      <c r="C42" s="508"/>
-      <c r="D42" s="508"/>
-      <c r="E42" s="508"/>
-      <c r="F42" s="508"/>
-      <c r="G42" s="508" t="s">
+      <c r="B42" s="404"/>
+      <c r="C42" s="404"/>
+      <c r="D42" s="404"/>
+      <c r="E42" s="404"/>
+      <c r="F42" s="404"/>
+      <c r="G42" s="404" t="s">
         <v>319</v>
       </c>
-      <c r="H42" s="508"/>
-      <c r="I42" s="508"/>
-      <c r="J42" s="508"/>
-      <c r="K42" s="508"/>
-      <c r="L42" s="508"/>
-      <c r="M42" s="509" t="s">
+      <c r="H42" s="404"/>
+      <c r="I42" s="404"/>
+      <c r="J42" s="404"/>
+      <c r="K42" s="404"/>
+      <c r="L42" s="404"/>
+      <c r="M42" s="401" t="s">
         <v>320</v>
       </c>
-      <c r="N42" s="509"/>
-      <c r="O42" s="509"/>
+      <c r="N42" s="401"/>
+      <c r="O42" s="401"/>
     </row>
     <row r="43" spans="1:15" ht="24" customHeight="1">
-      <c r="A43" s="372"/>
-      <c r="B43" s="372"/>
-      <c r="C43" s="372"/>
-      <c r="D43" s="372"/>
-      <c r="E43" s="372"/>
-      <c r="F43" s="372"/>
-      <c r="G43" s="397"/>
-      <c r="H43" s="397"/>
-      <c r="I43" s="397"/>
-      <c r="J43" s="397"/>
-      <c r="K43" s="397"/>
-      <c r="L43" s="397"/>
-      <c r="M43" s="397"/>
-      <c r="N43" s="397"/>
-      <c r="O43" s="397"/>
+      <c r="A43" s="405"/>
+      <c r="B43" s="405"/>
+      <c r="C43" s="405"/>
+      <c r="D43" s="405"/>
+      <c r="E43" s="405"/>
+      <c r="F43" s="405"/>
+      <c r="G43" s="402"/>
+      <c r="H43" s="402"/>
+      <c r="I43" s="402"/>
+      <c r="J43" s="402"/>
+      <c r="K43" s="402"/>
+      <c r="L43" s="402"/>
+      <c r="M43" s="402"/>
+      <c r="N43" s="402"/>
+      <c r="O43" s="402"/>
     </row>
     <row r="44" spans="1:15" ht="24" customHeight="1">
-      <c r="A44" s="372"/>
-      <c r="B44" s="372"/>
-      <c r="C44" s="372"/>
-      <c r="D44" s="372"/>
-      <c r="E44" s="372"/>
-      <c r="F44" s="372"/>
-      <c r="G44" s="397"/>
-      <c r="H44" s="397"/>
-      <c r="I44" s="397"/>
-      <c r="J44" s="397"/>
-      <c r="K44" s="397"/>
-      <c r="L44" s="397"/>
-      <c r="M44" s="397"/>
-      <c r="N44" s="397"/>
-      <c r="O44" s="397"/>
+      <c r="A44" s="405"/>
+      <c r="B44" s="405"/>
+      <c r="C44" s="405"/>
+      <c r="D44" s="405"/>
+      <c r="E44" s="405"/>
+      <c r="F44" s="405"/>
+      <c r="G44" s="402"/>
+      <c r="H44" s="402"/>
+      <c r="I44" s="402"/>
+      <c r="J44" s="402"/>
+      <c r="K44" s="402"/>
+      <c r="L44" s="402"/>
+      <c r="M44" s="402"/>
+      <c r="N44" s="402"/>
+      <c r="O44" s="402"/>
     </row>
     <row r="45" spans="1:15" ht="24" customHeight="1">
-      <c r="A45" s="372"/>
-      <c r="B45" s="372"/>
-      <c r="C45" s="372"/>
-      <c r="D45" s="372"/>
-      <c r="E45" s="372"/>
-      <c r="F45" s="372"/>
-      <c r="G45" s="397"/>
-      <c r="H45" s="397"/>
-      <c r="I45" s="397"/>
-      <c r="J45" s="397"/>
-      <c r="K45" s="397"/>
-      <c r="L45" s="397"/>
-      <c r="M45" s="397"/>
-      <c r="N45" s="397"/>
-      <c r="O45" s="397"/>
+      <c r="A45" s="405"/>
+      <c r="B45" s="405"/>
+      <c r="C45" s="405"/>
+      <c r="D45" s="405"/>
+      <c r="E45" s="405"/>
+      <c r="F45" s="405"/>
+      <c r="G45" s="402"/>
+      <c r="H45" s="402"/>
+      <c r="I45" s="402"/>
+      <c r="J45" s="402"/>
+      <c r="K45" s="402"/>
+      <c r="L45" s="402"/>
+      <c r="M45" s="402"/>
+      <c r="N45" s="402"/>
+      <c r="O45" s="402"/>
     </row>
     <row r="46" spans="1:15" ht="25.5" customHeight="1"/>
     <row r="47" spans="1:15" ht="24.75" customHeight="1"/>
     <row r="48" spans="1:15" ht="20.25" customHeight="1"/>
-    <row r="49" s="447" customFormat="1" ht="18.75" customHeight="1"/>
-    <row r="50" s="447" customFormat="1" ht="21" customHeight="1"/>
-    <row r="51" s="447" customFormat="1" ht="17.25" customHeight="1"/>
-    <row r="52" s="447" customFormat="1" ht="25.5" customHeight="1"/>
-    <row r="53" s="447" customFormat="1" ht="9" customHeight="1"/>
-    <row r="54" s="447" customFormat="1" ht="12" customHeight="1"/>
-    <row r="55" s="447" customFormat="1" ht="10.5" customHeight="1"/>
-    <row r="56" s="447" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" s="447" customFormat="1" ht="8.25" customHeight="1"/>
-    <row r="58" s="447" customFormat="1" ht="28.5" customHeight="1"/>
-    <row r="59" s="447" customFormat="1" ht="53.25" customHeight="1"/>
-    <row r="60" s="447" customFormat="1" ht="18" customHeight="1"/>
-    <row r="61" s="510" customFormat="1" ht="11.25" customHeight="1"/>
-    <row r="62" s="447" customFormat="1" ht="10.5" customHeight="1"/>
+    <row r="49" ht="18.75" customHeight="1"/>
+    <row r="50" ht="21" customHeight="1"/>
+    <row r="51" ht="17.25" customHeight="1"/>
+    <row r="52" ht="25.5" customHeight="1"/>
+    <row r="53" ht="9" customHeight="1"/>
+    <row r="54" ht="12" customHeight="1"/>
+    <row r="55" ht="10.5" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="8.25" customHeight="1"/>
+    <row r="58" ht="28.5" customHeight="1"/>
+    <row r="59" ht="53.25" customHeight="1"/>
+    <row r="60" ht="18" customHeight="1"/>
+    <row r="61" s="192" customFormat="1" ht="11.25" customHeight="1"/>
+    <row r="62" ht="10.5" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7SN7gQhMc2L/QZEPTsNbc3O37PQbXozh/RTZKf32xffVzsWz8OMtK/2iKlpkGg8jYPHkoJCSCjUVTAAkxsRikw==" saltValue="flMHZbMDHNP+h0uUNZF58Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HI85KqrIlc4ZUvr4vE3j0rj3W0Chi9WgtPzlWo/mdrwAzWNT9dNb0YpZRAEzFL8reZXNhOo2wz63CKtOZyRuoA==" saltValue="CDdHUzJEkadi4P8irYdFyw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="97">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="C24:F25"/>
+    <mergeCell ref="C21:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:O13"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:F11"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="G33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="A39:F40"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="I39:O39"/>
+    <mergeCell ref="G40:O40"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I9:O9"/>
+    <mergeCell ref="I10:O10"/>
+    <mergeCell ref="G11:O11"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C36:F37"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="C27:F29"/>
+    <mergeCell ref="C30:F32"/>
+    <mergeCell ref="G26:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="C13:F17"/>
+    <mergeCell ref="C18:F20"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G2:O4"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="I7:O7"/>
+    <mergeCell ref="G8:O8"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G29:O29"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="G32:O32"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="I15:O15"/>
+    <mergeCell ref="I16:O16"/>
+    <mergeCell ref="G17:O17"/>
+    <mergeCell ref="I18:O18"/>
+    <mergeCell ref="I19:O19"/>
+    <mergeCell ref="G20:O20"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G23:O23"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="I26:O27"/>
+    <mergeCell ref="I28:O28"/>
     <mergeCell ref="M42:O42"/>
     <mergeCell ref="M43:O43"/>
     <mergeCell ref="M44:O44"/>
@@ -17158,90 +17243,6 @@
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="G23:O23"/>
-    <mergeCell ref="I24:O24"/>
-    <mergeCell ref="I25:O25"/>
-    <mergeCell ref="I26:O27"/>
-    <mergeCell ref="I28:O28"/>
-    <mergeCell ref="G29:O29"/>
-    <mergeCell ref="I30:O30"/>
-    <mergeCell ref="I31:O31"/>
-    <mergeCell ref="G32:O32"/>
-    <mergeCell ref="I14:O14"/>
-    <mergeCell ref="I15:O15"/>
-    <mergeCell ref="I16:O16"/>
-    <mergeCell ref="G17:O17"/>
-    <mergeCell ref="I18:O18"/>
-    <mergeCell ref="I19:O19"/>
-    <mergeCell ref="G20:O20"/>
-    <mergeCell ref="I21:O21"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="G2:O4"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="I7:O7"/>
-    <mergeCell ref="G8:O8"/>
-    <mergeCell ref="I9:O9"/>
-    <mergeCell ref="I10:O10"/>
-    <mergeCell ref="G11:O11"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C36:F37"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="A39:F40"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="I39:O39"/>
-    <mergeCell ref="G40:O40"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="C27:F29"/>
-    <mergeCell ref="C30:F32"/>
-    <mergeCell ref="G26:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C13:F17"/>
-    <mergeCell ref="C18:F20"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:F11"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:O13"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="C24:F25"/>
-    <mergeCell ref="C21:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -17252,7 +17253,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8193" r:id="rId3" name="Check Box 1">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17274,7 +17275,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8194" r:id="rId4" name="Check Box 2">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17296,7 +17297,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8195" r:id="rId5" name="Check Box 3">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17318,7 +17319,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8196" r:id="rId6" name="Check Box 4">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17340,7 +17341,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8201" r:id="rId7" name="Check Box 9">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17362,7 +17363,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8202" r:id="rId8" name="Check Box 10">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17384,7 +17385,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8203" r:id="rId9" name="Check Box 11">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17406,7 +17407,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8204" r:id="rId10" name="Check Box 12">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17428,7 +17429,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8205" r:id="rId11" name="Check Box 13">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17450,7 +17451,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8206" r:id="rId12" name="Check Box 14">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17472,7 +17473,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8207" r:id="rId13" name="Check Box 15">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17494,7 +17495,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8210" r:id="rId14" name="Check Box 18">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17516,7 +17517,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8212" r:id="rId15" name="Check Box 20">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17538,7 +17539,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8214" r:id="rId16" name="Check Box 22">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17560,7 +17561,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8215" r:id="rId17" name="Check Box 23">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17582,7 +17583,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8216" r:id="rId18" name="Check Box 24">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17604,7 +17605,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8217" r:id="rId19" name="Check Box 25">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17626,7 +17627,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8197" r:id="rId20" name="Check Box 5">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17648,7 +17649,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8198" r:id="rId21" name="Check Box 6">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17670,7 +17671,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8209" r:id="rId22" name="Check Box 17">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17692,7 +17693,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8221" r:id="rId23" name="Check Box 29">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17714,7 +17715,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8220" r:id="rId24" name="Check Box 28">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17736,7 +17737,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8227" r:id="rId25" name="Check Box 35">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
@@ -17758,7 +17759,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="8228" r:id="rId26" name="Check Box 36">
-              <controlPr defaultSize="0" autoPict="0">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
@@ -17779,20 +17780,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="8229" r:id="rId27" name="Check Box 37">
-              <controlPr defaultSize="0" autoPict="0">
+            <control shapeId="8230" r:id="rId27" name="Check Box 38">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>47625</xdr:colOff>
+                    <xdr:col>9</xdr:col>
+                    <xdr:colOff>57150</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>123825</xdr:rowOff>
+                    <xdr:rowOff>95250</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>1304925</xdr:colOff>
+                    <xdr:col>9</xdr:col>
+                    <xdr:colOff>1943100</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>304800</xdr:rowOff>
+                    <xdr:rowOff>276225</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -17801,20 +17802,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="8230" r:id="rId28" name="Check Box 38">
-              <controlPr defaultSize="0" autoPict="0">
+            <control shapeId="8231" r:id="rId28" name="Check Box 39">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>38100</xdr:colOff>
+                    <xdr:col>10</xdr:col>
+                    <xdr:colOff>19050</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>133350</xdr:rowOff>
+                    <xdr:rowOff>104775</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>1924050</xdr:colOff>
+                    <xdr:col>10</xdr:col>
+                    <xdr:colOff>1085850</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>314325</xdr:rowOff>
+                    <xdr:rowOff>276225</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -17823,18 +17824,40 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="8231" r:id="rId29" name="Check Box 39">
-              <controlPr defaultSize="0" autoPict="0">
+            <control shapeId="8232" r:id="rId29" name="Check Box 40">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>1962150</xdr:colOff>
+                    <xdr:col>11</xdr:col>
+                    <xdr:colOff>28575</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>123825</xdr:rowOff>
+                    <xdr:rowOff>95250</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>10</xdr:col>
+                    <xdr:col>11</xdr:col>
                     <xdr:colOff>1047750</xdr:colOff>
+                    <xdr:row>36</xdr:row>
+                    <xdr:rowOff>276225</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="8233" r:id="rId30" name="Check Box 41">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:row>36</xdr:row>
+                    <xdr:rowOff>104775</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>1009650</xdr:colOff>
                     <xdr:row>36</xdr:row>
                     <xdr:rowOff>295275</xdr:rowOff>
                   </to>
@@ -17845,18 +17868,18 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="8232" r:id="rId30" name="Check Box 40">
-              <controlPr defaultSize="0" autoPict="0">
+            <control shapeId="8234" r:id="rId31" name="Check Box 42">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>1095375</xdr:colOff>
+                    <xdr:col>13</xdr:col>
+                    <xdr:colOff>28575</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>114300</xdr:rowOff>
+                    <xdr:rowOff>104775</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>1000125</xdr:colOff>
+                    <xdr:col>13</xdr:col>
+                    <xdr:colOff>1190625</xdr:colOff>
                     <xdr:row>36</xdr:row>
                     <xdr:rowOff>295275</xdr:rowOff>
                   </to>
@@ -17867,20 +17890,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="8233" r:id="rId31" name="Check Box 41">
-              <controlPr defaultSize="0" autoPict="0">
+            <control shapeId="8235" r:id="rId32" name="Check Box 43">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>12</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:col>14</xdr:col>
+                    <xdr:colOff>19050</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>114300</xdr:rowOff>
+                    <xdr:rowOff>95250</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>12</xdr:col>
-                    <xdr:colOff>1000125</xdr:colOff>
+                    <xdr:col>14</xdr:col>
+                    <xdr:colOff>1352550</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>304800</xdr:rowOff>
+                    <xdr:rowOff>276225</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -17889,42 +17912,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="8234" r:id="rId32" name="Check Box 42">
-              <controlPr defaultSize="0" autoPict="0">
+            <control shapeId="8229" r:id="rId33" name="Check Box 37">
+              <controlPr locked="0" defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>13</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>47625</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>114300</xdr:rowOff>
+                    <xdr:rowOff>104775</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>13</xdr:col>
-                    <xdr:colOff>1162050</xdr:colOff>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>1304925</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>304800</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="8235" r:id="rId33" name="Check Box 43">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>14</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>36</xdr:row>
-                    <xdr:rowOff>123825</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>14</xdr:col>
-                    <xdr:colOff>1352550</xdr:colOff>
-                    <xdr:row>36</xdr:row>
-                    <xdr:rowOff>304800</xdr:rowOff>
+                    <xdr:rowOff>285750</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -17954,227 +17955,244 @@
       <c r="A1" s="92" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="287" t="s">
+      <c r="B1" s="335" t="s">
         <v>250</v>
       </c>
-      <c r="C1" s="287"/>
-      <c r="D1" s="287"/>
-      <c r="E1" s="287"/>
-      <c r="F1" s="287"/>
-      <c r="G1" s="287"/>
-      <c r="H1" s="287"/>
-      <c r="I1" s="287"/>
-      <c r="J1" s="287"/>
+      <c r="C1" s="335"/>
+      <c r="D1" s="335"/>
+      <c r="E1" s="335"/>
+      <c r="F1" s="335"/>
+      <c r="G1" s="335"/>
+      <c r="H1" s="335"/>
+      <c r="I1" s="335"/>
+      <c r="J1" s="335"/>
     </row>
     <row r="2" spans="1:10" ht="21" customHeight="1">
       <c r="A2" s="93">
         <v>22</v>
       </c>
-      <c r="B2" s="286" t="s">
+      <c r="B2" s="327" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="286"/>
-      <c r="D2" s="288"/>
-      <c r="E2" s="289"/>
-      <c r="F2" s="289"/>
-      <c r="G2" s="289"/>
-      <c r="H2" s="289"/>
-      <c r="I2" s="289"/>
-      <c r="J2" s="290"/>
+      <c r="C2" s="327"/>
+      <c r="D2" s="336"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="338"/>
     </row>
     <row r="3" spans="1:10" ht="21" customHeight="1">
       <c r="A3" s="94"/>
-      <c r="B3" s="286" t="s">
+      <c r="B3" s="327" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="286"/>
-      <c r="D3" s="291"/>
-      <c r="E3" s="292"/>
-      <c r="F3" s="293"/>
-      <c r="G3" s="294" t="s">
+      <c r="C3" s="327"/>
+      <c r="D3" s="329"/>
+      <c r="E3" s="330"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="340" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="295"/>
-      <c r="I3" s="296"/>
-      <c r="J3" s="297"/>
+      <c r="H3" s="341"/>
+      <c r="I3" s="342"/>
+      <c r="J3" s="322"/>
     </row>
     <row r="4" spans="1:10" ht="21" customHeight="1">
       <c r="A4" s="94"/>
-      <c r="B4" s="286" t="s">
+      <c r="B4" s="327" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="286"/>
-      <c r="D4" s="291"/>
-      <c r="E4" s="292"/>
-      <c r="F4" s="292"/>
-      <c r="G4" s="292"/>
-      <c r="H4" s="292"/>
-      <c r="I4" s="292"/>
-      <c r="J4" s="298"/>
+      <c r="C4" s="327"/>
+      <c r="D4" s="329"/>
+      <c r="E4" s="330"/>
+      <c r="F4" s="330"/>
+      <c r="G4" s="330"/>
+      <c r="H4" s="330"/>
+      <c r="I4" s="330"/>
+      <c r="J4" s="331"/>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1">
       <c r="A5" s="95"/>
-      <c r="B5" s="286" t="s">
+      <c r="B5" s="327" t="s">
         <v>252</v>
       </c>
-      <c r="C5" s="286"/>
-      <c r="D5" s="299"/>
-      <c r="E5" s="300"/>
-      <c r="F5" s="300"/>
-      <c r="G5" s="300"/>
-      <c r="H5" s="300"/>
-      <c r="I5" s="300"/>
-      <c r="J5" s="301"/>
+      <c r="C5" s="327"/>
+      <c r="D5" s="315"/>
+      <c r="E5" s="316"/>
+      <c r="F5" s="316"/>
+      <c r="G5" s="316"/>
+      <c r="H5" s="316"/>
+      <c r="I5" s="316"/>
+      <c r="J5" s="317"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="95"/>
-      <c r="B6" s="286" t="s">
+      <c r="B6" s="327" t="s">
         <v>253</v>
       </c>
-      <c r="C6" s="286"/>
-      <c r="D6" s="299"/>
-      <c r="E6" s="300"/>
-      <c r="F6" s="300"/>
-      <c r="G6" s="300"/>
-      <c r="H6" s="300"/>
-      <c r="I6" s="300"/>
-      <c r="J6" s="301"/>
+      <c r="C6" s="327"/>
+      <c r="D6" s="315"/>
+      <c r="E6" s="316"/>
+      <c r="F6" s="316"/>
+      <c r="G6" s="316"/>
+      <c r="H6" s="316"/>
+      <c r="I6" s="316"/>
+      <c r="J6" s="317"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="95"/>
-      <c r="B7" s="286" t="s">
+      <c r="B7" s="327" t="s">
         <v>254</v>
       </c>
-      <c r="C7" s="286"/>
-      <c r="D7" s="302"/>
-      <c r="E7" s="303"/>
-      <c r="F7" s="303"/>
-      <c r="G7" s="303"/>
-      <c r="H7" s="303"/>
-      <c r="I7" s="303"/>
-      <c r="J7" s="304"/>
+      <c r="C7" s="327"/>
+      <c r="D7" s="332"/>
+      <c r="E7" s="333"/>
+      <c r="F7" s="333"/>
+      <c r="G7" s="333"/>
+      <c r="H7" s="333"/>
+      <c r="I7" s="333"/>
+      <c r="J7" s="334"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="95"/>
-      <c r="B8" s="286" t="s">
+      <c r="B8" s="327" t="s">
         <v>255</v>
       </c>
-      <c r="C8" s="286"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="303"/>
-      <c r="F8" s="303"/>
-      <c r="G8" s="303"/>
-      <c r="H8" s="303"/>
-      <c r="I8" s="303"/>
-      <c r="J8" s="304"/>
+      <c r="C8" s="327"/>
+      <c r="D8" s="332"/>
+      <c r="E8" s="333"/>
+      <c r="F8" s="333"/>
+      <c r="G8" s="333"/>
+      <c r="H8" s="333"/>
+      <c r="I8" s="333"/>
+      <c r="J8" s="334"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="96">
         <v>24</v>
       </c>
-      <c r="B9" s="313" t="s">
+      <c r="B9" s="328" t="s">
         <v>256</v>
       </c>
-      <c r="C9" s="313"/>
-      <c r="D9" s="299"/>
-      <c r="E9" s="300"/>
-      <c r="F9" s="300"/>
-      <c r="G9" s="300"/>
-      <c r="H9" s="300"/>
-      <c r="I9" s="300"/>
-      <c r="J9" s="301"/>
+      <c r="C9" s="328"/>
+      <c r="D9" s="315"/>
+      <c r="E9" s="316"/>
+      <c r="F9" s="316"/>
+      <c r="G9" s="316"/>
+      <c r="H9" s="316"/>
+      <c r="I9" s="316"/>
+      <c r="J9" s="317"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="94"/>
-      <c r="B10" s="286" t="s">
+      <c r="B10" s="327" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="286"/>
-      <c r="D10" s="299"/>
-      <c r="E10" s="300"/>
-      <c r="F10" s="305"/>
-      <c r="G10" s="306" t="s">
+      <c r="C10" s="327"/>
+      <c r="D10" s="315"/>
+      <c r="E10" s="316"/>
+      <c r="F10" s="318"/>
+      <c r="G10" s="319" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="307"/>
-      <c r="I10" s="308"/>
-      <c r="J10" s="297"/>
+      <c r="H10" s="320"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="322"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="94"/>
-      <c r="B11" s="286" t="s">
+      <c r="B11" s="327" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="286"/>
-      <c r="D11" s="309"/>
-      <c r="E11" s="300"/>
-      <c r="F11" s="300"/>
-      <c r="G11" s="300"/>
-      <c r="H11" s="300"/>
-      <c r="I11" s="300"/>
-      <c r="J11" s="301"/>
+      <c r="C11" s="327"/>
+      <c r="D11" s="323"/>
+      <c r="E11" s="316"/>
+      <c r="F11" s="316"/>
+      <c r="G11" s="316"/>
+      <c r="H11" s="316"/>
+      <c r="I11" s="316"/>
+      <c r="J11" s="317"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="97">
         <v>25</v>
       </c>
-      <c r="B12" s="310" t="s">
+      <c r="B12" s="324" t="s">
         <v>257</v>
       </c>
-      <c r="C12" s="311"/>
-      <c r="D12" s="311"/>
-      <c r="E12" s="311"/>
-      <c r="F12" s="311"/>
-      <c r="G12" s="311"/>
-      <c r="H12" s="311"/>
-      <c r="I12" s="311"/>
-      <c r="J12" s="312"/>
+      <c r="C12" s="325"/>
+      <c r="D12" s="325"/>
+      <c r="E12" s="325"/>
+      <c r="F12" s="325"/>
+      <c r="G12" s="325"/>
+      <c r="H12" s="325"/>
+      <c r="I12" s="325"/>
+      <c r="J12" s="326"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="94"/>
-      <c r="B13" s="286" t="s">
+      <c r="B13" s="327" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="286"/>
-      <c r="D13" s="299"/>
-      <c r="E13" s="300"/>
-      <c r="F13" s="300"/>
-      <c r="G13" s="300"/>
-      <c r="H13" s="300"/>
-      <c r="I13" s="300"/>
-      <c r="J13" s="301"/>
+      <c r="C13" s="327"/>
+      <c r="D13" s="315"/>
+      <c r="E13" s="316"/>
+      <c r="F13" s="316"/>
+      <c r="G13" s="316"/>
+      <c r="H13" s="316"/>
+      <c r="I13" s="316"/>
+      <c r="J13" s="317"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="94"/>
-      <c r="B14" s="286" t="s">
+      <c r="B14" s="327" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="286"/>
-      <c r="D14" s="299"/>
-      <c r="E14" s="300"/>
-      <c r="F14" s="300"/>
-      <c r="G14" s="300"/>
-      <c r="H14" s="300"/>
-      <c r="I14" s="300"/>
-      <c r="J14" s="301"/>
+      <c r="C14" s="327"/>
+      <c r="D14" s="315"/>
+      <c r="E14" s="316"/>
+      <c r="F14" s="316"/>
+      <c r="G14" s="316"/>
+      <c r="H14" s="316"/>
+      <c r="I14" s="316"/>
+      <c r="J14" s="317"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1" thickBot="1">
       <c r="A15" s="98"/>
-      <c r="B15" s="286" t="s">
+      <c r="B15" s="327" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="286"/>
-      <c r="D15" s="299"/>
-      <c r="E15" s="300"/>
-      <c r="F15" s="300"/>
-      <c r="G15" s="300"/>
-      <c r="H15" s="300"/>
-      <c r="I15" s="300"/>
-      <c r="J15" s="301"/>
+      <c r="C15" s="327"/>
+      <c r="D15" s="315"/>
+      <c r="E15" s="316"/>
+      <c r="F15" s="316"/>
+      <c r="G15" s="316"/>
+      <c r="H15" s="316"/>
+      <c r="I15" s="316"/>
+      <c r="J15" s="317"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="94KVciG4kdECMCBRaZ/kGUPIuUdTIjG67RnmSldA6WYOzuQmRnZSJRxdUi03GpwtwoEXd0J15wJilUTAVO1QkA==" saltValue="4px6JZ8PPWxSqTy644m1tg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="32">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D14:J14"/>
     <mergeCell ref="D15:J15"/>
@@ -18190,23 +18208,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18357,14 +18358,14 @@
       <c r="F1" s="120"/>
       <c r="G1" s="121"/>
       <c r="H1" s="119"/>
-      <c r="I1" s="314" t="s">
+      <c r="I1" s="343" t="s">
         <v>261</v>
       </c>
-      <c r="J1" s="314"/>
-      <c r="K1" s="314"/>
-      <c r="L1" s="314"/>
-      <c r="M1" s="314"/>
-      <c r="N1" s="314"/>
+      <c r="J1" s="343"/>
+      <c r="K1" s="343"/>
+      <c r="L1" s="343"/>
+      <c r="M1" s="343"/>
+      <c r="N1" s="343"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1">
       <c r="A2" s="107" t="s">
@@ -18372,17 +18373,17 @@
       </c>
       <c r="B2" s="108"/>
       <c r="C2" s="108"/>
-      <c r="D2" s="321" t="s">
+      <c r="D2" s="350" t="s">
         <v>262</v>
       </c>
-      <c r="E2" s="322"/>
-      <c r="F2" s="315" t="s">
+      <c r="E2" s="351"/>
+      <c r="F2" s="344" t="s">
         <v>263</v>
       </c>
-      <c r="G2" s="315" t="s">
+      <c r="G2" s="344" t="s">
         <v>326</v>
       </c>
-      <c r="H2" s="318" t="s">
+      <c r="H2" s="347" t="s">
         <v>264</v>
       </c>
     </row>
@@ -18396,11 +18397,11 @@
       <c r="C3" s="110" t="s">
         <v>266</v>
       </c>
-      <c r="D3" s="323"/>
-      <c r="E3" s="324"/>
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="319"/>
+      <c r="D3" s="352"/>
+      <c r="E3" s="353"/>
+      <c r="F3" s="345"/>
+      <c r="G3" s="345"/>
+      <c r="H3" s="348"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1">
       <c r="A4" s="111"/>
@@ -18412,9 +18413,9 @@
       <c r="E4" s="115" t="s">
         <v>268</v>
       </c>
-      <c r="F4" s="317"/>
-      <c r="G4" s="317"/>
-      <c r="H4" s="320"/>
+      <c r="F4" s="346"/>
+      <c r="G4" s="346"/>
+      <c r="H4" s="349"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="122"/>
@@ -18591,13 +18592,13 @@
       <c r="D1" s="133"/>
       <c r="E1" s="133"/>
       <c r="F1" s="133"/>
-      <c r="G1" s="327"/>
-      <c r="H1" s="327"/>
-      <c r="I1" s="327"/>
-      <c r="J1" s="327"/>
-      <c r="K1" s="327"/>
-      <c r="L1" s="327"/>
-      <c r="M1" s="327"/>
+      <c r="G1" s="356"/>
+      <c r="H1" s="356"/>
+      <c r="I1" s="356"/>
+      <c r="J1" s="356"/>
+      <c r="K1" s="356"/>
+      <c r="L1" s="356"/>
+      <c r="M1" s="356"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1">
       <c r="A2" s="134"/>
@@ -18621,10 +18622,10 @@
       <c r="D3" s="141" t="s">
         <v>271</v>
       </c>
-      <c r="E3" s="325" t="s">
+      <c r="E3" s="354" t="s">
         <v>272</v>
       </c>
-      <c r="F3" s="326"/>
+      <c r="F3" s="355"/>
       <c r="N3" s="103"/>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1">
@@ -19616,63 +19617,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A1" s="328" t="s">
+      <c r="A1" s="357" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="329"/>
-      <c r="C1" s="329"/>
-      <c r="D1" s="329"/>
-      <c r="E1" s="329"/>
-      <c r="F1" s="329"/>
-      <c r="G1" s="329"/>
-      <c r="H1" s="330"/>
+      <c r="B1" s="358"/>
+      <c r="C1" s="358"/>
+      <c r="D1" s="358"/>
+      <c r="E1" s="358"/>
+      <c r="F1" s="358"/>
+      <c r="G1" s="358"/>
+      <c r="H1" s="359"/>
     </row>
     <row r="2" spans="1:14" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A2" s="331" t="s">
+      <c r="A2" s="360" t="s">
         <v>275</v>
       </c>
-      <c r="B2" s="332"/>
-      <c r="C2" s="332"/>
-      <c r="D2" s="332"/>
-      <c r="E2" s="332"/>
-      <c r="F2" s="332"/>
-      <c r="G2" s="332"/>
-      <c r="H2" s="333"/>
+      <c r="B2" s="361"/>
+      <c r="C2" s="361"/>
+      <c r="D2" s="361"/>
+      <c r="E2" s="361"/>
+      <c r="F2" s="361"/>
+      <c r="G2" s="361"/>
+      <c r="H2" s="362"/>
     </row>
     <row r="3" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A3" s="343" t="s">
+      <c r="A3" s="372" t="s">
         <v>329</v>
       </c>
-      <c r="B3" s="344"/>
-      <c r="C3" s="334" t="s">
+      <c r="B3" s="373"/>
+      <c r="C3" s="363" t="s">
         <v>276</v>
       </c>
-      <c r="D3" s="337" t="s">
+      <c r="D3" s="366" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="337" t="s">
+      <c r="E3" s="366" t="s">
         <v>278</v>
       </c>
-      <c r="F3" s="337" t="s">
+      <c r="F3" s="366" t="s">
         <v>279</v>
       </c>
-      <c r="G3" s="315" t="s">
+      <c r="G3" s="344" t="s">
         <v>280</v>
       </c>
-      <c r="H3" s="340" t="s">
+      <c r="H3" s="369" t="s">
         <v>325</v>
       </c>
       <c r="N3" s="152"/>
     </row>
     <row r="4" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A4" s="345"/>
-      <c r="B4" s="346"/>
-      <c r="C4" s="335"/>
-      <c r="D4" s="338"/>
-      <c r="E4" s="338"/>
-      <c r="F4" s="338"/>
-      <c r="G4" s="316"/>
-      <c r="H4" s="341"/>
+      <c r="A4" s="374"/>
+      <c r="B4" s="375"/>
+      <c r="C4" s="364"/>
+      <c r="D4" s="367"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="345"/>
+      <c r="H4" s="370"/>
       <c r="N4" s="152"/>
     </row>
     <row r="5" spans="1:14" ht="30.75" customHeight="1">
@@ -19682,12 +19683,12 @@
       <c r="B5" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="C5" s="336"/>
-      <c r="D5" s="339"/>
-      <c r="E5" s="339"/>
-      <c r="F5" s="339"/>
-      <c r="G5" s="317"/>
-      <c r="H5" s="342"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="368"/>
+      <c r="E5" s="368"/>
+      <c r="F5" s="368"/>
+      <c r="G5" s="346"/>
+      <c r="H5" s="371"/>
       <c r="N5" s="152"/>
     </row>
     <row r="6" spans="1:14">
@@ -19999,17 +20000,17 @@
       <c r="Q1" s="142"/>
     </row>
     <row r="2" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A2" s="347" t="s">
+      <c r="A2" s="376" t="s">
         <v>282</v>
       </c>
-      <c r="B2" s="334" t="s">
+      <c r="B2" s="363" t="s">
         <v>330</v>
       </c>
-      <c r="C2" s="353"/>
-      <c r="D2" s="337" t="s">
+      <c r="C2" s="382"/>
+      <c r="D2" s="366" t="s">
         <v>283</v>
       </c>
-      <c r="E2" s="350" t="s">
+      <c r="E2" s="379" t="s">
         <v>284</v>
       </c>
       <c r="F2" s="158"/>
@@ -20026,11 +20027,11 @@
       <c r="Q2" s="142"/>
     </row>
     <row r="3" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A3" s="348"/>
-      <c r="B3" s="335"/>
-      <c r="C3" s="354"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="351"/>
+      <c r="A3" s="377"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="383"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="380"/>
       <c r="F3" s="158"/>
       <c r="G3" s="142"/>
       <c r="H3" s="142"/>
@@ -20045,15 +20046,15 @@
       <c r="Q3" s="142"/>
     </row>
     <row r="4" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A4" s="349"/>
+      <c r="A4" s="378"/>
       <c r="B4" s="146" t="s">
         <v>267</v>
       </c>
       <c r="C4" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="339"/>
-      <c r="E4" s="352"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="381"/>
       <c r="F4" s="158"/>
       <c r="G4" s="142"/>
       <c r="H4" s="142"/>
@@ -20542,62 +20543,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A1" s="355" t="s">
+      <c r="A1" s="384" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="356"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="357"/>
+      <c r="B1" s="385"/>
+      <c r="C1" s="385"/>
+      <c r="D1" s="385"/>
+      <c r="E1" s="385"/>
+      <c r="F1" s="386"/>
     </row>
     <row r="2" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A2" s="358" t="s">
+      <c r="A2" s="387" t="s">
         <v>286</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="360"/>
+      <c r="B2" s="388"/>
+      <c r="C2" s="388"/>
+      <c r="D2" s="388"/>
+      <c r="E2" s="388"/>
+      <c r="F2" s="389"/>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A3" s="361" t="s">
+      <c r="A3" s="390" t="s">
         <v>287</v>
       </c>
-      <c r="B3" s="366" t="s">
+      <c r="B3" s="395" t="s">
         <v>331</v>
       </c>
-      <c r="C3" s="367"/>
-      <c r="D3" s="363" t="s">
+      <c r="C3" s="396"/>
+      <c r="D3" s="392" t="s">
         <v>283</v>
       </c>
-      <c r="E3" s="338" t="s">
+      <c r="E3" s="367" t="s">
         <v>288</v>
       </c>
-      <c r="F3" s="365" t="s">
+      <c r="F3" s="394" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A4" s="362"/>
-      <c r="B4" s="335"/>
-      <c r="C4" s="368"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="338"/>
-      <c r="F4" s="351"/>
+      <c r="A4" s="391"/>
+      <c r="B4" s="364"/>
+      <c r="C4" s="397"/>
+      <c r="D4" s="392"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="380"/>
     </row>
     <row r="5" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A5" s="345"/>
+      <c r="A5" s="374"/>
       <c r="B5" s="146" t="s">
         <v>267</v>
       </c>
       <c r="C5" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="364"/>
-      <c r="E5" s="339"/>
-      <c r="F5" s="352"/>
+      <c r="D5" s="393"/>
+      <c r="E5" s="368"/>
+      <c r="F5" s="381"/>
     </row>
     <row r="6" spans="1:8" ht="18.75" customHeight="1">
       <c r="A6" s="161"/>
@@ -20799,11 +20800,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A1" s="369" t="s">
+      <c r="A1" s="398" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="370"/>
-      <c r="C1" s="371"/>
+      <c r="B1" s="399"/>
+      <c r="C1" s="400"/>
     </row>
     <row r="2" spans="1:13" ht="38.25" customHeight="1">
       <c r="A2" s="163" t="s">

--- a/public/pds.xlsx
+++ b/public/pds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cenro\PMS-intern\rsp-hr-tagum-cityhall\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D5EEFF-FECB-4AA3-B426-EC2F25DEE780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422C164A-D023-4B8C-B273-E9308DED200F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3745,7 +3745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="508">
+  <cellXfs count="507">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -4370,6 +4370,390 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="28" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4381,10 +4765,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4405,389 +4785,57 @@
     </xf>
     <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4802,6 +4850,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4816,10 +4876,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4833,64 +4889,8 @@
     <xf numFmtId="49" fontId="50" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -5064,288 +5064,104 @@
     <xf numFmtId="49" fontId="52" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5360,11 +5176,123 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5381,53 +5309,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5438,13 +5397,50 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6389,7 +6385,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6476,7 +6472,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6563,7 +6559,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6650,7 +6646,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6737,7 +6733,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6824,7 +6820,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6911,7 +6907,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -6998,7 +6994,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7085,7 +7081,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7172,7 +7168,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7259,7 +7255,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7733,7 +7729,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7753,7 +7749,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -7820,7 +7816,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7840,7 +7836,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -7907,7 +7903,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -7927,7 +7923,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -7994,7 +7990,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8014,7 +8010,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8081,7 +8077,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8101,7 +8097,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8168,7 +8164,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8188,7 +8184,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8255,7 +8251,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8275,7 +8271,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8342,7 +8338,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8362,7 +8358,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8429,7 +8425,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8449,7 +8445,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8516,7 +8512,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8536,7 +8532,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8603,7 +8599,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8623,7 +8619,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8690,7 +8686,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8710,7 +8706,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8777,7 +8773,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8797,7 +8793,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8864,7 +8860,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8884,7 +8880,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -8951,7 +8947,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -8971,7 +8967,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -9038,7 +9034,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9058,7 +9054,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -9125,7 +9121,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9145,7 +9141,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -9212,7 +9208,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9232,7 +9228,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -9299,7 +9295,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9319,7 +9315,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -9386,7 +9382,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9406,7 +9402,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -9473,7 +9469,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9493,7 +9489,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -9560,7 +9556,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9580,7 +9576,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -9883,7 +9879,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9903,7 +9899,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -9970,7 +9966,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -9990,7 +9986,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -10000,15 +9996,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>47626</xdr:colOff>
+          <xdr:colOff>47625</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>101844</xdr:rowOff>
+          <xdr:rowOff>104775</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>1304926</xdr:colOff>
+          <xdr:colOff>1304925</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>282819</xdr:rowOff>
+          <xdr:rowOff>285750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10057,7 +10053,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10077,7 +10073,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -10087,15 +10083,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>60080</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>96716</xdr:rowOff>
+          <xdr:rowOff>95250</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>1946030</xdr:colOff>
+          <xdr:colOff>1943100</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>277691</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10144,7 +10140,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10164,7 +10160,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -10174,15 +10170,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>20514</xdr:colOff>
+          <xdr:colOff>19050</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>101844</xdr:rowOff>
+          <xdr:rowOff>104775</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>1084384</xdr:colOff>
+          <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>273294</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10231,7 +10227,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10251,7 +10247,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -10261,15 +10257,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>32972</xdr:colOff>
+          <xdr:colOff>28575</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>99646</xdr:rowOff>
+          <xdr:rowOff>95250</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>1044087</xdr:colOff>
+          <xdr:colOff>1047750</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>280621</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10318,7 +10314,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10338,7 +10334,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -10348,15 +10344,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>16851</xdr:colOff>
+          <xdr:colOff>19050</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>106973</xdr:rowOff>
+          <xdr:rowOff>104775</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>1007451</xdr:colOff>
+          <xdr:colOff>1009650</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>297473</xdr:rowOff>
+          <xdr:rowOff>295275</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10405,7 +10401,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10425,7 +10421,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -10435,15 +10431,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>13</xdr:col>
-          <xdr:colOff>29308</xdr:colOff>
+          <xdr:colOff>28575</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>106973</xdr:rowOff>
+          <xdr:rowOff>104775</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>13</xdr:col>
-          <xdr:colOff>1191358</xdr:colOff>
+          <xdr:colOff>1190625</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>297473</xdr:rowOff>
+          <xdr:rowOff>295275</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10492,7 +10488,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10512,7 +10508,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -10524,13 +10520,13 @@
           <xdr:col>14</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>94517</xdr:rowOff>
+          <xdr:rowOff>95250</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
           <xdr:colOff>1352550</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>275492</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10579,7 +10575,7 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -10599,7 +10595,7 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:clientData/>
+        <xdr:clientData fLocksWithSheet="0"/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -10890,20 +10886,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
-      <c r="A1" s="226"/>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="228"/>
+      <c r="A1" s="275"/>
+      <c r="B1" s="276"/>
+      <c r="C1" s="276"/>
+      <c r="D1" s="276"/>
+      <c r="E1" s="276"/>
+      <c r="F1" s="276"/>
+      <c r="G1" s="276"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="276"/>
+      <c r="J1" s="276"/>
+      <c r="K1" s="276"/>
+      <c r="L1" s="276"/>
+      <c r="M1" s="276"/>
+      <c r="N1" s="277"/>
     </row>
     <row r="2" spans="1:22" ht="11.25" customHeight="1">
       <c r="A2" s="40"/>
@@ -10933,73 +10929,73 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="41.25" customHeight="1">
-      <c r="A3" s="229" t="s">
+      <c r="A3" s="278" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="230"/>
-      <c r="C3" s="230"/>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
-      <c r="G3" s="230"/>
-      <c r="H3" s="230"/>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
-      <c r="M3" s="230"/>
-      <c r="N3" s="231"/>
-      <c r="R3" s="271"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="273"/>
+      <c r="B3" s="279"/>
+      <c r="C3" s="279"/>
+      <c r="D3" s="279"/>
+      <c r="E3" s="279"/>
+      <c r="F3" s="279"/>
+      <c r="G3" s="279"/>
+      <c r="H3" s="279"/>
+      <c r="I3" s="279"/>
+      <c r="J3" s="279"/>
+      <c r="K3" s="279"/>
+      <c r="L3" s="279"/>
+      <c r="M3" s="279"/>
+      <c r="N3" s="280"/>
+      <c r="R3" s="218"/>
+      <c r="S3" s="219"/>
+      <c r="T3" s="219"/>
+      <c r="U3" s="219"/>
+      <c r="V3" s="220"/>
     </row>
     <row r="4" spans="1:22" ht="21.75" customHeight="1">
-      <c r="A4" s="232" t="s">
+      <c r="A4" s="281" t="s">
         <v>340</v>
       </c>
-      <c r="B4" s="233"/>
-      <c r="C4" s="233"/>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
-      <c r="M4" s="233"/>
-      <c r="N4" s="234"/>
-      <c r="R4" s="274"/>
-      <c r="S4" s="275"/>
-      <c r="T4" s="275"/>
-      <c r="U4" s="275"/>
-      <c r="V4" s="276"/>
+      <c r="B4" s="282"/>
+      <c r="C4" s="282"/>
+      <c r="D4" s="282"/>
+      <c r="E4" s="282"/>
+      <c r="F4" s="282"/>
+      <c r="G4" s="282"/>
+      <c r="H4" s="282"/>
+      <c r="I4" s="282"/>
+      <c r="J4" s="282"/>
+      <c r="K4" s="282"/>
+      <c r="L4" s="282"/>
+      <c r="M4" s="282"/>
+      <c r="N4" s="283"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="222"/>
+      <c r="T4" s="222"/>
+      <c r="U4" s="222"/>
+      <c r="V4" s="223"/>
     </row>
     <row r="5" spans="1:22" ht="11.25" customHeight="1">
-      <c r="A5" s="235" t="s">
+      <c r="A5" s="284" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="236"/>
-      <c r="C5" s="236"/>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
-      <c r="M5" s="236"/>
-      <c r="N5" s="237"/>
-      <c r="R5" s="274"/>
-      <c r="S5" s="275"/>
-      <c r="T5" s="275"/>
-      <c r="U5" s="275"/>
-      <c r="V5" s="276"/>
+      <c r="B5" s="285"/>
+      <c r="C5" s="285"/>
+      <c r="D5" s="285"/>
+      <c r="E5" s="285"/>
+      <c r="F5" s="285"/>
+      <c r="G5" s="285"/>
+      <c r="H5" s="285"/>
+      <c r="I5" s="285"/>
+      <c r="J5" s="285"/>
+      <c r="K5" s="285"/>
+      <c r="L5" s="285"/>
+      <c r="M5" s="285"/>
+      <c r="N5" s="286"/>
+      <c r="R5" s="221"/>
+      <c r="S5" s="222"/>
+      <c r="T5" s="222"/>
+      <c r="U5" s="222"/>
+      <c r="V5" s="223"/>
     </row>
     <row r="6" spans="1:22" ht="36.75" hidden="1" customHeight="1">
       <c r="A6" s="43"/>
@@ -11016,11 +11012,11 @@
       <c r="L6" s="45"/>
       <c r="M6" s="45"/>
       <c r="N6" s="46"/>
-      <c r="R6" s="274"/>
-      <c r="S6" s="275"/>
-      <c r="T6" s="275"/>
-      <c r="U6" s="275"/>
-      <c r="V6" s="276"/>
+      <c r="R6" s="221"/>
+      <c r="S6" s="222"/>
+      <c r="T6" s="222"/>
+      <c r="U6" s="222"/>
+      <c r="V6" s="223"/>
     </row>
     <row r="7" spans="1:22" s="53" customFormat="1" ht="12.75" customHeight="1" thickBot="1">
       <c r="A7" s="47" t="s">
@@ -11038,197 +11034,197 @@
       <c r="K7" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="238" t="s">
+      <c r="L7" s="287" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="239"/>
-      <c r="N7" s="240"/>
-      <c r="R7" s="274"/>
-      <c r="S7" s="275"/>
-      <c r="T7" s="275"/>
-      <c r="U7" s="275"/>
-      <c r="V7" s="276"/>
+      <c r="M7" s="288"/>
+      <c r="N7" s="289"/>
+      <c r="R7" s="221"/>
+      <c r="S7" s="222"/>
+      <c r="T7" s="222"/>
+      <c r="U7" s="222"/>
+      <c r="V7" s="223"/>
     </row>
     <row r="8" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
       <c r="A8" s="54"/>
       <c r="N8" s="55"/>
-      <c r="R8" s="274"/>
-      <c r="S8" s="275"/>
-      <c r="T8" s="275"/>
-      <c r="U8" s="275"/>
-      <c r="V8" s="276"/>
+      <c r="R8" s="221"/>
+      <c r="S8" s="222"/>
+      <c r="T8" s="222"/>
+      <c r="U8" s="222"/>
+      <c r="V8" s="223"/>
     </row>
     <row r="9" spans="1:22" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A9" s="285" t="s">
+      <c r="A9" s="232" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="286"/>
-      <c r="C9" s="286"/>
-      <c r="D9" s="286"/>
-      <c r="E9" s="286"/>
-      <c r="F9" s="286"/>
-      <c r="G9" s="286"/>
-      <c r="H9" s="286"/>
-      <c r="I9" s="286"/>
-      <c r="J9" s="286"/>
-      <c r="K9" s="286"/>
-      <c r="L9" s="286"/>
-      <c r="M9" s="286"/>
-      <c r="N9" s="287"/>
-      <c r="R9" s="274"/>
-      <c r="S9" s="275"/>
-      <c r="T9" s="275"/>
-      <c r="U9" s="275"/>
-      <c r="V9" s="276"/>
+      <c r="B9" s="233"/>
+      <c r="C9" s="233"/>
+      <c r="D9" s="233"/>
+      <c r="E9" s="233"/>
+      <c r="F9" s="233"/>
+      <c r="G9" s="233"/>
+      <c r="H9" s="233"/>
+      <c r="I9" s="233"/>
+      <c r="J9" s="233"/>
+      <c r="K9" s="233"/>
+      <c r="L9" s="233"/>
+      <c r="M9" s="233"/>
+      <c r="N9" s="234"/>
+      <c r="R9" s="221"/>
+      <c r="S9" s="222"/>
+      <c r="T9" s="222"/>
+      <c r="U9" s="222"/>
+      <c r="V9" s="223"/>
     </row>
     <row r="10" spans="1:22" ht="22.5" customHeight="1">
       <c r="A10" s="56">
         <v>2</v>
       </c>
-      <c r="B10" s="257" t="s">
+      <c r="B10" s="235" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="245"/>
-      <c r="D10" s="288"/>
-      <c r="E10" s="288"/>
-      <c r="F10" s="288"/>
-      <c r="G10" s="288"/>
-      <c r="H10" s="288"/>
-      <c r="I10" s="288"/>
-      <c r="J10" s="288"/>
-      <c r="K10" s="288"/>
-      <c r="L10" s="288"/>
-      <c r="M10" s="288"/>
-      <c r="N10" s="289"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="237"/>
+      <c r="F10" s="237"/>
+      <c r="G10" s="237"/>
+      <c r="H10" s="237"/>
+      <c r="I10" s="237"/>
+      <c r="J10" s="237"/>
+      <c r="K10" s="237"/>
+      <c r="L10" s="237"/>
+      <c r="M10" s="237"/>
+      <c r="N10" s="238"/>
       <c r="P10" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="R10" s="274"/>
-      <c r="S10" s="275"/>
-      <c r="T10" s="275"/>
-      <c r="U10" s="275"/>
-      <c r="V10" s="276"/>
+      <c r="R10" s="221"/>
+      <c r="S10" s="222"/>
+      <c r="T10" s="222"/>
+      <c r="U10" s="222"/>
+      <c r="V10" s="223"/>
     </row>
     <row r="11" spans="1:22" ht="22.5" customHeight="1">
       <c r="A11" s="58"/>
-      <c r="B11" s="258" t="s">
+      <c r="B11" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="259"/>
-      <c r="D11" s="290"/>
-      <c r="E11" s="291"/>
-      <c r="F11" s="291"/>
-      <c r="G11" s="291"/>
-      <c r="H11" s="292"/>
-      <c r="I11" s="293" t="s">
+      <c r="C11" s="240"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="243"/>
+      <c r="I11" s="244" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="294"/>
-      <c r="K11" s="294"/>
-      <c r="L11" s="295"/>
-      <c r="M11" s="296"/>
-      <c r="N11" s="297"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="246"/>
+      <c r="M11" s="247"/>
+      <c r="N11" s="248"/>
       <c r="P11" s="60" t="s">
         <v>14</v>
       </c>
       <c r="Q11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="R11" s="274"/>
-      <c r="S11" s="275"/>
-      <c r="T11" s="275"/>
-      <c r="U11" s="275"/>
-      <c r="V11" s="276"/>
+      <c r="R11" s="221"/>
+      <c r="S11" s="222"/>
+      <c r="T11" s="222"/>
+      <c r="U11" s="222"/>
+      <c r="V11" s="223"/>
     </row>
     <row r="12" spans="1:22" ht="21.75" customHeight="1" thickBot="1">
       <c r="A12" s="62"/>
-      <c r="B12" s="280" t="s">
+      <c r="B12" s="227" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="281"/>
-      <c r="D12" s="282"/>
-      <c r="E12" s="283"/>
-      <c r="F12" s="283"/>
-      <c r="G12" s="283" t="b">
+      <c r="C12" s="228"/>
+      <c r="D12" s="229"/>
+      <c r="E12" s="230"/>
+      <c r="F12" s="230"/>
+      <c r="G12" s="230" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="283"/>
-      <c r="I12" s="283" t="b">
+      <c r="H12" s="230"/>
+      <c r="I12" s="230" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="283"/>
-      <c r="K12" s="283"/>
-      <c r="L12" s="283"/>
-      <c r="M12" s="283"/>
-      <c r="N12" s="284"/>
+      <c r="J12" s="230"/>
+      <c r="K12" s="230"/>
+      <c r="L12" s="230"/>
+      <c r="M12" s="230"/>
+      <c r="N12" s="231"/>
       <c r="P12" s="60" t="s">
         <v>17</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="R12" s="274"/>
-      <c r="S12" s="275"/>
-      <c r="T12" s="275"/>
-      <c r="U12" s="275"/>
-      <c r="V12" s="276"/>
+      <c r="R12" s="221"/>
+      <c r="S12" s="222"/>
+      <c r="T12" s="222"/>
+      <c r="U12" s="222"/>
+      <c r="V12" s="223"/>
     </row>
     <row r="13" spans="1:22" ht="24" customHeight="1">
       <c r="A13" s="63">
         <v>3</v>
       </c>
-      <c r="B13" s="244" t="s">
+      <c r="B13" s="252" t="s">
         <v>332</v>
       </c>
-      <c r="C13" s="245"/>
-      <c r="D13" s="253"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="254"/>
-      <c r="G13" s="257" t="s">
+      <c r="C13" s="236"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="261"/>
+      <c r="G13" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="257"/>
-      <c r="I13" s="245"/>
-      <c r="J13" s="260" t="b">
+      <c r="H13" s="235"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="264" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="261"/>
-      <c r="L13" s="261" t="b">
+      <c r="K13" s="265"/>
+      <c r="L13" s="265" t="b">
         <v>0</v>
       </c>
-      <c r="M13" s="261"/>
-      <c r="N13" s="262"/>
+      <c r="M13" s="265"/>
+      <c r="N13" s="266"/>
       <c r="P13" s="60" t="s">
         <v>20</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="277"/>
-      <c r="S13" s="278"/>
-      <c r="T13" s="278"/>
-      <c r="U13" s="278"/>
-      <c r="V13" s="279"/>
+      <c r="R13" s="224"/>
+      <c r="S13" s="225"/>
+      <c r="T13" s="225"/>
+      <c r="U13" s="225"/>
+      <c r="V13" s="226"/>
     </row>
     <row r="14" spans="1:22" ht="21.6" customHeight="1">
       <c r="A14" s="58"/>
       <c r="B14" s="64"/>
       <c r="C14" s="64"/>
-      <c r="D14" s="255"/>
-      <c r="E14" s="256"/>
-      <c r="F14" s="256"/>
-      <c r="G14" s="258"/>
-      <c r="H14" s="258"/>
-      <c r="I14" s="259"/>
-      <c r="J14" s="263" t="b">
+      <c r="D14" s="262"/>
+      <c r="E14" s="263"/>
+      <c r="F14" s="263"/>
+      <c r="G14" s="239"/>
+      <c r="H14" s="239"/>
+      <c r="I14" s="240"/>
+      <c r="J14" s="267" t="b">
         <v>0</v>
       </c>
-      <c r="K14" s="264"/>
-      <c r="L14" s="264" t="b">
+      <c r="K14" s="268"/>
+      <c r="L14" s="268" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="264"/>
-      <c r="N14" s="265"/>
+      <c r="M14" s="268"/>
+      <c r="N14" s="269"/>
       <c r="P14" s="60"/>
       <c r="Q14" s="2"/>
       <c r="S14"/>
@@ -11243,21 +11239,21 @@
         <v>22</v>
       </c>
       <c r="C15" s="66"/>
-      <c r="D15" s="246"/>
-      <c r="E15" s="246"/>
-      <c r="F15" s="247"/>
-      <c r="G15" s="248" t="s">
+      <c r="D15" s="253"/>
+      <c r="E15" s="253"/>
+      <c r="F15" s="254"/>
+      <c r="G15" s="255" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="249"/>
-      <c r="I15" s="249"/>
-      <c r="J15" s="250" t="s">
+      <c r="H15" s="256"/>
+      <c r="I15" s="256"/>
+      <c r="J15" s="257" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="251"/>
-      <c r="L15" s="251"/>
-      <c r="M15" s="251"/>
-      <c r="N15" s="252"/>
+      <c r="K15" s="258"/>
+      <c r="L15" s="258"/>
+      <c r="M15" s="258"/>
+      <c r="N15" s="259"/>
       <c r="P15" s="60" t="s">
         <v>25</v>
       </c>
@@ -11279,22 +11275,22 @@
       <c r="D16" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="266" t="b">
+      <c r="E16" s="270" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="267"/>
-      <c r="G16" s="268" t="s">
+      <c r="F16" s="271"/>
+      <c r="G16" s="272" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="269"/>
-      <c r="I16" s="270"/>
-      <c r="J16" s="241">
+      <c r="H16" s="273"/>
+      <c r="I16" s="274"/>
+      <c r="J16" s="249">
         <v>1</v>
       </c>
-      <c r="K16" s="242"/>
-      <c r="L16" s="242"/>
-      <c r="M16" s="242"/>
-      <c r="N16" s="243"/>
+      <c r="K16" s="250"/>
+      <c r="L16" s="250"/>
+      <c r="M16" s="250"/>
+      <c r="N16" s="251"/>
       <c r="O16" s="69"/>
       <c r="P16" s="60" t="s">
         <v>29</v>
@@ -11304,60 +11300,60 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="27" customHeight="1">
-      <c r="A17" s="197">
+      <c r="A17" s="307">
         <v>6</v>
       </c>
-      <c r="B17" s="309" t="s">
+      <c r="B17" s="211" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="310"/>
+      <c r="C17" s="212"/>
       <c r="D17" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="313" t="b">
+      <c r="E17" s="216" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="314"/>
+      <c r="F17" s="217"/>
       <c r="G17" s="70" t="s">
         <v>32</v>
       </c>
       <c r="H17" s="71"/>
-      <c r="I17" s="196"/>
-      <c r="J17" s="196"/>
-      <c r="K17" s="196"/>
-      <c r="L17" s="196"/>
-      <c r="M17" s="213"/>
-      <c r="N17" s="213"/>
+      <c r="I17" s="205"/>
+      <c r="J17" s="205"/>
+      <c r="K17" s="205"/>
+      <c r="L17" s="205"/>
+      <c r="M17" s="206"/>
+      <c r="N17" s="206"/>
       <c r="Q17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="R17" s="72"/>
     </row>
     <row r="18" spans="1:23" ht="27" customHeight="1">
-      <c r="A18" s="198"/>
-      <c r="B18" s="311"/>
-      <c r="C18" s="312"/>
+      <c r="A18" s="308"/>
+      <c r="B18" s="213"/>
+      <c r="C18" s="214"/>
       <c r="D18" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="222" t="b">
+      <c r="E18" s="203" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="223"/>
+      <c r="F18" s="204"/>
       <c r="G18" s="74"/>
       <c r="H18" s="75"/>
-      <c r="I18" s="217" t="s">
+      <c r="I18" s="290" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="217"/>
-      <c r="K18" s="217" t="s">
+      <c r="J18" s="290"/>
+      <c r="K18" s="290" t="s">
         <v>341</v>
       </c>
-      <c r="L18" s="217"/>
-      <c r="M18" s="217" t="s">
+      <c r="L18" s="290"/>
+      <c r="M18" s="290" t="s">
         <v>35</v>
       </c>
-      <c r="N18" s="217"/>
+      <c r="N18" s="290"/>
       <c r="Q18" s="2" t="s">
         <v>36</v>
       </c>
@@ -11366,19 +11362,19 @@
       <c r="A19" s="56"/>
       <c r="B19" s="76"/>
       <c r="C19" s="73"/>
-      <c r="D19" s="221" t="b">
+      <c r="D19" s="302" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="222"/>
-      <c r="F19" s="223"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="204"/>
       <c r="G19" s="74"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="196"/>
-      <c r="J19" s="213"/>
-      <c r="K19" s="213"/>
-      <c r="L19" s="196"/>
-      <c r="M19" s="213"/>
-      <c r="N19" s="213"/>
+      <c r="I19" s="205"/>
+      <c r="J19" s="206"/>
+      <c r="K19" s="206"/>
+      <c r="L19" s="205"/>
+      <c r="M19" s="206"/>
+      <c r="N19" s="206"/>
       <c r="Q19" s="2" t="s">
         <v>37</v>
       </c>
@@ -11387,67 +11383,67 @@
       <c r="A20" s="77"/>
       <c r="B20" s="78"/>
       <c r="C20" s="79"/>
-      <c r="D20" s="218"/>
-      <c r="E20" s="219"/>
-      <c r="F20" s="220"/>
+      <c r="D20" s="299"/>
+      <c r="E20" s="300"/>
+      <c r="F20" s="301"/>
       <c r="G20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="214" t="s">
+      <c r="I20" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="J20" s="215"/>
-      <c r="K20" s="215"/>
-      <c r="L20" s="216" t="s">
+      <c r="J20" s="209"/>
+      <c r="K20" s="209"/>
+      <c r="L20" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="M20" s="308"/>
-      <c r="N20" s="308"/>
+      <c r="M20" s="210"/>
+      <c r="N20" s="210"/>
       <c r="Q20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A21" s="198">
+      <c r="A21" s="308">
         <v>7</v>
       </c>
-      <c r="B21" s="200" t="s">
+      <c r="B21" s="310" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="201"/>
-      <c r="D21" s="207"/>
-      <c r="E21" s="207"/>
-      <c r="F21" s="207"/>
+      <c r="C21" s="311"/>
+      <c r="D21" s="314"/>
+      <c r="E21" s="314"/>
+      <c r="F21" s="314"/>
       <c r="G21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="196"/>
-      <c r="J21" s="213"/>
-      <c r="K21" s="213"/>
-      <c r="L21" s="196"/>
-      <c r="M21" s="213"/>
-      <c r="N21" s="213"/>
+      <c r="I21" s="205"/>
+      <c r="J21" s="206"/>
+      <c r="K21" s="206"/>
+      <c r="L21" s="205"/>
+      <c r="M21" s="206"/>
+      <c r="N21" s="206"/>
       <c r="Q21" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="26.25" customHeight="1">
-      <c r="A22" s="199"/>
-      <c r="B22" s="202"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="206"/>
-      <c r="E22" s="206"/>
-      <c r="F22" s="206"/>
+      <c r="A22" s="309"/>
+      <c r="B22" s="312"/>
+      <c r="C22" s="313"/>
+      <c r="D22" s="298"/>
+      <c r="E22" s="298"/>
+      <c r="F22" s="298"/>
       <c r="G22" s="58"/>
       <c r="H22" s="59"/>
-      <c r="I22" s="214" t="s">
+      <c r="I22" s="207" t="s">
         <v>43</v>
       </c>
-      <c r="J22" s="214"/>
-      <c r="K22" s="214"/>
-      <c r="L22" s="216" t="s">
+      <c r="J22" s="207"/>
+      <c r="K22" s="207"/>
+      <c r="L22" s="208" t="s">
         <v>44</v>
       </c>
-      <c r="M22" s="216"/>
-      <c r="N22" s="216"/>
+      <c r="M22" s="208"/>
+      <c r="N22" s="208"/>
       <c r="Q22" s="2" t="s">
         <v>45</v>
       </c>
@@ -11456,166 +11452,166 @@
       <c r="A23" s="56">
         <v>8</v>
       </c>
-      <c r="B23" s="208" t="s">
+      <c r="B23" s="303" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="209"/>
-      <c r="D23" s="210"/>
-      <c r="E23" s="210"/>
-      <c r="F23" s="210"/>
-      <c r="G23" s="211" t="s">
+      <c r="C23" s="292"/>
+      <c r="D23" s="215"/>
+      <c r="E23" s="215"/>
+      <c r="F23" s="215"/>
+      <c r="G23" s="296" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="212"/>
-      <c r="I23" s="213"/>
-      <c r="J23" s="213"/>
-      <c r="K23" s="213"/>
-      <c r="L23" s="213"/>
-      <c r="M23" s="213"/>
-      <c r="N23" s="213"/>
+      <c r="H23" s="297"/>
+      <c r="I23" s="206"/>
+      <c r="J23" s="206"/>
+      <c r="K23" s="206"/>
+      <c r="L23" s="206"/>
+      <c r="M23" s="206"/>
+      <c r="N23" s="206"/>
       <c r="Q23" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A24" s="197">
+      <c r="A24" s="307">
         <v>9</v>
       </c>
-      <c r="B24" s="200" t="s">
+      <c r="B24" s="310" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="201"/>
-      <c r="D24" s="205"/>
-      <c r="E24" s="205"/>
-      <c r="F24" s="205"/>
+      <c r="C24" s="311"/>
+      <c r="D24" s="295"/>
+      <c r="E24" s="295"/>
+      <c r="F24" s="295"/>
       <c r="G24" s="82" t="s">
         <v>50</v>
       </c>
       <c r="H24" s="80"/>
-      <c r="I24" s="196"/>
-      <c r="J24" s="196"/>
-      <c r="K24" s="196"/>
-      <c r="L24" s="196"/>
-      <c r="M24" s="213"/>
-      <c r="N24" s="213"/>
+      <c r="I24" s="205"/>
+      <c r="J24" s="205"/>
+      <c r="K24" s="205"/>
+      <c r="L24" s="205"/>
+      <c r="M24" s="206"/>
+      <c r="N24" s="206"/>
       <c r="Q24" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A25" s="199"/>
-      <c r="B25" s="202"/>
-      <c r="C25" s="203"/>
-      <c r="D25" s="206"/>
-      <c r="E25" s="206"/>
-      <c r="F25" s="206"/>
+      <c r="A25" s="309"/>
+      <c r="B25" s="312"/>
+      <c r="C25" s="313"/>
+      <c r="D25" s="298"/>
+      <c r="E25" s="298"/>
+      <c r="F25" s="298"/>
       <c r="G25" s="58"/>
       <c r="H25" s="59"/>
-      <c r="I25" s="217" t="s">
+      <c r="I25" s="290" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="217"/>
-      <c r="K25" s="217" t="s">
+      <c r="J25" s="290"/>
+      <c r="K25" s="290" t="s">
         <v>341</v>
       </c>
-      <c r="L25" s="217"/>
-      <c r="M25" s="217" t="s">
+      <c r="L25" s="290"/>
+      <c r="M25" s="290" t="s">
         <v>35</v>
       </c>
-      <c r="N25" s="217"/>
+      <c r="N25" s="290"/>
       <c r="Q25" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A26" s="197">
+      <c r="A26" s="307">
         <v>10</v>
       </c>
-      <c r="B26" s="200" t="s">
+      <c r="B26" s="310" t="s">
         <v>338</v>
       </c>
-      <c r="C26" s="201"/>
-      <c r="D26" s="205"/>
-      <c r="E26" s="205"/>
-      <c r="F26" s="205"/>
+      <c r="C26" s="311"/>
+      <c r="D26" s="295"/>
+      <c r="E26" s="295"/>
+      <c r="F26" s="295"/>
       <c r="G26" s="74"/>
       <c r="H26" s="75"/>
-      <c r="I26" s="196"/>
-      <c r="J26" s="213"/>
-      <c r="K26" s="213"/>
-      <c r="L26" s="196"/>
-      <c r="M26" s="213"/>
-      <c r="N26" s="213"/>
+      <c r="I26" s="205"/>
+      <c r="J26" s="206"/>
+      <c r="K26" s="206"/>
+      <c r="L26" s="205"/>
+      <c r="M26" s="206"/>
+      <c r="N26" s="206"/>
       <c r="Q26" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="35.25" customHeight="1">
-      <c r="A27" s="199"/>
-      <c r="B27" s="202"/>
-      <c r="C27" s="203"/>
-      <c r="D27" s="206"/>
-      <c r="E27" s="206"/>
-      <c r="F27" s="206"/>
+      <c r="A27" s="309"/>
+      <c r="B27" s="312"/>
+      <c r="C27" s="313"/>
+      <c r="D27" s="298"/>
+      <c r="E27" s="298"/>
+      <c r="F27" s="298"/>
       <c r="G27" s="74"/>
       <c r="H27" s="75"/>
-      <c r="I27" s="214" t="s">
+      <c r="I27" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="J27" s="215"/>
-      <c r="K27" s="215"/>
-      <c r="L27" s="216" t="s">
+      <c r="J27" s="209"/>
+      <c r="K27" s="209"/>
+      <c r="L27" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="M27" s="215"/>
-      <c r="N27" s="215"/>
+      <c r="M27" s="209"/>
+      <c r="N27" s="209"/>
       <c r="Q27" s="2" t="s">
         <v>54</v>
       </c>
       <c r="S27" s="83"/>
     </row>
     <row r="28" spans="1:23" ht="33" customHeight="1">
-      <c r="A28" s="197">
+      <c r="A28" s="307">
         <v>11</v>
       </c>
-      <c r="B28" s="200" t="s">
+      <c r="B28" s="310" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="201"/>
-      <c r="D28" s="204"/>
-      <c r="E28" s="205"/>
-      <c r="F28" s="205"/>
+      <c r="C28" s="311"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="295"/>
+      <c r="F28" s="295"/>
       <c r="G28" s="74"/>
       <c r="H28" s="84"/>
-      <c r="I28" s="196"/>
-      <c r="J28" s="213"/>
-      <c r="K28" s="213"/>
-      <c r="L28" s="196"/>
-      <c r="M28" s="213"/>
-      <c r="N28" s="213"/>
+      <c r="I28" s="205"/>
+      <c r="J28" s="206"/>
+      <c r="K28" s="206"/>
+      <c r="L28" s="205"/>
+      <c r="M28" s="206"/>
+      <c r="N28" s="206"/>
       <c r="Q28" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="32.25" customHeight="1">
-      <c r="A29" s="199"/>
-      <c r="B29" s="202"/>
-      <c r="C29" s="203"/>
-      <c r="D29" s="206"/>
-      <c r="E29" s="206"/>
-      <c r="F29" s="206"/>
+      <c r="A29" s="309"/>
+      <c r="B29" s="312"/>
+      <c r="C29" s="313"/>
+      <c r="D29" s="298"/>
+      <c r="E29" s="298"/>
+      <c r="F29" s="298"/>
       <c r="G29" s="74"/>
       <c r="H29" s="84"/>
-      <c r="I29" s="214" t="s">
+      <c r="I29" s="207" t="s">
         <v>43</v>
       </c>
-      <c r="J29" s="214"/>
-      <c r="K29" s="214"/>
-      <c r="L29" s="214" t="s">
+      <c r="J29" s="207"/>
+      <c r="K29" s="207"/>
+      <c r="L29" s="207" t="s">
         <v>44</v>
       </c>
-      <c r="M29" s="214"/>
-      <c r="N29" s="214"/>
+      <c r="M29" s="207"/>
+      <c r="N29" s="207"/>
       <c r="Q29" s="2" t="s">
         <v>57</v>
       </c>
@@ -11629,19 +11625,19 @@
         <v>58</v>
       </c>
       <c r="C30" s="68"/>
-      <c r="D30" s="204"/>
-      <c r="E30" s="205"/>
-      <c r="F30" s="205"/>
-      <c r="G30" s="211" t="s">
+      <c r="D30" s="294"/>
+      <c r="E30" s="295"/>
+      <c r="F30" s="295"/>
+      <c r="G30" s="296" t="s">
         <v>47</v>
       </c>
-      <c r="H30" s="212"/>
-      <c r="I30" s="213"/>
-      <c r="J30" s="213"/>
-      <c r="K30" s="213"/>
-      <c r="L30" s="213"/>
-      <c r="M30" s="213"/>
-      <c r="N30" s="213"/>
+      <c r="H30" s="297"/>
+      <c r="I30" s="206"/>
+      <c r="J30" s="206"/>
+      <c r="K30" s="206"/>
+      <c r="L30" s="206"/>
+      <c r="M30" s="206"/>
+      <c r="N30" s="206"/>
       <c r="Q30" s="2" t="s">
         <v>59</v>
       </c>
@@ -11658,42 +11654,42 @@
         <v>337</v>
       </c>
       <c r="C31" s="68"/>
-      <c r="D31" s="210"/>
-      <c r="E31" s="210"/>
-      <c r="F31" s="210"/>
+      <c r="D31" s="215"/>
+      <c r="E31" s="215"/>
+      <c r="F31" s="215"/>
       <c r="G31" s="85" t="s">
         <v>60</v>
       </c>
       <c r="H31" s="81"/>
-      <c r="I31" s="196"/>
-      <c r="J31" s="196"/>
-      <c r="K31" s="196"/>
-      <c r="L31" s="196"/>
-      <c r="M31" s="196"/>
-      <c r="N31" s="196"/>
+      <c r="I31" s="205"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="205"/>
+      <c r="L31" s="205"/>
+      <c r="M31" s="205"/>
+      <c r="N31" s="205"/>
       <c r="Q31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="39.75" customHeight="1">
-      <c r="A32" s="224" t="s">
+      <c r="A32" s="291" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="209"/>
-      <c r="C32" s="225"/>
-      <c r="D32" s="210"/>
-      <c r="E32" s="210"/>
-      <c r="F32" s="210"/>
+      <c r="B32" s="292"/>
+      <c r="C32" s="293"/>
+      <c r="D32" s="215"/>
+      <c r="E32" s="215"/>
+      <c r="F32" s="215"/>
       <c r="G32" s="86" t="s">
         <v>63</v>
       </c>
       <c r="H32" s="87"/>
-      <c r="I32" s="196"/>
-      <c r="J32" s="196"/>
-      <c r="K32" s="196"/>
-      <c r="L32" s="196"/>
-      <c r="M32" s="196"/>
-      <c r="N32" s="196"/>
+      <c r="I32" s="205"/>
+      <c r="J32" s="205"/>
+      <c r="K32" s="205"/>
+      <c r="L32" s="205"/>
+      <c r="M32" s="205"/>
+      <c r="N32" s="205"/>
       <c r="Q32" s="2" t="s">
         <v>64</v>
       </c>
@@ -11702,69 +11698,69 @@
       <c r="A33" s="65">
         <v>15</v>
       </c>
-      <c r="B33" s="306" t="s">
+      <c r="B33" s="201" t="s">
         <v>336</v>
       </c>
-      <c r="C33" s="307"/>
-      <c r="D33" s="303"/>
-      <c r="E33" s="304"/>
-      <c r="F33" s="305"/>
+      <c r="C33" s="202"/>
+      <c r="D33" s="198"/>
+      <c r="E33" s="199"/>
+      <c r="F33" s="200"/>
       <c r="G33" s="88" t="s">
         <v>65</v>
       </c>
       <c r="H33" s="81"/>
-      <c r="I33" s="195"/>
-      <c r="J33" s="196"/>
-      <c r="K33" s="196"/>
-      <c r="L33" s="196"/>
-      <c r="M33" s="196"/>
-      <c r="N33" s="196"/>
+      <c r="I33" s="306"/>
+      <c r="J33" s="205"/>
+      <c r="K33" s="205"/>
+      <c r="L33" s="205"/>
+      <c r="M33" s="205"/>
+      <c r="N33" s="205"/>
       <c r="Q33" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A34" s="300" t="s">
+      <c r="A34" s="195" t="s">
         <v>342</v>
       </c>
-      <c r="B34" s="301"/>
-      <c r="C34" s="301"/>
-      <c r="D34" s="301"/>
-      <c r="E34" s="301"/>
-      <c r="F34" s="301"/>
-      <c r="G34" s="301"/>
-      <c r="H34" s="301"/>
-      <c r="I34" s="301"/>
-      <c r="J34" s="301"/>
-      <c r="K34" s="301"/>
-      <c r="L34" s="301"/>
-      <c r="M34" s="301"/>
-      <c r="N34" s="302"/>
+      <c r="B34" s="196"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="196"/>
+      <c r="E34" s="196"/>
+      <c r="F34" s="196"/>
+      <c r="G34" s="196"/>
+      <c r="H34" s="196"/>
+      <c r="I34" s="196"/>
+      <c r="J34" s="196"/>
+      <c r="K34" s="196"/>
+      <c r="L34" s="196"/>
+      <c r="M34" s="196"/>
+      <c r="N34" s="197"/>
       <c r="Q34" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="21" customHeight="1">
-      <c r="A35" s="193" t="s">
+      <c r="A35" s="304" t="s">
         <v>343</v>
       </c>
-      <c r="B35" s="193"/>
-      <c r="C35" s="193"/>
-      <c r="D35" s="194" t="s">
+      <c r="B35" s="304"/>
+      <c r="C35" s="304"/>
+      <c r="D35" s="305" t="s">
         <v>345</v>
       </c>
-      <c r="E35" s="194"/>
-      <c r="F35" s="194"/>
-      <c r="G35" s="298" t="s">
+      <c r="E35" s="305"/>
+      <c r="F35" s="305"/>
+      <c r="G35" s="193" t="s">
         <v>344</v>
       </c>
-      <c r="H35" s="299"/>
-      <c r="I35" s="194"/>
-      <c r="J35" s="194"/>
-      <c r="K35" s="194"/>
-      <c r="L35" s="194"/>
-      <c r="M35" s="194"/>
-      <c r="N35" s="194"/>
+      <c r="H35" s="194"/>
+      <c r="I35" s="305"/>
+      <c r="J35" s="305"/>
+      <c r="K35" s="305"/>
+      <c r="L35" s="305"/>
+      <c r="M35" s="305"/>
+      <c r="N35" s="305"/>
       <c r="Q35" s="2" t="s">
         <v>68</v>
       </c>
@@ -15610,6 +15606,84 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="/BaTTcDf+hqrv5TIoBNyRq0Sgn7nIwb4e4ttNsiQ6OfLPr1xfXEFwk9PJciGh81xM7VBkq1YdaQd4Z9lMQvbfg==" saltValue="KdyJu3hMujoMijewA5fQqg==" spinCount="100000" sheet="1" scenarios="1"/>
   <mergeCells count="94">
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="I35:N35"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:F29"/>
+    <mergeCell ref="B21:C22"/>
+    <mergeCell ref="D21:F22"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:F25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:N23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="D26:F27"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:N15"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:I14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="R3:V13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
     <mergeCell ref="G35:H35"/>
     <mergeCell ref="A34:N34"/>
     <mergeCell ref="D33:F33"/>
@@ -15626,84 +15700,6 @@
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="I31:N31"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="R3:V13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:N15"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:I14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="D26:F27"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:N23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:F29"/>
-    <mergeCell ref="B21:C22"/>
-    <mergeCell ref="D21:F22"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="D24:F25"/>
-    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35" xr:uid="{5EC3205D-4079-402B-BBE7-9B917DF21EB0}">
@@ -16215,201 +16211,201 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="3" customHeight="1" thickBot="1">
-      <c r="A1" s="476"/>
-      <c r="B1" s="477"/>
-      <c r="C1" s="477"/>
-      <c r="D1" s="477"/>
-      <c r="E1" s="477"/>
-      <c r="F1" s="477"/>
-      <c r="G1" s="477"/>
-      <c r="H1" s="477"/>
-      <c r="I1" s="477"/>
-      <c r="J1" s="477"/>
+      <c r="A1" s="430"/>
+      <c r="B1" s="431"/>
+      <c r="C1" s="431"/>
+      <c r="D1" s="431"/>
+      <c r="E1" s="431"/>
+      <c r="F1" s="431"/>
+      <c r="G1" s="431"/>
+      <c r="H1" s="431"/>
+      <c r="I1" s="431"/>
+      <c r="J1" s="431"/>
     </row>
     <row r="2" spans="1:15" ht="13.5" customHeight="1">
-      <c r="A2" s="478">
+      <c r="A2" s="432">
         <v>34</v>
       </c>
-      <c r="B2" s="479"/>
-      <c r="C2" s="480" t="s">
+      <c r="B2" s="433"/>
+      <c r="C2" s="434" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="480"/>
-      <c r="E2" s="480"/>
-      <c r="F2" s="481"/>
-      <c r="G2" s="431"/>
-      <c r="H2" s="432"/>
-      <c r="I2" s="432"/>
-      <c r="J2" s="432"/>
-      <c r="K2" s="432"/>
-      <c r="L2" s="432"/>
-      <c r="M2" s="432"/>
-      <c r="N2" s="432"/>
-      <c r="O2" s="433"/>
+      <c r="D2" s="434"/>
+      <c r="E2" s="434"/>
+      <c r="F2" s="435"/>
+      <c r="G2" s="473"/>
+      <c r="H2" s="474"/>
+      <c r="I2" s="474"/>
+      <c r="J2" s="474"/>
+      <c r="K2" s="474"/>
+      <c r="L2" s="474"/>
+      <c r="M2" s="474"/>
+      <c r="N2" s="474"/>
+      <c r="O2" s="475"/>
     </row>
     <row r="3" spans="1:15" ht="12.75" customHeight="1">
       <c r="A3" s="170"/>
       <c r="B3" s="171"/>
-      <c r="C3" s="482" t="s">
+      <c r="C3" s="422" t="s">
         <v>295</v>
       </c>
-      <c r="D3" s="482"/>
-      <c r="E3" s="482"/>
-      <c r="F3" s="483"/>
-      <c r="G3" s="431"/>
-      <c r="H3" s="432"/>
-      <c r="I3" s="432"/>
-      <c r="J3" s="432"/>
-      <c r="K3" s="432"/>
-      <c r="L3" s="432"/>
-      <c r="M3" s="432"/>
-      <c r="N3" s="432"/>
-      <c r="O3" s="433"/>
+      <c r="D3" s="422"/>
+      <c r="E3" s="422"/>
+      <c r="F3" s="423"/>
+      <c r="G3" s="473"/>
+      <c r="H3" s="474"/>
+      <c r="I3" s="474"/>
+      <c r="J3" s="474"/>
+      <c r="K3" s="474"/>
+      <c r="L3" s="474"/>
+      <c r="M3" s="474"/>
+      <c r="N3" s="474"/>
+      <c r="O3" s="475"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="170"/>
       <c r="B4" s="171"/>
-      <c r="C4" s="482" t="s">
+      <c r="C4" s="422" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="482"/>
-      <c r="E4" s="482"/>
-      <c r="F4" s="483"/>
-      <c r="G4" s="431"/>
-      <c r="H4" s="432"/>
-      <c r="I4" s="432"/>
-      <c r="J4" s="432"/>
-      <c r="K4" s="432"/>
-      <c r="L4" s="432"/>
-      <c r="M4" s="432"/>
-      <c r="N4" s="432"/>
-      <c r="O4" s="433"/>
+      <c r="D4" s="422"/>
+      <c r="E4" s="422"/>
+      <c r="F4" s="423"/>
+      <c r="G4" s="473"/>
+      <c r="H4" s="474"/>
+      <c r="I4" s="474"/>
+      <c r="J4" s="474"/>
+      <c r="K4" s="474"/>
+      <c r="L4" s="474"/>
+      <c r="M4" s="474"/>
+      <c r="N4" s="474"/>
+      <c r="O4" s="475"/>
     </row>
     <row r="5" spans="1:15" ht="24.75" customHeight="1">
       <c r="A5" s="170"/>
       <c r="B5" s="171"/>
-      <c r="C5" s="482" t="s">
+      <c r="C5" s="422" t="s">
         <v>297</v>
       </c>
-      <c r="D5" s="482"/>
-      <c r="E5" s="482"/>
-      <c r="F5" s="483"/>
-      <c r="G5" s="458" t="b">
+      <c r="D5" s="422"/>
+      <c r="E5" s="422"/>
+      <c r="F5" s="423"/>
+      <c r="G5" s="438" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="434"/>
-      <c r="I5" s="434" t="b">
+      <c r="H5" s="439"/>
+      <c r="I5" s="439" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="434"/>
-      <c r="K5" s="434"/>
-      <c r="L5" s="434"/>
-      <c r="M5" s="434"/>
-      <c r="N5" s="434"/>
-      <c r="O5" s="435"/>
+      <c r="J5" s="439"/>
+      <c r="K5" s="439"/>
+      <c r="L5" s="439"/>
+      <c r="M5" s="439"/>
+      <c r="N5" s="439"/>
+      <c r="O5" s="443"/>
     </row>
     <row r="6" spans="1:15" ht="24" customHeight="1">
       <c r="A6" s="170"/>
       <c r="B6" s="171"/>
-      <c r="C6" s="482" t="s">
+      <c r="C6" s="422" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="482"/>
-      <c r="E6" s="482"/>
-      <c r="F6" s="483"/>
-      <c r="G6" s="458" t="b">
+      <c r="D6" s="422"/>
+      <c r="E6" s="422"/>
+      <c r="F6" s="423"/>
+      <c r="G6" s="438" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="434"/>
-      <c r="I6" s="434" t="b">
+      <c r="H6" s="439"/>
+      <c r="I6" s="439" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="434"/>
-      <c r="K6" s="434"/>
-      <c r="L6" s="434"/>
-      <c r="M6" s="434"/>
-      <c r="N6" s="434"/>
-      <c r="O6" s="435"/>
+      <c r="J6" s="439"/>
+      <c r="K6" s="439"/>
+      <c r="L6" s="439"/>
+      <c r="M6" s="439"/>
+      <c r="N6" s="439"/>
+      <c r="O6" s="443"/>
     </row>
     <row r="7" spans="1:15" ht="27" customHeight="1">
       <c r="A7" s="170"/>
       <c r="B7" s="171"/>
-      <c r="C7" s="482"/>
-      <c r="D7" s="482"/>
-      <c r="E7" s="482"/>
-      <c r="F7" s="482"/>
+      <c r="C7" s="422"/>
+      <c r="D7" s="422"/>
+      <c r="E7" s="422"/>
+      <c r="F7" s="422"/>
       <c r="G7" s="167" t="s">
         <v>321</v>
       </c>
       <c r="H7" s="168"/>
-      <c r="I7" s="436"/>
-      <c r="J7" s="436"/>
-      <c r="K7" s="436"/>
-      <c r="L7" s="436"/>
-      <c r="M7" s="436"/>
-      <c r="N7" s="436"/>
-      <c r="O7" s="437"/>
+      <c r="I7" s="476"/>
+      <c r="J7" s="476"/>
+      <c r="K7" s="476"/>
+      <c r="L7" s="476"/>
+      <c r="M7" s="476"/>
+      <c r="N7" s="476"/>
+      <c r="O7" s="477"/>
     </row>
     <row r="8" spans="1:15" ht="31.5" customHeight="1">
       <c r="A8" s="172"/>
       <c r="B8" s="173"/>
-      <c r="C8" s="493"/>
-      <c r="D8" s="493"/>
-      <c r="E8" s="493"/>
-      <c r="F8" s="494"/>
-      <c r="G8" s="438"/>
-      <c r="H8" s="439"/>
-      <c r="I8" s="439"/>
-      <c r="J8" s="439"/>
-      <c r="K8" s="439"/>
-      <c r="L8" s="439"/>
-      <c r="M8" s="439"/>
-      <c r="N8" s="439"/>
-      <c r="O8" s="440"/>
+      <c r="C8" s="424"/>
+      <c r="D8" s="424"/>
+      <c r="E8" s="424"/>
+      <c r="F8" s="425"/>
+      <c r="G8" s="478"/>
+      <c r="H8" s="479"/>
+      <c r="I8" s="479"/>
+      <c r="J8" s="479"/>
+      <c r="K8" s="479"/>
+      <c r="L8" s="479"/>
+      <c r="M8" s="479"/>
+      <c r="N8" s="479"/>
+      <c r="O8" s="480"/>
     </row>
     <row r="9" spans="1:15" ht="20.45" customHeight="1">
-      <c r="A9" s="495">
+      <c r="A9" s="426">
         <v>35</v>
       </c>
-      <c r="B9" s="496"/>
-      <c r="C9" s="470" t="s">
+      <c r="B9" s="427"/>
+      <c r="C9" s="428" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="470"/>
+      <c r="D9" s="428"/>
       <c r="E9" s="356"/>
-      <c r="F9" s="497"/>
-      <c r="G9" s="462" t="b">
+      <c r="F9" s="429"/>
+      <c r="G9" s="407" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="463"/>
-      <c r="I9" s="409" t="b">
+      <c r="H9" s="408"/>
+      <c r="I9" s="454" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="409"/>
-      <c r="K9" s="409"/>
-      <c r="L9" s="409"/>
-      <c r="M9" s="409"/>
-      <c r="N9" s="409"/>
-      <c r="O9" s="410"/>
+      <c r="J9" s="454"/>
+      <c r="K9" s="454"/>
+      <c r="L9" s="454"/>
+      <c r="M9" s="454"/>
+      <c r="N9" s="454"/>
+      <c r="O9" s="455"/>
     </row>
     <row r="10" spans="1:15" ht="26.25" customHeight="1">
       <c r="A10" s="174"/>
       <c r="B10" s="175"/>
-      <c r="C10" s="470"/>
-      <c r="D10" s="470"/>
+      <c r="C10" s="428"/>
+      <c r="D10" s="428"/>
       <c r="E10" s="356"/>
-      <c r="F10" s="497"/>
-      <c r="G10" s="498" t="s">
+      <c r="F10" s="429"/>
+      <c r="G10" s="415" t="s">
         <v>321</v>
       </c>
-      <c r="H10" s="499"/>
-      <c r="I10" s="427"/>
-      <c r="J10" s="427"/>
-      <c r="K10" s="427"/>
-      <c r="L10" s="427"/>
-      <c r="M10" s="427"/>
-      <c r="N10" s="427"/>
-      <c r="O10" s="428"/>
+      <c r="H10" s="416"/>
+      <c r="I10" s="456"/>
+      <c r="J10" s="456"/>
+      <c r="K10" s="456"/>
+      <c r="L10" s="456"/>
+      <c r="M10" s="456"/>
+      <c r="N10" s="456"/>
+      <c r="O10" s="457"/>
     </row>
     <row r="11" spans="1:15" ht="21.75" customHeight="1">
       <c r="A11" s="174"/>
@@ -16418,15 +16414,15 @@
       <c r="D11" s="356"/>
       <c r="E11" s="356"/>
       <c r="F11" s="356"/>
-      <c r="G11" s="441"/>
-      <c r="H11" s="442"/>
-      <c r="I11" s="442"/>
-      <c r="J11" s="442"/>
-      <c r="K11" s="442"/>
-      <c r="L11" s="442"/>
-      <c r="M11" s="442"/>
-      <c r="N11" s="442"/>
-      <c r="O11" s="443"/>
+      <c r="G11" s="458"/>
+      <c r="H11" s="459"/>
+      <c r="I11" s="459"/>
+      <c r="J11" s="459"/>
+      <c r="K11" s="459"/>
+      <c r="L11" s="459"/>
+      <c r="M11" s="459"/>
+      <c r="N11" s="459"/>
+      <c r="O11" s="460"/>
     </row>
     <row r="12" spans="1:15" ht="18.75" customHeight="1">
       <c r="A12" s="176"/>
@@ -16435,282 +16431,282 @@
       <c r="D12" s="178"/>
       <c r="E12" s="179"/>
       <c r="F12" s="180"/>
-      <c r="G12" s="500" t="b">
+      <c r="G12" s="417" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="501"/>
-      <c r="I12" s="501" t="b">
+      <c r="H12" s="418"/>
+      <c r="I12" s="418" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="501"/>
-      <c r="K12" s="501"/>
-      <c r="L12" s="501"/>
-      <c r="M12" s="501"/>
-      <c r="N12" s="501"/>
-      <c r="O12" s="502"/>
+      <c r="J12" s="418"/>
+      <c r="K12" s="418"/>
+      <c r="L12" s="418"/>
+      <c r="M12" s="418"/>
+      <c r="N12" s="418"/>
+      <c r="O12" s="419"/>
     </row>
     <row r="13" spans="1:15" ht="21.75" customHeight="1">
       <c r="A13" s="176"/>
       <c r="B13" s="177"/>
-      <c r="C13" s="484" t="s">
+      <c r="C13" s="468" t="s">
         <v>300</v>
       </c>
-      <c r="D13" s="484"/>
-      <c r="E13" s="485"/>
-      <c r="F13" s="486"/>
-      <c r="G13" s="500"/>
-      <c r="H13" s="501"/>
-      <c r="I13" s="501"/>
-      <c r="J13" s="501"/>
-      <c r="K13" s="501"/>
-      <c r="L13" s="501"/>
-      <c r="M13" s="501"/>
-      <c r="N13" s="501"/>
-      <c r="O13" s="502"/>
+      <c r="D13" s="468"/>
+      <c r="E13" s="469"/>
+      <c r="F13" s="470"/>
+      <c r="G13" s="417"/>
+      <c r="H13" s="418"/>
+      <c r="I13" s="418"/>
+      <c r="J13" s="418"/>
+      <c r="K13" s="418"/>
+      <c r="L13" s="418"/>
+      <c r="M13" s="418"/>
+      <c r="N13" s="418"/>
+      <c r="O13" s="419"/>
     </row>
     <row r="14" spans="1:15" ht="23.25" customHeight="1">
       <c r="A14" s="176"/>
       <c r="B14" s="177"/>
-      <c r="C14" s="484"/>
-      <c r="D14" s="484"/>
-      <c r="E14" s="485"/>
-      <c r="F14" s="486"/>
-      <c r="G14" s="444" t="s">
+      <c r="C14" s="468"/>
+      <c r="D14" s="468"/>
+      <c r="E14" s="469"/>
+      <c r="F14" s="470"/>
+      <c r="G14" s="403" t="s">
         <v>324</v>
       </c>
-      <c r="H14" s="445"/>
-      <c r="I14" s="425"/>
-      <c r="J14" s="425"/>
-      <c r="K14" s="425"/>
-      <c r="L14" s="425"/>
-      <c r="M14" s="425"/>
-      <c r="N14" s="425"/>
-      <c r="O14" s="426"/>
+      <c r="H14" s="404"/>
+      <c r="I14" s="421"/>
+      <c r="J14" s="421"/>
+      <c r="K14" s="421"/>
+      <c r="L14" s="421"/>
+      <c r="M14" s="421"/>
+      <c r="N14" s="421"/>
+      <c r="O14" s="487"/>
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1">
       <c r="A15" s="176"/>
       <c r="B15" s="177"/>
-      <c r="C15" s="484"/>
-      <c r="D15" s="484"/>
-      <c r="E15" s="485"/>
-      <c r="F15" s="486"/>
-      <c r="G15" s="503" t="s">
+      <c r="C15" s="468"/>
+      <c r="D15" s="468"/>
+      <c r="E15" s="469"/>
+      <c r="F15" s="470"/>
+      <c r="G15" s="420" t="s">
         <v>301</v>
       </c>
-      <c r="H15" s="425"/>
-      <c r="I15" s="427"/>
-      <c r="J15" s="427"/>
-      <c r="K15" s="427"/>
-      <c r="L15" s="427"/>
-      <c r="M15" s="427"/>
-      <c r="N15" s="427"/>
-      <c r="O15" s="428"/>
+      <c r="H15" s="421"/>
+      <c r="I15" s="456"/>
+      <c r="J15" s="456"/>
+      <c r="K15" s="456"/>
+      <c r="L15" s="456"/>
+      <c r="M15" s="456"/>
+      <c r="N15" s="456"/>
+      <c r="O15" s="457"/>
     </row>
     <row r="16" spans="1:15" ht="27.75" customHeight="1">
       <c r="A16" s="176"/>
       <c r="B16" s="177"/>
-      <c r="C16" s="484"/>
-      <c r="D16" s="484"/>
-      <c r="E16" s="485"/>
-      <c r="F16" s="486"/>
-      <c r="G16" s="504" t="s">
+      <c r="C16" s="468"/>
+      <c r="D16" s="468"/>
+      <c r="E16" s="469"/>
+      <c r="F16" s="470"/>
+      <c r="G16" s="493" t="s">
         <v>302</v>
       </c>
-      <c r="H16" s="505"/>
-      <c r="I16" s="429"/>
-      <c r="J16" s="429"/>
-      <c r="K16" s="429"/>
-      <c r="L16" s="429"/>
-      <c r="M16" s="429"/>
-      <c r="N16" s="429"/>
-      <c r="O16" s="430"/>
+      <c r="H16" s="494"/>
+      <c r="I16" s="488"/>
+      <c r="J16" s="488"/>
+      <c r="K16" s="488"/>
+      <c r="L16" s="488"/>
+      <c r="M16" s="488"/>
+      <c r="N16" s="488"/>
+      <c r="O16" s="489"/>
     </row>
     <row r="17" spans="1:15" ht="21" customHeight="1">
       <c r="A17" s="181"/>
       <c r="B17" s="182"/>
-      <c r="C17" s="487"/>
-      <c r="D17" s="487"/>
-      <c r="E17" s="487"/>
-      <c r="F17" s="488"/>
-      <c r="G17" s="406" t="s">
+      <c r="C17" s="471"/>
+      <c r="D17" s="471"/>
+      <c r="E17" s="471"/>
+      <c r="F17" s="472"/>
+      <c r="G17" s="490" t="s">
         <v>303</v>
       </c>
-      <c r="H17" s="407"/>
-      <c r="I17" s="407"/>
-      <c r="J17" s="407"/>
-      <c r="K17" s="407"/>
-      <c r="L17" s="407"/>
-      <c r="M17" s="407"/>
-      <c r="N17" s="407"/>
-      <c r="O17" s="408"/>
+      <c r="H17" s="491"/>
+      <c r="I17" s="491"/>
+      <c r="J17" s="491"/>
+      <c r="K17" s="491"/>
+      <c r="L17" s="491"/>
+      <c r="M17" s="491"/>
+      <c r="N17" s="491"/>
+      <c r="O17" s="492"/>
     </row>
     <row r="18" spans="1:15" ht="33" customHeight="1">
-      <c r="A18" s="491">
+      <c r="A18" s="401">
         <v>36</v>
       </c>
-      <c r="B18" s="492"/>
-      <c r="C18" s="489" t="s">
+      <c r="B18" s="402"/>
+      <c r="C18" s="409" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="489" t="b">
+      <c r="D18" s="409" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="489"/>
-      <c r="F18" s="490"/>
-      <c r="G18" s="462" t="b">
+      <c r="E18" s="409"/>
+      <c r="F18" s="410"/>
+      <c r="G18" s="407" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="463"/>
-      <c r="I18" s="409" t="b">
+      <c r="H18" s="408"/>
+      <c r="I18" s="454" t="b">
         <v>0</v>
       </c>
-      <c r="J18" s="409"/>
-      <c r="K18" s="409"/>
-      <c r="L18" s="409"/>
-      <c r="M18" s="409"/>
-      <c r="N18" s="409"/>
-      <c r="O18" s="410"/>
+      <c r="J18" s="454"/>
+      <c r="K18" s="454"/>
+      <c r="L18" s="454"/>
+      <c r="M18" s="454"/>
+      <c r="N18" s="454"/>
+      <c r="O18" s="455"/>
     </row>
     <row r="19" spans="1:15" ht="26.25" customHeight="1">
       <c r="A19" s="174"/>
       <c r="B19" s="175"/>
-      <c r="C19" s="446"/>
-      <c r="D19" s="446"/>
-      <c r="E19" s="446"/>
-      <c r="F19" s="447"/>
-      <c r="G19" s="464" t="s">
+      <c r="C19" s="411"/>
+      <c r="D19" s="411"/>
+      <c r="E19" s="411"/>
+      <c r="F19" s="412"/>
+      <c r="G19" s="405" t="s">
         <v>323</v>
       </c>
-      <c r="H19" s="465"/>
-      <c r="I19" s="427"/>
-      <c r="J19" s="427"/>
-      <c r="K19" s="427"/>
-      <c r="L19" s="427"/>
-      <c r="M19" s="427"/>
-      <c r="N19" s="427"/>
-      <c r="O19" s="428"/>
+      <c r="H19" s="406"/>
+      <c r="I19" s="456"/>
+      <c r="J19" s="456"/>
+      <c r="K19" s="456"/>
+      <c r="L19" s="456"/>
+      <c r="M19" s="456"/>
+      <c r="N19" s="456"/>
+      <c r="O19" s="457"/>
     </row>
     <row r="20" spans="1:15" ht="25.5" customHeight="1">
       <c r="A20" s="185"/>
       <c r="B20" s="186"/>
-      <c r="C20" s="466"/>
-      <c r="D20" s="466"/>
-      <c r="E20" s="466"/>
-      <c r="F20" s="467"/>
-      <c r="G20" s="406"/>
-      <c r="H20" s="407"/>
-      <c r="I20" s="407"/>
-      <c r="J20" s="407"/>
-      <c r="K20" s="407"/>
-      <c r="L20" s="407"/>
-      <c r="M20" s="407"/>
-      <c r="N20" s="407"/>
-      <c r="O20" s="408"/>
+      <c r="C20" s="413"/>
+      <c r="D20" s="413"/>
+      <c r="E20" s="413"/>
+      <c r="F20" s="414"/>
+      <c r="G20" s="490"/>
+      <c r="H20" s="491"/>
+      <c r="I20" s="491"/>
+      <c r="J20" s="491"/>
+      <c r="K20" s="491"/>
+      <c r="L20" s="491"/>
+      <c r="M20" s="491"/>
+      <c r="N20" s="491"/>
+      <c r="O20" s="492"/>
     </row>
     <row r="21" spans="1:15" ht="26.25" customHeight="1">
-      <c r="A21" s="491">
+      <c r="A21" s="401">
         <v>37</v>
       </c>
-      <c r="B21" s="492"/>
-      <c r="C21" s="489" t="s">
+      <c r="B21" s="402"/>
+      <c r="C21" s="409" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="489"/>
-      <c r="E21" s="489"/>
-      <c r="F21" s="490"/>
-      <c r="G21" s="462" t="b">
+      <c r="D21" s="409"/>
+      <c r="E21" s="409"/>
+      <c r="F21" s="410"/>
+      <c r="G21" s="407" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="463"/>
-      <c r="I21" s="409" t="b">
+      <c r="H21" s="408"/>
+      <c r="I21" s="454" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="409"/>
-      <c r="K21" s="409"/>
-      <c r="L21" s="409"/>
-      <c r="M21" s="409"/>
-      <c r="N21" s="409"/>
-      <c r="O21" s="410"/>
+      <c r="J21" s="454"/>
+      <c r="K21" s="454"/>
+      <c r="L21" s="454"/>
+      <c r="M21" s="454"/>
+      <c r="N21" s="454"/>
+      <c r="O21" s="455"/>
     </row>
     <row r="22" spans="1:15" ht="27.75" customHeight="1">
       <c r="A22" s="174"/>
       <c r="B22" s="175"/>
-      <c r="C22" s="446"/>
-      <c r="D22" s="446"/>
-      <c r="E22" s="446"/>
-      <c r="F22" s="447"/>
-      <c r="G22" s="464" t="s">
+      <c r="C22" s="411"/>
+      <c r="D22" s="411"/>
+      <c r="E22" s="411"/>
+      <c r="F22" s="412"/>
+      <c r="G22" s="405" t="s">
         <v>322</v>
       </c>
-      <c r="H22" s="465"/>
-      <c r="I22" s="427"/>
-      <c r="J22" s="427"/>
-      <c r="K22" s="427"/>
-      <c r="L22" s="427"/>
-      <c r="M22" s="427"/>
-      <c r="N22" s="427"/>
-      <c r="O22" s="428"/>
+      <c r="H22" s="406"/>
+      <c r="I22" s="456"/>
+      <c r="J22" s="456"/>
+      <c r="K22" s="456"/>
+      <c r="L22" s="456"/>
+      <c r="M22" s="456"/>
+      <c r="N22" s="456"/>
+      <c r="O22" s="457"/>
     </row>
     <row r="23" spans="1:15" ht="39.75" customHeight="1">
       <c r="A23" s="185"/>
       <c r="B23" s="186"/>
-      <c r="C23" s="466"/>
-      <c r="D23" s="466"/>
-      <c r="E23" s="466"/>
-      <c r="F23" s="467"/>
-      <c r="G23" s="406"/>
-      <c r="H23" s="407"/>
-      <c r="I23" s="407"/>
-      <c r="J23" s="407"/>
-      <c r="K23" s="407"/>
-      <c r="L23" s="407"/>
-      <c r="M23" s="407"/>
-      <c r="N23" s="407"/>
-      <c r="O23" s="408"/>
+      <c r="C23" s="413"/>
+      <c r="D23" s="413"/>
+      <c r="E23" s="413"/>
+      <c r="F23" s="414"/>
+      <c r="G23" s="490"/>
+      <c r="H23" s="491"/>
+      <c r="I23" s="491"/>
+      <c r="J23" s="491"/>
+      <c r="K23" s="491"/>
+      <c r="L23" s="491"/>
+      <c r="M23" s="491"/>
+      <c r="N23" s="491"/>
+      <c r="O23" s="492"/>
     </row>
     <row r="24" spans="1:15" ht="38.25" customHeight="1">
-      <c r="A24" s="491">
+      <c r="A24" s="401">
         <v>38</v>
       </c>
-      <c r="B24" s="492"/>
-      <c r="C24" s="489" t="s">
+      <c r="B24" s="402"/>
+      <c r="C24" s="409" t="s">
         <v>306</v>
       </c>
-      <c r="D24" s="489"/>
-      <c r="E24" s="489"/>
-      <c r="F24" s="490"/>
-      <c r="G24" s="462" t="b">
+      <c r="D24" s="409"/>
+      <c r="E24" s="409"/>
+      <c r="F24" s="410"/>
+      <c r="G24" s="407" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="463"/>
-      <c r="I24" s="409" t="b">
+      <c r="H24" s="408"/>
+      <c r="I24" s="454" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="409"/>
-      <c r="K24" s="409"/>
-      <c r="L24" s="409"/>
-      <c r="M24" s="409"/>
-      <c r="N24" s="409"/>
-      <c r="O24" s="410"/>
+      <c r="J24" s="454"/>
+      <c r="K24" s="454"/>
+      <c r="L24" s="454"/>
+      <c r="M24" s="454"/>
+      <c r="N24" s="454"/>
+      <c r="O24" s="455"/>
     </row>
     <row r="25" spans="1:15" ht="28.5" customHeight="1">
       <c r="A25" s="174"/>
       <c r="B25" s="175"/>
-      <c r="C25" s="446"/>
-      <c r="D25" s="446"/>
-      <c r="E25" s="446"/>
-      <c r="F25" s="447"/>
-      <c r="G25" s="444" t="s">
+      <c r="C25" s="411"/>
+      <c r="D25" s="411"/>
+      <c r="E25" s="411"/>
+      <c r="F25" s="412"/>
+      <c r="G25" s="403" t="s">
         <v>307</v>
       </c>
-      <c r="H25" s="445"/>
-      <c r="I25" s="411"/>
-      <c r="J25" s="411"/>
-      <c r="K25" s="411"/>
-      <c r="L25" s="411"/>
-      <c r="M25" s="411"/>
-      <c r="N25" s="411"/>
-      <c r="O25" s="412"/>
+      <c r="H25" s="404"/>
+      <c r="I25" s="495"/>
+      <c r="J25" s="495"/>
+      <c r="K25" s="495"/>
+      <c r="L25" s="495"/>
+      <c r="M25" s="495"/>
+      <c r="N25" s="495"/>
+      <c r="O25" s="496"/>
     </row>
     <row r="26" spans="1:15" ht="23.25" customHeight="1">
       <c r="A26" s="174"/>
@@ -16719,256 +16715,256 @@
       <c r="D26" s="183"/>
       <c r="E26" s="183"/>
       <c r="F26" s="184"/>
-      <c r="G26" s="474" t="b">
+      <c r="G26" s="466" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="475"/>
-      <c r="I26" s="413" t="b">
+      <c r="H26" s="467"/>
+      <c r="I26" s="497" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="413"/>
-      <c r="K26" s="413"/>
-      <c r="L26" s="413"/>
-      <c r="M26" s="413"/>
-      <c r="N26" s="413"/>
-      <c r="O26" s="414"/>
+      <c r="J26" s="497"/>
+      <c r="K26" s="497"/>
+      <c r="L26" s="497"/>
+      <c r="M26" s="497"/>
+      <c r="N26" s="497"/>
+      <c r="O26" s="498"/>
     </row>
     <row r="27" spans="1:15" ht="24.75" customHeight="1">
       <c r="A27" s="174"/>
       <c r="B27" s="175"/>
-      <c r="C27" s="446" t="s">
+      <c r="C27" s="411" t="s">
         <v>308</v>
       </c>
-      <c r="D27" s="446"/>
-      <c r="E27" s="446"/>
-      <c r="F27" s="447"/>
-      <c r="G27" s="474"/>
-      <c r="H27" s="475"/>
-      <c r="I27" s="415"/>
-      <c r="J27" s="415"/>
-      <c r="K27" s="415"/>
-      <c r="L27" s="415"/>
-      <c r="M27" s="415"/>
-      <c r="N27" s="415"/>
-      <c r="O27" s="416"/>
+      <c r="D27" s="411"/>
+      <c r="E27" s="411"/>
+      <c r="F27" s="412"/>
+      <c r="G27" s="466"/>
+      <c r="H27" s="467"/>
+      <c r="I27" s="499"/>
+      <c r="J27" s="499"/>
+      <c r="K27" s="499"/>
+      <c r="L27" s="499"/>
+      <c r="M27" s="499"/>
+      <c r="N27" s="499"/>
+      <c r="O27" s="500"/>
     </row>
     <row r="28" spans="1:15" ht="36" customHeight="1">
       <c r="A28" s="174"/>
       <c r="B28" s="175"/>
-      <c r="C28" s="446"/>
-      <c r="D28" s="446"/>
-      <c r="E28" s="446"/>
-      <c r="F28" s="447"/>
-      <c r="G28" s="444" t="s">
+      <c r="C28" s="411"/>
+      <c r="D28" s="411"/>
+      <c r="E28" s="411"/>
+      <c r="F28" s="412"/>
+      <c r="G28" s="403" t="s">
         <v>307</v>
       </c>
-      <c r="H28" s="445"/>
-      <c r="I28" s="411"/>
-      <c r="J28" s="411"/>
-      <c r="K28" s="411"/>
-      <c r="L28" s="411"/>
-      <c r="M28" s="411"/>
-      <c r="N28" s="411"/>
-      <c r="O28" s="412"/>
+      <c r="H28" s="404"/>
+      <c r="I28" s="495"/>
+      <c r="J28" s="495"/>
+      <c r="K28" s="495"/>
+      <c r="L28" s="495"/>
+      <c r="M28" s="495"/>
+      <c r="N28" s="495"/>
+      <c r="O28" s="496"/>
     </row>
     <row r="29" spans="1:15" ht="30.75" customHeight="1">
       <c r="A29" s="185"/>
       <c r="B29" s="186"/>
-      <c r="C29" s="466"/>
-      <c r="D29" s="466"/>
-      <c r="E29" s="466"/>
-      <c r="F29" s="467"/>
-      <c r="G29" s="417"/>
-      <c r="H29" s="418"/>
-      <c r="I29" s="418"/>
-      <c r="J29" s="418"/>
-      <c r="K29" s="418"/>
-      <c r="L29" s="418"/>
-      <c r="M29" s="418"/>
-      <c r="N29" s="418"/>
-      <c r="O29" s="419"/>
+      <c r="C29" s="413"/>
+      <c r="D29" s="413"/>
+      <c r="E29" s="413"/>
+      <c r="F29" s="414"/>
+      <c r="G29" s="481"/>
+      <c r="H29" s="482"/>
+      <c r="I29" s="482"/>
+      <c r="J29" s="482"/>
+      <c r="K29" s="482"/>
+      <c r="L29" s="482"/>
+      <c r="M29" s="482"/>
+      <c r="N29" s="482"/>
+      <c r="O29" s="483"/>
     </row>
     <row r="30" spans="1:15" ht="23.45" customHeight="1">
-      <c r="A30" s="491">
+      <c r="A30" s="401">
         <v>39</v>
       </c>
-      <c r="B30" s="492"/>
-      <c r="C30" s="468" t="s">
+      <c r="B30" s="402"/>
+      <c r="C30" s="461" t="s">
         <v>309</v>
       </c>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="469"/>
-      <c r="G30" s="462" t="b">
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="462"/>
+      <c r="G30" s="407" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="463"/>
-      <c r="I30" s="409" t="b">
+      <c r="H30" s="408"/>
+      <c r="I30" s="454" t="b">
         <v>0</v>
       </c>
-      <c r="J30" s="409"/>
-      <c r="K30" s="409"/>
-      <c r="L30" s="409"/>
-      <c r="M30" s="409"/>
-      <c r="N30" s="409"/>
-      <c r="O30" s="410"/>
+      <c r="J30" s="454"/>
+      <c r="K30" s="454"/>
+      <c r="L30" s="454"/>
+      <c r="M30" s="454"/>
+      <c r="N30" s="454"/>
+      <c r="O30" s="455"/>
     </row>
     <row r="31" spans="1:15" ht="27" customHeight="1">
       <c r="A31" s="174"/>
       <c r="B31" s="175"/>
-      <c r="C31" s="470"/>
-      <c r="D31" s="470"/>
-      <c r="E31" s="470"/>
-      <c r="F31" s="471"/>
-      <c r="G31" s="464" t="s">
+      <c r="C31" s="428"/>
+      <c r="D31" s="428"/>
+      <c r="E31" s="428"/>
+      <c r="F31" s="463"/>
+      <c r="G31" s="405" t="s">
         <v>310</v>
       </c>
-      <c r="H31" s="465"/>
-      <c r="I31" s="420"/>
-      <c r="J31" s="420"/>
-      <c r="K31" s="420"/>
-      <c r="L31" s="420"/>
-      <c r="M31" s="420"/>
-      <c r="N31" s="420"/>
-      <c r="O31" s="421"/>
+      <c r="H31" s="406"/>
+      <c r="I31" s="444"/>
+      <c r="J31" s="444"/>
+      <c r="K31" s="444"/>
+      <c r="L31" s="444"/>
+      <c r="M31" s="444"/>
+      <c r="N31" s="444"/>
+      <c r="O31" s="445"/>
     </row>
     <row r="32" spans="1:15" ht="33.75" customHeight="1">
       <c r="A32" s="185"/>
       <c r="B32" s="186"/>
-      <c r="C32" s="472"/>
-      <c r="D32" s="472"/>
-      <c r="E32" s="472"/>
-      <c r="F32" s="473"/>
-      <c r="G32" s="422"/>
-      <c r="H32" s="423"/>
-      <c r="I32" s="423"/>
-      <c r="J32" s="423"/>
-      <c r="K32" s="423"/>
-      <c r="L32" s="423"/>
-      <c r="M32" s="423"/>
-      <c r="N32" s="423"/>
-      <c r="O32" s="424"/>
+      <c r="C32" s="464"/>
+      <c r="D32" s="464"/>
+      <c r="E32" s="464"/>
+      <c r="F32" s="465"/>
+      <c r="G32" s="484"/>
+      <c r="H32" s="485"/>
+      <c r="I32" s="485"/>
+      <c r="J32" s="485"/>
+      <c r="K32" s="485"/>
+      <c r="L32" s="485"/>
+      <c r="M32" s="485"/>
+      <c r="N32" s="485"/>
+      <c r="O32" s="486"/>
     </row>
     <row r="33" spans="1:15" ht="46.5" customHeight="1">
-      <c r="A33" s="456">
+      <c r="A33" s="436">
         <v>40</v>
       </c>
-      <c r="B33" s="457"/>
-      <c r="C33" s="446" t="s">
+      <c r="B33" s="437"/>
+      <c r="C33" s="411" t="s">
         <v>311</v>
       </c>
-      <c r="D33" s="446"/>
-      <c r="E33" s="446"/>
-      <c r="F33" s="447"/>
-      <c r="G33" s="459"/>
-      <c r="H33" s="460"/>
-      <c r="I33" s="460"/>
-      <c r="J33" s="460"/>
-      <c r="K33" s="460"/>
-      <c r="L33" s="460"/>
-      <c r="M33" s="460"/>
-      <c r="N33" s="460"/>
-      <c r="O33" s="461"/>
+      <c r="D33" s="411"/>
+      <c r="E33" s="411"/>
+      <c r="F33" s="412"/>
+      <c r="G33" s="440"/>
+      <c r="H33" s="441"/>
+      <c r="I33" s="441"/>
+      <c r="J33" s="441"/>
+      <c r="K33" s="441"/>
+      <c r="L33" s="441"/>
+      <c r="M33" s="441"/>
+      <c r="N33" s="441"/>
+      <c r="O33" s="442"/>
     </row>
     <row r="34" spans="1:15" ht="39.75" customHeight="1">
       <c r="A34" s="187" t="s">
         <v>312</v>
       </c>
       <c r="B34" s="188"/>
-      <c r="C34" s="446" t="s">
+      <c r="C34" s="411" t="s">
         <v>313</v>
       </c>
-      <c r="D34" s="446"/>
-      <c r="E34" s="446"/>
-      <c r="F34" s="447"/>
-      <c r="G34" s="458" t="b">
+      <c r="D34" s="411"/>
+      <c r="E34" s="411"/>
+      <c r="F34" s="412"/>
+      <c r="G34" s="438" t="b">
         <v>0</v>
       </c>
-      <c r="H34" s="434"/>
-      <c r="I34" s="434" t="b">
+      <c r="H34" s="439"/>
+      <c r="I34" s="439" t="b">
         <v>0</v>
       </c>
-      <c r="J34" s="434"/>
-      <c r="K34" s="434"/>
-      <c r="L34" s="434"/>
-      <c r="M34" s="434"/>
-      <c r="N34" s="434"/>
-      <c r="O34" s="435"/>
+      <c r="J34" s="439"/>
+      <c r="K34" s="439"/>
+      <c r="L34" s="439"/>
+      <c r="M34" s="439"/>
+      <c r="N34" s="439"/>
+      <c r="O34" s="443"/>
     </row>
     <row r="35" spans="1:15" ht="36.75" customHeight="1">
       <c r="A35" s="189"/>
       <c r="B35" s="188"/>
-      <c r="C35" s="446"/>
-      <c r="D35" s="446"/>
-      <c r="E35" s="446"/>
-      <c r="F35" s="447"/>
-      <c r="G35" s="444" t="s">
+      <c r="C35" s="411"/>
+      <c r="D35" s="411"/>
+      <c r="E35" s="411"/>
+      <c r="F35" s="412"/>
+      <c r="G35" s="403" t="s">
         <v>307</v>
       </c>
-      <c r="H35" s="445"/>
-      <c r="I35" s="420"/>
-      <c r="J35" s="420"/>
-      <c r="K35" s="420"/>
-      <c r="L35" s="420"/>
-      <c r="M35" s="420"/>
-      <c r="N35" s="420"/>
-      <c r="O35" s="421"/>
+      <c r="H35" s="404"/>
+      <c r="I35" s="444"/>
+      <c r="J35" s="444"/>
+      <c r="K35" s="444"/>
+      <c r="L35" s="444"/>
+      <c r="M35" s="444"/>
+      <c r="N35" s="444"/>
+      <c r="O35" s="445"/>
     </row>
     <row r="36" spans="1:15" ht="33" customHeight="1">
       <c r="A36" s="187" t="s">
         <v>314</v>
       </c>
       <c r="B36" s="188"/>
-      <c r="C36" s="447" t="s">
+      <c r="C36" s="412" t="s">
         <v>315</v>
       </c>
-      <c r="D36" s="447"/>
-      <c r="E36" s="447"/>
-      <c r="F36" s="447"/>
-      <c r="G36" s="458" t="b">
+      <c r="D36" s="412"/>
+      <c r="E36" s="412"/>
+      <c r="F36" s="412"/>
+      <c r="G36" s="438" t="b">
         <v>0</v>
       </c>
-      <c r="H36" s="434"/>
-      <c r="I36" s="453" t="b">
+      <c r="H36" s="439"/>
+      <c r="I36" s="451" t="b">
         <v>0</v>
       </c>
-      <c r="J36" s="453"/>
-      <c r="K36" s="453"/>
-      <c r="L36" s="453"/>
-      <c r="M36" s="453"/>
-      <c r="N36" s="453"/>
-      <c r="O36" s="454"/>
+      <c r="J36" s="451"/>
+      <c r="K36" s="451"/>
+      <c r="L36" s="451"/>
+      <c r="M36" s="451"/>
+      <c r="N36" s="451"/>
+      <c r="O36" s="452"/>
     </row>
     <row r="37" spans="1:15" ht="27.75" customHeight="1">
       <c r="A37" s="189"/>
       <c r="B37" s="188"/>
-      <c r="C37" s="447"/>
-      <c r="D37" s="447"/>
-      <c r="E37" s="447"/>
-      <c r="F37" s="447"/>
-      <c r="G37" s="444" t="s">
+      <c r="C37" s="412"/>
+      <c r="D37" s="412"/>
+      <c r="E37" s="412"/>
+      <c r="F37" s="412"/>
+      <c r="G37" s="403" t="s">
         <v>307</v>
       </c>
-      <c r="H37" s="445"/>
-      <c r="I37" s="506" t="b">
+      <c r="H37" s="404"/>
+      <c r="I37" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="J37" s="506" t="b">
+      <c r="J37" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="K37" s="506" t="b">
+      <c r="K37" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="L37" s="506" t="b">
+      <c r="L37" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="M37" s="506" t="b">
+      <c r="M37" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="N37" s="506" t="b">
+      <c r="N37" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="O37" s="507" t="b">
+      <c r="O37" s="506" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16977,16 +16973,16 @@
         <v>316</v>
       </c>
       <c r="B38" s="188"/>
-      <c r="C38" s="446" t="s">
+      <c r="C38" s="411" t="s">
         <v>317</v>
       </c>
-      <c r="D38" s="446"/>
+      <c r="D38" s="411"/>
       <c r="E38" s="190"/>
       <c r="F38" s="191"/>
-      <c r="G38" s="448" t="b">
+      <c r="G38" s="446" t="b">
         <v>0</v>
       </c>
-      <c r="H38" s="449"/>
+      <c r="H38" s="447"/>
       <c r="I38" s="166" t="b">
         <v>0</v>
       </c>
@@ -16998,133 +16994,133 @@
       <c r="O38" s="169"/>
     </row>
     <row r="39" spans="1:15" ht="28.5" customHeight="1">
-      <c r="A39" s="450"/>
-      <c r="B39" s="451"/>
-      <c r="C39" s="451"/>
-      <c r="D39" s="451"/>
-      <c r="E39" s="451"/>
-      <c r="F39" s="452"/>
-      <c r="G39" s="444" t="s">
+      <c r="A39" s="448"/>
+      <c r="B39" s="449"/>
+      <c r="C39" s="449"/>
+      <c r="D39" s="449"/>
+      <c r="E39" s="449"/>
+      <c r="F39" s="450"/>
+      <c r="G39" s="403" t="s">
         <v>307</v>
       </c>
-      <c r="H39" s="445"/>
-      <c r="I39" s="420"/>
-      <c r="J39" s="420"/>
-      <c r="K39" s="420"/>
-      <c r="L39" s="420"/>
-      <c r="M39" s="420"/>
-      <c r="N39" s="420"/>
-      <c r="O39" s="421"/>
+      <c r="H39" s="404"/>
+      <c r="I39" s="444"/>
+      <c r="J39" s="444"/>
+      <c r="K39" s="444"/>
+      <c r="L39" s="444"/>
+      <c r="M39" s="444"/>
+      <c r="N39" s="444"/>
+      <c r="O39" s="445"/>
     </row>
     <row r="40" spans="1:15" ht="37.5" customHeight="1">
-      <c r="A40" s="450"/>
-      <c r="B40" s="451"/>
-      <c r="C40" s="451"/>
-      <c r="D40" s="451"/>
-      <c r="E40" s="451"/>
-      <c r="F40" s="452"/>
-      <c r="G40" s="444"/>
-      <c r="H40" s="445"/>
-      <c r="I40" s="445"/>
-      <c r="J40" s="445"/>
-      <c r="K40" s="445"/>
-      <c r="L40" s="445"/>
-      <c r="M40" s="445"/>
-      <c r="N40" s="445"/>
-      <c r="O40" s="455"/>
+      <c r="A40" s="448"/>
+      <c r="B40" s="449"/>
+      <c r="C40" s="449"/>
+      <c r="D40" s="449"/>
+      <c r="E40" s="449"/>
+      <c r="F40" s="450"/>
+      <c r="G40" s="403"/>
+      <c r="H40" s="404"/>
+      <c r="I40" s="404"/>
+      <c r="J40" s="404"/>
+      <c r="K40" s="404"/>
+      <c r="L40" s="404"/>
+      <c r="M40" s="404"/>
+      <c r="N40" s="404"/>
+      <c r="O40" s="453"/>
     </row>
     <row r="41" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A41" s="403" t="s">
+      <c r="A41" s="503" t="s">
         <v>346</v>
       </c>
-      <c r="B41" s="403"/>
-      <c r="C41" s="403"/>
-      <c r="D41" s="403"/>
-      <c r="E41" s="403"/>
-      <c r="F41" s="403"/>
-      <c r="G41" s="403"/>
-      <c r="H41" s="403"/>
-      <c r="I41" s="403"/>
-      <c r="J41" s="403"/>
-      <c r="K41" s="403"/>
-      <c r="L41" s="403"/>
-      <c r="M41" s="403"/>
-      <c r="N41" s="403"/>
-      <c r="O41" s="403"/>
+      <c r="B41" s="503"/>
+      <c r="C41" s="503"/>
+      <c r="D41" s="503"/>
+      <c r="E41" s="503"/>
+      <c r="F41" s="503"/>
+      <c r="G41" s="503"/>
+      <c r="H41" s="503"/>
+      <c r="I41" s="503"/>
+      <c r="J41" s="503"/>
+      <c r="K41" s="503"/>
+      <c r="L41" s="503"/>
+      <c r="M41" s="503"/>
+      <c r="N41" s="503"/>
+      <c r="O41" s="503"/>
     </row>
     <row r="42" spans="1:15" ht="18" customHeight="1">
-      <c r="A42" s="404" t="s">
+      <c r="A42" s="504" t="s">
         <v>318</v>
       </c>
-      <c r="B42" s="404"/>
-      <c r="C42" s="404"/>
-      <c r="D42" s="404"/>
-      <c r="E42" s="404"/>
-      <c r="F42" s="404"/>
-      <c r="G42" s="404" t="s">
+      <c r="B42" s="504"/>
+      <c r="C42" s="504"/>
+      <c r="D42" s="504"/>
+      <c r="E42" s="504"/>
+      <c r="F42" s="504"/>
+      <c r="G42" s="504" t="s">
         <v>319</v>
       </c>
-      <c r="H42" s="404"/>
-      <c r="I42" s="404"/>
-      <c r="J42" s="404"/>
-      <c r="K42" s="404"/>
-      <c r="L42" s="404"/>
-      <c r="M42" s="401" t="s">
+      <c r="H42" s="504"/>
+      <c r="I42" s="504"/>
+      <c r="J42" s="504"/>
+      <c r="K42" s="504"/>
+      <c r="L42" s="504"/>
+      <c r="M42" s="501" t="s">
         <v>320</v>
       </c>
-      <c r="N42" s="401"/>
-      <c r="O42" s="401"/>
+      <c r="N42" s="501"/>
+      <c r="O42" s="501"/>
     </row>
     <row r="43" spans="1:15" ht="24" customHeight="1">
-      <c r="A43" s="405"/>
-      <c r="B43" s="405"/>
-      <c r="C43" s="405"/>
-      <c r="D43" s="405"/>
-      <c r="E43" s="405"/>
-      <c r="F43" s="405"/>
-      <c r="G43" s="402"/>
-      <c r="H43" s="402"/>
-      <c r="I43" s="402"/>
-      <c r="J43" s="402"/>
-      <c r="K43" s="402"/>
-      <c r="L43" s="402"/>
-      <c r="M43" s="402"/>
-      <c r="N43" s="402"/>
-      <c r="O43" s="402"/>
+      <c r="A43" s="505"/>
+      <c r="B43" s="505"/>
+      <c r="C43" s="505"/>
+      <c r="D43" s="505"/>
+      <c r="E43" s="505"/>
+      <c r="F43" s="505"/>
+      <c r="G43" s="502"/>
+      <c r="H43" s="502"/>
+      <c r="I43" s="502"/>
+      <c r="J43" s="502"/>
+      <c r="K43" s="502"/>
+      <c r="L43" s="502"/>
+      <c r="M43" s="502"/>
+      <c r="N43" s="502"/>
+      <c r="O43" s="502"/>
     </row>
     <row r="44" spans="1:15" ht="24" customHeight="1">
-      <c r="A44" s="405"/>
-      <c r="B44" s="405"/>
-      <c r="C44" s="405"/>
-      <c r="D44" s="405"/>
-      <c r="E44" s="405"/>
-      <c r="F44" s="405"/>
-      <c r="G44" s="402"/>
-      <c r="H44" s="402"/>
-      <c r="I44" s="402"/>
-      <c r="J44" s="402"/>
-      <c r="K44" s="402"/>
-      <c r="L44" s="402"/>
-      <c r="M44" s="402"/>
-      <c r="N44" s="402"/>
-      <c r="O44" s="402"/>
+      <c r="A44" s="505"/>
+      <c r="B44" s="505"/>
+      <c r="C44" s="505"/>
+      <c r="D44" s="505"/>
+      <c r="E44" s="505"/>
+      <c r="F44" s="505"/>
+      <c r="G44" s="502"/>
+      <c r="H44" s="502"/>
+      <c r="I44" s="502"/>
+      <c r="J44" s="502"/>
+      <c r="K44" s="502"/>
+      <c r="L44" s="502"/>
+      <c r="M44" s="502"/>
+      <c r="N44" s="502"/>
+      <c r="O44" s="502"/>
     </row>
     <row r="45" spans="1:15" ht="24" customHeight="1">
-      <c r="A45" s="405"/>
-      <c r="B45" s="405"/>
-      <c r="C45" s="405"/>
-      <c r="D45" s="405"/>
-      <c r="E45" s="405"/>
-      <c r="F45" s="405"/>
-      <c r="G45" s="402"/>
-      <c r="H45" s="402"/>
-      <c r="I45" s="402"/>
-      <c r="J45" s="402"/>
-      <c r="K45" s="402"/>
-      <c r="L45" s="402"/>
-      <c r="M45" s="402"/>
-      <c r="N45" s="402"/>
-      <c r="O45" s="402"/>
+      <c r="A45" s="505"/>
+      <c r="B45" s="505"/>
+      <c r="C45" s="505"/>
+      <c r="D45" s="505"/>
+      <c r="E45" s="505"/>
+      <c r="F45" s="505"/>
+      <c r="G45" s="502"/>
+      <c r="H45" s="502"/>
+      <c r="I45" s="502"/>
+      <c r="J45" s="502"/>
+      <c r="K45" s="502"/>
+      <c r="L45" s="502"/>
+      <c r="M45" s="502"/>
+      <c r="N45" s="502"/>
+      <c r="O45" s="502"/>
     </row>
     <row r="46" spans="1:15" ht="25.5" customHeight="1"/>
     <row r="47" spans="1:15" ht="24.75" customHeight="1"/>
@@ -17144,93 +17140,8 @@
     <row r="61" s="192" customFormat="1" ht="11.25" customHeight="1"/>
     <row r="62" ht="10.5" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="HI85KqrIlc4ZUvr4vE3j0rj3W0Chi9WgtPzlWo/mdrwAzWNT9dNb0YpZRAEzFL8reZXNhOo2wz63CKtOZyRuoA==" saltValue="CDdHUzJEkadi4P8irYdFyw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="moz/kMrc4w/3TybL4Jbf9Ljv02c+w1IYbDsLXgFxhj9i0cQ70dtskMPWJE2kL6SU3TVZhvaxb9utMuybc0e0bw==" saltValue="eKGRhgfvUJeFv04A4oQ6cQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="97">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="C24:F25"/>
-    <mergeCell ref="C21:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:O13"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:F11"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="G33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="A39:F40"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="I39:O39"/>
-    <mergeCell ref="G40:O40"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I9:O9"/>
-    <mergeCell ref="I10:O10"/>
-    <mergeCell ref="G11:O11"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C36:F37"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="C27:F29"/>
-    <mergeCell ref="C30:F32"/>
-    <mergeCell ref="G26:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="C13:F17"/>
-    <mergeCell ref="C18:F20"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G2:O4"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="I7:O7"/>
-    <mergeCell ref="G8:O8"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G29:O29"/>
-    <mergeCell ref="I30:O30"/>
-    <mergeCell ref="I31:O31"/>
-    <mergeCell ref="G32:O32"/>
-    <mergeCell ref="I14:O14"/>
-    <mergeCell ref="I15:O15"/>
-    <mergeCell ref="I16:O16"/>
-    <mergeCell ref="G17:O17"/>
-    <mergeCell ref="I18:O18"/>
-    <mergeCell ref="I19:O19"/>
-    <mergeCell ref="G20:O20"/>
-    <mergeCell ref="I21:O21"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G23:O23"/>
-    <mergeCell ref="I24:O24"/>
-    <mergeCell ref="I25:O25"/>
-    <mergeCell ref="I26:O27"/>
-    <mergeCell ref="I28:O28"/>
-    <mergeCell ref="M42:O42"/>
     <mergeCell ref="M43:O43"/>
     <mergeCell ref="M44:O44"/>
     <mergeCell ref="M45:O45"/>
@@ -17243,6 +17154,91 @@
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="I26:O27"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="G20:O20"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G23:O23"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G2:O4"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="I7:O7"/>
+    <mergeCell ref="G8:O8"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="I15:O15"/>
+    <mergeCell ref="I16:O16"/>
+    <mergeCell ref="G17:O17"/>
+    <mergeCell ref="I18:O18"/>
+    <mergeCell ref="I19:O19"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="C27:F29"/>
+    <mergeCell ref="C30:F32"/>
+    <mergeCell ref="G26:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:O29"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="G32:O32"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="A39:F40"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="I39:O39"/>
+    <mergeCell ref="G40:O40"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C36:F37"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="G33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:F11"/>
+    <mergeCell ref="C13:F17"/>
+    <mergeCell ref="C18:F20"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:O13"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I9:O9"/>
+    <mergeCell ref="I10:O10"/>
+    <mergeCell ref="G11:O11"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="C24:F25"/>
+    <mergeCell ref="C21:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G30:H30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -17955,244 +17951,227 @@
       <c r="A1" s="92" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="335" t="s">
+      <c r="B1" s="316" t="s">
         <v>250</v>
       </c>
-      <c r="C1" s="335"/>
-      <c r="D1" s="335"/>
-      <c r="E1" s="335"/>
-      <c r="F1" s="335"/>
-      <c r="G1" s="335"/>
-      <c r="H1" s="335"/>
-      <c r="I1" s="335"/>
-      <c r="J1" s="335"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
     </row>
     <row r="2" spans="1:10" ht="21" customHeight="1">
       <c r="A2" s="93">
         <v>22</v>
       </c>
-      <c r="B2" s="327" t="s">
+      <c r="B2" s="315" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="327"/>
-      <c r="D2" s="336"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="338"/>
+      <c r="C2" s="315"/>
+      <c r="D2" s="317"/>
+      <c r="E2" s="318"/>
+      <c r="F2" s="318"/>
+      <c r="G2" s="318"/>
+      <c r="H2" s="318"/>
+      <c r="I2" s="318"/>
+      <c r="J2" s="319"/>
     </row>
     <row r="3" spans="1:10" ht="21" customHeight="1">
       <c r="A3" s="94"/>
-      <c r="B3" s="327" t="s">
+      <c r="B3" s="315" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="327"/>
-      <c r="D3" s="329"/>
-      <c r="E3" s="330"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="340" t="s">
+      <c r="C3" s="315"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="322"/>
+      <c r="G3" s="323" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="341"/>
-      <c r="I3" s="342"/>
-      <c r="J3" s="322"/>
+      <c r="H3" s="324"/>
+      <c r="I3" s="325"/>
+      <c r="J3" s="326"/>
     </row>
     <row r="4" spans="1:10" ht="21" customHeight="1">
       <c r="A4" s="94"/>
-      <c r="B4" s="327" t="s">
+      <c r="B4" s="315" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="327"/>
-      <c r="D4" s="329"/>
-      <c r="E4" s="330"/>
-      <c r="F4" s="330"/>
-      <c r="G4" s="330"/>
-      <c r="H4" s="330"/>
-      <c r="I4" s="330"/>
-      <c r="J4" s="331"/>
+      <c r="C4" s="315"/>
+      <c r="D4" s="320"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
+      <c r="H4" s="321"/>
+      <c r="I4" s="321"/>
+      <c r="J4" s="327"/>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1">
       <c r="A5" s="95"/>
-      <c r="B5" s="327" t="s">
+      <c r="B5" s="315" t="s">
         <v>252</v>
       </c>
-      <c r="C5" s="327"/>
-      <c r="D5" s="315"/>
-      <c r="E5" s="316"/>
-      <c r="F5" s="316"/>
-      <c r="G5" s="316"/>
-      <c r="H5" s="316"/>
-      <c r="I5" s="316"/>
-      <c r="J5" s="317"/>
+      <c r="C5" s="315"/>
+      <c r="D5" s="328"/>
+      <c r="E5" s="329"/>
+      <c r="F5" s="329"/>
+      <c r="G5" s="329"/>
+      <c r="H5" s="329"/>
+      <c r="I5" s="329"/>
+      <c r="J5" s="330"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="95"/>
-      <c r="B6" s="327" t="s">
+      <c r="B6" s="315" t="s">
         <v>253</v>
       </c>
-      <c r="C6" s="327"/>
-      <c r="D6" s="315"/>
-      <c r="E6" s="316"/>
-      <c r="F6" s="316"/>
-      <c r="G6" s="316"/>
-      <c r="H6" s="316"/>
-      <c r="I6" s="316"/>
-      <c r="J6" s="317"/>
+      <c r="C6" s="315"/>
+      <c r="D6" s="328"/>
+      <c r="E6" s="329"/>
+      <c r="F6" s="329"/>
+      <c r="G6" s="329"/>
+      <c r="H6" s="329"/>
+      <c r="I6" s="329"/>
+      <c r="J6" s="330"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="95"/>
-      <c r="B7" s="327" t="s">
+      <c r="B7" s="315" t="s">
         <v>254</v>
       </c>
-      <c r="C7" s="327"/>
-      <c r="D7" s="332"/>
-      <c r="E7" s="333"/>
-      <c r="F7" s="333"/>
-      <c r="G7" s="333"/>
-      <c r="H7" s="333"/>
-      <c r="I7" s="333"/>
-      <c r="J7" s="334"/>
+      <c r="C7" s="315"/>
+      <c r="D7" s="331"/>
+      <c r="E7" s="332"/>
+      <c r="F7" s="332"/>
+      <c r="G7" s="332"/>
+      <c r="H7" s="332"/>
+      <c r="I7" s="332"/>
+      <c r="J7" s="333"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="95"/>
-      <c r="B8" s="327" t="s">
+      <c r="B8" s="315" t="s">
         <v>255</v>
       </c>
-      <c r="C8" s="327"/>
-      <c r="D8" s="332"/>
-      <c r="E8" s="333"/>
-      <c r="F8" s="333"/>
-      <c r="G8" s="333"/>
-      <c r="H8" s="333"/>
-      <c r="I8" s="333"/>
-      <c r="J8" s="334"/>
+      <c r="C8" s="315"/>
+      <c r="D8" s="331"/>
+      <c r="E8" s="332"/>
+      <c r="F8" s="332"/>
+      <c r="G8" s="332"/>
+      <c r="H8" s="332"/>
+      <c r="I8" s="332"/>
+      <c r="J8" s="333"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="96">
         <v>24</v>
       </c>
-      <c r="B9" s="328" t="s">
+      <c r="B9" s="342" t="s">
         <v>256</v>
       </c>
-      <c r="C9" s="328"/>
-      <c r="D9" s="315"/>
-      <c r="E9" s="316"/>
-      <c r="F9" s="316"/>
-      <c r="G9" s="316"/>
-      <c r="H9" s="316"/>
-      <c r="I9" s="316"/>
-      <c r="J9" s="317"/>
+      <c r="C9" s="342"/>
+      <c r="D9" s="328"/>
+      <c r="E9" s="329"/>
+      <c r="F9" s="329"/>
+      <c r="G9" s="329"/>
+      <c r="H9" s="329"/>
+      <c r="I9" s="329"/>
+      <c r="J9" s="330"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="94"/>
-      <c r="B10" s="327" t="s">
+      <c r="B10" s="315" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="327"/>
-      <c r="D10" s="315"/>
-      <c r="E10" s="316"/>
-      <c r="F10" s="318"/>
-      <c r="G10" s="319" t="s">
+      <c r="C10" s="315"/>
+      <c r="D10" s="328"/>
+      <c r="E10" s="329"/>
+      <c r="F10" s="334"/>
+      <c r="G10" s="335" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="320"/>
-      <c r="I10" s="321"/>
-      <c r="J10" s="322"/>
+      <c r="H10" s="336"/>
+      <c r="I10" s="337"/>
+      <c r="J10" s="326"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="94"/>
-      <c r="B11" s="327" t="s">
+      <c r="B11" s="315" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="327"/>
-      <c r="D11" s="323"/>
-      <c r="E11" s="316"/>
-      <c r="F11" s="316"/>
-      <c r="G11" s="316"/>
-      <c r="H11" s="316"/>
-      <c r="I11" s="316"/>
-      <c r="J11" s="317"/>
+      <c r="C11" s="315"/>
+      <c r="D11" s="338"/>
+      <c r="E11" s="329"/>
+      <c r="F11" s="329"/>
+      <c r="G11" s="329"/>
+      <c r="H11" s="329"/>
+      <c r="I11" s="329"/>
+      <c r="J11" s="330"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="97">
         <v>25</v>
       </c>
-      <c r="B12" s="324" t="s">
+      <c r="B12" s="339" t="s">
         <v>257</v>
       </c>
-      <c r="C12" s="325"/>
-      <c r="D12" s="325"/>
-      <c r="E12" s="325"/>
-      <c r="F12" s="325"/>
-      <c r="G12" s="325"/>
-      <c r="H12" s="325"/>
-      <c r="I12" s="325"/>
-      <c r="J12" s="326"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
+      <c r="G12" s="340"/>
+      <c r="H12" s="340"/>
+      <c r="I12" s="340"/>
+      <c r="J12" s="341"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="94"/>
-      <c r="B13" s="327" t="s">
+      <c r="B13" s="315" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="327"/>
-      <c r="D13" s="315"/>
-      <c r="E13" s="316"/>
-      <c r="F13" s="316"/>
-      <c r="G13" s="316"/>
-      <c r="H13" s="316"/>
-      <c r="I13" s="316"/>
-      <c r="J13" s="317"/>
+      <c r="C13" s="315"/>
+      <c r="D13" s="328"/>
+      <c r="E13" s="329"/>
+      <c r="F13" s="329"/>
+      <c r="G13" s="329"/>
+      <c r="H13" s="329"/>
+      <c r="I13" s="329"/>
+      <c r="J13" s="330"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="94"/>
-      <c r="B14" s="327" t="s">
+      <c r="B14" s="315" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="327"/>
-      <c r="D14" s="315"/>
-      <c r="E14" s="316"/>
-      <c r="F14" s="316"/>
-      <c r="G14" s="316"/>
-      <c r="H14" s="316"/>
-      <c r="I14" s="316"/>
-      <c r="J14" s="317"/>
+      <c r="C14" s="315"/>
+      <c r="D14" s="328"/>
+      <c r="E14" s="329"/>
+      <c r="F14" s="329"/>
+      <c r="G14" s="329"/>
+      <c r="H14" s="329"/>
+      <c r="I14" s="329"/>
+      <c r="J14" s="330"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1" thickBot="1">
       <c r="A15" s="98"/>
-      <c r="B15" s="327" t="s">
+      <c r="B15" s="315" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="327"/>
-      <c r="D15" s="315"/>
-      <c r="E15" s="316"/>
-      <c r="F15" s="316"/>
-      <c r="G15" s="316"/>
-      <c r="H15" s="316"/>
-      <c r="I15" s="316"/>
-      <c r="J15" s="317"/>
+      <c r="C15" s="315"/>
+      <c r="D15" s="328"/>
+      <c r="E15" s="329"/>
+      <c r="F15" s="329"/>
+      <c r="G15" s="329"/>
+      <c r="H15" s="329"/>
+      <c r="I15" s="329"/>
+      <c r="J15" s="330"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="94KVciG4kdECMCBRaZ/kGUPIuUdTIjG67RnmSldA6WYOzuQmRnZSJRxdUi03GpwtwoEXd0J15wJilUTAVO1QkA==" saltValue="4px6JZ8PPWxSqTy644m1tg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="32">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D14:J14"/>
     <mergeCell ref="D15:J15"/>
@@ -18208,6 +18187,23 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/pds.xlsx
+++ b/public/pds.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cenro\PMS-intern\rsp-hr-tagum-cityhall\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cenro\Deniel\System\rsp-hr-tagum-cityhall\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5636AD-BE95-49F9-A931-C90C64D19572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81820010-C7FF-4838-B143-B260213F869E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="795" yWindow="2490" windowWidth="28800" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Personal Information" sheetId="16" r:id="rId1"/>
@@ -1615,7 +1615,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="345">
   <si>
     <t xml:space="preserve">        </t>
   </si>
@@ -1627,12 +1627,6 @@
   </si>
   <si>
     <t xml:space="preserve">                                    </t>
-  </si>
-  <si>
-    <t>PERSONAL DATA SHEET</t>
-  </si>
-  <si>
-    <t>READ THE ATTACHED GUIDE TO FILLING OUT THE PERSONAL DATA SHEET (PDS) BEFORE ACCOMPLISHING THE PDS FORM.</t>
   </si>
   <si>
     <r>
@@ -2678,9 +2672,6 @@
 Validity(dd/mm.yy)</t>
   </si>
   <si>
-    <t>WARNING: Any misrepresentation made in the Personal Data Sheet and the Work Experience Sheet shall cause the filing of administrative/criminal case/s against the person concern</t>
-  </si>
-  <si>
     <t>Purok</t>
   </si>
   <si>
@@ -2709,6 +2700,9 @@
       <t>(Person not related by consanguinity or affinity to applicant /appointee)</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve"> DATA SHEET</t>
+  </si>
 </sst>
 </file>
 
@@ -2720,7 +2714,7 @@
     <numFmt numFmtId="166" formatCode=";;;"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2891,14 +2885,6 @@
       <sz val="22"/>
       <color indexed="8"/>
       <name val="Arial Black"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="8"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -3743,20 +3729,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="507">
+  <cellXfs count="501">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -3816,63 +3802,360 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3880,318 +4163,21 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4237,7 +4223,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -4254,10 +4240,10 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4273,7 +4259,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -4374,74 +4360,51 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="27" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4449,324 +4412,10 @@
     <xf numFmtId="49" fontId="24" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="33" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4780,6 +4429,10 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4788,6 +4441,374 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4800,6 +4821,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4814,82 +4847,22 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -4902,25 +4875,25 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4930,22 +4903,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5011,22 +4984,22 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5053,27 +5026,89 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5084,45 +5119,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -5131,214 +5127,54 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -5354,95 +5190,227 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10888,20 +10856,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
-      <c r="A1" s="227"/>
-      <c r="B1" s="228"/>
-      <c r="C1" s="228"/>
-      <c r="D1" s="228"/>
-      <c r="E1" s="228"/>
-      <c r="F1" s="228"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="228"/>
-      <c r="I1" s="228"/>
-      <c r="J1" s="228"/>
-      <c r="K1" s="228"/>
-      <c r="L1" s="228"/>
-      <c r="M1" s="228"/>
-      <c r="N1" s="229"/>
+      <c r="A1" s="276"/>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+      <c r="I1" s="277"/>
+      <c r="J1" s="277"/>
+      <c r="K1" s="277"/>
+      <c r="L1" s="277"/>
+      <c r="M1" s="277"/>
+      <c r="N1" s="278"/>
     </row>
     <row r="2" spans="1:22" ht="11.25" customHeight="1">
       <c r="A2" s="40"/>
@@ -10931,73 +10899,69 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="41.25" customHeight="1">
-      <c r="A3" s="230" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="231"/>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
-      <c r="G3" s="231"/>
-      <c r="H3" s="231"/>
-      <c r="I3" s="231"/>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
-      <c r="M3" s="231"/>
-      <c r="N3" s="232"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="273"/>
-      <c r="U3" s="273"/>
-      <c r="V3" s="274"/>
+      <c r="A3" s="279" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3" s="500"/>
+      <c r="C3" s="500"/>
+      <c r="D3" s="500"/>
+      <c r="E3" s="500"/>
+      <c r="F3" s="500"/>
+      <c r="G3" s="500"/>
+      <c r="H3" s="500"/>
+      <c r="I3" s="500"/>
+      <c r="J3" s="500"/>
+      <c r="K3" s="500"/>
+      <c r="L3" s="500"/>
+      <c r="M3" s="500"/>
+      <c r="N3" s="280"/>
+      <c r="R3" s="219"/>
+      <c r="S3" s="220"/>
+      <c r="T3" s="220"/>
+      <c r="U3" s="220"/>
+      <c r="V3" s="221"/>
     </row>
     <row r="4" spans="1:22" ht="21.75" customHeight="1">
-      <c r="A4" s="233" t="s">
-        <v>340</v>
-      </c>
-      <c r="B4" s="234"/>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
-      <c r="M4" s="234"/>
-      <c r="N4" s="235"/>
-      <c r="R4" s="275"/>
-      <c r="S4" s="276"/>
-      <c r="T4" s="276"/>
-      <c r="U4" s="276"/>
-      <c r="V4" s="277"/>
+      <c r="A4" s="279"/>
+      <c r="B4" s="500"/>
+      <c r="C4" s="500"/>
+      <c r="D4" s="500"/>
+      <c r="E4" s="500"/>
+      <c r="F4" s="500"/>
+      <c r="G4" s="500"/>
+      <c r="H4" s="500"/>
+      <c r="I4" s="500"/>
+      <c r="J4" s="500"/>
+      <c r="K4" s="500"/>
+      <c r="L4" s="500"/>
+      <c r="M4" s="500"/>
+      <c r="N4" s="280"/>
+      <c r="R4" s="222"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
     </row>
     <row r="5" spans="1:22" ht="11.25" customHeight="1">
-      <c r="A5" s="236" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="237"/>
-      <c r="C5" s="237"/>
-      <c r="D5" s="237"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="237"/>
-      <c r="G5" s="237"/>
-      <c r="H5" s="237"/>
-      <c r="I5" s="237"/>
-      <c r="J5" s="237"/>
-      <c r="K5" s="237"/>
-      <c r="L5" s="237"/>
-      <c r="M5" s="237"/>
-      <c r="N5" s="238"/>
-      <c r="R5" s="275"/>
-      <c r="S5" s="276"/>
-      <c r="T5" s="276"/>
-      <c r="U5" s="276"/>
-      <c r="V5" s="277"/>
+      <c r="A5" s="279"/>
+      <c r="B5" s="500"/>
+      <c r="C5" s="500"/>
+      <c r="D5" s="500"/>
+      <c r="E5" s="500"/>
+      <c r="F5" s="500"/>
+      <c r="G5" s="500"/>
+      <c r="H5" s="500"/>
+      <c r="I5" s="500"/>
+      <c r="J5" s="500"/>
+      <c r="K5" s="500"/>
+      <c r="L5" s="500"/>
+      <c r="M5" s="500"/>
+      <c r="N5" s="280"/>
+      <c r="R5" s="222"/>
+      <c r="S5" s="223"/>
+      <c r="T5" s="223"/>
+      <c r="U5" s="223"/>
+      <c r="V5" s="224"/>
     </row>
     <row r="6" spans="1:22" ht="36.75" hidden="1" customHeight="1">
       <c r="A6" s="43"/>
@@ -11014,15 +10978,15 @@
       <c r="L6" s="45"/>
       <c r="M6" s="45"/>
       <c r="N6" s="46"/>
-      <c r="R6" s="275"/>
-      <c r="S6" s="276"/>
-      <c r="T6" s="276"/>
-      <c r="U6" s="276"/>
-      <c r="V6" s="277"/>
+      <c r="R6" s="222"/>
+      <c r="S6" s="223"/>
+      <c r="T6" s="223"/>
+      <c r="U6" s="223"/>
+      <c r="V6" s="224"/>
     </row>
     <row r="7" spans="1:22" s="53" customFormat="1" ht="12.75" customHeight="1" thickBot="1">
       <c r="A7" s="47" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="48"/>
       <c r="C7" s="49"/>
@@ -11034,199 +10998,199 @@
       <c r="I7" s="49"/>
       <c r="J7" s="50"/>
       <c r="K7" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7" s="239" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="240"/>
-      <c r="N7" s="241"/>
-      <c r="R7" s="275"/>
-      <c r="S7" s="276"/>
-      <c r="T7" s="276"/>
-      <c r="U7" s="276"/>
-      <c r="V7" s="277"/>
+        <v>5</v>
+      </c>
+      <c r="L7" s="281" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="282"/>
+      <c r="N7" s="283"/>
+      <c r="R7" s="222"/>
+      <c r="S7" s="223"/>
+      <c r="T7" s="223"/>
+      <c r="U7" s="223"/>
+      <c r="V7" s="224"/>
     </row>
     <row r="8" spans="1:22" ht="2.25" customHeight="1" thickBot="1">
       <c r="A8" s="54"/>
       <c r="N8" s="55"/>
-      <c r="R8" s="275"/>
-      <c r="S8" s="276"/>
-      <c r="T8" s="276"/>
-      <c r="U8" s="276"/>
-      <c r="V8" s="277"/>
+      <c r="R8" s="222"/>
+      <c r="S8" s="223"/>
+      <c r="T8" s="223"/>
+      <c r="U8" s="223"/>
+      <c r="V8" s="224"/>
     </row>
     <row r="9" spans="1:22" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A9" s="286" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="287"/>
-      <c r="C9" s="287"/>
-      <c r="D9" s="287"/>
-      <c r="E9" s="287"/>
-      <c r="F9" s="287"/>
-      <c r="G9" s="287"/>
-      <c r="H9" s="287"/>
-      <c r="I9" s="287"/>
-      <c r="J9" s="287"/>
-      <c r="K9" s="287"/>
-      <c r="L9" s="287"/>
-      <c r="M9" s="287"/>
-      <c r="N9" s="288"/>
-      <c r="R9" s="275"/>
-      <c r="S9" s="276"/>
-      <c r="T9" s="276"/>
-      <c r="U9" s="276"/>
-      <c r="V9" s="277"/>
+      <c r="A9" s="233" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="234"/>
+      <c r="C9" s="234"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="234"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="234"/>
+      <c r="L9" s="234"/>
+      <c r="M9" s="234"/>
+      <c r="N9" s="235"/>
+      <c r="R9" s="222"/>
+      <c r="S9" s="223"/>
+      <c r="T9" s="223"/>
+      <c r="U9" s="223"/>
+      <c r="V9" s="224"/>
     </row>
     <row r="10" spans="1:22" ht="22.5" customHeight="1">
       <c r="A10" s="56">
         <v>2</v>
       </c>
-      <c r="B10" s="258" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="246"/>
-      <c r="D10" s="505"/>
-      <c r="E10" s="505"/>
-      <c r="F10" s="505"/>
-      <c r="G10" s="505"/>
-      <c r="H10" s="505"/>
-      <c r="I10" s="505"/>
-      <c r="J10" s="505"/>
-      <c r="K10" s="505"/>
-      <c r="L10" s="505"/>
-      <c r="M10" s="505"/>
-      <c r="N10" s="506"/>
+      <c r="B10" s="236" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="237"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="238"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="238"/>
+      <c r="H10" s="238"/>
+      <c r="I10" s="238"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="238"/>
+      <c r="L10" s="238"/>
+      <c r="M10" s="238"/>
+      <c r="N10" s="239"/>
       <c r="P10" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="R10" s="275"/>
-      <c r="S10" s="276"/>
-      <c r="T10" s="276"/>
-      <c r="U10" s="276"/>
-      <c r="V10" s="277"/>
+        <v>9</v>
+      </c>
+      <c r="R10" s="222"/>
+      <c r="S10" s="223"/>
+      <c r="T10" s="223"/>
+      <c r="U10" s="223"/>
+      <c r="V10" s="224"/>
     </row>
     <row r="11" spans="1:22" ht="22.5" customHeight="1">
       <c r="A11" s="58"/>
-      <c r="B11" s="259" t="s">
+      <c r="B11" s="240" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="243"/>
+      <c r="F11" s="243"/>
+      <c r="G11" s="243"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="245" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="247"/>
+      <c r="M11" s="248"/>
+      <c r="N11" s="249"/>
+      <c r="P11" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="260"/>
-      <c r="D11" s="289"/>
-      <c r="E11" s="290"/>
-      <c r="F11" s="290"/>
-      <c r="G11" s="290"/>
-      <c r="H11" s="291"/>
-      <c r="I11" s="292" t="s">
+      <c r="Q11" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="293"/>
-      <c r="K11" s="293"/>
-      <c r="L11" s="294"/>
-      <c r="M11" s="295"/>
-      <c r="N11" s="296"/>
-      <c r="P11" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q11" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="R11" s="275"/>
-      <c r="S11" s="276"/>
-      <c r="T11" s="276"/>
-      <c r="U11" s="276"/>
-      <c r="V11" s="277"/>
+      <c r="R11" s="222"/>
+      <c r="S11" s="223"/>
+      <c r="T11" s="223"/>
+      <c r="U11" s="223"/>
+      <c r="V11" s="224"/>
     </row>
     <row r="12" spans="1:22" ht="21.75" customHeight="1" thickBot="1">
       <c r="A12" s="62"/>
-      <c r="B12" s="281" t="s">
+      <c r="B12" s="228" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="229"/>
+      <c r="D12" s="230"/>
+      <c r="E12" s="231"/>
+      <c r="F12" s="231"/>
+      <c r="G12" s="231" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="231"/>
+      <c r="I12" s="231" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="231"/>
+      <c r="K12" s="231"/>
+      <c r="L12" s="231"/>
+      <c r="M12" s="231"/>
+      <c r="N12" s="232"/>
+      <c r="P12" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="282"/>
-      <c r="D12" s="283"/>
-      <c r="E12" s="284"/>
-      <c r="F12" s="284"/>
-      <c r="G12" s="284" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="284"/>
-      <c r="I12" s="284" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="284"/>
-      <c r="K12" s="284"/>
-      <c r="L12" s="284"/>
-      <c r="M12" s="284"/>
-      <c r="N12" s="285"/>
-      <c r="P12" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R12" s="275"/>
-      <c r="S12" s="276"/>
-      <c r="T12" s="276"/>
-      <c r="U12" s="276"/>
-      <c r="V12" s="277"/>
+      <c r="R12" s="222"/>
+      <c r="S12" s="223"/>
+      <c r="T12" s="223"/>
+      <c r="U12" s="223"/>
+      <c r="V12" s="224"/>
     </row>
     <row r="13" spans="1:22" ht="24" customHeight="1">
       <c r="A13" s="63">
         <v>3</v>
       </c>
-      <c r="B13" s="245" t="s">
-        <v>332</v>
-      </c>
-      <c r="C13" s="246"/>
-      <c r="D13" s="254"/>
-      <c r="E13" s="255"/>
-      <c r="F13" s="255"/>
-      <c r="G13" s="258" t="s">
+      <c r="B13" s="253" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="237"/>
+      <c r="D13" s="261"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="236" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="236"/>
+      <c r="I13" s="237"/>
+      <c r="J13" s="265" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="266"/>
+      <c r="L13" s="266" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="266"/>
+      <c r="N13" s="267"/>
+      <c r="P13" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="258"/>
-      <c r="I13" s="246"/>
-      <c r="J13" s="261" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="262"/>
-      <c r="L13" s="262" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13" s="262"/>
-      <c r="N13" s="263"/>
-      <c r="P13" s="60" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" s="278"/>
-      <c r="S13" s="279"/>
-      <c r="T13" s="279"/>
-      <c r="U13" s="279"/>
-      <c r="V13" s="280"/>
+      <c r="R13" s="225"/>
+      <c r="S13" s="226"/>
+      <c r="T13" s="226"/>
+      <c r="U13" s="226"/>
+      <c r="V13" s="227"/>
     </row>
     <row r="14" spans="1:22" ht="21.6" customHeight="1">
       <c r="A14" s="58"/>
       <c r="B14" s="64"/>
       <c r="C14" s="64"/>
-      <c r="D14" s="256"/>
-      <c r="E14" s="257"/>
-      <c r="F14" s="257"/>
-      <c r="G14" s="259"/>
-      <c r="H14" s="259"/>
-      <c r="I14" s="260"/>
-      <c r="J14" s="264" t="b">
+      <c r="D14" s="263"/>
+      <c r="E14" s="264"/>
+      <c r="F14" s="264"/>
+      <c r="G14" s="240"/>
+      <c r="H14" s="240"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="268" t="b">
         <v>0</v>
       </c>
-      <c r="K14" s="265"/>
-      <c r="L14" s="265" t="b">
+      <c r="K14" s="269"/>
+      <c r="L14" s="269" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="265"/>
-      <c r="N14" s="266"/>
+      <c r="M14" s="269"/>
+      <c r="N14" s="270"/>
       <c r="P14" s="60"/>
       <c r="Q14" s="2"/>
       <c r="S14"/>
@@ -11238,29 +11202,29 @@
         <v>4</v>
       </c>
       <c r="B15" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="66"/>
+      <c r="D15" s="254"/>
+      <c r="E15" s="254"/>
+      <c r="F15" s="255"/>
+      <c r="G15" s="256" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="257"/>
+      <c r="I15" s="257"/>
+      <c r="J15" s="258" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="66"/>
-      <c r="D15" s="247"/>
-      <c r="E15" s="247"/>
-      <c r="F15" s="248"/>
-      <c r="G15" s="249" t="s">
+      <c r="K15" s="259"/>
+      <c r="L15" s="259"/>
+      <c r="M15" s="259"/>
+      <c r="N15" s="260"/>
+      <c r="P15" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="250"/>
-      <c r="I15" s="250"/>
-      <c r="J15" s="251" t="s">
+      <c r="Q15" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="K15" s="252"/>
-      <c r="L15" s="252"/>
-      <c r="M15" s="252"/>
-      <c r="N15" s="253"/>
-      <c r="P15" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="S15"/>
       <c r="T15"/>
@@ -11271,351 +11235,351 @@
         <v>5</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C16" s="68"/>
       <c r="D16" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="267" t="b">
+      <c r="E16" s="271" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="268"/>
-      <c r="G16" s="269" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="270"/>
-      <c r="I16" s="271"/>
-      <c r="J16" s="242">
+      <c r="F16" s="272"/>
+      <c r="G16" s="273" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="274"/>
+      <c r="I16" s="275"/>
+      <c r="J16" s="250">
         <v>1</v>
       </c>
-      <c r="K16" s="243"/>
-      <c r="L16" s="243"/>
-      <c r="M16" s="243"/>
-      <c r="N16" s="244"/>
+      <c r="K16" s="251"/>
+      <c r="L16" s="251"/>
+      <c r="M16" s="251"/>
+      <c r="N16" s="252"/>
       <c r="O16" s="69"/>
       <c r="P16" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="27" customHeight="1">
+      <c r="A17" s="301">
+        <v>6</v>
+      </c>
+      <c r="B17" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" ht="27" customHeight="1">
-      <c r="A17" s="198">
-        <v>6</v>
-      </c>
-      <c r="B17" s="308" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="309"/>
+      <c r="C17" s="213"/>
       <c r="D17" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="312" t="b">
+      <c r="E17" s="217" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="313"/>
+      <c r="F17" s="218"/>
       <c r="G17" s="70" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H17" s="71"/>
-      <c r="I17" s="197"/>
-      <c r="J17" s="197"/>
-      <c r="K17" s="197"/>
-      <c r="L17" s="197"/>
-      <c r="M17" s="214"/>
-      <c r="N17" s="214"/>
+      <c r="I17" s="206"/>
+      <c r="J17" s="206"/>
+      <c r="K17" s="206"/>
+      <c r="L17" s="206"/>
+      <c r="M17" s="207"/>
+      <c r="N17" s="207"/>
       <c r="Q17" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="R17" s="72"/>
     </row>
     <row r="18" spans="1:23" ht="27" customHeight="1">
-      <c r="A18" s="199"/>
-      <c r="B18" s="310"/>
-      <c r="C18" s="311"/>
+      <c r="A18" s="302"/>
+      <c r="B18" s="214"/>
+      <c r="C18" s="215"/>
       <c r="D18" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="223" t="b">
+      <c r="E18" s="204" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="224"/>
+      <c r="F18" s="205"/>
       <c r="G18" s="74"/>
       <c r="H18" s="75"/>
-      <c r="I18" s="218" t="s">
+      <c r="I18" s="284" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="284"/>
+      <c r="K18" s="284" t="s">
+        <v>338</v>
+      </c>
+      <c r="L18" s="284"/>
+      <c r="M18" s="284" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" s="284"/>
+      <c r="Q18" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="J18" s="218"/>
-      <c r="K18" s="218" t="s">
-        <v>341</v>
-      </c>
-      <c r="L18" s="218"/>
-      <c r="M18" s="218" t="s">
-        <v>35</v>
-      </c>
-      <c r="N18" s="218"/>
-      <c r="Q18" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="24" customHeight="1">
       <c r="A19" s="56"/>
       <c r="B19" s="76"/>
       <c r="C19" s="73"/>
-      <c r="D19" s="222" t="b">
+      <c r="D19" s="296" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="223"/>
-      <c r="F19" s="224"/>
+      <c r="E19" s="204"/>
+      <c r="F19" s="205"/>
       <c r="G19" s="74"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="197"/>
-      <c r="J19" s="214"/>
-      <c r="K19" s="214"/>
-      <c r="L19" s="197"/>
-      <c r="M19" s="214"/>
-      <c r="N19" s="214"/>
+      <c r="I19" s="206"/>
+      <c r="J19" s="207"/>
+      <c r="K19" s="207"/>
+      <c r="L19" s="206"/>
+      <c r="M19" s="207"/>
+      <c r="N19" s="207"/>
       <c r="Q19" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="26.25" customHeight="1">
       <c r="A20" s="77"/>
       <c r="B20" s="78"/>
       <c r="C20" s="79"/>
-      <c r="D20" s="219"/>
-      <c r="E20" s="220"/>
-      <c r="F20" s="221"/>
+      <c r="D20" s="293"/>
+      <c r="E20" s="294"/>
+      <c r="F20" s="295"/>
       <c r="G20" s="58"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="215" t="s">
+      <c r="I20" s="208" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="210"/>
+      <c r="K20" s="210"/>
+      <c r="L20" s="209" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="211"/>
+      <c r="N20" s="211"/>
+      <c r="Q20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J20" s="216"/>
-      <c r="K20" s="216"/>
-      <c r="L20" s="217" t="s">
+    </row>
+    <row r="21" spans="1:23" ht="30.75" customHeight="1">
+      <c r="A21" s="302">
+        <v>7</v>
+      </c>
+      <c r="B21" s="304" t="s">
         <v>39</v>
       </c>
-      <c r="M20" s="307"/>
-      <c r="N20" s="307"/>
-      <c r="Q20" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A21" s="199">
-        <v>7</v>
-      </c>
-      <c r="B21" s="201" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="202"/>
-      <c r="D21" s="208"/>
-      <c r="E21" s="208"/>
-      <c r="F21" s="208"/>
+      <c r="C21" s="305"/>
+      <c r="D21" s="308"/>
+      <c r="E21" s="308"/>
+      <c r="F21" s="308"/>
       <c r="G21" s="58"/>
       <c r="H21" s="59"/>
-      <c r="I21" s="197"/>
-      <c r="J21" s="214"/>
-      <c r="K21" s="214"/>
-      <c r="L21" s="197"/>
-      <c r="M21" s="214"/>
-      <c r="N21" s="214"/>
+      <c r="I21" s="206"/>
+      <c r="J21" s="207"/>
+      <c r="K21" s="207"/>
+      <c r="L21" s="206"/>
+      <c r="M21" s="207"/>
+      <c r="N21" s="207"/>
       <c r="Q21" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="26.25" customHeight="1">
-      <c r="A22" s="200"/>
-      <c r="B22" s="203"/>
-      <c r="C22" s="204"/>
-      <c r="D22" s="207"/>
-      <c r="E22" s="207"/>
-      <c r="F22" s="207"/>
+      <c r="A22" s="303"/>
+      <c r="B22" s="306"/>
+      <c r="C22" s="307"/>
+      <c r="D22" s="292"/>
+      <c r="E22" s="292"/>
+      <c r="F22" s="292"/>
       <c r="G22" s="58"/>
       <c r="H22" s="59"/>
-      <c r="I22" s="215" t="s">
+      <c r="I22" s="208" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" s="208"/>
+      <c r="K22" s="208"/>
+      <c r="L22" s="209" t="s">
+        <v>42</v>
+      </c>
+      <c r="M22" s="209"/>
+      <c r="N22" s="209"/>
+      <c r="Q22" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="J22" s="215"/>
-      <c r="K22" s="215"/>
-      <c r="L22" s="217" t="s">
-        <v>44</v>
-      </c>
-      <c r="M22" s="217"/>
-      <c r="N22" s="217"/>
-      <c r="Q22" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="37.5" customHeight="1">
       <c r="A23" s="56">
         <v>8</v>
       </c>
-      <c r="B23" s="209" t="s">
+      <c r="B23" s="297" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="286"/>
+      <c r="D23" s="216"/>
+      <c r="E23" s="216"/>
+      <c r="F23" s="216"/>
+      <c r="G23" s="290" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="291"/>
+      <c r="I23" s="207"/>
+      <c r="J23" s="207"/>
+      <c r="K23" s="207"/>
+      <c r="L23" s="207"/>
+      <c r="M23" s="207"/>
+      <c r="N23" s="207"/>
+      <c r="Q23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="210"/>
-      <c r="D23" s="211"/>
-      <c r="E23" s="211"/>
-      <c r="F23" s="211"/>
-      <c r="G23" s="212" t="s">
+    </row>
+    <row r="24" spans="1:23" ht="30.75" customHeight="1">
+      <c r="A24" s="301">
+        <v>9</v>
+      </c>
+      <c r="B24" s="304" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="213"/>
-      <c r="I23" s="214"/>
-      <c r="J23" s="214"/>
-      <c r="K23" s="214"/>
-      <c r="L23" s="214"/>
-      <c r="M23" s="214"/>
-      <c r="N23" s="214"/>
-      <c r="Q23" s="2" t="s">
+      <c r="C24" s="305"/>
+      <c r="D24" s="289"/>
+      <c r="E24" s="289"/>
+      <c r="F24" s="289"/>
+      <c r="G24" s="82" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" ht="30.75" customHeight="1">
-      <c r="A24" s="198">
-        <v>9</v>
-      </c>
-      <c r="B24" s="201" t="s">
+      <c r="H24" s="80"/>
+      <c r="I24" s="206"/>
+      <c r="J24" s="206"/>
+      <c r="K24" s="206"/>
+      <c r="L24" s="206"/>
+      <c r="M24" s="207"/>
+      <c r="N24" s="207"/>
+      <c r="Q24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="202"/>
-      <c r="D24" s="206"/>
-      <c r="E24" s="206"/>
-      <c r="F24" s="206"/>
-      <c r="G24" s="82" t="s">
-        <v>50</v>
-      </c>
-      <c r="H24" s="80"/>
-      <c r="I24" s="197"/>
-      <c r="J24" s="197"/>
-      <c r="K24" s="197"/>
-      <c r="L24" s="197"/>
-      <c r="M24" s="214"/>
-      <c r="N24" s="214"/>
-      <c r="Q24" s="2" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="25" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A25" s="200"/>
-      <c r="B25" s="203"/>
-      <c r="C25" s="204"/>
-      <c r="D25" s="207"/>
-      <c r="E25" s="207"/>
-      <c r="F25" s="207"/>
+      <c r="A25" s="303"/>
+      <c r="B25" s="306"/>
+      <c r="C25" s="307"/>
+      <c r="D25" s="292"/>
+      <c r="E25" s="292"/>
+      <c r="F25" s="292"/>
       <c r="G25" s="58"/>
       <c r="H25" s="59"/>
-      <c r="I25" s="218" t="s">
-        <v>34</v>
-      </c>
-      <c r="J25" s="218"/>
-      <c r="K25" s="218" t="s">
-        <v>341</v>
-      </c>
-      <c r="L25" s="218"/>
-      <c r="M25" s="218" t="s">
-        <v>35</v>
-      </c>
-      <c r="N25" s="218"/>
+      <c r="I25" s="284" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" s="284"/>
+      <c r="K25" s="284" t="s">
+        <v>338</v>
+      </c>
+      <c r="L25" s="284"/>
+      <c r="M25" s="284" t="s">
+        <v>33</v>
+      </c>
+      <c r="N25" s="284"/>
       <c r="Q25" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="29.25" customHeight="1">
-      <c r="A26" s="198">
+      <c r="A26" s="301">
         <v>10</v>
       </c>
-      <c r="B26" s="201" t="s">
-        <v>338</v>
-      </c>
-      <c r="C26" s="202"/>
-      <c r="D26" s="206"/>
-      <c r="E26" s="206"/>
-      <c r="F26" s="206"/>
+      <c r="B26" s="304" t="s">
+        <v>336</v>
+      </c>
+      <c r="C26" s="305"/>
+      <c r="D26" s="289"/>
+      <c r="E26" s="289"/>
+      <c r="F26" s="289"/>
       <c r="G26" s="74"/>
       <c r="H26" s="75"/>
-      <c r="I26" s="197"/>
-      <c r="J26" s="214"/>
-      <c r="K26" s="214"/>
-      <c r="L26" s="197"/>
-      <c r="M26" s="214"/>
-      <c r="N26" s="214"/>
+      <c r="I26" s="206"/>
+      <c r="J26" s="207"/>
+      <c r="K26" s="207"/>
+      <c r="L26" s="206"/>
+      <c r="M26" s="207"/>
+      <c r="N26" s="207"/>
       <c r="Q26" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="35.25" customHeight="1">
-      <c r="A27" s="200"/>
-      <c r="B27" s="203"/>
-      <c r="C27" s="204"/>
-      <c r="D27" s="207"/>
-      <c r="E27" s="207"/>
-      <c r="F27" s="207"/>
+      <c r="A27" s="303"/>
+      <c r="B27" s="306"/>
+      <c r="C27" s="307"/>
+      <c r="D27" s="292"/>
+      <c r="E27" s="292"/>
+      <c r="F27" s="292"/>
       <c r="G27" s="74"/>
       <c r="H27" s="75"/>
-      <c r="I27" s="215" t="s">
-        <v>38</v>
-      </c>
-      <c r="J27" s="216"/>
-      <c r="K27" s="216"/>
-      <c r="L27" s="217" t="s">
-        <v>39</v>
-      </c>
-      <c r="M27" s="216"/>
-      <c r="N27" s="216"/>
+      <c r="I27" s="208" t="s">
+        <v>36</v>
+      </c>
+      <c r="J27" s="210"/>
+      <c r="K27" s="210"/>
+      <c r="L27" s="209" t="s">
+        <v>37</v>
+      </c>
+      <c r="M27" s="210"/>
+      <c r="N27" s="210"/>
       <c r="Q27" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S27" s="83"/>
     </row>
     <row r="28" spans="1:23" ht="33" customHeight="1">
-      <c r="A28" s="198">
+      <c r="A28" s="301">
         <v>11</v>
       </c>
-      <c r="B28" s="201" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="202"/>
-      <c r="D28" s="205"/>
-      <c r="E28" s="206"/>
-      <c r="F28" s="206"/>
+      <c r="B28" s="304" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="305"/>
+      <c r="D28" s="288"/>
+      <c r="E28" s="289"/>
+      <c r="F28" s="289"/>
       <c r="G28" s="74"/>
       <c r="H28" s="84"/>
-      <c r="I28" s="197"/>
-      <c r="J28" s="214"/>
-      <c r="K28" s="214"/>
-      <c r="L28" s="197"/>
-      <c r="M28" s="214"/>
-      <c r="N28" s="214"/>
+      <c r="I28" s="206"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="207"/>
+      <c r="L28" s="206"/>
+      <c r="M28" s="207"/>
+      <c r="N28" s="207"/>
       <c r="Q28" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="32.25" customHeight="1">
-      <c r="A29" s="200"/>
-      <c r="B29" s="203"/>
-      <c r="C29" s="204"/>
-      <c r="D29" s="207"/>
-      <c r="E29" s="207"/>
-      <c r="F29" s="207"/>
+      <c r="A29" s="303"/>
+      <c r="B29" s="306"/>
+      <c r="C29" s="307"/>
+      <c r="D29" s="292"/>
+      <c r="E29" s="292"/>
+      <c r="F29" s="292"/>
       <c r="G29" s="74"/>
       <c r="H29" s="84"/>
-      <c r="I29" s="215" t="s">
-        <v>43</v>
-      </c>
-      <c r="J29" s="215"/>
-      <c r="K29" s="215"/>
-      <c r="L29" s="215" t="s">
-        <v>44</v>
-      </c>
-      <c r="M29" s="215"/>
-      <c r="N29" s="215"/>
+      <c r="I29" s="208" t="s">
+        <v>41</v>
+      </c>
+      <c r="J29" s="208"/>
+      <c r="K29" s="208"/>
+      <c r="L29" s="208" t="s">
+        <v>42</v>
+      </c>
+      <c r="M29" s="208"/>
+      <c r="N29" s="208"/>
       <c r="Q29" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="U29" s="91"/>
     </row>
@@ -11624,24 +11588,24 @@
         <v>12</v>
       </c>
       <c r="B30" s="66" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C30" s="68"/>
-      <c r="D30" s="205"/>
-      <c r="E30" s="206"/>
-      <c r="F30" s="206"/>
-      <c r="G30" s="212" t="s">
-        <v>47</v>
-      </c>
-      <c r="H30" s="213"/>
-      <c r="I30" s="214"/>
-      <c r="J30" s="214"/>
-      <c r="K30" s="214"/>
-      <c r="L30" s="214"/>
-      <c r="M30" s="214"/>
-      <c r="N30" s="214"/>
+      <c r="D30" s="288"/>
+      <c r="E30" s="289"/>
+      <c r="F30" s="289"/>
+      <c r="G30" s="290" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="291"/>
+      <c r="I30" s="207"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="207"/>
+      <c r="L30" s="207"/>
+      <c r="M30" s="207"/>
+      <c r="N30" s="207"/>
       <c r="Q30" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T30" s="91"/>
       <c r="U30" s="91"/>
@@ -11653,245 +11617,245 @@
         <v>13</v>
       </c>
       <c r="B31" s="66" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C31" s="68"/>
-      <c r="D31" s="211"/>
-      <c r="E31" s="211"/>
-      <c r="F31" s="211"/>
+      <c r="D31" s="216"/>
+      <c r="E31" s="216"/>
+      <c r="F31" s="216"/>
       <c r="G31" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" s="81"/>
+      <c r="I31" s="206"/>
+      <c r="J31" s="206"/>
+      <c r="K31" s="206"/>
+      <c r="L31" s="206"/>
+      <c r="M31" s="206"/>
+      <c r="N31" s="206"/>
+      <c r="Q31" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="39.75" customHeight="1">
+      <c r="A32" s="285" t="s">
         <v>60</v>
       </c>
-      <c r="H31" s="81"/>
-      <c r="I31" s="197"/>
-      <c r="J31" s="197"/>
-      <c r="K31" s="197"/>
-      <c r="L31" s="197"/>
-      <c r="M31" s="197"/>
-      <c r="N31" s="197"/>
-      <c r="Q31" s="2" t="s">
+      <c r="B32" s="286"/>
+      <c r="C32" s="287"/>
+      <c r="D32" s="216"/>
+      <c r="E32" s="216"/>
+      <c r="F32" s="216"/>
+      <c r="G32" s="86" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" ht="39.75" customHeight="1">
-      <c r="A32" s="225" t="s">
+      <c r="H32" s="87"/>
+      <c r="I32" s="206"/>
+      <c r="J32" s="206"/>
+      <c r="K32" s="206"/>
+      <c r="L32" s="206"/>
+      <c r="M32" s="206"/>
+      <c r="N32" s="206"/>
+      <c r="Q32" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="B32" s="210"/>
-      <c r="C32" s="226"/>
-      <c r="D32" s="211"/>
-      <c r="E32" s="211"/>
-      <c r="F32" s="211"/>
-      <c r="G32" s="86" t="s">
-        <v>63</v>
-      </c>
-      <c r="H32" s="87"/>
-      <c r="I32" s="197"/>
-      <c r="J32" s="197"/>
-      <c r="K32" s="197"/>
-      <c r="L32" s="197"/>
-      <c r="M32" s="197"/>
-      <c r="N32" s="197"/>
-      <c r="Q32" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="43.5" customHeight="1" thickBot="1">
       <c r="A33" s="65">
         <v>15</v>
       </c>
-      <c r="B33" s="305" t="s">
-        <v>336</v>
-      </c>
-      <c r="C33" s="306"/>
-      <c r="D33" s="302"/>
-      <c r="E33" s="303"/>
-      <c r="F33" s="304"/>
+      <c r="B33" s="202" t="s">
+        <v>334</v>
+      </c>
+      <c r="C33" s="203"/>
+      <c r="D33" s="199"/>
+      <c r="E33" s="200"/>
+      <c r="F33" s="201"/>
       <c r="G33" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="H33" s="81"/>
+      <c r="I33" s="300"/>
+      <c r="J33" s="206"/>
+      <c r="K33" s="206"/>
+      <c r="L33" s="206"/>
+      <c r="M33" s="206"/>
+      <c r="N33" s="206"/>
+      <c r="Q33" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A34" s="196" t="s">
+        <v>339</v>
+      </c>
+      <c r="B34" s="197"/>
+      <c r="C34" s="197"/>
+      <c r="D34" s="197"/>
+      <c r="E34" s="197"/>
+      <c r="F34" s="197"/>
+      <c r="G34" s="197"/>
+      <c r="H34" s="197"/>
+      <c r="I34" s="197"/>
+      <c r="J34" s="197"/>
+      <c r="K34" s="197"/>
+      <c r="L34" s="197"/>
+      <c r="M34" s="197"/>
+      <c r="N34" s="198"/>
+      <c r="Q34" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H33" s="81"/>
-      <c r="I33" s="196"/>
-      <c r="J33" s="197"/>
-      <c r="K33" s="197"/>
-      <c r="L33" s="197"/>
-      <c r="M33" s="197"/>
-      <c r="N33" s="197"/>
-      <c r="Q33" s="2" t="s">
+    </row>
+    <row r="35" spans="1:17" ht="21" customHeight="1">
+      <c r="A35" s="298" t="s">
+        <v>340</v>
+      </c>
+      <c r="B35" s="298"/>
+      <c r="C35" s="298"/>
+      <c r="D35" s="299" t="s">
+        <v>342</v>
+      </c>
+      <c r="E35" s="299"/>
+      <c r="F35" s="299"/>
+      <c r="G35" s="194" t="s">
+        <v>341</v>
+      </c>
+      <c r="H35" s="195"/>
+      <c r="I35" s="299"/>
+      <c r="J35" s="299"/>
+      <c r="K35" s="299"/>
+      <c r="L35" s="299"/>
+      <c r="M35" s="299"/>
+      <c r="N35" s="299"/>
+      <c r="Q35" s="2" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A34" s="299" t="s">
-        <v>342</v>
-      </c>
-      <c r="B34" s="300"/>
-      <c r="C34" s="300"/>
-      <c r="D34" s="300"/>
-      <c r="E34" s="300"/>
-      <c r="F34" s="300"/>
-      <c r="G34" s="300"/>
-      <c r="H34" s="300"/>
-      <c r="I34" s="300"/>
-      <c r="J34" s="300"/>
-      <c r="K34" s="300"/>
-      <c r="L34" s="300"/>
-      <c r="M34" s="300"/>
-      <c r="N34" s="301"/>
-      <c r="Q34" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="21" customHeight="1">
-      <c r="A35" s="194" t="s">
-        <v>343</v>
-      </c>
-      <c r="B35" s="194"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="195" t="s">
-        <v>345</v>
-      </c>
-      <c r="E35" s="195"/>
-      <c r="F35" s="195"/>
-      <c r="G35" s="297" t="s">
-        <v>344</v>
-      </c>
-      <c r="H35" s="298"/>
-      <c r="I35" s="195"/>
-      <c r="J35" s="195"/>
-      <c r="K35" s="195"/>
-      <c r="L35" s="195"/>
-      <c r="M35" s="195"/>
-      <c r="N35" s="195"/>
-      <c r="Q35" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="21" customHeight="1">
       <c r="Q36" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="21" customHeight="1">
       <c r="Q37" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="21" customHeight="1">
       <c r="Q38" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="21" customHeight="1">
       <c r="Q39" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="21" customHeight="1">
       <c r="Q40" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="21" customHeight="1">
       <c r="Q41" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="21" customHeight="1">
       <c r="Q42" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="21" customHeight="1">
       <c r="Q43" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="21" customHeight="1">
       <c r="Q44" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="21" customHeight="1">
       <c r="Q45" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="21" customHeight="1">
       <c r="Q46" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="21" customHeight="1">
       <c r="Q47" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="21" customHeight="1">
       <c r="Q48" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="Q49" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="14.25" customHeight="1">
       <c r="Q50" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="13.5" customHeight="1">
       <c r="Q51" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="14.25" customHeight="1">
       <c r="O52" s="89"/>
       <c r="P52" s="89"/>
       <c r="Q52" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="21.95" customHeight="1">
       <c r="Q53" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="21.95" customHeight="1">
       <c r="Q54" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="21.95" customHeight="1">
       <c r="Q55" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="21.95" customHeight="1">
       <c r="Q56" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="21.95" customHeight="1">
       <c r="Q57" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="12" customHeight="1">
       <c r="Q58" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="24" customHeight="1">
       <c r="Q59" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="61" customFormat="1" ht="12" customHeight="1">
       <c r="Q60" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -11910,7 +11874,7 @@
       <c r="M61" s="90"/>
       <c r="N61" s="90"/>
       <c r="Q61" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -11929,7 +11893,7 @@
       <c r="M62" s="90"/>
       <c r="N62" s="90"/>
       <c r="Q62" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="28.5">
@@ -11948,7 +11912,7 @@
       <c r="M63" s="90"/>
       <c r="N63" s="90"/>
       <c r="Q63" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -11967,7 +11931,7 @@
       <c r="M64" s="90"/>
       <c r="N64" s="90"/>
       <c r="Q64" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -11986,7 +11950,7 @@
       <c r="M65" s="90"/>
       <c r="N65" s="90"/>
       <c r="Q65" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:17">
@@ -12005,7 +11969,7 @@
       <c r="M66" s="90"/>
       <c r="N66" s="90"/>
       <c r="Q66" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -12024,7 +11988,7 @@
       <c r="M67" s="90"/>
       <c r="N67" s="90"/>
       <c r="Q67" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="28.5">
@@ -12043,7 +12007,7 @@
       <c r="M68" s="90"/>
       <c r="N68" s="90"/>
       <c r="Q68" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:17">
@@ -12062,7 +12026,7 @@
       <c r="M69" s="90"/>
       <c r="N69" s="90"/>
       <c r="Q69" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:17">
@@ -12081,7 +12045,7 @@
       <c r="M70" s="90"/>
       <c r="N70" s="90"/>
       <c r="Q70" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:17">
@@ -12100,7 +12064,7 @@
       <c r="M71" s="90"/>
       <c r="N71" s="90"/>
       <c r="Q71" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:17">
@@ -12119,7 +12083,7 @@
       <c r="M72" s="90"/>
       <c r="N72" s="90"/>
       <c r="Q72" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:17">
@@ -12138,7 +12102,7 @@
       <c r="M73" s="90"/>
       <c r="N73" s="90"/>
       <c r="Q73" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:17">
@@ -12157,7 +12121,7 @@
       <c r="M74" s="90"/>
       <c r="N74" s="90"/>
       <c r="Q74" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:17">
@@ -12176,7 +12140,7 @@
       <c r="M75" s="90"/>
       <c r="N75" s="90"/>
       <c r="Q75" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:17">
@@ -12195,7 +12159,7 @@
       <c r="M76" s="90"/>
       <c r="N76" s="90"/>
       <c r="Q76" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:17">
@@ -12214,7 +12178,7 @@
       <c r="M77" s="90"/>
       <c r="N77" s="90"/>
       <c r="Q77" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:17">
@@ -12233,7 +12197,7 @@
       <c r="M78" s="90"/>
       <c r="N78" s="90"/>
       <c r="Q78" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:17">
@@ -12252,7 +12216,7 @@
       <c r="M79" s="90"/>
       <c r="N79" s="90"/>
       <c r="Q79" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:17">
@@ -12271,7 +12235,7 @@
       <c r="M80" s="90"/>
       <c r="N80" s="90"/>
       <c r="Q80" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:17">
@@ -12290,7 +12254,7 @@
       <c r="M81" s="90"/>
       <c r="N81" s="90"/>
       <c r="Q81" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="1:17">
@@ -12309,7 +12273,7 @@
       <c r="M82" s="90"/>
       <c r="N82" s="90"/>
       <c r="Q82" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:17">
@@ -12328,7 +12292,7 @@
       <c r="M83" s="90"/>
       <c r="N83" s="90"/>
       <c r="Q83" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:17" ht="28.5">
@@ -12347,7 +12311,7 @@
       <c r="M84" s="90"/>
       <c r="N84" s="90"/>
       <c r="Q84" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85" spans="1:17">
@@ -12366,7 +12330,7 @@
       <c r="M85" s="90"/>
       <c r="N85" s="90"/>
       <c r="Q85" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:17">
@@ -12385,7 +12349,7 @@
       <c r="M86" s="90"/>
       <c r="N86" s="90"/>
       <c r="Q86" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87" spans="1:17">
@@ -12404,7 +12368,7 @@
       <c r="M87" s="90"/>
       <c r="N87" s="90"/>
       <c r="Q87" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:17">
@@ -12423,7 +12387,7 @@
       <c r="M88" s="90"/>
       <c r="N88" s="90"/>
       <c r="Q88" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:17">
@@ -12442,7 +12406,7 @@
       <c r="M89" s="90"/>
       <c r="N89" s="90"/>
       <c r="Q89" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90" spans="1:17">
@@ -12461,7 +12425,7 @@
       <c r="M90" s="90"/>
       <c r="N90" s="90"/>
       <c r="Q90" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:17">
@@ -12480,7 +12444,7 @@
       <c r="M91" s="90"/>
       <c r="N91" s="90"/>
       <c r="Q91" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92" spans="1:17">
@@ -12499,7 +12463,7 @@
       <c r="M92" s="90"/>
       <c r="N92" s="90"/>
       <c r="Q92" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:17">
@@ -12518,7 +12482,7 @@
       <c r="M93" s="90"/>
       <c r="N93" s="90"/>
       <c r="Q93" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="1:17">
@@ -12537,7 +12501,7 @@
       <c r="M94" s="90"/>
       <c r="N94" s="90"/>
       <c r="Q94" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="1:17">
@@ -12556,7 +12520,7 @@
       <c r="M95" s="90"/>
       <c r="N95" s="90"/>
       <c r="Q95" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="96" spans="1:17">
@@ -12575,7 +12539,7 @@
       <c r="M96" s="90"/>
       <c r="N96" s="90"/>
       <c r="Q96" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="97" spans="1:17">
@@ -12594,7 +12558,7 @@
       <c r="M97" s="90"/>
       <c r="N97" s="90"/>
       <c r="Q97" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:17">
@@ -12613,7 +12577,7 @@
       <c r="M98" s="90"/>
       <c r="N98" s="90"/>
       <c r="Q98" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="99" spans="1:17">
@@ -12632,7 +12596,7 @@
       <c r="M99" s="90"/>
       <c r="N99" s="90"/>
       <c r="Q99" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="1:17">
@@ -12651,7 +12615,7 @@
       <c r="M100" s="90"/>
       <c r="N100" s="90"/>
       <c r="Q100" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101" spans="1:17">
@@ -12670,7 +12634,7 @@
       <c r="M101" s="90"/>
       <c r="N101" s="90"/>
       <c r="Q101" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102" spans="1:17">
@@ -12689,7 +12653,7 @@
       <c r="M102" s="90"/>
       <c r="N102" s="90"/>
       <c r="Q102" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="1:17">
@@ -12708,7 +12672,7 @@
       <c r="M103" s="90"/>
       <c r="N103" s="90"/>
       <c r="Q103" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="104" spans="1:17">
@@ -12727,7 +12691,7 @@
       <c r="M104" s="90"/>
       <c r="N104" s="90"/>
       <c r="Q104" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="105" spans="1:17">
@@ -12746,7 +12710,7 @@
       <c r="M105" s="90"/>
       <c r="N105" s="90"/>
       <c r="Q105" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="1:17">
@@ -12765,7 +12729,7 @@
       <c r="M106" s="90"/>
       <c r="N106" s="90"/>
       <c r="Q106" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="1:17">
@@ -12784,7 +12748,7 @@
       <c r="M107" s="90"/>
       <c r="N107" s="90"/>
       <c r="Q107" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="108" spans="1:17">
@@ -12803,7 +12767,7 @@
       <c r="M108" s="90"/>
       <c r="N108" s="90"/>
       <c r="Q108" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="1:17">
@@ -12822,7 +12786,7 @@
       <c r="M109" s="90"/>
       <c r="N109" s="90"/>
       <c r="Q109" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110" spans="1:17">
@@ -12841,7 +12805,7 @@
       <c r="M110" s="90"/>
       <c r="N110" s="90"/>
       <c r="Q110" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="111" spans="1:17">
@@ -12860,7 +12824,7 @@
       <c r="M111" s="90"/>
       <c r="N111" s="90"/>
       <c r="Q111" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="112" spans="1:17">
@@ -12879,7 +12843,7 @@
       <c r="M112" s="90"/>
       <c r="N112" s="90"/>
       <c r="Q112" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="113" spans="1:17">
@@ -12898,7 +12862,7 @@
       <c r="M113" s="90"/>
       <c r="N113" s="90"/>
       <c r="Q113" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="114" spans="1:17">
@@ -12917,7 +12881,7 @@
       <c r="M114" s="90"/>
       <c r="N114" s="90"/>
       <c r="Q114" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="115" spans="1:17">
@@ -12936,7 +12900,7 @@
       <c r="M115" s="90"/>
       <c r="N115" s="90"/>
       <c r="Q115" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="1:17">
@@ -12955,7 +12919,7 @@
       <c r="M116" s="90"/>
       <c r="N116" s="90"/>
       <c r="Q116" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="117" spans="1:17">
@@ -12974,7 +12938,7 @@
       <c r="M117" s="90"/>
       <c r="N117" s="90"/>
       <c r="Q117" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="118" spans="1:17">
@@ -12993,7 +12957,7 @@
       <c r="M118" s="90"/>
       <c r="N118" s="90"/>
       <c r="Q118" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="119" spans="1:17">
@@ -13012,7 +12976,7 @@
       <c r="M119" s="90"/>
       <c r="N119" s="90"/>
       <c r="Q119" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="120" spans="1:17">
@@ -13031,7 +12995,7 @@
       <c r="M120" s="90"/>
       <c r="N120" s="90"/>
       <c r="Q120" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="121" spans="1:17">
@@ -13050,7 +13014,7 @@
       <c r="M121" s="90"/>
       <c r="N121" s="90"/>
       <c r="Q121" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="122" spans="1:17">
@@ -13069,7 +13033,7 @@
       <c r="M122" s="90"/>
       <c r="N122" s="90"/>
       <c r="Q122" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="123" spans="1:17">
@@ -13088,7 +13052,7 @@
       <c r="M123" s="90"/>
       <c r="N123" s="90"/>
       <c r="Q123" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" spans="1:17">
@@ -13107,7 +13071,7 @@
       <c r="M124" s="90"/>
       <c r="N124" s="90"/>
       <c r="Q124" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="125" spans="1:17">
@@ -13126,7 +13090,7 @@
       <c r="M125" s="90"/>
       <c r="N125" s="90"/>
       <c r="Q125" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126" spans="1:17">
@@ -13145,7 +13109,7 @@
       <c r="M126" s="90"/>
       <c r="N126" s="90"/>
       <c r="Q126" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127" spans="1:17" ht="28.5">
@@ -13164,7 +13128,7 @@
       <c r="M127" s="90"/>
       <c r="N127" s="90"/>
       <c r="Q127" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="128" spans="1:17">
@@ -13183,7 +13147,7 @@
       <c r="M128" s="90"/>
       <c r="N128" s="90"/>
       <c r="Q128" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" spans="1:17">
@@ -13202,7 +13166,7 @@
       <c r="M129" s="90"/>
       <c r="N129" s="90"/>
       <c r="Q129" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="1:17">
@@ -13221,7 +13185,7 @@
       <c r="M130" s="90"/>
       <c r="N130" s="90"/>
       <c r="Q130" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="131" spans="1:17">
@@ -13240,7 +13204,7 @@
       <c r="M131" s="90"/>
       <c r="N131" s="90"/>
       <c r="Q131" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="1:17">
@@ -13259,7 +13223,7 @@
       <c r="M132" s="90"/>
       <c r="N132" s="90"/>
       <c r="Q132" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="1:17">
@@ -13278,7 +13242,7 @@
       <c r="M133" s="90"/>
       <c r="N133" s="90"/>
       <c r="Q133" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="134" spans="1:17">
@@ -13297,7 +13261,7 @@
       <c r="M134" s="90"/>
       <c r="N134" s="90"/>
       <c r="Q134" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:17">
@@ -13316,7 +13280,7 @@
       <c r="M135" s="90"/>
       <c r="N135" s="90"/>
       <c r="Q135" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="136" spans="1:17">
@@ -13335,7 +13299,7 @@
       <c r="M136" s="90"/>
       <c r="N136" s="90"/>
       <c r="Q136" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="137" spans="1:17">
@@ -13354,7 +13318,7 @@
       <c r="M137" s="90"/>
       <c r="N137" s="90"/>
       <c r="Q137" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="138" spans="1:17">
@@ -13373,7 +13337,7 @@
       <c r="M138" s="90"/>
       <c r="N138" s="90"/>
       <c r="Q138" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="139" spans="1:17">
@@ -13392,7 +13356,7 @@
       <c r="M139" s="90"/>
       <c r="N139" s="90"/>
       <c r="Q139" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="140" spans="1:17">
@@ -13411,7 +13375,7 @@
       <c r="M140" s="90"/>
       <c r="N140" s="90"/>
       <c r="Q140" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="141" spans="1:17">
@@ -13430,7 +13394,7 @@
       <c r="M141" s="90"/>
       <c r="N141" s="90"/>
       <c r="Q141" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="142" spans="1:17" ht="28.5">
@@ -13449,7 +13413,7 @@
       <c r="M142" s="90"/>
       <c r="N142" s="90"/>
       <c r="Q142" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="143" spans="1:17">
@@ -13468,7 +13432,7 @@
       <c r="M143" s="90"/>
       <c r="N143" s="90"/>
       <c r="Q143" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="144" spans="1:17">
@@ -13487,7 +13451,7 @@
       <c r="M144" s="90"/>
       <c r="N144" s="90"/>
       <c r="Q144" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="145" spans="1:17">
@@ -13506,7 +13470,7 @@
       <c r="M145" s="90"/>
       <c r="N145" s="90"/>
       <c r="Q145" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="146" spans="1:17">
@@ -13525,7 +13489,7 @@
       <c r="M146" s="90"/>
       <c r="N146" s="90"/>
       <c r="Q146" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="147" spans="1:17">
@@ -13544,7 +13508,7 @@
       <c r="M147" s="90"/>
       <c r="N147" s="90"/>
       <c r="Q147" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="148" spans="1:17">
@@ -13563,7 +13527,7 @@
       <c r="M148" s="90"/>
       <c r="N148" s="90"/>
       <c r="Q148" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="149" spans="1:17">
@@ -13582,7 +13546,7 @@
       <c r="M149" s="90"/>
       <c r="N149" s="90"/>
       <c r="Q149" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="150" spans="1:17">
@@ -13601,7 +13565,7 @@
       <c r="M150" s="90"/>
       <c r="N150" s="90"/>
       <c r="Q150" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="151" spans="1:17">
@@ -13620,7 +13584,7 @@
       <c r="M151" s="90"/>
       <c r="N151" s="90"/>
       <c r="Q151" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="152" spans="1:17" ht="28.5">
@@ -13639,7 +13603,7 @@
       <c r="M152" s="90"/>
       <c r="N152" s="90"/>
       <c r="Q152" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="153" spans="1:17">
@@ -13658,7 +13622,7 @@
       <c r="M153" s="90"/>
       <c r="N153" s="90"/>
       <c r="Q153" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="154" spans="1:17" ht="28.5">
@@ -13677,7 +13641,7 @@
       <c r="M154" s="90"/>
       <c r="N154" s="90"/>
       <c r="Q154" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="155" spans="1:17">
@@ -13696,7 +13660,7 @@
       <c r="M155" s="90"/>
       <c r="N155" s="90"/>
       <c r="Q155" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="156" spans="1:17">
@@ -13715,7 +13679,7 @@
       <c r="M156" s="90"/>
       <c r="N156" s="90"/>
       <c r="Q156" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="157" spans="1:17">
@@ -13734,7 +13698,7 @@
       <c r="M157" s="90"/>
       <c r="N157" s="90"/>
       <c r="Q157" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="158" spans="1:17">
@@ -13753,7 +13717,7 @@
       <c r="M158" s="90"/>
       <c r="N158" s="90"/>
       <c r="Q158" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="159" spans="1:17">
@@ -13772,7 +13736,7 @@
       <c r="M159" s="90"/>
       <c r="N159" s="90"/>
       <c r="Q159" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="160" spans="1:17">
@@ -13791,7 +13755,7 @@
       <c r="M160" s="90"/>
       <c r="N160" s="90"/>
       <c r="Q160" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="161" spans="1:17">
@@ -13810,7 +13774,7 @@
       <c r="M161" s="90"/>
       <c r="N161" s="90"/>
       <c r="Q161" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="162" spans="1:17">
@@ -13829,7 +13793,7 @@
       <c r="M162" s="90"/>
       <c r="N162" s="90"/>
       <c r="Q162" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="163" spans="1:17">
@@ -13848,7 +13812,7 @@
       <c r="M163" s="90"/>
       <c r="N163" s="90"/>
       <c r="Q163" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="164" spans="1:17" ht="28.5">
@@ -13867,7 +13831,7 @@
       <c r="M164" s="90"/>
       <c r="N164" s="90"/>
       <c r="Q164" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="165" spans="1:17">
@@ -13886,7 +13850,7 @@
       <c r="M165" s="90"/>
       <c r="N165" s="90"/>
       <c r="Q165" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="166" spans="1:17" ht="42.75">
@@ -13905,7 +13869,7 @@
       <c r="M166" s="90"/>
       <c r="N166" s="90"/>
       <c r="Q166" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="167" spans="1:17">
@@ -13924,7 +13888,7 @@
       <c r="M167" s="90"/>
       <c r="N167" s="90"/>
       <c r="Q167" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="168" spans="1:17">
@@ -13943,7 +13907,7 @@
       <c r="M168" s="90"/>
       <c r="N168" s="90"/>
       <c r="Q168" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="169" spans="1:17" ht="28.5">
@@ -13962,7 +13926,7 @@
       <c r="M169" s="90"/>
       <c r="N169" s="90"/>
       <c r="Q169" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170" spans="1:17">
@@ -13981,7 +13945,7 @@
       <c r="M170" s="90"/>
       <c r="N170" s="90"/>
       <c r="Q170" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="171" spans="1:17">
@@ -14000,7 +13964,7 @@
       <c r="M171" s="90"/>
       <c r="N171" s="90"/>
       <c r="Q171" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="172" spans="1:17">
@@ -14019,7 +13983,7 @@
       <c r="M172" s="90"/>
       <c r="N172" s="90"/>
       <c r="Q172" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="173" spans="1:17">
@@ -14038,7 +14002,7 @@
       <c r="M173" s="90"/>
       <c r="N173" s="90"/>
       <c r="Q173" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="174" spans="1:17">
@@ -14057,7 +14021,7 @@
       <c r="M174" s="90"/>
       <c r="N174" s="90"/>
       <c r="Q174" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="175" spans="1:17">
@@ -14076,7 +14040,7 @@
       <c r="M175" s="90"/>
       <c r="N175" s="90"/>
       <c r="Q175" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="176" spans="1:17">
@@ -14095,7 +14059,7 @@
       <c r="M176" s="90"/>
       <c r="N176" s="90"/>
       <c r="Q176" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="177" spans="1:17">
@@ -14114,7 +14078,7 @@
       <c r="M177" s="90"/>
       <c r="N177" s="90"/>
       <c r="Q177" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="178" spans="1:17">
@@ -14133,7 +14097,7 @@
       <c r="M178" s="90"/>
       <c r="N178" s="90"/>
       <c r="Q178" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="179" spans="1:17" ht="28.5">
@@ -14152,7 +14116,7 @@
       <c r="M179" s="90"/>
       <c r="N179" s="90"/>
       <c r="Q179" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="180" spans="1:17">
@@ -14171,7 +14135,7 @@
       <c r="M180" s="90"/>
       <c r="N180" s="90"/>
       <c r="Q180" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="181" spans="1:17">
@@ -14190,7 +14154,7 @@
       <c r="M181" s="90"/>
       <c r="N181" s="90"/>
       <c r="Q181" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="182" spans="1:17">
@@ -14209,7 +14173,7 @@
       <c r="M182" s="90"/>
       <c r="N182" s="90"/>
       <c r="Q182" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="183" spans="1:17">
@@ -14228,7 +14192,7 @@
       <c r="M183" s="90"/>
       <c r="N183" s="90"/>
       <c r="Q183" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="184" spans="1:17">
@@ -14247,7 +14211,7 @@
       <c r="M184" s="90"/>
       <c r="N184" s="90"/>
       <c r="Q184" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="185" spans="1:17">
@@ -14266,7 +14230,7 @@
       <c r="M185" s="90"/>
       <c r="N185" s="90"/>
       <c r="Q185" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="186" spans="1:17">
@@ -14285,7 +14249,7 @@
       <c r="M186" s="90"/>
       <c r="N186" s="90"/>
       <c r="Q186" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="187" spans="1:17">
@@ -14304,7 +14268,7 @@
       <c r="M187" s="90"/>
       <c r="N187" s="90"/>
       <c r="Q187" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="188" spans="1:17">
@@ -14323,7 +14287,7 @@
       <c r="M188" s="90"/>
       <c r="N188" s="90"/>
       <c r="Q188" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="189" spans="1:17">
@@ -14342,7 +14306,7 @@
       <c r="M189" s="90"/>
       <c r="N189" s="90"/>
       <c r="Q189" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="190" spans="1:17">
@@ -14361,7 +14325,7 @@
       <c r="M190" s="90"/>
       <c r="N190" s="90"/>
       <c r="Q190" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="191" spans="1:17">
@@ -14380,7 +14344,7 @@
       <c r="M191" s="90"/>
       <c r="N191" s="90"/>
       <c r="Q191" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="192" spans="1:17">
@@ -14399,7 +14363,7 @@
       <c r="M192" s="90"/>
       <c r="N192" s="90"/>
       <c r="Q192" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="193" spans="1:17">
@@ -14418,7 +14382,7 @@
       <c r="M193" s="90"/>
       <c r="N193" s="90"/>
       <c r="Q193" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="194" spans="1:17">
@@ -14437,7 +14401,7 @@
       <c r="M194" s="90"/>
       <c r="N194" s="90"/>
       <c r="Q194" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="195" spans="1:17">
@@ -14456,7 +14420,7 @@
       <c r="M195" s="90"/>
       <c r="N195" s="90"/>
       <c r="Q195" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="196" spans="1:17">
@@ -14475,7 +14439,7 @@
       <c r="M196" s="90"/>
       <c r="N196" s="90"/>
       <c r="Q196" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="197" spans="1:17">
@@ -14494,7 +14458,7 @@
       <c r="M197" s="90"/>
       <c r="N197" s="90"/>
       <c r="Q197" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="198" spans="1:17">
@@ -14513,7 +14477,7 @@
       <c r="M198" s="90"/>
       <c r="N198" s="90"/>
       <c r="Q198" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="199" spans="1:17" ht="28.5">
@@ -14532,7 +14496,7 @@
       <c r="M199" s="90"/>
       <c r="N199" s="90"/>
       <c r="Q199" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="200" spans="1:17">
@@ -14551,7 +14515,7 @@
       <c r="M200" s="90"/>
       <c r="N200" s="90"/>
       <c r="Q200" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="201" spans="1:17">
@@ -14570,7 +14534,7 @@
       <c r="M201" s="90"/>
       <c r="N201" s="90"/>
       <c r="Q201" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="202" spans="1:17">
@@ -14589,7 +14553,7 @@
       <c r="M202" s="90"/>
       <c r="N202" s="90"/>
       <c r="Q202" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="203" spans="1:17">
@@ -14608,7 +14572,7 @@
       <c r="M203" s="90"/>
       <c r="N203" s="90"/>
       <c r="Q203" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="204" spans="1:17">
@@ -14627,7 +14591,7 @@
       <c r="M204" s="90"/>
       <c r="N204" s="90"/>
       <c r="Q204" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="205" spans="1:17">
@@ -14646,7 +14610,7 @@
       <c r="M205" s="90"/>
       <c r="N205" s="90"/>
       <c r="Q205" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="206" spans="1:17" ht="28.5">
@@ -14665,7 +14629,7 @@
       <c r="M206" s="90"/>
       <c r="N206" s="90"/>
       <c r="Q206" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="207" spans="1:17" ht="28.5">
@@ -14684,7 +14648,7 @@
       <c r="M207" s="90"/>
       <c r="N207" s="90"/>
       <c r="Q207" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="208" spans="1:17">
@@ -14703,7 +14667,7 @@
       <c r="M208" s="90"/>
       <c r="N208" s="90"/>
       <c r="Q208" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="209" spans="1:17">
@@ -14722,7 +14686,7 @@
       <c r="M209" s="90"/>
       <c r="N209" s="90"/>
       <c r="Q209" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="210" spans="1:17">
@@ -14741,7 +14705,7 @@
       <c r="M210" s="90"/>
       <c r="N210" s="90"/>
       <c r="Q210" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="211" spans="1:17">
@@ -14760,7 +14724,7 @@
       <c r="M211" s="90"/>
       <c r="N211" s="90"/>
       <c r="Q211" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="212" spans="1:17">
@@ -14779,7 +14743,7 @@
       <c r="M212" s="90"/>
       <c r="N212" s="90"/>
       <c r="Q212" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="213" spans="1:17">
@@ -14798,7 +14762,7 @@
       <c r="M213" s="90"/>
       <c r="N213" s="90"/>
       <c r="Q213" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214" spans="1:17">
@@ -14817,7 +14781,7 @@
       <c r="M214" s="90"/>
       <c r="N214" s="90"/>
       <c r="Q214" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="215" spans="1:17">
@@ -14836,7 +14800,7 @@
       <c r="M215" s="90"/>
       <c r="N215" s="90"/>
       <c r="Q215" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="216" spans="1:17">
@@ -15606,8 +15570,84 @@
       <c r="N263" s="90"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kWAtKR+5bXFXtub776LusOjx6zzocBPS8z5glSxwqvDtFArb75P9JFFjb4AUJ+J9gIRiAjX/CPl22GzXP5ayNQ==" saltValue="X1JDOFPYU+SdGE81qtkPRg==" spinCount="100000" sheet="1" scenarios="1"/>
-  <mergeCells count="94">
+  <sheetProtection algorithmName="SHA-512" hashValue="lsBUdkx7pyp9jnxRbgWH0wseXPwbKxBHGRCUMhh0iFic4bawFcpB1W2dxYq1VIQEu83b62nQPiFHTwK91YjhZQ==" saltValue="iCAlI6Z4uSqol81SzHxo/g==" spinCount="100000" sheet="1" scenarios="1"/>
+  <mergeCells count="92">
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="I35:N35"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="D28:F29"/>
+    <mergeCell ref="B21:C22"/>
+    <mergeCell ref="D21:F22"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:F25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:N23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="D26:F27"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A3:N5"/>
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:N15"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:I14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="R3:V13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
     <mergeCell ref="G35:H35"/>
     <mergeCell ref="A34:N34"/>
     <mergeCell ref="D33:F33"/>
@@ -15624,84 +15664,6 @@
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="I31:N31"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="R3:V13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:N15"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:I14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="D26:F27"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:N23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:F29"/>
-    <mergeCell ref="B21:C22"/>
-    <mergeCell ref="D21:F22"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="D24:F25"/>
-    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35" xr:uid="{5EC3205D-4079-402B-BBE7-9B917DF21EB0}">
@@ -16213,218 +16175,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="3" customHeight="1" thickBot="1">
-      <c r="A1" s="474"/>
-      <c r="B1" s="475"/>
-      <c r="C1" s="475"/>
-      <c r="D1" s="475"/>
-      <c r="E1" s="475"/>
-      <c r="F1" s="475"/>
-      <c r="G1" s="475"/>
-      <c r="H1" s="475"/>
-      <c r="I1" s="475"/>
-      <c r="J1" s="475"/>
+      <c r="A1" s="436"/>
+      <c r="B1" s="437"/>
+      <c r="C1" s="437"/>
+      <c r="D1" s="437"/>
+      <c r="E1" s="437"/>
+      <c r="F1" s="437"/>
+      <c r="G1" s="437"/>
+      <c r="H1" s="437"/>
+      <c r="I1" s="437"/>
+      <c r="J1" s="437"/>
     </row>
     <row r="2" spans="1:15" ht="13.5" customHeight="1">
-      <c r="A2" s="476">
+      <c r="A2" s="438">
         <v>34</v>
       </c>
-      <c r="B2" s="477"/>
-      <c r="C2" s="478" t="s">
-        <v>294</v>
-      </c>
-      <c r="D2" s="478"/>
-      <c r="E2" s="478"/>
-      <c r="F2" s="479"/>
-      <c r="G2" s="424"/>
-      <c r="H2" s="425"/>
-      <c r="I2" s="425"/>
-      <c r="J2" s="425"/>
-      <c r="K2" s="425"/>
-      <c r="L2" s="425"/>
-      <c r="M2" s="425"/>
-      <c r="N2" s="425"/>
-      <c r="O2" s="426"/>
+      <c r="B2" s="439"/>
+      <c r="C2" s="440" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="440"/>
+      <c r="E2" s="440"/>
+      <c r="F2" s="441"/>
+      <c r="G2" s="479"/>
+      <c r="H2" s="480"/>
+      <c r="I2" s="480"/>
+      <c r="J2" s="480"/>
+      <c r="K2" s="480"/>
+      <c r="L2" s="480"/>
+      <c r="M2" s="480"/>
+      <c r="N2" s="480"/>
+      <c r="O2" s="481"/>
     </row>
     <row r="3" spans="1:15" ht="12.75" customHeight="1">
       <c r="A3" s="170"/>
       <c r="B3" s="171"/>
-      <c r="C3" s="480" t="s">
-        <v>295</v>
-      </c>
-      <c r="D3" s="480"/>
-      <c r="E3" s="480"/>
-      <c r="F3" s="481"/>
-      <c r="G3" s="424"/>
-      <c r="H3" s="425"/>
-      <c r="I3" s="425"/>
-      <c r="J3" s="425"/>
-      <c r="K3" s="425"/>
-      <c r="L3" s="425"/>
-      <c r="M3" s="425"/>
-      <c r="N3" s="425"/>
-      <c r="O3" s="426"/>
+      <c r="C3" s="423" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" s="423"/>
+      <c r="E3" s="423"/>
+      <c r="F3" s="424"/>
+      <c r="G3" s="479"/>
+      <c r="H3" s="480"/>
+      <c r="I3" s="480"/>
+      <c r="J3" s="480"/>
+      <c r="K3" s="480"/>
+      <c r="L3" s="480"/>
+      <c r="M3" s="480"/>
+      <c r="N3" s="480"/>
+      <c r="O3" s="481"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="170"/>
       <c r="B4" s="171"/>
-      <c r="C4" s="480" t="s">
-        <v>296</v>
-      </c>
-      <c r="D4" s="480"/>
-      <c r="E4" s="480"/>
-      <c r="F4" s="481"/>
-      <c r="G4" s="424"/>
-      <c r="H4" s="425"/>
-      <c r="I4" s="425"/>
-      <c r="J4" s="425"/>
-      <c r="K4" s="425"/>
-      <c r="L4" s="425"/>
-      <c r="M4" s="425"/>
-      <c r="N4" s="425"/>
-      <c r="O4" s="426"/>
+      <c r="C4" s="423" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" s="423"/>
+      <c r="E4" s="423"/>
+      <c r="F4" s="424"/>
+      <c r="G4" s="479"/>
+      <c r="H4" s="480"/>
+      <c r="I4" s="480"/>
+      <c r="J4" s="480"/>
+      <c r="K4" s="480"/>
+      <c r="L4" s="480"/>
+      <c r="M4" s="480"/>
+      <c r="N4" s="480"/>
+      <c r="O4" s="481"/>
     </row>
     <row r="5" spans="1:15" ht="24.75" customHeight="1">
       <c r="A5" s="170"/>
       <c r="B5" s="171"/>
-      <c r="C5" s="480" t="s">
-        <v>297</v>
-      </c>
-      <c r="D5" s="480"/>
-      <c r="E5" s="480"/>
-      <c r="F5" s="481"/>
-      <c r="G5" s="434" t="b">
+      <c r="C5" s="423" t="s">
+        <v>295</v>
+      </c>
+      <c r="D5" s="423"/>
+      <c r="E5" s="423"/>
+      <c r="F5" s="424"/>
+      <c r="G5" s="444" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="427"/>
-      <c r="I5" s="427" t="b">
+      <c r="H5" s="445"/>
+      <c r="I5" s="445" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="427"/>
-      <c r="K5" s="427"/>
-      <c r="L5" s="427"/>
-      <c r="M5" s="427"/>
-      <c r="N5" s="427"/>
-      <c r="O5" s="428"/>
+      <c r="J5" s="445"/>
+      <c r="K5" s="445"/>
+      <c r="L5" s="445"/>
+      <c r="M5" s="445"/>
+      <c r="N5" s="445"/>
+      <c r="O5" s="449"/>
     </row>
     <row r="6" spans="1:15" ht="24" customHeight="1">
       <c r="A6" s="170"/>
       <c r="B6" s="171"/>
-      <c r="C6" s="480" t="s">
-        <v>298</v>
-      </c>
-      <c r="D6" s="480"/>
-      <c r="E6" s="480"/>
-      <c r="F6" s="481"/>
-      <c r="G6" s="434" t="b">
+      <c r="C6" s="423" t="s">
+        <v>296</v>
+      </c>
+      <c r="D6" s="423"/>
+      <c r="E6" s="423"/>
+      <c r="F6" s="424"/>
+      <c r="G6" s="444" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="427"/>
-      <c r="I6" s="427" t="b">
+      <c r="H6" s="445"/>
+      <c r="I6" s="445" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="427"/>
-      <c r="K6" s="427"/>
-      <c r="L6" s="427"/>
-      <c r="M6" s="427"/>
-      <c r="N6" s="427"/>
-      <c r="O6" s="428"/>
+      <c r="J6" s="445"/>
+      <c r="K6" s="445"/>
+      <c r="L6" s="445"/>
+      <c r="M6" s="445"/>
+      <c r="N6" s="445"/>
+      <c r="O6" s="449"/>
     </row>
     <row r="7" spans="1:15" ht="27" customHeight="1">
       <c r="A7" s="170"/>
       <c r="B7" s="171"/>
-      <c r="C7" s="480"/>
-      <c r="D7" s="480"/>
-      <c r="E7" s="480"/>
-      <c r="F7" s="480"/>
+      <c r="C7" s="423"/>
+      <c r="D7" s="423"/>
+      <c r="E7" s="423"/>
+      <c r="F7" s="423"/>
       <c r="G7" s="167" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H7" s="168"/>
-      <c r="I7" s="429"/>
-      <c r="J7" s="429"/>
-      <c r="K7" s="429"/>
-      <c r="L7" s="429"/>
-      <c r="M7" s="429"/>
-      <c r="N7" s="429"/>
-      <c r="O7" s="430"/>
+      <c r="I7" s="482"/>
+      <c r="J7" s="482"/>
+      <c r="K7" s="482"/>
+      <c r="L7" s="482"/>
+      <c r="M7" s="482"/>
+      <c r="N7" s="482"/>
+      <c r="O7" s="483"/>
     </row>
     <row r="8" spans="1:15" ht="31.5" customHeight="1">
       <c r="A8" s="172"/>
       <c r="B8" s="173"/>
-      <c r="C8" s="484"/>
-      <c r="D8" s="484"/>
-      <c r="E8" s="484"/>
-      <c r="F8" s="485"/>
-      <c r="G8" s="431"/>
-      <c r="H8" s="432"/>
-      <c r="I8" s="432"/>
-      <c r="J8" s="432"/>
-      <c r="K8" s="432"/>
-      <c r="L8" s="432"/>
-      <c r="M8" s="432"/>
-      <c r="N8" s="432"/>
-      <c r="O8" s="433"/>
+      <c r="C8" s="425"/>
+      <c r="D8" s="425"/>
+      <c r="E8" s="425"/>
+      <c r="F8" s="426"/>
+      <c r="G8" s="484"/>
+      <c r="H8" s="485"/>
+      <c r="I8" s="485"/>
+      <c r="J8" s="485"/>
+      <c r="K8" s="485"/>
+      <c r="L8" s="485"/>
+      <c r="M8" s="485"/>
+      <c r="N8" s="485"/>
+      <c r="O8" s="486"/>
     </row>
     <row r="9" spans="1:15" ht="20.45" customHeight="1">
-      <c r="A9" s="486">
+      <c r="A9" s="427">
         <v>35</v>
       </c>
-      <c r="B9" s="487"/>
-      <c r="C9" s="445" t="s">
-        <v>299</v>
-      </c>
-      <c r="D9" s="445"/>
-      <c r="E9" s="355"/>
-      <c r="F9" s="488"/>
-      <c r="G9" s="420" t="b">
+      <c r="B9" s="428"/>
+      <c r="C9" s="429" t="s">
+        <v>297</v>
+      </c>
+      <c r="D9" s="429"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="430"/>
+      <c r="G9" s="401" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="421"/>
-      <c r="I9" s="404" t="b">
+      <c r="H9" s="402"/>
+      <c r="I9" s="416" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="404"/>
-      <c r="K9" s="404"/>
-      <c r="L9" s="404"/>
-      <c r="M9" s="404"/>
-      <c r="N9" s="404"/>
-      <c r="O9" s="405"/>
+      <c r="J9" s="416"/>
+      <c r="K9" s="416"/>
+      <c r="L9" s="416"/>
+      <c r="M9" s="416"/>
+      <c r="N9" s="416"/>
+      <c r="O9" s="417"/>
     </row>
     <row r="10" spans="1:15" ht="26.25" customHeight="1">
       <c r="A10" s="174"/>
       <c r="B10" s="175"/>
-      <c r="C10" s="445"/>
-      <c r="D10" s="445"/>
-      <c r="E10" s="355"/>
-      <c r="F10" s="488"/>
-      <c r="G10" s="496" t="s">
-        <v>321</v>
-      </c>
-      <c r="H10" s="497"/>
-      <c r="I10" s="416"/>
-      <c r="J10" s="416"/>
-      <c r="K10" s="416"/>
-      <c r="L10" s="416"/>
-      <c r="M10" s="416"/>
-      <c r="N10" s="416"/>
-      <c r="O10" s="417"/>
+      <c r="C10" s="429"/>
+      <c r="D10" s="429"/>
+      <c r="E10" s="350"/>
+      <c r="F10" s="430"/>
+      <c r="G10" s="409" t="s">
+        <v>319</v>
+      </c>
+      <c r="H10" s="410"/>
+      <c r="I10" s="418"/>
+      <c r="J10" s="418"/>
+      <c r="K10" s="418"/>
+      <c r="L10" s="418"/>
+      <c r="M10" s="418"/>
+      <c r="N10" s="418"/>
+      <c r="O10" s="419"/>
     </row>
     <row r="11" spans="1:15" ht="21.75" customHeight="1">
       <c r="A11" s="174"/>
       <c r="B11" s="175"/>
-      <c r="C11" s="355"/>
-      <c r="D11" s="355"/>
-      <c r="E11" s="355"/>
-      <c r="F11" s="355"/>
-      <c r="G11" s="502"/>
-      <c r="H11" s="503"/>
-      <c r="I11" s="503"/>
-      <c r="J11" s="503"/>
-      <c r="K11" s="503"/>
-      <c r="L11" s="503"/>
-      <c r="M11" s="503"/>
-      <c r="N11" s="503"/>
-      <c r="O11" s="504"/>
+      <c r="C11" s="350"/>
+      <c r="D11" s="350"/>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
+      <c r="G11" s="420"/>
+      <c r="H11" s="421"/>
+      <c r="I11" s="421"/>
+      <c r="J11" s="421"/>
+      <c r="K11" s="421"/>
+      <c r="L11" s="421"/>
+      <c r="M11" s="421"/>
+      <c r="N11" s="421"/>
+      <c r="O11" s="422"/>
     </row>
     <row r="12" spans="1:15" ht="18.75" customHeight="1">
       <c r="A12" s="176"/>
@@ -16433,282 +16395,282 @@
       <c r="D12" s="178"/>
       <c r="E12" s="179"/>
       <c r="F12" s="180"/>
-      <c r="G12" s="498" t="b">
+      <c r="G12" s="411" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="499"/>
-      <c r="I12" s="499" t="b">
+      <c r="H12" s="412"/>
+      <c r="I12" s="412" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="499"/>
-      <c r="K12" s="499"/>
-      <c r="L12" s="499"/>
-      <c r="M12" s="499"/>
-      <c r="N12" s="499"/>
-      <c r="O12" s="500"/>
+      <c r="J12" s="412"/>
+      <c r="K12" s="412"/>
+      <c r="L12" s="412"/>
+      <c r="M12" s="412"/>
+      <c r="N12" s="412"/>
+      <c r="O12" s="413"/>
     </row>
     <row r="13" spans="1:15" ht="21.75" customHeight="1">
       <c r="A13" s="176"/>
       <c r="B13" s="177"/>
-      <c r="C13" s="489" t="s">
-        <v>300</v>
-      </c>
-      <c r="D13" s="489"/>
-      <c r="E13" s="490"/>
-      <c r="F13" s="491"/>
-      <c r="G13" s="498"/>
-      <c r="H13" s="499"/>
-      <c r="I13" s="499"/>
-      <c r="J13" s="499"/>
-      <c r="K13" s="499"/>
-      <c r="L13" s="499"/>
-      <c r="M13" s="499"/>
-      <c r="N13" s="499"/>
-      <c r="O13" s="500"/>
+      <c r="C13" s="431" t="s">
+        <v>298</v>
+      </c>
+      <c r="D13" s="431"/>
+      <c r="E13" s="432"/>
+      <c r="F13" s="433"/>
+      <c r="G13" s="411"/>
+      <c r="H13" s="412"/>
+      <c r="I13" s="412"/>
+      <c r="J13" s="412"/>
+      <c r="K13" s="412"/>
+      <c r="L13" s="412"/>
+      <c r="M13" s="412"/>
+      <c r="N13" s="412"/>
+      <c r="O13" s="413"/>
     </row>
     <row r="14" spans="1:15" ht="23.25" customHeight="1">
       <c r="A14" s="176"/>
       <c r="B14" s="177"/>
-      <c r="C14" s="489"/>
-      <c r="D14" s="489"/>
-      <c r="E14" s="490"/>
-      <c r="F14" s="491"/>
-      <c r="G14" s="451" t="s">
-        <v>324</v>
-      </c>
-      <c r="H14" s="452"/>
-      <c r="I14" s="435"/>
-      <c r="J14" s="435"/>
-      <c r="K14" s="435"/>
-      <c r="L14" s="435"/>
-      <c r="M14" s="435"/>
-      <c r="N14" s="435"/>
-      <c r="O14" s="436"/>
+      <c r="C14" s="431"/>
+      <c r="D14" s="431"/>
+      <c r="E14" s="432"/>
+      <c r="F14" s="433"/>
+      <c r="G14" s="397" t="s">
+        <v>322</v>
+      </c>
+      <c r="H14" s="398"/>
+      <c r="I14" s="415"/>
+      <c r="J14" s="415"/>
+      <c r="K14" s="415"/>
+      <c r="L14" s="415"/>
+      <c r="M14" s="415"/>
+      <c r="N14" s="415"/>
+      <c r="O14" s="473"/>
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1">
       <c r="A15" s="176"/>
       <c r="B15" s="177"/>
-      <c r="C15" s="489"/>
-      <c r="D15" s="489"/>
-      <c r="E15" s="490"/>
-      <c r="F15" s="491"/>
-      <c r="G15" s="501" t="s">
-        <v>301</v>
-      </c>
-      <c r="H15" s="435"/>
-      <c r="I15" s="416"/>
-      <c r="J15" s="416"/>
-      <c r="K15" s="416"/>
-      <c r="L15" s="416"/>
-      <c r="M15" s="416"/>
-      <c r="N15" s="416"/>
-      <c r="O15" s="417"/>
+      <c r="C15" s="431"/>
+      <c r="D15" s="431"/>
+      <c r="E15" s="432"/>
+      <c r="F15" s="433"/>
+      <c r="G15" s="414" t="s">
+        <v>299</v>
+      </c>
+      <c r="H15" s="415"/>
+      <c r="I15" s="418"/>
+      <c r="J15" s="418"/>
+      <c r="K15" s="418"/>
+      <c r="L15" s="418"/>
+      <c r="M15" s="418"/>
+      <c r="N15" s="418"/>
+      <c r="O15" s="419"/>
     </row>
     <row r="16" spans="1:15" ht="27.75" customHeight="1">
       <c r="A16" s="176"/>
       <c r="B16" s="177"/>
-      <c r="C16" s="489"/>
-      <c r="D16" s="489"/>
-      <c r="E16" s="490"/>
-      <c r="F16" s="491"/>
-      <c r="G16" s="418" t="s">
-        <v>302</v>
-      </c>
-      <c r="H16" s="419"/>
-      <c r="I16" s="437"/>
-      <c r="J16" s="437"/>
-      <c r="K16" s="437"/>
-      <c r="L16" s="437"/>
-      <c r="M16" s="437"/>
-      <c r="N16" s="437"/>
-      <c r="O16" s="438"/>
+      <c r="C16" s="431"/>
+      <c r="D16" s="431"/>
+      <c r="E16" s="432"/>
+      <c r="F16" s="433"/>
+      <c r="G16" s="487" t="s">
+        <v>300</v>
+      </c>
+      <c r="H16" s="488"/>
+      <c r="I16" s="474"/>
+      <c r="J16" s="474"/>
+      <c r="K16" s="474"/>
+      <c r="L16" s="474"/>
+      <c r="M16" s="474"/>
+      <c r="N16" s="474"/>
+      <c r="O16" s="475"/>
     </row>
     <row r="17" spans="1:15" ht="21" customHeight="1">
       <c r="A17" s="181"/>
       <c r="B17" s="182"/>
-      <c r="C17" s="492"/>
-      <c r="D17" s="492"/>
-      <c r="E17" s="492"/>
-      <c r="F17" s="493"/>
-      <c r="G17" s="413" t="s">
-        <v>303</v>
-      </c>
-      <c r="H17" s="414"/>
-      <c r="I17" s="414"/>
-      <c r="J17" s="414"/>
-      <c r="K17" s="414"/>
-      <c r="L17" s="414"/>
-      <c r="M17" s="414"/>
-      <c r="N17" s="414"/>
-      <c r="O17" s="415"/>
+      <c r="C17" s="434"/>
+      <c r="D17" s="434"/>
+      <c r="E17" s="434"/>
+      <c r="F17" s="435"/>
+      <c r="G17" s="476" t="s">
+        <v>301</v>
+      </c>
+      <c r="H17" s="477"/>
+      <c r="I17" s="477"/>
+      <c r="J17" s="477"/>
+      <c r="K17" s="477"/>
+      <c r="L17" s="477"/>
+      <c r="M17" s="477"/>
+      <c r="N17" s="477"/>
+      <c r="O17" s="478"/>
     </row>
     <row r="18" spans="1:15" ht="33" customHeight="1">
-      <c r="A18" s="482">
+      <c r="A18" s="395">
         <v>36</v>
       </c>
-      <c r="B18" s="483"/>
-      <c r="C18" s="494" t="s">
-        <v>304</v>
-      </c>
-      <c r="D18" s="494" t="b">
+      <c r="B18" s="396"/>
+      <c r="C18" s="403" t="s">
+        <v>302</v>
+      </c>
+      <c r="D18" s="403" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="494"/>
-      <c r="F18" s="495"/>
-      <c r="G18" s="420" t="b">
+      <c r="E18" s="403"/>
+      <c r="F18" s="404"/>
+      <c r="G18" s="401" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="421"/>
-      <c r="I18" s="404" t="b">
+      <c r="H18" s="402"/>
+      <c r="I18" s="416" t="b">
         <v>0</v>
       </c>
-      <c r="J18" s="404"/>
-      <c r="K18" s="404"/>
-      <c r="L18" s="404"/>
-      <c r="M18" s="404"/>
-      <c r="N18" s="404"/>
-      <c r="O18" s="405"/>
+      <c r="J18" s="416"/>
+      <c r="K18" s="416"/>
+      <c r="L18" s="416"/>
+      <c r="M18" s="416"/>
+      <c r="N18" s="416"/>
+      <c r="O18" s="417"/>
     </row>
     <row r="19" spans="1:15" ht="26.25" customHeight="1">
       <c r="A19" s="174"/>
       <c r="B19" s="175"/>
-      <c r="C19" s="439"/>
-      <c r="D19" s="439"/>
-      <c r="E19" s="439"/>
-      <c r="F19" s="440"/>
-      <c r="G19" s="422" t="s">
-        <v>323</v>
-      </c>
-      <c r="H19" s="423"/>
-      <c r="I19" s="416"/>
-      <c r="J19" s="416"/>
-      <c r="K19" s="416"/>
-      <c r="L19" s="416"/>
-      <c r="M19" s="416"/>
-      <c r="N19" s="416"/>
-      <c r="O19" s="417"/>
+      <c r="C19" s="405"/>
+      <c r="D19" s="405"/>
+      <c r="E19" s="405"/>
+      <c r="F19" s="406"/>
+      <c r="G19" s="399" t="s">
+        <v>321</v>
+      </c>
+      <c r="H19" s="400"/>
+      <c r="I19" s="418"/>
+      <c r="J19" s="418"/>
+      <c r="K19" s="418"/>
+      <c r="L19" s="418"/>
+      <c r="M19" s="418"/>
+      <c r="N19" s="418"/>
+      <c r="O19" s="419"/>
     </row>
     <row r="20" spans="1:15" ht="25.5" customHeight="1">
       <c r="A20" s="185"/>
       <c r="B20" s="186"/>
-      <c r="C20" s="441"/>
-      <c r="D20" s="441"/>
-      <c r="E20" s="441"/>
-      <c r="F20" s="442"/>
-      <c r="G20" s="413"/>
-      <c r="H20" s="414"/>
-      <c r="I20" s="414"/>
-      <c r="J20" s="414"/>
-      <c r="K20" s="414"/>
-      <c r="L20" s="414"/>
-      <c r="M20" s="414"/>
-      <c r="N20" s="414"/>
-      <c r="O20" s="415"/>
+      <c r="C20" s="407"/>
+      <c r="D20" s="407"/>
+      <c r="E20" s="407"/>
+      <c r="F20" s="408"/>
+      <c r="G20" s="476"/>
+      <c r="H20" s="477"/>
+      <c r="I20" s="477"/>
+      <c r="J20" s="477"/>
+      <c r="K20" s="477"/>
+      <c r="L20" s="477"/>
+      <c r="M20" s="477"/>
+      <c r="N20" s="477"/>
+      <c r="O20" s="478"/>
     </row>
     <row r="21" spans="1:15" ht="26.25" customHeight="1">
-      <c r="A21" s="482">
+      <c r="A21" s="395">
         <v>37</v>
       </c>
-      <c r="B21" s="483"/>
-      <c r="C21" s="494" t="s">
-        <v>305</v>
-      </c>
-      <c r="D21" s="494"/>
-      <c r="E21" s="494"/>
-      <c r="F21" s="495"/>
-      <c r="G21" s="420" t="b">
+      <c r="B21" s="396"/>
+      <c r="C21" s="403" t="s">
+        <v>303</v>
+      </c>
+      <c r="D21" s="403"/>
+      <c r="E21" s="403"/>
+      <c r="F21" s="404"/>
+      <c r="G21" s="401" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="421"/>
-      <c r="I21" s="404" t="b">
+      <c r="H21" s="402"/>
+      <c r="I21" s="416" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="404"/>
-      <c r="K21" s="404"/>
-      <c r="L21" s="404"/>
-      <c r="M21" s="404"/>
-      <c r="N21" s="404"/>
-      <c r="O21" s="405"/>
+      <c r="J21" s="416"/>
+      <c r="K21" s="416"/>
+      <c r="L21" s="416"/>
+      <c r="M21" s="416"/>
+      <c r="N21" s="416"/>
+      <c r="O21" s="417"/>
     </row>
     <row r="22" spans="1:15" ht="27.75" customHeight="1">
       <c r="A22" s="174"/>
       <c r="B22" s="175"/>
-      <c r="C22" s="439"/>
-      <c r="D22" s="439"/>
-      <c r="E22" s="439"/>
-      <c r="F22" s="440"/>
-      <c r="G22" s="422" t="s">
-        <v>322</v>
-      </c>
-      <c r="H22" s="423"/>
-      <c r="I22" s="416"/>
-      <c r="J22" s="416"/>
-      <c r="K22" s="416"/>
-      <c r="L22" s="416"/>
-      <c r="M22" s="416"/>
-      <c r="N22" s="416"/>
-      <c r="O22" s="417"/>
+      <c r="C22" s="405"/>
+      <c r="D22" s="405"/>
+      <c r="E22" s="405"/>
+      <c r="F22" s="406"/>
+      <c r="G22" s="399" t="s">
+        <v>320</v>
+      </c>
+      <c r="H22" s="400"/>
+      <c r="I22" s="418"/>
+      <c r="J22" s="418"/>
+      <c r="K22" s="418"/>
+      <c r="L22" s="418"/>
+      <c r="M22" s="418"/>
+      <c r="N22" s="418"/>
+      <c r="O22" s="419"/>
     </row>
     <row r="23" spans="1:15" ht="39.75" customHeight="1">
       <c r="A23" s="185"/>
       <c r="B23" s="186"/>
-      <c r="C23" s="441"/>
-      <c r="D23" s="441"/>
-      <c r="E23" s="441"/>
-      <c r="F23" s="442"/>
-      <c r="G23" s="413"/>
-      <c r="H23" s="414"/>
-      <c r="I23" s="414"/>
-      <c r="J23" s="414"/>
-      <c r="K23" s="414"/>
-      <c r="L23" s="414"/>
-      <c r="M23" s="414"/>
-      <c r="N23" s="414"/>
-      <c r="O23" s="415"/>
+      <c r="C23" s="407"/>
+      <c r="D23" s="407"/>
+      <c r="E23" s="407"/>
+      <c r="F23" s="408"/>
+      <c r="G23" s="476"/>
+      <c r="H23" s="477"/>
+      <c r="I23" s="477"/>
+      <c r="J23" s="477"/>
+      <c r="K23" s="477"/>
+      <c r="L23" s="477"/>
+      <c r="M23" s="477"/>
+      <c r="N23" s="477"/>
+      <c r="O23" s="478"/>
     </row>
     <row r="24" spans="1:15" ht="38.25" customHeight="1">
-      <c r="A24" s="482">
+      <c r="A24" s="395">
         <v>38</v>
       </c>
-      <c r="B24" s="483"/>
-      <c r="C24" s="494" t="s">
-        <v>306</v>
-      </c>
-      <c r="D24" s="494"/>
-      <c r="E24" s="494"/>
-      <c r="F24" s="495"/>
-      <c r="G24" s="420" t="b">
+      <c r="B24" s="396"/>
+      <c r="C24" s="403" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" s="403"/>
+      <c r="E24" s="403"/>
+      <c r="F24" s="404"/>
+      <c r="G24" s="401" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="421"/>
-      <c r="I24" s="404" t="b">
+      <c r="H24" s="402"/>
+      <c r="I24" s="416" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="404"/>
-      <c r="K24" s="404"/>
-      <c r="L24" s="404"/>
-      <c r="M24" s="404"/>
-      <c r="N24" s="404"/>
-      <c r="O24" s="405"/>
+      <c r="J24" s="416"/>
+      <c r="K24" s="416"/>
+      <c r="L24" s="416"/>
+      <c r="M24" s="416"/>
+      <c r="N24" s="416"/>
+      <c r="O24" s="417"/>
     </row>
     <row r="25" spans="1:15" ht="28.5" customHeight="1">
       <c r="A25" s="174"/>
       <c r="B25" s="175"/>
-      <c r="C25" s="439"/>
-      <c r="D25" s="439"/>
-      <c r="E25" s="439"/>
-      <c r="F25" s="440"/>
-      <c r="G25" s="451" t="s">
-        <v>307</v>
-      </c>
-      <c r="H25" s="452"/>
-      <c r="I25" s="406"/>
-      <c r="J25" s="406"/>
-      <c r="K25" s="406"/>
-      <c r="L25" s="406"/>
-      <c r="M25" s="406"/>
-      <c r="N25" s="406"/>
-      <c r="O25" s="407"/>
+      <c r="C25" s="405"/>
+      <c r="D25" s="405"/>
+      <c r="E25" s="405"/>
+      <c r="F25" s="406"/>
+      <c r="G25" s="397" t="s">
+        <v>305</v>
+      </c>
+      <c r="H25" s="398"/>
+      <c r="I25" s="489"/>
+      <c r="J25" s="489"/>
+      <c r="K25" s="489"/>
+      <c r="L25" s="489"/>
+      <c r="M25" s="489"/>
+      <c r="N25" s="489"/>
+      <c r="O25" s="490"/>
     </row>
     <row r="26" spans="1:15" ht="23.25" customHeight="1">
       <c r="A26" s="174"/>
@@ -16717,237 +16679,237 @@
       <c r="D26" s="183"/>
       <c r="E26" s="183"/>
       <c r="F26" s="184"/>
-      <c r="G26" s="449" t="b">
+      <c r="G26" s="465" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="450"/>
-      <c r="I26" s="408" t="b">
+      <c r="H26" s="466"/>
+      <c r="I26" s="491" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="408"/>
-      <c r="K26" s="408"/>
-      <c r="L26" s="408"/>
-      <c r="M26" s="408"/>
-      <c r="N26" s="408"/>
-      <c r="O26" s="409"/>
+      <c r="J26" s="491"/>
+      <c r="K26" s="491"/>
+      <c r="L26" s="491"/>
+      <c r="M26" s="491"/>
+      <c r="N26" s="491"/>
+      <c r="O26" s="492"/>
     </row>
     <row r="27" spans="1:15" ht="24.75" customHeight="1">
       <c r="A27" s="174"/>
       <c r="B27" s="175"/>
-      <c r="C27" s="439" t="s">
-        <v>308</v>
-      </c>
-      <c r="D27" s="439"/>
-      <c r="E27" s="439"/>
-      <c r="F27" s="440"/>
-      <c r="G27" s="449"/>
-      <c r="H27" s="450"/>
-      <c r="I27" s="410"/>
-      <c r="J27" s="410"/>
-      <c r="K27" s="410"/>
-      <c r="L27" s="410"/>
-      <c r="M27" s="410"/>
-      <c r="N27" s="410"/>
-      <c r="O27" s="411"/>
+      <c r="C27" s="405" t="s">
+        <v>306</v>
+      </c>
+      <c r="D27" s="405"/>
+      <c r="E27" s="405"/>
+      <c r="F27" s="406"/>
+      <c r="G27" s="465"/>
+      <c r="H27" s="466"/>
+      <c r="I27" s="493"/>
+      <c r="J27" s="493"/>
+      <c r="K27" s="493"/>
+      <c r="L27" s="493"/>
+      <c r="M27" s="493"/>
+      <c r="N27" s="493"/>
+      <c r="O27" s="494"/>
     </row>
     <row r="28" spans="1:15" ht="36" customHeight="1">
       <c r="A28" s="174"/>
       <c r="B28" s="175"/>
-      <c r="C28" s="439"/>
-      <c r="D28" s="439"/>
-      <c r="E28" s="439"/>
-      <c r="F28" s="440"/>
-      <c r="G28" s="451" t="s">
-        <v>307</v>
-      </c>
-      <c r="H28" s="452"/>
-      <c r="I28" s="406"/>
-      <c r="J28" s="406"/>
-      <c r="K28" s="406"/>
-      <c r="L28" s="406"/>
-      <c r="M28" s="406"/>
-      <c r="N28" s="406"/>
-      <c r="O28" s="407"/>
+      <c r="C28" s="405"/>
+      <c r="D28" s="405"/>
+      <c r="E28" s="405"/>
+      <c r="F28" s="406"/>
+      <c r="G28" s="397" t="s">
+        <v>305</v>
+      </c>
+      <c r="H28" s="398"/>
+      <c r="I28" s="489"/>
+      <c r="J28" s="489"/>
+      <c r="K28" s="489"/>
+      <c r="L28" s="489"/>
+      <c r="M28" s="489"/>
+      <c r="N28" s="489"/>
+      <c r="O28" s="490"/>
     </row>
     <row r="29" spans="1:15" ht="30.75" customHeight="1">
       <c r="A29" s="185"/>
       <c r="B29" s="186"/>
-      <c r="C29" s="441"/>
-      <c r="D29" s="441"/>
-      <c r="E29" s="441"/>
-      <c r="F29" s="442"/>
-      <c r="G29" s="453"/>
-      <c r="H29" s="454"/>
-      <c r="I29" s="454"/>
-      <c r="J29" s="454"/>
-      <c r="K29" s="454"/>
-      <c r="L29" s="454"/>
-      <c r="M29" s="454"/>
-      <c r="N29" s="454"/>
-      <c r="O29" s="455"/>
+      <c r="C29" s="407"/>
+      <c r="D29" s="407"/>
+      <c r="E29" s="407"/>
+      <c r="F29" s="408"/>
+      <c r="G29" s="467"/>
+      <c r="H29" s="468"/>
+      <c r="I29" s="468"/>
+      <c r="J29" s="468"/>
+      <c r="K29" s="468"/>
+      <c r="L29" s="468"/>
+      <c r="M29" s="468"/>
+      <c r="N29" s="468"/>
+      <c r="O29" s="469"/>
     </row>
     <row r="30" spans="1:15" ht="23.45" customHeight="1">
-      <c r="A30" s="482">
+      <c r="A30" s="395">
         <v>39</v>
       </c>
-      <c r="B30" s="483"/>
-      <c r="C30" s="443" t="s">
-        <v>309</v>
-      </c>
-      <c r="D30" s="443"/>
-      <c r="E30" s="443"/>
-      <c r="F30" s="444"/>
-      <c r="G30" s="420" t="b">
+      <c r="B30" s="396"/>
+      <c r="C30" s="460" t="s">
+        <v>307</v>
+      </c>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="461"/>
+      <c r="G30" s="401" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="421"/>
-      <c r="I30" s="404" t="b">
+      <c r="H30" s="402"/>
+      <c r="I30" s="416" t="b">
         <v>0</v>
       </c>
-      <c r="J30" s="404"/>
-      <c r="K30" s="404"/>
-      <c r="L30" s="404"/>
-      <c r="M30" s="404"/>
-      <c r="N30" s="404"/>
-      <c r="O30" s="405"/>
+      <c r="J30" s="416"/>
+      <c r="K30" s="416"/>
+      <c r="L30" s="416"/>
+      <c r="M30" s="416"/>
+      <c r="N30" s="416"/>
+      <c r="O30" s="417"/>
     </row>
     <row r="31" spans="1:15" ht="27" customHeight="1">
       <c r="A31" s="174"/>
       <c r="B31" s="175"/>
-      <c r="C31" s="445"/>
-      <c r="D31" s="445"/>
-      <c r="E31" s="445"/>
-      <c r="F31" s="446"/>
-      <c r="G31" s="422" t="s">
-        <v>310</v>
-      </c>
-      <c r="H31" s="423"/>
-      <c r="I31" s="456"/>
-      <c r="J31" s="456"/>
-      <c r="K31" s="456"/>
-      <c r="L31" s="456"/>
-      <c r="M31" s="456"/>
-      <c r="N31" s="456"/>
-      <c r="O31" s="457"/>
+      <c r="C31" s="429"/>
+      <c r="D31" s="429"/>
+      <c r="E31" s="429"/>
+      <c r="F31" s="462"/>
+      <c r="G31" s="399" t="s">
+        <v>308</v>
+      </c>
+      <c r="H31" s="400"/>
+      <c r="I31" s="450"/>
+      <c r="J31" s="450"/>
+      <c r="K31" s="450"/>
+      <c r="L31" s="450"/>
+      <c r="M31" s="450"/>
+      <c r="N31" s="450"/>
+      <c r="O31" s="451"/>
     </row>
     <row r="32" spans="1:15" ht="33.75" customHeight="1">
       <c r="A32" s="185"/>
       <c r="B32" s="186"/>
-      <c r="C32" s="447"/>
-      <c r="D32" s="447"/>
-      <c r="E32" s="447"/>
-      <c r="F32" s="448"/>
-      <c r="G32" s="458"/>
-      <c r="H32" s="459"/>
-      <c r="I32" s="459"/>
-      <c r="J32" s="459"/>
-      <c r="K32" s="459"/>
-      <c r="L32" s="459"/>
-      <c r="M32" s="459"/>
-      <c r="N32" s="459"/>
-      <c r="O32" s="460"/>
+      <c r="C32" s="463"/>
+      <c r="D32" s="463"/>
+      <c r="E32" s="463"/>
+      <c r="F32" s="464"/>
+      <c r="G32" s="470"/>
+      <c r="H32" s="471"/>
+      <c r="I32" s="471"/>
+      <c r="J32" s="471"/>
+      <c r="K32" s="471"/>
+      <c r="L32" s="471"/>
+      <c r="M32" s="471"/>
+      <c r="N32" s="471"/>
+      <c r="O32" s="472"/>
     </row>
     <row r="33" spans="1:15" ht="46.5" customHeight="1">
-      <c r="A33" s="469">
+      <c r="A33" s="442">
         <v>40</v>
       </c>
-      <c r="B33" s="470"/>
-      <c r="C33" s="439" t="s">
-        <v>311</v>
-      </c>
-      <c r="D33" s="439"/>
-      <c r="E33" s="439"/>
-      <c r="F33" s="440"/>
-      <c r="G33" s="471"/>
-      <c r="H33" s="472"/>
-      <c r="I33" s="472"/>
-      <c r="J33" s="472"/>
-      <c r="K33" s="472"/>
-      <c r="L33" s="472"/>
-      <c r="M33" s="472"/>
-      <c r="N33" s="472"/>
-      <c r="O33" s="473"/>
+      <c r="B33" s="443"/>
+      <c r="C33" s="405" t="s">
+        <v>309</v>
+      </c>
+      <c r="D33" s="405"/>
+      <c r="E33" s="405"/>
+      <c r="F33" s="406"/>
+      <c r="G33" s="446"/>
+      <c r="H33" s="447"/>
+      <c r="I33" s="447"/>
+      <c r="J33" s="447"/>
+      <c r="K33" s="447"/>
+      <c r="L33" s="447"/>
+      <c r="M33" s="447"/>
+      <c r="N33" s="447"/>
+      <c r="O33" s="448"/>
     </row>
     <row r="34" spans="1:15" ht="39.75" customHeight="1">
       <c r="A34" s="187" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B34" s="188"/>
-      <c r="C34" s="439" t="s">
-        <v>313</v>
-      </c>
-      <c r="D34" s="439"/>
-      <c r="E34" s="439"/>
-      <c r="F34" s="440"/>
-      <c r="G34" s="434" t="b">
+      <c r="C34" s="405" t="s">
+        <v>311</v>
+      </c>
+      <c r="D34" s="405"/>
+      <c r="E34" s="405"/>
+      <c r="F34" s="406"/>
+      <c r="G34" s="444" t="b">
         <v>0</v>
       </c>
-      <c r="H34" s="427"/>
-      <c r="I34" s="427" t="b">
+      <c r="H34" s="445"/>
+      <c r="I34" s="445" t="b">
         <v>0</v>
       </c>
-      <c r="J34" s="427"/>
-      <c r="K34" s="427"/>
-      <c r="L34" s="427"/>
-      <c r="M34" s="427"/>
-      <c r="N34" s="427"/>
-      <c r="O34" s="428"/>
+      <c r="J34" s="445"/>
+      <c r="K34" s="445"/>
+      <c r="L34" s="445"/>
+      <c r="M34" s="445"/>
+      <c r="N34" s="445"/>
+      <c r="O34" s="449"/>
     </row>
     <row r="35" spans="1:15" ht="36.75" customHeight="1">
       <c r="A35" s="189"/>
       <c r="B35" s="188"/>
-      <c r="C35" s="439"/>
-      <c r="D35" s="439"/>
-      <c r="E35" s="439"/>
-      <c r="F35" s="440"/>
-      <c r="G35" s="451" t="s">
-        <v>307</v>
-      </c>
-      <c r="H35" s="452"/>
-      <c r="I35" s="456"/>
-      <c r="J35" s="456"/>
-      <c r="K35" s="456"/>
-      <c r="L35" s="456"/>
-      <c r="M35" s="456"/>
-      <c r="N35" s="456"/>
-      <c r="O35" s="457"/>
+      <c r="C35" s="405"/>
+      <c r="D35" s="405"/>
+      <c r="E35" s="405"/>
+      <c r="F35" s="406"/>
+      <c r="G35" s="397" t="s">
+        <v>305</v>
+      </c>
+      <c r="H35" s="398"/>
+      <c r="I35" s="450"/>
+      <c r="J35" s="450"/>
+      <c r="K35" s="450"/>
+      <c r="L35" s="450"/>
+      <c r="M35" s="450"/>
+      <c r="N35" s="450"/>
+      <c r="O35" s="451"/>
     </row>
     <row r="36" spans="1:15" ht="33" customHeight="1">
       <c r="A36" s="187" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B36" s="188"/>
-      <c r="C36" s="440" t="s">
-        <v>315</v>
-      </c>
-      <c r="D36" s="440"/>
-      <c r="E36" s="440"/>
-      <c r="F36" s="440"/>
-      <c r="G36" s="434" t="b">
+      <c r="C36" s="406" t="s">
+        <v>313</v>
+      </c>
+      <c r="D36" s="406"/>
+      <c r="E36" s="406"/>
+      <c r="F36" s="406"/>
+      <c r="G36" s="444" t="b">
         <v>0</v>
       </c>
-      <c r="H36" s="427"/>
-      <c r="I36" s="466" t="b">
+      <c r="H36" s="445"/>
+      <c r="I36" s="457" t="b">
         <v>0</v>
       </c>
-      <c r="J36" s="466"/>
-      <c r="K36" s="466"/>
-      <c r="L36" s="466"/>
-      <c r="M36" s="466"/>
-      <c r="N36" s="466"/>
-      <c r="O36" s="467"/>
+      <c r="J36" s="457"/>
+      <c r="K36" s="457"/>
+      <c r="L36" s="457"/>
+      <c r="M36" s="457"/>
+      <c r="N36" s="457"/>
+      <c r="O36" s="458"/>
     </row>
     <row r="37" spans="1:15" ht="27.75" customHeight="1">
       <c r="A37" s="189"/>
       <c r="B37" s="188"/>
-      <c r="C37" s="440"/>
-      <c r="D37" s="440"/>
-      <c r="E37" s="440"/>
-      <c r="F37" s="440"/>
-      <c r="G37" s="451" t="s">
-        <v>307</v>
-      </c>
-      <c r="H37" s="452"/>
+      <c r="C37" s="406"/>
+      <c r="D37" s="406"/>
+      <c r="E37" s="406"/>
+      <c r="F37" s="406"/>
+      <c r="G37" s="397" t="s">
+        <v>305</v>
+      </c>
+      <c r="H37" s="398"/>
       <c r="I37" s="29" t="b">
         <v>0</v>
       </c>
@@ -16972,19 +16934,19 @@
     </row>
     <row r="38" spans="1:15" ht="30.75" customHeight="1">
       <c r="A38" s="187" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B38" s="188"/>
-      <c r="C38" s="439" t="s">
-        <v>317</v>
-      </c>
-      <c r="D38" s="439"/>
+      <c r="C38" s="405" t="s">
+        <v>315</v>
+      </c>
+      <c r="D38" s="405"/>
       <c r="E38" s="190"/>
       <c r="F38" s="191"/>
-      <c r="G38" s="461" t="b">
+      <c r="G38" s="452" t="b">
         <v>0</v>
       </c>
-      <c r="H38" s="462"/>
+      <c r="H38" s="453"/>
       <c r="I38" s="166" t="b">
         <v>0</v>
       </c>
@@ -16996,133 +16958,133 @@
       <c r="O38" s="169"/>
     </row>
     <row r="39" spans="1:15" ht="28.5" customHeight="1">
-      <c r="A39" s="463"/>
-      <c r="B39" s="464"/>
-      <c r="C39" s="464"/>
-      <c r="D39" s="464"/>
-      <c r="E39" s="464"/>
-      <c r="F39" s="465"/>
-      <c r="G39" s="451" t="s">
-        <v>307</v>
-      </c>
-      <c r="H39" s="452"/>
-      <c r="I39" s="456"/>
-      <c r="J39" s="456"/>
-      <c r="K39" s="456"/>
-      <c r="L39" s="456"/>
-      <c r="M39" s="456"/>
-      <c r="N39" s="456"/>
-      <c r="O39" s="457"/>
+      <c r="A39" s="454"/>
+      <c r="B39" s="455"/>
+      <c r="C39" s="455"/>
+      <c r="D39" s="455"/>
+      <c r="E39" s="455"/>
+      <c r="F39" s="456"/>
+      <c r="G39" s="397" t="s">
+        <v>305</v>
+      </c>
+      <c r="H39" s="398"/>
+      <c r="I39" s="450"/>
+      <c r="J39" s="450"/>
+      <c r="K39" s="450"/>
+      <c r="L39" s="450"/>
+      <c r="M39" s="450"/>
+      <c r="N39" s="450"/>
+      <c r="O39" s="451"/>
     </row>
     <row r="40" spans="1:15" ht="37.5" customHeight="1">
-      <c r="A40" s="463"/>
-      <c r="B40" s="464"/>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="465"/>
-      <c r="G40" s="451"/>
-      <c r="H40" s="452"/>
-      <c r="I40" s="452"/>
-      <c r="J40" s="452"/>
-      <c r="K40" s="452"/>
-      <c r="L40" s="452"/>
-      <c r="M40" s="452"/>
-      <c r="N40" s="452"/>
-      <c r="O40" s="468"/>
+      <c r="A40" s="454"/>
+      <c r="B40" s="455"/>
+      <c r="C40" s="455"/>
+      <c r="D40" s="455"/>
+      <c r="E40" s="455"/>
+      <c r="F40" s="456"/>
+      <c r="G40" s="397"/>
+      <c r="H40" s="398"/>
+      <c r="I40" s="398"/>
+      <c r="J40" s="398"/>
+      <c r="K40" s="398"/>
+      <c r="L40" s="398"/>
+      <c r="M40" s="398"/>
+      <c r="N40" s="398"/>
+      <c r="O40" s="459"/>
     </row>
     <row r="41" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A41" s="401" t="s">
-        <v>346</v>
-      </c>
-      <c r="B41" s="401"/>
-      <c r="C41" s="401"/>
-      <c r="D41" s="401"/>
-      <c r="E41" s="401"/>
-      <c r="F41" s="401"/>
-      <c r="G41" s="401"/>
-      <c r="H41" s="401"/>
-      <c r="I41" s="401"/>
-      <c r="J41" s="401"/>
-      <c r="K41" s="401"/>
-      <c r="L41" s="401"/>
-      <c r="M41" s="401"/>
-      <c r="N41" s="401"/>
-      <c r="O41" s="401"/>
+      <c r="A41" s="497" t="s">
+        <v>343</v>
+      </c>
+      <c r="B41" s="497"/>
+      <c r="C41" s="497"/>
+      <c r="D41" s="497"/>
+      <c r="E41" s="497"/>
+      <c r="F41" s="497"/>
+      <c r="G41" s="497"/>
+      <c r="H41" s="497"/>
+      <c r="I41" s="497"/>
+      <c r="J41" s="497"/>
+      <c r="K41" s="497"/>
+      <c r="L41" s="497"/>
+      <c r="M41" s="497"/>
+      <c r="N41" s="497"/>
+      <c r="O41" s="497"/>
     </row>
     <row r="42" spans="1:15" ht="18" customHeight="1">
-      <c r="A42" s="402" t="s">
+      <c r="A42" s="498" t="s">
+        <v>316</v>
+      </c>
+      <c r="B42" s="498"/>
+      <c r="C42" s="498"/>
+      <c r="D42" s="498"/>
+      <c r="E42" s="498"/>
+      <c r="F42" s="498"/>
+      <c r="G42" s="498" t="s">
+        <v>317</v>
+      </c>
+      <c r="H42" s="498"/>
+      <c r="I42" s="498"/>
+      <c r="J42" s="498"/>
+      <c r="K42" s="498"/>
+      <c r="L42" s="498"/>
+      <c r="M42" s="495" t="s">
         <v>318</v>
       </c>
-      <c r="B42" s="402"/>
-      <c r="C42" s="402"/>
-      <c r="D42" s="402"/>
-      <c r="E42" s="402"/>
-      <c r="F42" s="402"/>
-      <c r="G42" s="402" t="s">
-        <v>319</v>
-      </c>
-      <c r="H42" s="402"/>
-      <c r="I42" s="402"/>
-      <c r="J42" s="402"/>
-      <c r="K42" s="402"/>
-      <c r="L42" s="402"/>
-      <c r="M42" s="412" t="s">
-        <v>320</v>
-      </c>
-      <c r="N42" s="412"/>
-      <c r="O42" s="412"/>
+      <c r="N42" s="495"/>
+      <c r="O42" s="495"/>
     </row>
     <row r="43" spans="1:15" ht="24" customHeight="1">
-      <c r="A43" s="403"/>
-      <c r="B43" s="403"/>
-      <c r="C43" s="403"/>
-      <c r="D43" s="403"/>
-      <c r="E43" s="403"/>
-      <c r="F43" s="403"/>
-      <c r="G43" s="400"/>
-      <c r="H43" s="400"/>
-      <c r="I43" s="400"/>
-      <c r="J43" s="400"/>
-      <c r="K43" s="400"/>
-      <c r="L43" s="400"/>
-      <c r="M43" s="400"/>
-      <c r="N43" s="400"/>
-      <c r="O43" s="400"/>
+      <c r="A43" s="499"/>
+      <c r="B43" s="499"/>
+      <c r="C43" s="499"/>
+      <c r="D43" s="499"/>
+      <c r="E43" s="499"/>
+      <c r="F43" s="499"/>
+      <c r="G43" s="496"/>
+      <c r="H43" s="496"/>
+      <c r="I43" s="496"/>
+      <c r="J43" s="496"/>
+      <c r="K43" s="496"/>
+      <c r="L43" s="496"/>
+      <c r="M43" s="496"/>
+      <c r="N43" s="496"/>
+      <c r="O43" s="496"/>
     </row>
     <row r="44" spans="1:15" ht="24" customHeight="1">
-      <c r="A44" s="403"/>
-      <c r="B44" s="403"/>
-      <c r="C44" s="403"/>
-      <c r="D44" s="403"/>
-      <c r="E44" s="403"/>
-      <c r="F44" s="403"/>
-      <c r="G44" s="400"/>
-      <c r="H44" s="400"/>
-      <c r="I44" s="400"/>
-      <c r="J44" s="400"/>
-      <c r="K44" s="400"/>
-      <c r="L44" s="400"/>
-      <c r="M44" s="400"/>
-      <c r="N44" s="400"/>
-      <c r="O44" s="400"/>
+      <c r="A44" s="499"/>
+      <c r="B44" s="499"/>
+      <c r="C44" s="499"/>
+      <c r="D44" s="499"/>
+      <c r="E44" s="499"/>
+      <c r="F44" s="499"/>
+      <c r="G44" s="496"/>
+      <c r="H44" s="496"/>
+      <c r="I44" s="496"/>
+      <c r="J44" s="496"/>
+      <c r="K44" s="496"/>
+      <c r="L44" s="496"/>
+      <c r="M44" s="496"/>
+      <c r="N44" s="496"/>
+      <c r="O44" s="496"/>
     </row>
     <row r="45" spans="1:15" ht="24" customHeight="1">
-      <c r="A45" s="403"/>
-      <c r="B45" s="403"/>
-      <c r="C45" s="403"/>
-      <c r="D45" s="403"/>
-      <c r="E45" s="403"/>
-      <c r="F45" s="403"/>
-      <c r="G45" s="400"/>
-      <c r="H45" s="400"/>
-      <c r="I45" s="400"/>
-      <c r="J45" s="400"/>
-      <c r="K45" s="400"/>
-      <c r="L45" s="400"/>
-      <c r="M45" s="400"/>
-      <c r="N45" s="400"/>
-      <c r="O45" s="400"/>
+      <c r="A45" s="499"/>
+      <c r="B45" s="499"/>
+      <c r="C45" s="499"/>
+      <c r="D45" s="499"/>
+      <c r="E45" s="499"/>
+      <c r="F45" s="499"/>
+      <c r="G45" s="496"/>
+      <c r="H45" s="496"/>
+      <c r="I45" s="496"/>
+      <c r="J45" s="496"/>
+      <c r="K45" s="496"/>
+      <c r="L45" s="496"/>
+      <c r="M45" s="496"/>
+      <c r="N45" s="496"/>
+      <c r="O45" s="496"/>
     </row>
     <row r="46" spans="1:15" ht="25.5" customHeight="1"/>
     <row r="47" spans="1:15" ht="24.75" customHeight="1"/>
@@ -17144,91 +17106,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="moz/kMrc4w/3TybL4Jbf9Ljv02c+w1IYbDsLXgFxhj9i0cQ70dtskMPWJE2kL6SU3TVZhvaxb9utMuybc0e0bw==" saltValue="eKGRhgfvUJeFv04A4oQ6cQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="97">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="C24:F25"/>
-    <mergeCell ref="C21:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:O13"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I9:O9"/>
-    <mergeCell ref="I10:O10"/>
-    <mergeCell ref="G11:O11"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:F11"/>
-    <mergeCell ref="C13:F17"/>
-    <mergeCell ref="C18:F20"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="G33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="A39:F40"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="I39:O39"/>
-    <mergeCell ref="G40:O40"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C36:F37"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="C27:F29"/>
-    <mergeCell ref="C30:F32"/>
-    <mergeCell ref="G26:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:O29"/>
-    <mergeCell ref="I30:O30"/>
-    <mergeCell ref="I31:O31"/>
-    <mergeCell ref="G32:O32"/>
-    <mergeCell ref="I14:O14"/>
-    <mergeCell ref="I15:O15"/>
-    <mergeCell ref="I16:O16"/>
-    <mergeCell ref="G17:O17"/>
-    <mergeCell ref="I18:O18"/>
-    <mergeCell ref="G2:O4"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="I7:O7"/>
-    <mergeCell ref="G8:O8"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G20:O20"/>
-    <mergeCell ref="I21:O21"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G23:O23"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:O19"/>
-    <mergeCell ref="I24:O24"/>
-    <mergeCell ref="I25:O25"/>
-    <mergeCell ref="I26:O27"/>
-    <mergeCell ref="I28:O28"/>
-    <mergeCell ref="M42:O42"/>
     <mergeCell ref="M43:O43"/>
     <mergeCell ref="M44:O44"/>
     <mergeCell ref="M45:O45"/>
@@ -17241,6 +17118,91 @@
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="I26:O27"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="G20:O20"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G23:O23"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:O19"/>
+    <mergeCell ref="I16:O16"/>
+    <mergeCell ref="G17:O17"/>
+    <mergeCell ref="I18:O18"/>
+    <mergeCell ref="G2:O4"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="I7:O7"/>
+    <mergeCell ref="G8:O8"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="C27:F29"/>
+    <mergeCell ref="C30:F32"/>
+    <mergeCell ref="G26:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:O29"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="G32:O32"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="A39:F40"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="I39:O39"/>
+    <mergeCell ref="G40:O40"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C36:F37"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="G33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:F11"/>
+    <mergeCell ref="C13:F17"/>
+    <mergeCell ref="C18:F20"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:O13"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I9:O9"/>
+    <mergeCell ref="I10:O10"/>
+    <mergeCell ref="G11:O11"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="I15:O15"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="C24:F25"/>
+    <mergeCell ref="C21:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G30:H30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -17951,246 +17913,229 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" customHeight="1" thickBot="1">
       <c r="A1" s="92" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" s="334" t="s">
-        <v>250</v>
-      </c>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
-      <c r="I1" s="334"/>
-      <c r="J1" s="334"/>
+        <v>247</v>
+      </c>
+      <c r="B1" s="310" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" s="310"/>
+      <c r="D1" s="310"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="310"/>
+      <c r="G1" s="310"/>
+      <c r="H1" s="310"/>
+      <c r="I1" s="310"/>
+      <c r="J1" s="310"/>
     </row>
     <row r="2" spans="1:10" ht="21" customHeight="1">
       <c r="A2" s="93">
         <v>22</v>
       </c>
-      <c r="B2" s="326" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" s="326"/>
-      <c r="D2" s="335"/>
-      <c r="E2" s="336"/>
-      <c r="F2" s="336"/>
-      <c r="G2" s="336"/>
-      <c r="H2" s="336"/>
-      <c r="I2" s="336"/>
-      <c r="J2" s="337"/>
+      <c r="B2" s="309" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="309"/>
+      <c r="D2" s="311"/>
+      <c r="E2" s="312"/>
+      <c r="F2" s="312"/>
+      <c r="G2" s="312"/>
+      <c r="H2" s="312"/>
+      <c r="I2" s="312"/>
+      <c r="J2" s="313"/>
     </row>
     <row r="3" spans="1:10" ht="21" customHeight="1">
       <c r="A3" s="94"/>
-      <c r="B3" s="326" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="326"/>
-      <c r="D3" s="328"/>
-      <c r="E3" s="329"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="339" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="340"/>
-      <c r="I3" s="341"/>
-      <c r="J3" s="321"/>
+      <c r="B3" s="309" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="309"/>
+      <c r="D3" s="314"/>
+      <c r="E3" s="315"/>
+      <c r="F3" s="316"/>
+      <c r="G3" s="317" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="318"/>
+      <c r="I3" s="319"/>
+      <c r="J3" s="320"/>
     </row>
     <row r="4" spans="1:10" ht="21" customHeight="1">
       <c r="A4" s="94"/>
-      <c r="B4" s="326" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="326"/>
-      <c r="D4" s="328"/>
-      <c r="E4" s="329"/>
-      <c r="F4" s="329"/>
-      <c r="G4" s="329"/>
-      <c r="H4" s="329"/>
-      <c r="I4" s="329"/>
-      <c r="J4" s="330"/>
+      <c r="B4" s="309" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="309"/>
+      <c r="D4" s="314"/>
+      <c r="E4" s="315"/>
+      <c r="F4" s="315"/>
+      <c r="G4" s="315"/>
+      <c r="H4" s="315"/>
+      <c r="I4" s="315"/>
+      <c r="J4" s="321"/>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1">
       <c r="A5" s="95"/>
-      <c r="B5" s="326" t="s">
-        <v>252</v>
-      </c>
-      <c r="C5" s="326"/>
-      <c r="D5" s="314"/>
-      <c r="E5" s="315"/>
-      <c r="F5" s="315"/>
-      <c r="G5" s="315"/>
-      <c r="H5" s="315"/>
-      <c r="I5" s="315"/>
-      <c r="J5" s="316"/>
+      <c r="B5" s="309" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" s="309"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="323"/>
+      <c r="F5" s="323"/>
+      <c r="G5" s="323"/>
+      <c r="H5" s="323"/>
+      <c r="I5" s="323"/>
+      <c r="J5" s="324"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="95"/>
-      <c r="B6" s="326" t="s">
-        <v>253</v>
-      </c>
-      <c r="C6" s="326"/>
-      <c r="D6" s="314"/>
-      <c r="E6" s="315"/>
-      <c r="F6" s="315"/>
-      <c r="G6" s="315"/>
-      <c r="H6" s="315"/>
-      <c r="I6" s="315"/>
-      <c r="J6" s="316"/>
+      <c r="B6" s="309" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" s="309"/>
+      <c r="D6" s="322"/>
+      <c r="E6" s="323"/>
+      <c r="F6" s="323"/>
+      <c r="G6" s="323"/>
+      <c r="H6" s="323"/>
+      <c r="I6" s="323"/>
+      <c r="J6" s="324"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="95"/>
-      <c r="B7" s="326" t="s">
-        <v>254</v>
-      </c>
-      <c r="C7" s="326"/>
-      <c r="D7" s="331"/>
-      <c r="E7" s="332"/>
-      <c r="F7" s="332"/>
-      <c r="G7" s="332"/>
-      <c r="H7" s="332"/>
-      <c r="I7" s="332"/>
-      <c r="J7" s="333"/>
+      <c r="B7" s="309" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="309"/>
+      <c r="D7" s="325"/>
+      <c r="E7" s="326"/>
+      <c r="F7" s="326"/>
+      <c r="G7" s="326"/>
+      <c r="H7" s="326"/>
+      <c r="I7" s="326"/>
+      <c r="J7" s="327"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="95"/>
-      <c r="B8" s="326" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="326"/>
-      <c r="D8" s="331"/>
-      <c r="E8" s="332"/>
-      <c r="F8" s="332"/>
-      <c r="G8" s="332"/>
-      <c r="H8" s="332"/>
-      <c r="I8" s="332"/>
-      <c r="J8" s="333"/>
+      <c r="B8" s="309" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="309"/>
+      <c r="D8" s="325"/>
+      <c r="E8" s="326"/>
+      <c r="F8" s="326"/>
+      <c r="G8" s="326"/>
+      <c r="H8" s="326"/>
+      <c r="I8" s="326"/>
+      <c r="J8" s="327"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="96">
         <v>24</v>
       </c>
-      <c r="B9" s="327" t="s">
-        <v>256</v>
-      </c>
-      <c r="C9" s="327"/>
-      <c r="D9" s="314"/>
-      <c r="E9" s="315"/>
-      <c r="F9" s="315"/>
-      <c r="G9" s="315"/>
-      <c r="H9" s="315"/>
-      <c r="I9" s="315"/>
-      <c r="J9" s="316"/>
+      <c r="B9" s="336" t="s">
+        <v>254</v>
+      </c>
+      <c r="C9" s="336"/>
+      <c r="D9" s="322"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="323"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="324"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="94"/>
-      <c r="B10" s="326" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="326"/>
-      <c r="D10" s="314"/>
-      <c r="E10" s="315"/>
-      <c r="F10" s="317"/>
-      <c r="G10" s="318" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="319"/>
-      <c r="I10" s="320"/>
-      <c r="J10" s="321"/>
+      <c r="B10" s="309" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="309"/>
+      <c r="D10" s="322"/>
+      <c r="E10" s="323"/>
+      <c r="F10" s="328"/>
+      <c r="G10" s="329" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="330"/>
+      <c r="I10" s="331"/>
+      <c r="J10" s="320"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="94"/>
-      <c r="B11" s="326" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="326"/>
-      <c r="D11" s="322"/>
-      <c r="E11" s="315"/>
-      <c r="F11" s="315"/>
-      <c r="G11" s="315"/>
-      <c r="H11" s="315"/>
-      <c r="I11" s="315"/>
-      <c r="J11" s="316"/>
+      <c r="B11" s="309" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="309"/>
+      <c r="D11" s="332"/>
+      <c r="E11" s="323"/>
+      <c r="F11" s="323"/>
+      <c r="G11" s="323"/>
+      <c r="H11" s="323"/>
+      <c r="I11" s="323"/>
+      <c r="J11" s="324"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="97">
         <v>25</v>
       </c>
-      <c r="B12" s="323" t="s">
-        <v>257</v>
-      </c>
-      <c r="C12" s="324"/>
-      <c r="D12" s="324"/>
-      <c r="E12" s="324"/>
-      <c r="F12" s="324"/>
-      <c r="G12" s="324"/>
-      <c r="H12" s="324"/>
-      <c r="I12" s="324"/>
-      <c r="J12" s="325"/>
+      <c r="B12" s="333" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="334"/>
+      <c r="D12" s="334"/>
+      <c r="E12" s="334"/>
+      <c r="F12" s="334"/>
+      <c r="G12" s="334"/>
+      <c r="H12" s="334"/>
+      <c r="I12" s="334"/>
+      <c r="J12" s="335"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="94"/>
-      <c r="B13" s="326" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="326"/>
-      <c r="D13" s="314"/>
-      <c r="E13" s="315"/>
-      <c r="F13" s="315"/>
-      <c r="G13" s="315"/>
-      <c r="H13" s="315"/>
-      <c r="I13" s="315"/>
-      <c r="J13" s="316"/>
+      <c r="B13" s="309" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="309"/>
+      <c r="D13" s="322"/>
+      <c r="E13" s="323"/>
+      <c r="F13" s="323"/>
+      <c r="G13" s="323"/>
+      <c r="H13" s="323"/>
+      <c r="I13" s="323"/>
+      <c r="J13" s="324"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="94"/>
-      <c r="B14" s="326" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="326"/>
-      <c r="D14" s="314"/>
-      <c r="E14" s="315"/>
-      <c r="F14" s="315"/>
-      <c r="G14" s="315"/>
-      <c r="H14" s="315"/>
-      <c r="I14" s="315"/>
-      <c r="J14" s="316"/>
+      <c r="B14" s="309" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="309"/>
+      <c r="D14" s="322"/>
+      <c r="E14" s="323"/>
+      <c r="F14" s="323"/>
+      <c r="G14" s="323"/>
+      <c r="H14" s="323"/>
+      <c r="I14" s="323"/>
+      <c r="J14" s="324"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1" thickBot="1">
       <c r="A15" s="98"/>
-      <c r="B15" s="326" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="326"/>
-      <c r="D15" s="314"/>
-      <c r="E15" s="315"/>
-      <c r="F15" s="315"/>
-      <c r="G15" s="315"/>
-      <c r="H15" s="315"/>
-      <c r="I15" s="315"/>
-      <c r="J15" s="316"/>
+      <c r="B15" s="309" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="309"/>
+      <c r="D15" s="322"/>
+      <c r="E15" s="323"/>
+      <c r="F15" s="323"/>
+      <c r="G15" s="323"/>
+      <c r="H15" s="323"/>
+      <c r="I15" s="323"/>
+      <c r="J15" s="324"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="94KVciG4kdECMCBRaZ/kGUPIuUdTIjG67RnmSldA6WYOzuQmRnZSJRxdUi03GpwtwoEXd0J15wJilUTAVO1QkA==" saltValue="4px6JZ8PPWxSqTy644m1tg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="32">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D14:J14"/>
     <mergeCell ref="D15:J15"/>
@@ -18206,6 +18151,23 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18223,16 +18185,16 @@
   <sheetData>
     <row r="1" spans="1:2" ht="33" customHeight="1" thickBot="1">
       <c r="A1" s="99" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B1" s="100"/>
     </row>
     <row r="2" spans="1:2" ht="33" customHeight="1">
       <c r="A2" s="101" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B2" s="102" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -18347,7 +18309,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" thickBot="1">
       <c r="A1" s="116" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B1" s="117"/>
       <c r="C1" s="118"/>
@@ -18356,64 +18318,64 @@
       <c r="F1" s="120"/>
       <c r="G1" s="121"/>
       <c r="H1" s="119"/>
-      <c r="I1" s="342" t="s">
-        <v>261</v>
-      </c>
-      <c r="J1" s="342"/>
-      <c r="K1" s="342"/>
-      <c r="L1" s="342"/>
-      <c r="M1" s="342"/>
-      <c r="N1" s="342"/>
+      <c r="I1" s="337" t="s">
+        <v>259</v>
+      </c>
+      <c r="J1" s="337"/>
+      <c r="K1" s="337"/>
+      <c r="L1" s="337"/>
+      <c r="M1" s="337"/>
+      <c r="N1" s="337"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1">
       <c r="A2" s="107" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B2" s="108"/>
       <c r="C2" s="108"/>
-      <c r="D2" s="349" t="s">
+      <c r="D2" s="344" t="s">
+        <v>260</v>
+      </c>
+      <c r="E2" s="345"/>
+      <c r="F2" s="338" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" s="338" t="s">
+        <v>324</v>
+      </c>
+      <c r="H2" s="341" t="s">
         <v>262</v>
-      </c>
-      <c r="E2" s="350"/>
-      <c r="F2" s="343" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" s="343" t="s">
-        <v>326</v>
-      </c>
-      <c r="H2" s="346" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1">
       <c r="A3" s="109" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B3" s="110" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C3" s="110" t="s">
-        <v>266</v>
-      </c>
-      <c r="D3" s="351"/>
-      <c r="E3" s="352"/>
-      <c r="F3" s="344"/>
-      <c r="G3" s="344"/>
-      <c r="H3" s="347"/>
+        <v>264</v>
+      </c>
+      <c r="D3" s="346"/>
+      <c r="E3" s="347"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="342"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1">
       <c r="A4" s="111"/>
       <c r="B4" s="112"/>
       <c r="C4" s="113"/>
       <c r="D4" s="114" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E4" s="115" t="s">
-        <v>268</v>
-      </c>
-      <c r="F4" s="345"/>
-      <c r="G4" s="345"/>
-      <c r="H4" s="348"/>
+        <v>266</v>
+      </c>
+      <c r="F4" s="340"/>
+      <c r="G4" s="340"/>
+      <c r="H4" s="343"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="122"/>
@@ -18583,20 +18545,20 @@
   <sheetData>
     <row r="1" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A1" s="132" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B1" s="133"/>
       <c r="C1" s="133"/>
       <c r="D1" s="133"/>
       <c r="E1" s="133"/>
       <c r="F1" s="133"/>
-      <c r="G1" s="355"/>
-      <c r="H1" s="355"/>
-      <c r="I1" s="355"/>
-      <c r="J1" s="355"/>
-      <c r="K1" s="355"/>
-      <c r="L1" s="355"/>
-      <c r="M1" s="355"/>
+      <c r="G1" s="350"/>
+      <c r="H1" s="350"/>
+      <c r="I1" s="350"/>
+      <c r="J1" s="350"/>
+      <c r="K1" s="350"/>
+      <c r="L1" s="350"/>
+      <c r="M1" s="350"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1">
       <c r="A2" s="134"/>
@@ -18609,21 +18571,21 @@
     </row>
     <row r="3" spans="1:14" s="142" customFormat="1" ht="39.75" customHeight="1">
       <c r="A3" s="139" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B3" s="140" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="139" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" s="141" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="348" t="s">
         <v>270</v>
       </c>
-      <c r="C3" s="139" t="s">
-        <v>328</v>
-      </c>
-      <c r="D3" s="141" t="s">
-        <v>271</v>
-      </c>
-      <c r="E3" s="353" t="s">
-        <v>272</v>
-      </c>
-      <c r="F3" s="354"/>
+      <c r="F3" s="349"/>
       <c r="N3" s="103"/>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1">
@@ -18632,10 +18594,10 @@
       <c r="C4" s="145"/>
       <c r="D4" s="145"/>
       <c r="E4" s="146" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F4" s="147" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -19615,78 +19577,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A1" s="356" t="s">
+      <c r="A1" s="351" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="352"/>
+      <c r="C1" s="352"/>
+      <c r="D1" s="352"/>
+      <c r="E1" s="352"/>
+      <c r="F1" s="352"/>
+      <c r="G1" s="352"/>
+      <c r="H1" s="353"/>
+    </row>
+    <row r="2" spans="1:14" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A2" s="354" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="355"/>
+      <c r="C2" s="355"/>
+      <c r="D2" s="355"/>
+      <c r="E2" s="355"/>
+      <c r="F2" s="355"/>
+      <c r="G2" s="355"/>
+      <c r="H2" s="356"/>
+    </row>
+    <row r="3" spans="1:14" ht="30.75" customHeight="1">
+      <c r="A3" s="366" t="s">
+        <v>327</v>
+      </c>
+      <c r="B3" s="367"/>
+      <c r="C3" s="357" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="357"/>
-      <c r="C1" s="357"/>
-      <c r="D1" s="357"/>
-      <c r="E1" s="357"/>
-      <c r="F1" s="357"/>
-      <c r="G1" s="357"/>
-      <c r="H1" s="358"/>
-    </row>
-    <row r="2" spans="1:14" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A2" s="359" t="s">
+      <c r="D3" s="360" t="s">
         <v>275</v>
       </c>
-      <c r="B2" s="360"/>
-      <c r="C2" s="360"/>
-      <c r="D2" s="360"/>
-      <c r="E2" s="360"/>
-      <c r="F2" s="360"/>
-      <c r="G2" s="360"/>
-      <c r="H2" s="361"/>
-    </row>
-    <row r="3" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A3" s="371" t="s">
-        <v>329</v>
-      </c>
-      <c r="B3" s="372"/>
-      <c r="C3" s="362" t="s">
+      <c r="E3" s="360" t="s">
         <v>276</v>
       </c>
-      <c r="D3" s="365" t="s">
+      <c r="F3" s="360" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="365" t="s">
+      <c r="G3" s="338" t="s">
         <v>278</v>
       </c>
-      <c r="F3" s="365" t="s">
-        <v>279</v>
-      </c>
-      <c r="G3" s="343" t="s">
-        <v>280</v>
-      </c>
-      <c r="H3" s="368" t="s">
-        <v>325</v>
+      <c r="H3" s="363" t="s">
+        <v>323</v>
       </c>
       <c r="N3" s="152"/>
     </row>
     <row r="4" spans="1:14" ht="30.75" customHeight="1">
-      <c r="A4" s="373"/>
-      <c r="B4" s="374"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="366"/>
-      <c r="E4" s="366"/>
-      <c r="F4" s="366"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="369"/>
+      <c r="A4" s="368"/>
+      <c r="B4" s="369"/>
+      <c r="C4" s="358"/>
+      <c r="D4" s="361"/>
+      <c r="E4" s="361"/>
+      <c r="F4" s="361"/>
+      <c r="G4" s="339"/>
+      <c r="H4" s="364"/>
       <c r="N4" s="152"/>
     </row>
     <row r="5" spans="1:14" ht="30.75" customHeight="1">
       <c r="A5" s="153" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B5" s="146" t="s">
-        <v>268</v>
-      </c>
-      <c r="C5" s="364"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="345"/>
-      <c r="H5" s="370"/>
+        <v>266</v>
+      </c>
+      <c r="C5" s="359"/>
+      <c r="D5" s="362"/>
+      <c r="E5" s="362"/>
+      <c r="F5" s="362"/>
+      <c r="G5" s="340"/>
+      <c r="H5" s="365"/>
       <c r="N5" s="152"/>
     </row>
     <row r="6" spans="1:14">
@@ -19978,7 +19940,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="23.25" customHeight="1">
       <c r="A1" s="154" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B1" s="155"/>
       <c r="C1" s="155"/>
@@ -19998,18 +19960,18 @@
       <c r="Q1" s="142"/>
     </row>
     <row r="2" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A2" s="375" t="s">
+      <c r="A2" s="370" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="357" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2" s="376"/>
+      <c r="D2" s="360" t="s">
+        <v>281</v>
+      </c>
+      <c r="E2" s="373" t="s">
         <v>282</v>
-      </c>
-      <c r="B2" s="362" t="s">
-        <v>330</v>
-      </c>
-      <c r="C2" s="381"/>
-      <c r="D2" s="365" t="s">
-        <v>283</v>
-      </c>
-      <c r="E2" s="378" t="s">
-        <v>284</v>
       </c>
       <c r="F2" s="158"/>
       <c r="G2" s="142"/>
@@ -20025,11 +19987,11 @@
       <c r="Q2" s="142"/>
     </row>
     <row r="3" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A3" s="376"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="382"/>
-      <c r="D3" s="366"/>
-      <c r="E3" s="379"/>
+      <c r="A3" s="371"/>
+      <c r="B3" s="358"/>
+      <c r="C3" s="377"/>
+      <c r="D3" s="361"/>
+      <c r="E3" s="374"/>
       <c r="F3" s="158"/>
       <c r="G3" s="142"/>
       <c r="H3" s="142"/>
@@ -20044,15 +20006,15 @@
       <c r="Q3" s="142"/>
     </row>
     <row r="4" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A4" s="377"/>
+      <c r="A4" s="372"/>
       <c r="B4" s="146" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C4" s="146" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4" s="367"/>
-      <c r="E4" s="380"/>
+        <v>266</v>
+      </c>
+      <c r="D4" s="362"/>
+      <c r="E4" s="375"/>
       <c r="F4" s="158"/>
       <c r="G4" s="142"/>
       <c r="H4" s="142"/>
@@ -20541,62 +20503,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A1" s="383" t="s">
+      <c r="A1" s="378" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="379"/>
+      <c r="C1" s="379"/>
+      <c r="D1" s="379"/>
+      <c r="E1" s="379"/>
+      <c r="F1" s="380"/>
+    </row>
+    <row r="2" spans="1:8" ht="30.75" customHeight="1">
+      <c r="A2" s="381" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" s="382"/>
+      <c r="C2" s="382"/>
+      <c r="D2" s="382"/>
+      <c r="E2" s="382"/>
+      <c r="F2" s="383"/>
+    </row>
+    <row r="3" spans="1:8" ht="30.75" customHeight="1">
+      <c r="A3" s="384" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="384"/>
-      <c r="C1" s="384"/>
-      <c r="D1" s="384"/>
-      <c r="E1" s="384"/>
-      <c r="F1" s="385"/>
-    </row>
-    <row r="2" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A2" s="386" t="s">
+      <c r="B3" s="389" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="390"/>
+      <c r="D3" s="386" t="s">
+        <v>281</v>
+      </c>
+      <c r="E3" s="361" t="s">
         <v>286</v>
       </c>
-      <c r="B2" s="387"/>
-      <c r="C2" s="387"/>
-      <c r="D2" s="387"/>
-      <c r="E2" s="387"/>
-      <c r="F2" s="388"/>
-    </row>
-    <row r="3" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A3" s="389" t="s">
+      <c r="F3" s="388" t="s">
         <v>287</v>
       </c>
-      <c r="B3" s="394" t="s">
-        <v>331</v>
-      </c>
-      <c r="C3" s="395"/>
-      <c r="D3" s="391" t="s">
-        <v>283</v>
-      </c>
-      <c r="E3" s="366" t="s">
-        <v>288</v>
-      </c>
-      <c r="F3" s="393" t="s">
-        <v>289</v>
-      </c>
     </row>
     <row r="4" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A4" s="390"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="396"/>
-      <c r="D4" s="391"/>
-      <c r="E4" s="366"/>
-      <c r="F4" s="379"/>
+      <c r="A4" s="385"/>
+      <c r="B4" s="358"/>
+      <c r="C4" s="391"/>
+      <c r="D4" s="386"/>
+      <c r="E4" s="361"/>
+      <c r="F4" s="374"/>
     </row>
     <row r="5" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A5" s="373"/>
+      <c r="A5" s="368"/>
       <c r="B5" s="146" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C5" s="146" t="s">
-        <v>268</v>
-      </c>
-      <c r="D5" s="392"/>
-      <c r="E5" s="367"/>
-      <c r="F5" s="380"/>
+        <v>266</v>
+      </c>
+      <c r="D5" s="387"/>
+      <c r="E5" s="362"/>
+      <c r="F5" s="375"/>
     </row>
     <row r="6" spans="1:8" ht="18.75" customHeight="1">
       <c r="A6" s="161"/>
@@ -20798,21 +20760,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A1" s="397" t="s">
-        <v>290</v>
-      </c>
-      <c r="B1" s="398"/>
-      <c r="C1" s="399"/>
+      <c r="A1" s="392" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="393"/>
+      <c r="C1" s="394"/>
     </row>
     <row r="2" spans="1:13" ht="38.25" customHeight="1">
       <c r="A2" s="163" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="C2" s="165" t="s">
         <v>291</v>
-      </c>
-      <c r="B2" s="164" t="s">
-        <v>292</v>
-      </c>
-      <c r="C2" s="165" t="s">
-        <v>293</v>
       </c>
       <c r="L2" s="138"/>
       <c r="M2" s="138"/>
